--- a/database/event/2027/event_2027_evp_summary.xlsx
+++ b/database/event/2027/event_2027_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.7093</v>
+        <v>7.8264</v>
       </c>
       <c r="C2" t="n">
-        <v>5.0579</v>
+        <v>5.1347</v>
       </c>
       <c r="D2" t="n">
-        <v>2.693</v>
+        <v>2.6741</v>
       </c>
       <c r="E2" t="n">
-        <v>7.7093</v>
+        <v>7.8264</v>
       </c>
       <c r="F2" t="n">
-        <v>4.2487</v>
+        <v>4.3658</v>
       </c>
       <c r="G2" t="n">
         <v>3.4606</v>
       </c>
       <c r="H2" t="n">
-        <v>4.5328</v>
+        <v>5.0043</v>
       </c>
       <c r="I2" t="n">
-        <v>3.674</v>
+        <v>4.0561</v>
       </c>
       <c r="J2" t="n">
         <v>3.4606</v>
@@ -529,7 +529,7 @@
         <v>123</v>
       </c>
       <c r="M2" t="n">
-        <v>7.1346</v>
+        <v>7.5167</v>
       </c>
       <c r="N2" t="n">
         <v>262</v>
@@ -542,28 +542,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.4255</v>
+        <v>6.5703</v>
       </c>
       <c r="C3" t="n">
-        <v>4.2156</v>
+        <v>4.3106</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1744</v>
+        <v>2.1737</v>
       </c>
       <c r="E3" t="n">
-        <v>6.4255</v>
+        <v>6.5703</v>
       </c>
       <c r="F3" t="n">
-        <v>4.1579</v>
+        <v>4.3027</v>
       </c>
       <c r="G3" t="n">
         <v>2.2677</v>
       </c>
       <c r="H3" t="n">
-        <v>4.1675</v>
+        <v>4.7501</v>
       </c>
       <c r="I3" t="n">
-        <v>3.3779</v>
+        <v>3.8501</v>
       </c>
       <c r="J3" t="n">
         <v>2.2677</v>
@@ -575,7 +575,7 @@
         <v>105</v>
       </c>
       <c r="M3" t="n">
-        <v>5.6456</v>
+        <v>6.1178</v>
       </c>
       <c r="N3" t="n">
         <v>201</v>
@@ -588,28 +588,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.8487</v>
+        <v>5.9749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.8372</v>
+        <v>3.92</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9414</v>
+        <v>1.9365</v>
       </c>
       <c r="E4" t="n">
-        <v>5.8487</v>
+        <v>5.9749</v>
       </c>
       <c r="F4" t="n">
-        <v>3.6748</v>
+        <v>3.801</v>
       </c>
       <c r="G4" t="n">
         <v>2.1739</v>
       </c>
       <c r="H4" t="n">
-        <v>3.6748</v>
+        <v>3.801</v>
       </c>
       <c r="I4" t="n">
-        <v>2.9785</v>
+        <v>3.0808</v>
       </c>
       <c r="J4" t="n">
         <v>2.1739</v>
@@ -621,7 +621,7 @@
         <v>105</v>
       </c>
       <c r="M4" t="n">
-        <v>5.1524</v>
+        <v>5.2547</v>
       </c>
       <c r="N4" t="n">
         <v>201</v>
@@ -630,35 +630,35 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>fnx</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.4259</v>
+        <v>4.7368</v>
       </c>
       <c r="C5" t="n">
-        <v>2.9037</v>
+        <v>3.1077</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3666</v>
+        <v>1.4432</v>
       </c>
       <c r="E5" t="n">
-        <v>4.4259</v>
+        <v>4.7368</v>
       </c>
       <c r="F5" t="n">
-        <v>3.997</v>
+        <v>1.4098</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4289</v>
+        <v>3.327</v>
       </c>
       <c r="H5" t="n">
-        <v>3.997</v>
+        <v>1.4098</v>
       </c>
       <c r="I5" t="n">
-        <v>3.2396</v>
+        <v>1.1427</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4289</v>
+        <v>3.327</v>
       </c>
       <c r="K5" t="n">
         <v>139</v>
@@ -667,7 +667,7 @@
         <v>123</v>
       </c>
       <c r="M5" t="n">
-        <v>3.6685</v>
+        <v>4.4697</v>
       </c>
       <c r="N5" t="n">
         <v>262</v>
@@ -676,35 +676,35 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>fnx</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.3825</v>
+        <v>4.6848</v>
       </c>
       <c r="C6" t="n">
-        <v>2.8753</v>
+        <v>3.0736</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3491</v>
+        <v>1.4225</v>
       </c>
       <c r="E6" t="n">
-        <v>4.3825</v>
+        <v>4.6848</v>
       </c>
       <c r="F6" t="n">
-        <v>1.0555</v>
+        <v>4.2559</v>
       </c>
       <c r="G6" t="n">
-        <v>3.327</v>
+        <v>0.4289</v>
       </c>
       <c r="H6" t="n">
-        <v>1.0555</v>
+        <v>4.5621</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8555</v>
+        <v>3.6977</v>
       </c>
       <c r="J6" t="n">
-        <v>3.327</v>
+        <v>0.4289</v>
       </c>
       <c r="K6" t="n">
         <v>139</v>
@@ -713,7 +713,7 @@
         <v>123</v>
       </c>
       <c r="M6" t="n">
-        <v>4.1825</v>
+        <v>4.1266</v>
       </c>
       <c r="N6" t="n">
         <v>262</v>
@@ -722,139 +722,139 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.767</v>
+        <v>3.8663</v>
       </c>
       <c r="C7" t="n">
-        <v>2.4714</v>
+        <v>2.5366</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1004</v>
+        <v>1.0964</v>
       </c>
       <c r="E7" t="n">
-        <v>3.767</v>
+        <v>3.8663</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8449</v>
+        <v>4.3498</v>
       </c>
       <c r="G7" t="n">
-        <v>2.9221</v>
+        <v>-0.4835</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8449</v>
+        <v>4.9397</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6848</v>
+        <v>4.0038</v>
       </c>
       <c r="J7" t="n">
-        <v>2.9221</v>
+        <v>-0.4835</v>
       </c>
       <c r="K7" t="n">
-        <v>139</v>
+        <v>98</v>
       </c>
       <c r="L7" t="n">
-        <v>123</v>
+        <v>51</v>
       </c>
       <c r="M7" t="n">
-        <v>3.6069</v>
+        <v>3.5203</v>
       </c>
       <c r="N7" t="n">
-        <v>262</v>
+        <v>149</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>s1mple</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.7047</v>
+        <v>3.8186</v>
       </c>
       <c r="C8" t="n">
-        <v>2.4306</v>
+        <v>2.5053</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0753</v>
+        <v>1.0774</v>
       </c>
       <c r="E8" t="n">
-        <v>3.7047</v>
+        <v>3.8186</v>
       </c>
       <c r="F8" t="n">
-        <v>4.1882</v>
+        <v>3.5041</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.4835</v>
+        <v>0.3145</v>
       </c>
       <c r="H8" t="n">
-        <v>4.2895</v>
+        <v>3.5041</v>
       </c>
       <c r="I8" t="n">
-        <v>3.4768</v>
+        <v>2.8401</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.4835</v>
+        <v>0.3145</v>
       </c>
       <c r="K8" t="n">
-        <v>98</v>
+        <v>119</v>
       </c>
       <c r="L8" t="n">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="M8" t="n">
-        <v>2.9933</v>
+        <v>3.1546</v>
       </c>
       <c r="N8" t="n">
-        <v>149</v>
+        <v>188</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>s1mple</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.5981</v>
+        <v>3.767</v>
       </c>
       <c r="C9" t="n">
-        <v>2.3606</v>
+        <v>2.4714</v>
       </c>
       <c r="D9" t="n">
-        <v>1.0322</v>
+        <v>1.0569</v>
       </c>
       <c r="E9" t="n">
-        <v>3.5981</v>
+        <v>3.767</v>
       </c>
       <c r="F9" t="n">
-        <v>3.2836</v>
+        <v>0.8449</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3145</v>
+        <v>2.9221</v>
       </c>
       <c r="H9" t="n">
-        <v>3.2836</v>
+        <v>0.8449</v>
       </c>
       <c r="I9" t="n">
-        <v>2.6615</v>
+        <v>0.6848</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3145</v>
+        <v>2.9221</v>
       </c>
       <c r="K9" t="n">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="L9" t="n">
-        <v>69</v>
+        <v>123</v>
       </c>
       <c r="M9" t="n">
-        <v>2.976</v>
+        <v>3.6069</v>
       </c>
       <c r="N9" t="n">
-        <v>188</v>
+        <v>262</v>
       </c>
     </row>
     <row r="10">
@@ -864,28 +864,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.4947</v>
+        <v>3.672</v>
       </c>
       <c r="C10" t="n">
-        <v>2.2928</v>
+        <v>2.4091</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9903999999999999</v>
+        <v>1.019</v>
       </c>
       <c r="E10" t="n">
-        <v>3.4947</v>
+        <v>3.672</v>
       </c>
       <c r="F10" t="n">
-        <v>3.8452</v>
+        <v>4.0225</v>
       </c>
       <c r="G10" t="n">
         <v>-0.3505</v>
       </c>
       <c r="H10" t="n">
-        <v>3.8452</v>
+        <v>4.0225</v>
       </c>
       <c r="I10" t="n">
-        <v>3.1166</v>
+        <v>3.2603</v>
       </c>
       <c r="J10" t="n">
         <v>-0.3505</v>
@@ -897,7 +897,7 @@
         <v>69</v>
       </c>
       <c r="M10" t="n">
-        <v>2.7661</v>
+        <v>2.9098</v>
       </c>
       <c r="N10" t="n">
         <v>188</v>
@@ -910,28 +910,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.2225</v>
+        <v>3.3008</v>
       </c>
       <c r="C11" t="n">
-        <v>2.1142</v>
+        <v>2.1656</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8804999999999999</v>
+        <v>0.8711</v>
       </c>
       <c r="E11" t="n">
-        <v>3.2225</v>
+        <v>3.3008</v>
       </c>
       <c r="F11" t="n">
-        <v>4.2149</v>
+        <v>4.2932</v>
       </c>
       <c r="G11" t="n">
         <v>-0.9923999999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>4.3968</v>
+        <v>4.712</v>
       </c>
       <c r="I11" t="n">
-        <v>3.5637</v>
+        <v>3.8192</v>
       </c>
       <c r="J11" t="n">
         <v>-0.9923999999999999</v>
@@ -943,7 +943,7 @@
         <v>105</v>
       </c>
       <c r="M11" t="n">
-        <v>2.5713</v>
+        <v>2.8268</v>
       </c>
       <c r="N11" t="n">
         <v>201</v>
@@ -956,28 +956,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.8751</v>
+        <v>3.0847</v>
       </c>
       <c r="C12" t="n">
-        <v>1.8863</v>
+        <v>2.0238</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7401</v>
+        <v>0.785</v>
       </c>
       <c r="E12" t="n">
-        <v>2.8751</v>
+        <v>3.0847</v>
       </c>
       <c r="F12" t="n">
-        <v>3.2742</v>
+        <v>3.4838</v>
       </c>
       <c r="G12" t="n">
         <v>-0.3991</v>
       </c>
       <c r="H12" t="n">
-        <v>3.2742</v>
+        <v>3.4838</v>
       </c>
       <c r="I12" t="n">
-        <v>2.6538</v>
+        <v>2.8237</v>
       </c>
       <c r="J12" t="n">
         <v>-0.3991</v>
@@ -989,7 +989,7 @@
         <v>51</v>
       </c>
       <c r="M12" t="n">
-        <v>2.2547</v>
+        <v>2.4246</v>
       </c>
       <c r="N12" t="n">
         <v>149</v>
@@ -1002,28 +1002,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.7422</v>
+        <v>3.07</v>
       </c>
       <c r="C13" t="n">
-        <v>1.7991</v>
+        <v>2.0142</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6864</v>
+        <v>0.7792</v>
       </c>
       <c r="E13" t="n">
-        <v>2.7422</v>
+        <v>3.07</v>
       </c>
       <c r="F13" t="n">
-        <v>3.1413</v>
+        <v>3.4691</v>
       </c>
       <c r="G13" t="n">
         <v>-0.3991</v>
       </c>
       <c r="H13" t="n">
-        <v>3.1413</v>
+        <v>3.4691</v>
       </c>
       <c r="I13" t="n">
-        <v>2.5461</v>
+        <v>2.8118</v>
       </c>
       <c r="J13" t="n">
         <v>-0.3991</v>
@@ -1035,7 +1035,7 @@
         <v>51</v>
       </c>
       <c r="M13" t="n">
-        <v>2.147</v>
+        <v>2.4127</v>
       </c>
       <c r="N13" t="n">
         <v>149</v>
@@ -1044,139 +1044,139 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>flusha</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.6595</v>
+        <v>2.9738</v>
       </c>
       <c r="C14" t="n">
-        <v>1.7448</v>
+        <v>1.951</v>
       </c>
       <c r="D14" t="n">
-        <v>0.653</v>
+        <v>0.7409</v>
       </c>
       <c r="E14" t="n">
-        <v>2.6595</v>
+        <v>2.9738</v>
       </c>
       <c r="F14" t="n">
-        <v>2.6595</v>
+        <v>2.9738</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>2.6595</v>
+        <v>2.9738</v>
       </c>
       <c r="I14" t="n">
-        <v>2.6595</v>
+        <v>2.9738</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.6595</v>
+        <v>2.9738</v>
       </c>
       <c r="N14" t="n">
-        <v>162</v>
+        <v>157</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>byali</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.4764</v>
+        <v>2.9169</v>
       </c>
       <c r="C15" t="n">
-        <v>1.6247</v>
+        <v>1.9137</v>
       </c>
       <c r="D15" t="n">
-        <v>0.579</v>
+        <v>0.7181999999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4764</v>
+        <v>2.9169</v>
       </c>
       <c r="F15" t="n">
-        <v>2.4764</v>
+        <v>2.9169</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2.4764</v>
+        <v>2.9169</v>
       </c>
       <c r="I15" t="n">
-        <v>2.4764</v>
+        <v>2.9169</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>182</v>
+        <v>199</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.4764</v>
+        <v>2.9169</v>
       </c>
       <c r="N15" t="n">
-        <v>182</v>
+        <v>199</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>flusha</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.4064</v>
+        <v>2.8249</v>
       </c>
       <c r="C16" t="n">
-        <v>1.5788</v>
+        <v>1.8533</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5508</v>
+        <v>0.6815</v>
       </c>
       <c r="E16" t="n">
-        <v>2.4064</v>
+        <v>2.8249</v>
       </c>
       <c r="F16" t="n">
-        <v>2.4064</v>
+        <v>2.8249</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2.4064</v>
+        <v>2.8249</v>
       </c>
       <c r="I16" t="n">
-        <v>2.4064</v>
+        <v>2.8249</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.4064</v>
+        <v>2.8249</v>
       </c>
       <c r="N16" t="n">
-        <v>157</v>
+        <v>162</v>
       </c>
     </row>
     <row r="17">
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.2612</v>
+        <v>2.8149</v>
       </c>
       <c r="C17" t="n">
-        <v>1.4835</v>
+        <v>1.8468</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4921</v>
+        <v>0.6775</v>
       </c>
       <c r="E17" t="n">
-        <v>2.2612</v>
+        <v>2.8149</v>
       </c>
       <c r="F17" t="n">
-        <v>2.2612</v>
+        <v>2.8149</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>2.2612</v>
+        <v>2.8149</v>
       </c>
       <c r="I17" t="n">
-        <v>2.2612</v>
+        <v>2.8149</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>2.2612</v>
+        <v>2.8149</v>
       </c>
       <c r="N17" t="n">
         <v>199</v>
@@ -1228,47 +1228,47 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>byali</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.0079</v>
+        <v>2.6181</v>
       </c>
       <c r="C18" t="n">
-        <v>1.3173</v>
+        <v>1.7177</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3898</v>
+        <v>0.5991</v>
       </c>
       <c r="E18" t="n">
-        <v>2.0079</v>
+        <v>2.6181</v>
       </c>
       <c r="F18" t="n">
-        <v>2.0079</v>
+        <v>2.6181</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>2.0079</v>
+        <v>2.6181</v>
       </c>
       <c r="I18" t="n">
-        <v>2.0079</v>
+        <v>2.6181</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>2.0079</v>
+        <v>2.6181</v>
       </c>
       <c r="N18" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="19">
@@ -1284,7 +1284,7 @@
         <v>1.315</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3883</v>
+        <v>0.3546</v>
       </c>
       <c r="E19" t="n">
         <v>2.0043</v>
@@ -1320,216 +1320,216 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Hiko</t>
+          <t>NEO</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.9375</v>
+        <v>1.986</v>
       </c>
       <c r="C20" t="n">
-        <v>1.2711</v>
+        <v>1.303</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3613</v>
+        <v>0.3473</v>
       </c>
       <c r="E20" t="n">
-        <v>1.9375</v>
+        <v>1.986</v>
       </c>
       <c r="F20" t="n">
-        <v>1.9659</v>
+        <v>1.986</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.0284</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.9659</v>
+        <v>1.986</v>
       </c>
       <c r="I20" t="n">
-        <v>1.5934</v>
+        <v>1.986</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.0284</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>119</v>
+        <v>199</v>
       </c>
       <c r="L20" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.565</v>
+        <v>1.986</v>
       </c>
       <c r="N20" t="n">
-        <v>188</v>
+        <v>199</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>GeT_RiGhT</t>
+          <t>Hiko</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.8051</v>
+        <v>1.9392</v>
       </c>
       <c r="C21" t="n">
-        <v>1.1843</v>
+        <v>1.2723</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3079</v>
+        <v>0.3287</v>
       </c>
       <c r="E21" t="n">
-        <v>1.8051</v>
+        <v>1.9392</v>
       </c>
       <c r="F21" t="n">
-        <v>1.8051</v>
+        <v>1.9676</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>-0.0284</v>
       </c>
       <c r="H21" t="n">
-        <v>1.8051</v>
+        <v>1.9676</v>
       </c>
       <c r="I21" t="n">
-        <v>1.8051</v>
+        <v>1.5948</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>-0.0284</v>
       </c>
       <c r="K21" t="n">
-        <v>182</v>
+        <v>119</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="M21" t="n">
-        <v>1.8051</v>
+        <v>1.5664</v>
       </c>
       <c r="N21" t="n">
-        <v>182</v>
+        <v>188</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>jdm64</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.7876</v>
+        <v>1.9153</v>
       </c>
       <c r="C22" t="n">
-        <v>1.1728</v>
+        <v>1.2566</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3008</v>
+        <v>0.3191</v>
       </c>
       <c r="E22" t="n">
-        <v>1.7876</v>
+        <v>1.9153</v>
       </c>
       <c r="F22" t="n">
-        <v>1.7876</v>
+        <v>1.9153</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.7876</v>
+        <v>1.9153</v>
       </c>
       <c r="I22" t="n">
-        <v>1.7876</v>
+        <v>1.9153</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>182</v>
+        <v>94</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.7876</v>
+        <v>1.9153</v>
       </c>
       <c r="N22" t="n">
-        <v>182</v>
+        <v>94</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>NEO</t>
+          <t>GeT_RiGhT</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.6978</v>
+        <v>1.9141</v>
       </c>
       <c r="C23" t="n">
-        <v>1.1139</v>
+        <v>1.2558</v>
       </c>
       <c r="D23" t="n">
-        <v>0.2645</v>
+        <v>0.3187</v>
       </c>
       <c r="E23" t="n">
-        <v>1.6978</v>
+        <v>1.9141</v>
       </c>
       <c r="F23" t="n">
-        <v>1.6978</v>
+        <v>1.9141</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.6978</v>
+        <v>1.9141</v>
       </c>
       <c r="I23" t="n">
-        <v>1.6978</v>
+        <v>1.9141</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.6978</v>
+        <v>1.9141</v>
       </c>
       <c r="N23" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>hazed</t>
+          <t>jdm64</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.5981</v>
+        <v>1.7876</v>
       </c>
       <c r="C24" t="n">
-        <v>1.0485</v>
+        <v>1.1728</v>
       </c>
       <c r="D24" t="n">
-        <v>0.2242</v>
+        <v>0.2683</v>
       </c>
       <c r="E24" t="n">
-        <v>1.5981</v>
+        <v>1.7876</v>
       </c>
       <c r="F24" t="n">
-        <v>1.5981</v>
+        <v>1.7876</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.5981</v>
+        <v>1.7876</v>
       </c>
       <c r="I24" t="n">
-        <v>1.5981</v>
+        <v>1.7876</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.5981</v>
+        <v>1.7876</v>
       </c>
       <c r="N24" t="n">
         <v>182</v>
@@ -1550,231 +1550,231 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.5031</v>
+        <v>1.6366</v>
       </c>
       <c r="C25" t="n">
-        <v>0.9861</v>
+        <v>1.0737</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1859</v>
+        <v>0.2081</v>
       </c>
       <c r="E25" t="n">
-        <v>1.5031</v>
+        <v>1.6366</v>
       </c>
       <c r="F25" t="n">
-        <v>1.8466</v>
+        <v>1.6366</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.3435</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1.8466</v>
+        <v>1.6366</v>
       </c>
       <c r="I25" t="n">
-        <v>1.4967</v>
+        <v>1.6366</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.3435</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>98</v>
+        <v>157</v>
       </c>
       <c r="L25" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1.1532</v>
+        <v>1.6366</v>
       </c>
       <c r="N25" t="n">
-        <v>149</v>
+        <v>157</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>hazed</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.4801</v>
+        <v>1.5981</v>
       </c>
       <c r="C26" t="n">
-        <v>0.9711</v>
+        <v>1.0485</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1766</v>
+        <v>0.1928</v>
       </c>
       <c r="E26" t="n">
-        <v>1.4801</v>
+        <v>1.5981</v>
       </c>
       <c r="F26" t="n">
-        <v>1.4801</v>
+        <v>1.5981</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1.4801</v>
+        <v>1.5981</v>
       </c>
       <c r="I26" t="n">
-        <v>1.4801</v>
+        <v>1.5981</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>157</v>
+        <v>182</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1.4801</v>
+        <v>1.5981</v>
       </c>
       <c r="N26" t="n">
-        <v>157</v>
+        <v>182</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.3487</v>
+        <v>1.5807</v>
       </c>
       <c r="C27" t="n">
-        <v>0.8848</v>
+        <v>1.0371</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1235</v>
+        <v>0.1858</v>
       </c>
       <c r="E27" t="n">
-        <v>1.3487</v>
+        <v>1.5807</v>
       </c>
       <c r="F27" t="n">
-        <v>1.3487</v>
+        <v>1.9242</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>-0.3435</v>
       </c>
       <c r="H27" t="n">
-        <v>1.3487</v>
+        <v>1.9242</v>
       </c>
       <c r="I27" t="n">
-        <v>1.3487</v>
+        <v>1.5596</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>-0.3435</v>
       </c>
       <c r="K27" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="M27" t="n">
-        <v>1.3487</v>
+        <v>1.2161</v>
       </c>
       <c r="N27" t="n">
-        <v>94</v>
+        <v>149</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>dennis</t>
+          <t>f0rest</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.2049</v>
+        <v>1.5698</v>
       </c>
       <c r="C28" t="n">
-        <v>0.7905</v>
+        <v>1.0299</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0654</v>
+        <v>0.1815</v>
       </c>
       <c r="E28" t="n">
-        <v>1.2049</v>
+        <v>1.5698</v>
       </c>
       <c r="F28" t="n">
-        <v>1.2049</v>
+        <v>1.5698</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1.2049</v>
+        <v>1.5698</v>
       </c>
       <c r="I28" t="n">
-        <v>1.2049</v>
+        <v>1.5698</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>157</v>
+        <v>182</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1.2049</v>
+        <v>1.5698</v>
       </c>
       <c r="N28" t="n">
-        <v>157</v>
+        <v>182</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>f0rest</t>
+          <t>dennis</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.1838</v>
+        <v>1.4531</v>
       </c>
       <c r="C29" t="n">
-        <v>0.7766999999999999</v>
+        <v>0.9533</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0569</v>
+        <v>0.135</v>
       </c>
       <c r="E29" t="n">
-        <v>1.1838</v>
+        <v>1.4531</v>
       </c>
       <c r="F29" t="n">
-        <v>1.1838</v>
+        <v>1.4531</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1.1838</v>
+        <v>1.4531</v>
       </c>
       <c r="I29" t="n">
-        <v>1.1838</v>
+        <v>1.4531</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>182</v>
+        <v>157</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1.1838</v>
+        <v>1.4531</v>
       </c>
       <c r="N29" t="n">
-        <v>182</v>
+        <v>157</v>
       </c>
     </row>
     <row r="30">
@@ -1790,7 +1790,7 @@
         <v>0.7399</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0342</v>
+        <v>0.0054</v>
       </c>
       <c r="E30" t="n">
         <v>1.1278</v>
@@ -1826,170 +1826,170 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>TaZ</t>
+          <t>olofmeister</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.8532999999999999</v>
+        <v>1.0996</v>
       </c>
       <c r="C31" t="n">
-        <v>0.5598</v>
+        <v>0.7214</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.0766</v>
+        <v>-0.0058</v>
       </c>
       <c r="E31" t="n">
-        <v>0.8532999999999999</v>
+        <v>1.0996</v>
       </c>
       <c r="F31" t="n">
-        <v>0.8532999999999999</v>
+        <v>1.0996</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.8532999999999999</v>
+        <v>1.0996</v>
       </c>
       <c r="I31" t="n">
-        <v>0.8532999999999999</v>
+        <v>1.0996</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>199</v>
+        <v>157</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0.8532999999999999</v>
+        <v>1.0996</v>
       </c>
       <c r="N31" t="n">
-        <v>199</v>
+        <v>157</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Shara</t>
+          <t>aizy</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.707</v>
+        <v>1.0227</v>
       </c>
       <c r="C32" t="n">
-        <v>0.4638</v>
+        <v>0.671</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.1357</v>
+        <v>-0.0365</v>
       </c>
       <c r="E32" t="n">
-        <v>0.707</v>
+        <v>1.0227</v>
       </c>
       <c r="F32" t="n">
-        <v>0.707</v>
+        <v>1.0227</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.707</v>
+        <v>1.0227</v>
       </c>
       <c r="I32" t="n">
-        <v>0.707</v>
+        <v>1.0227</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0.707</v>
+        <v>1.0227</v>
       </c>
       <c r="N32" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>olofmeister</t>
+          <t>TaZ</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6025</v>
+        <v>0.8532999999999999</v>
       </c>
       <c r="C33" t="n">
-        <v>0.3953</v>
+        <v>0.5598</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.178</v>
+        <v>-0.104</v>
       </c>
       <c r="E33" t="n">
-        <v>0.6025</v>
+        <v>0.8532999999999999</v>
       </c>
       <c r="F33" t="n">
-        <v>0.6025</v>
+        <v>0.8532999999999999</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.6025</v>
+        <v>0.8532999999999999</v>
       </c>
       <c r="I33" t="n">
-        <v>0.6025</v>
+        <v>0.8532999999999999</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>157</v>
+        <v>199</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0.6025</v>
+        <v>0.8532999999999999</v>
       </c>
       <c r="N33" t="n">
-        <v>157</v>
+        <v>199</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>bondik</t>
+          <t>Shara</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.5314</v>
+        <v>0.707</v>
       </c>
       <c r="C34" t="n">
-        <v>0.3486</v>
+        <v>0.4638</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.2067</v>
+        <v>-0.1622</v>
       </c>
       <c r="E34" t="n">
-        <v>0.5314</v>
+        <v>0.707</v>
       </c>
       <c r="F34" t="n">
-        <v>0.5314</v>
+        <v>0.707</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.5314</v>
+        <v>0.707</v>
       </c>
       <c r="I34" t="n">
-        <v>0.5314</v>
+        <v>0.707</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0.5314</v>
+        <v>0.707</v>
       </c>
       <c r="N34" t="n">
         <v>95</v>
@@ -2010,446 +2010,446 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>bondik</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.5173</v>
+        <v>0.6839</v>
       </c>
       <c r="C35" t="n">
-        <v>0.3394</v>
+        <v>0.4487</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.2124</v>
+        <v>-0.1714</v>
       </c>
       <c r="E35" t="n">
-        <v>0.5173</v>
+        <v>0.6839</v>
       </c>
       <c r="F35" t="n">
-        <v>0.6664</v>
+        <v>0.6839</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.1491</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0.6664</v>
+        <v>0.6839</v>
       </c>
       <c r="I35" t="n">
-        <v>0.5401</v>
+        <v>0.6839</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.1491</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="L35" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0.391</v>
+        <v>0.6839</v>
       </c>
       <c r="N35" t="n">
-        <v>188</v>
+        <v>95</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>aizy</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.4736</v>
+        <v>0.6788999999999999</v>
       </c>
       <c r="C36" t="n">
-        <v>0.3107</v>
+        <v>0.4454</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.23</v>
+        <v>-0.1734</v>
       </c>
       <c r="E36" t="n">
-        <v>0.4736</v>
+        <v>0.6788999999999999</v>
       </c>
       <c r="F36" t="n">
-        <v>0.4736</v>
+        <v>1.4228</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>-0.7439</v>
       </c>
       <c r="H36" t="n">
-        <v>0.4736</v>
+        <v>1.4228</v>
       </c>
       <c r="I36" t="n">
-        <v>0.4736</v>
+        <v>1.1532</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>-0.7439</v>
       </c>
       <c r="K36" t="n">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="M36" t="n">
-        <v>0.4736</v>
+        <v>0.4093</v>
       </c>
       <c r="N36" t="n">
-        <v>94</v>
+        <v>188</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>fox</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.4322</v>
+        <v>0.5286</v>
       </c>
       <c r="C37" t="n">
-        <v>0.2836</v>
+        <v>0.3468</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.2468</v>
+        <v>-0.2333</v>
       </c>
       <c r="E37" t="n">
-        <v>0.4322</v>
+        <v>0.5286</v>
       </c>
       <c r="F37" t="n">
-        <v>1.1761</v>
+        <v>0.5286</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.7439</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>1.1761</v>
+        <v>0.5286</v>
       </c>
       <c r="I37" t="n">
-        <v>0.9533</v>
+        <v>0.5286</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.7439</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>119</v>
+        <v>94</v>
       </c>
       <c r="L37" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.2094</v>
+        <v>0.5286</v>
       </c>
       <c r="N37" t="n">
-        <v>188</v>
+        <v>94</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>wayLander</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.4139</v>
+        <v>0.5259</v>
       </c>
       <c r="C38" t="n">
-        <v>0.2715</v>
+        <v>0.345</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.2542</v>
+        <v>-0.2344</v>
       </c>
       <c r="E38" t="n">
-        <v>0.4139</v>
+        <v>0.5259</v>
       </c>
       <c r="F38" t="n">
-        <v>0.4139</v>
+        <v>0.5259</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.4139</v>
+        <v>0.5259</v>
       </c>
       <c r="I38" t="n">
-        <v>0.4139</v>
+        <v>0.5259</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>53</v>
+        <v>137</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.4139</v>
+        <v>0.5259</v>
       </c>
       <c r="N38" t="n">
-        <v>53</v>
+        <v>137</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>RpK</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.4136</v>
+        <v>0.5173</v>
       </c>
       <c r="C39" t="n">
-        <v>0.2714</v>
+        <v>0.3394</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.2543</v>
+        <v>-0.2378</v>
       </c>
       <c r="E39" t="n">
-        <v>0.4136</v>
+        <v>0.5173</v>
       </c>
       <c r="F39" t="n">
-        <v>0.4136</v>
+        <v>0.6664</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>-0.1491</v>
       </c>
       <c r="H39" t="n">
-        <v>0.4136</v>
+        <v>0.6664</v>
       </c>
       <c r="I39" t="n">
-        <v>0.4136</v>
+        <v>0.5401</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>-0.1491</v>
       </c>
       <c r="K39" t="n">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="M39" t="n">
-        <v>0.4136</v>
+        <v>0.391</v>
       </c>
       <c r="N39" t="n">
-        <v>109</v>
+        <v>188</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>fox</t>
+          <t>shox</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.3878</v>
+        <v>0.4424</v>
       </c>
       <c r="C40" t="n">
-        <v>0.2544</v>
+        <v>0.2902</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.2647</v>
+        <v>-0.2677</v>
       </c>
       <c r="E40" t="n">
-        <v>0.3878</v>
+        <v>0.4424</v>
       </c>
       <c r="F40" t="n">
-        <v>0.3878</v>
+        <v>0.4424</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.3878</v>
+        <v>0.4424</v>
       </c>
       <c r="I40" t="n">
-        <v>0.3878</v>
+        <v>0.4424</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0.3878</v>
+        <v>0.4424</v>
       </c>
       <c r="N40" t="n">
-        <v>94</v>
+        <v>109</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AdreN</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.3511</v>
+        <v>0.4139</v>
       </c>
       <c r="C41" t="n">
-        <v>0.2303</v>
+        <v>0.2715</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.2795</v>
+        <v>-0.279</v>
       </c>
       <c r="E41" t="n">
-        <v>0.3511</v>
+        <v>0.4139</v>
       </c>
       <c r="F41" t="n">
-        <v>0.3511</v>
+        <v>0.4139</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.3511</v>
+        <v>0.4139</v>
       </c>
       <c r="I41" t="n">
-        <v>0.3511</v>
+        <v>0.4139</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>137</v>
+        <v>53</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.3511</v>
+        <v>0.4139</v>
       </c>
       <c r="N41" t="n">
-        <v>137</v>
+        <v>53</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>RpK</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.3115</v>
+        <v>0.4136</v>
       </c>
       <c r="C42" t="n">
-        <v>0.2044</v>
+        <v>0.2714</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.2955</v>
+        <v>-0.2791</v>
       </c>
       <c r="E42" t="n">
-        <v>0.3115</v>
+        <v>0.4136</v>
       </c>
       <c r="F42" t="n">
-        <v>0.3115</v>
+        <v>0.4136</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.3115</v>
+        <v>0.4136</v>
       </c>
       <c r="I42" t="n">
-        <v>0.3115</v>
+        <v>0.4136</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>53</v>
+        <v>109</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.3115</v>
+        <v>0.4136</v>
       </c>
       <c r="N42" t="n">
-        <v>53</v>
+        <v>109</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Xizt</t>
+          <t>AdreN</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.2931</v>
+        <v>0.3511</v>
       </c>
       <c r="C43" t="n">
-        <v>0.1923</v>
+        <v>0.2303</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.303</v>
+        <v>-0.304</v>
       </c>
       <c r="E43" t="n">
-        <v>0.2931</v>
+        <v>0.3511</v>
       </c>
       <c r="F43" t="n">
-        <v>0.2931</v>
+        <v>0.3511</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.2931</v>
+        <v>0.3511</v>
       </c>
       <c r="I43" t="n">
-        <v>0.2931</v>
+        <v>0.3511</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>182</v>
+        <v>137</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.2931</v>
+        <v>0.3511</v>
       </c>
       <c r="N43" t="n">
-        <v>182</v>
+        <v>137</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>shox</t>
+          <t>Ex6TenZ</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.2608</v>
+        <v>0.325</v>
       </c>
       <c r="C44" t="n">
-        <v>0.1711</v>
+        <v>0.2132</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.316</v>
+        <v>-0.3144</v>
       </c>
       <c r="E44" t="n">
-        <v>0.2608</v>
+        <v>0.325</v>
       </c>
       <c r="F44" t="n">
-        <v>0.2608</v>
+        <v>0.325</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.2608</v>
+        <v>0.325</v>
       </c>
       <c r="I44" t="n">
-        <v>0.2608</v>
+        <v>0.325</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -2461,7 +2461,7 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.2608</v>
+        <v>0.325</v>
       </c>
       <c r="N44" t="n">
         <v>109</v>
@@ -2470,231 +2470,231 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>markeloff</t>
+          <t>Happy</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.2578</v>
+        <v>0.3115</v>
       </c>
       <c r="C45" t="n">
-        <v>0.1691</v>
+        <v>0.2044</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.3172</v>
+        <v>-0.3198</v>
       </c>
       <c r="E45" t="n">
-        <v>0.2578</v>
+        <v>0.3115</v>
       </c>
       <c r="F45" t="n">
-        <v>0.2578</v>
+        <v>0.3115</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.2578</v>
+        <v>0.3115</v>
       </c>
       <c r="I45" t="n">
-        <v>0.2578</v>
+        <v>0.3115</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>95</v>
+        <v>53</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0.2578</v>
+        <v>0.3115</v>
       </c>
       <c r="N45" t="n">
-        <v>95</v>
+        <v>53</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Spiidi</t>
+          <t>Xizt</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.2222</v>
+        <v>0.2931</v>
       </c>
       <c r="C46" t="n">
-        <v>0.1458</v>
+        <v>0.1923</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.3316</v>
+        <v>-0.3271</v>
       </c>
       <c r="E46" t="n">
-        <v>0.2222</v>
+        <v>0.2931</v>
       </c>
       <c r="F46" t="n">
-        <v>0.2222</v>
+        <v>0.2931</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.2222</v>
+        <v>0.2931</v>
       </c>
       <c r="I46" t="n">
-        <v>0.2222</v>
+        <v>0.2931</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0.2222</v>
+        <v>0.2931</v>
       </c>
       <c r="N46" t="n">
-        <v>162</v>
+        <v>182</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Dosia</t>
+          <t>markeloff</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.2221</v>
+        <v>0.2578</v>
       </c>
       <c r="C47" t="n">
-        <v>0.1457</v>
+        <v>0.1691</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.3316</v>
+        <v>-0.3412</v>
       </c>
       <c r="E47" t="n">
-        <v>0.2221</v>
+        <v>0.2578</v>
       </c>
       <c r="F47" t="n">
-        <v>0.2221</v>
+        <v>0.2578</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.2221</v>
+        <v>0.2578</v>
       </c>
       <c r="I47" t="n">
-        <v>0.2221</v>
+        <v>0.2578</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>137</v>
+        <v>95</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0.2221</v>
+        <v>0.2578</v>
       </c>
       <c r="N47" t="n">
-        <v>137</v>
+        <v>95</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>DAVEY</t>
+          <t>Spiidi</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.1855</v>
+        <v>0.2222</v>
       </c>
       <c r="C48" t="n">
-        <v>0.1217</v>
+        <v>0.1458</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.3464</v>
+        <v>-0.3554</v>
       </c>
       <c r="E48" t="n">
-        <v>0.1855</v>
+        <v>0.2222</v>
       </c>
       <c r="F48" t="n">
-        <v>0.1855</v>
+        <v>0.2222</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.1855</v>
+        <v>0.2222</v>
       </c>
       <c r="I48" t="n">
-        <v>0.1855</v>
+        <v>0.2222</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>40</v>
+        <v>162</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0.1855</v>
+        <v>0.2222</v>
       </c>
       <c r="N48" t="n">
-        <v>40</v>
+        <v>162</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>chrisJ</t>
+          <t>Dosia</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.132</v>
+        <v>0.2221</v>
       </c>
       <c r="C49" t="n">
-        <v>0.0866</v>
+        <v>0.1457</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.368</v>
+        <v>-0.3554</v>
       </c>
       <c r="E49" t="n">
-        <v>0.132</v>
+        <v>0.2221</v>
       </c>
       <c r="F49" t="n">
-        <v>0.132</v>
+        <v>0.2221</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.132</v>
+        <v>0.2221</v>
       </c>
       <c r="I49" t="n">
-        <v>0.132</v>
+        <v>0.2221</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>162</v>
+        <v>137</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0.132</v>
+        <v>0.2221</v>
       </c>
       <c r="N49" t="n">
-        <v>162</v>
+        <v>137</v>
       </c>
     </row>
     <row r="50">
@@ -2704,28 +2704,28 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.1262</v>
+        <v>0.2033</v>
       </c>
       <c r="C50" t="n">
-        <v>0.0828</v>
+        <v>0.1334</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.3704</v>
+        <v>-0.3629</v>
       </c>
       <c r="E50" t="n">
-        <v>0.1262</v>
+        <v>0.2033</v>
       </c>
       <c r="F50" t="n">
-        <v>0.1262</v>
+        <v>0.2033</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0.1262</v>
+        <v>0.2033</v>
       </c>
       <c r="I50" t="n">
-        <v>0.1262</v>
+        <v>0.2033</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -2737,7 +2737,7 @@
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>0.1262</v>
+        <v>0.2033</v>
       </c>
       <c r="N50" t="n">
         <v>199</v>
@@ -2746,1059 +2746,1059 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ScreaM</t>
+          <t>DAVEY</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.0658</v>
+        <v>0.1855</v>
       </c>
       <c r="C51" t="n">
-        <v>0.0432</v>
+        <v>0.1217</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.3948</v>
+        <v>-0.37</v>
       </c>
       <c r="E51" t="n">
-        <v>0.0658</v>
+        <v>0.1855</v>
       </c>
       <c r="F51" t="n">
-        <v>0.0658</v>
+        <v>0.1855</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>0.0658</v>
+        <v>0.1855</v>
       </c>
       <c r="I51" t="n">
-        <v>0.0658</v>
+        <v>0.1855</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>109</v>
+        <v>40</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>0.0658</v>
+        <v>0.1855</v>
       </c>
       <c r="N51" t="n">
-        <v>109</v>
+        <v>40</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>WorldEdit</t>
+          <t>chrisJ</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.0126</v>
+        <v>0.132</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.0083</v>
+        <v>0.0866</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.4265</v>
+        <v>-0.3913</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.0126</v>
+        <v>0.132</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.0126</v>
+        <v>0.132</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.0126</v>
+        <v>0.132</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.0126</v>
+        <v>0.132</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>95</v>
+        <v>162</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>-0.0126</v>
+        <v>0.132</v>
       </c>
       <c r="N52" t="n">
-        <v>95</v>
+        <v>162</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>NBK-</t>
+          <t>ScreaM</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.0847</v>
+        <v>0.0658</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.0556</v>
+        <v>0.0432</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.4556</v>
+        <v>-0.4177</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.0847</v>
+        <v>0.0658</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.0847</v>
+        <v>0.0658</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.0847</v>
+        <v>0.0658</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.0847</v>
+        <v>0.0658</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>53</v>
+        <v>109</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>-0.0847</v>
+        <v>0.0658</v>
       </c>
       <c r="N53" t="n">
-        <v>53</v>
+        <v>109</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Skadoodle</t>
+          <t>WorldEdit</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.1461</v>
+        <v>-0.0126</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.0959</v>
+        <v>-0.0083</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.4804</v>
+        <v>-0.4489</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.1461</v>
+        <v>-0.0126</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.1461</v>
+        <v>-0.0126</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.1461</v>
+        <v>-0.0126</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.1461</v>
+        <v>-0.0126</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-0.1461</v>
+        <v>-0.0126</v>
       </c>
       <c r="N54" t="n">
-        <v>44</v>
+        <v>95</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>wayLander</t>
+          <t>NBK-</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.2217</v>
+        <v>-0.0847</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.1455</v>
+        <v>-0.0556</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.5109</v>
+        <v>-0.4777</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.2217</v>
+        <v>-0.0847</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.2217</v>
+        <v>-0.0847</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.2217</v>
+        <v>-0.0847</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.2217</v>
+        <v>-0.0847</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>137</v>
+        <v>53</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>-0.2217</v>
+        <v>-0.0847</v>
       </c>
       <c r="N55" t="n">
-        <v>137</v>
+        <v>53</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>hooch</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.2551</v>
+        <v>-0.14</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.1674</v>
+        <v>-0.0919</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.5244</v>
+        <v>-0.4997</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.2551</v>
+        <v>-0.14</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.2551</v>
+        <v>1.5423</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>-1.6823</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.2551</v>
+        <v>1.5423</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.2551</v>
+        <v>1.2501</v>
       </c>
       <c r="J56" t="n">
-        <v>0</v>
+        <v>-1.6823</v>
       </c>
       <c r="K56" t="n">
-        <v>137</v>
+        <v>96</v>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="M56" t="n">
-        <v>-0.2551</v>
+        <v>-0.4321999999999999</v>
       </c>
       <c r="N56" t="n">
-        <v>137</v>
+        <v>201</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>DEVIL</t>
+          <t>Skadoodle</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.2942</v>
+        <v>-0.1461</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.193</v>
+        <v>-0.0959</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.5402</v>
+        <v>-0.5021</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.2942</v>
+        <v>-0.1461</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.2942</v>
+        <v>-0.1461</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.2942</v>
+        <v>-0.1461</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.2942</v>
+        <v>-0.1461</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>-0.2942</v>
+        <v>-0.1461</v>
       </c>
       <c r="N57" t="n">
-        <v>53</v>
+        <v>44</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>denis</t>
+          <t>reltuC</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.3573</v>
+        <v>-0.1753</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.2344</v>
+        <v>-0.115</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.5657</v>
+        <v>-0.5137</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.3573</v>
+        <v>-0.1753</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.3573</v>
+        <v>-0.1753</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.3573</v>
+        <v>-0.1753</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.3573</v>
+        <v>-0.1753</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>-0.3573</v>
+        <v>-0.1753</v>
       </c>
       <c r="N58" t="n">
-        <v>162</v>
+        <v>182</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>arya</t>
+          <t>SmithZz</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.4357</v>
+        <v>-0.1907</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.2859</v>
+        <v>-0.1251</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.5974</v>
+        <v>-0.5199</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.4357</v>
+        <v>-0.1907</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.4357</v>
+        <v>-0.1907</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.4357</v>
+        <v>-0.1907</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.4357</v>
+        <v>-0.1907</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>40</v>
+        <v>109</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>-0.4357</v>
+        <v>-0.1907</v>
       </c>
       <c r="N59" t="n">
-        <v>40</v>
+        <v>109</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>shroud</t>
+          <t>hooch</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.4671</v>
+        <v>-0.2551</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.3065</v>
+        <v>-0.1674</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.6101</v>
+        <v>-0.5455</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.4671</v>
+        <v>-0.2551</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.4671</v>
+        <v>-0.2551</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.4671</v>
+        <v>-0.2551</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.4671</v>
+        <v>-0.2551</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>44</v>
+        <v>137</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>-0.4671</v>
+        <v>-0.2551</v>
       </c>
       <c r="N60" t="n">
-        <v>44</v>
+        <v>137</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>DEVIL</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.4791</v>
+        <v>-0.2942</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.3143</v>
+        <v>-0.193</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.6149</v>
+        <v>-0.5611</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.4791</v>
+        <v>-0.2942</v>
       </c>
       <c r="F61" t="n">
-        <v>1.2032</v>
+        <v>-0.2942</v>
       </c>
       <c r="G61" t="n">
-        <v>-1.6823</v>
+        <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>1.2032</v>
+        <v>-0.2942</v>
       </c>
       <c r="I61" t="n">
-        <v>0.9752</v>
+        <v>-0.2942</v>
       </c>
       <c r="J61" t="n">
-        <v>-1.6823</v>
+        <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>96</v>
+        <v>53</v>
       </c>
       <c r="L61" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>-0.7071</v>
+        <v>-0.2942</v>
       </c>
       <c r="N61" t="n">
-        <v>201</v>
+        <v>53</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>B1ad3</t>
+          <t>denis</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.5107</v>
+        <v>-0.3573</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.3351</v>
+        <v>-0.2344</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.6277</v>
+        <v>-0.5863</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.5107</v>
+        <v>-0.3573</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.5107</v>
+        <v>-0.3573</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.5107</v>
+        <v>-0.3573</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.5107</v>
+        <v>-0.3573</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>95</v>
+        <v>162</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.5107</v>
+        <v>-0.3573</v>
       </c>
       <c r="N62" t="n">
-        <v>95</v>
+        <v>162</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Ex6TenZ</t>
+          <t>arya</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.5692</v>
+        <v>-0.4357</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.3734</v>
+        <v>-0.2859</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.6513</v>
+        <v>-0.6175</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.5692</v>
+        <v>-0.4357</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.5692</v>
+        <v>-0.4357</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.5692</v>
+        <v>-0.4357</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.5692</v>
+        <v>-0.4357</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>109</v>
+        <v>40</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.5692</v>
+        <v>-0.4357</v>
       </c>
       <c r="N63" t="n">
-        <v>109</v>
+        <v>40</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Maikelele</t>
+          <t>shroud</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.7125</v>
+        <v>-0.4671</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.4675</v>
+        <v>-0.3065</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.7092000000000001</v>
+        <v>-0.63</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.7125</v>
+        <v>-0.4671</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.7125</v>
+        <v>-0.4671</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.7125</v>
+        <v>-0.4671</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.7125</v>
+        <v>-0.4671</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>94</v>
+        <v>44</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>-0.7125</v>
+        <v>-0.4671</v>
       </c>
       <c r="N64" t="n">
-        <v>94</v>
+        <v>44</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>jkaem</t>
+          <t>B1ad3</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.8021</v>
+        <v>-0.5107</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.5262</v>
+        <v>-0.3351</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.7454</v>
+        <v>-0.6474</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.8021</v>
+        <v>-0.5107</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.8021</v>
+        <v>-0.5107</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.8021</v>
+        <v>-0.5107</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.8021</v>
+        <v>-0.5107</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.8021</v>
+        <v>-0.5107</v>
       </c>
       <c r="N65" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>mou</t>
+          <t>Maikelele</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.8448</v>
+        <v>-0.7125</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.5543</v>
+        <v>-0.4675</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.7625999999999999</v>
+        <v>-0.7278</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.8448</v>
+        <v>-0.7125</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.8448</v>
+        <v>-0.7125</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.8448</v>
+        <v>-0.7125</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.8448</v>
+        <v>-0.7125</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>137</v>
+        <v>94</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>-0.8448</v>
+        <v>-0.7125</v>
       </c>
       <c r="N66" t="n">
-        <v>137</v>
+        <v>94</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>kennyS</t>
+          <t>jkaem</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.8482</v>
+        <v>-0.7631</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.5565</v>
+        <v>-0.5007</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.764</v>
+        <v>-0.7479</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.8482</v>
+        <v>-0.7631</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.8482</v>
+        <v>-0.7631</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.8482</v>
+        <v>-0.7631</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.8482</v>
+        <v>-0.7631</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>53</v>
+        <v>94</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>-0.8482</v>
+        <v>-0.7631</v>
       </c>
       <c r="N67" t="n">
-        <v>53</v>
+        <v>94</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>friberg</t>
+          <t>mou</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.8774</v>
+        <v>-0.8448</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.5756</v>
+        <v>-0.5543</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.7758</v>
+        <v>-0.7805</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.8774</v>
+        <v>-0.8448</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.8774</v>
+        <v>-0.8448</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.8774</v>
+        <v>-0.8448</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.8774</v>
+        <v>-0.8448</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>182</v>
+        <v>137</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>-0.8774</v>
+        <v>-0.8448</v>
       </c>
       <c r="N68" t="n">
-        <v>182</v>
+        <v>137</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>n0thing</t>
+          <t>kennyS</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-0.913</v>
+        <v>-0.8482</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.599</v>
+        <v>-0.5565</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.7902</v>
+        <v>-0.7818000000000001</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.913</v>
+        <v>-0.8482</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.913</v>
+        <v>-0.8482</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.913</v>
+        <v>-0.8482</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.913</v>
+        <v>-0.8482</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>-0.913</v>
+        <v>-0.8482</v>
       </c>
       <c r="N69" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>friberg</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-0.914</v>
+        <v>-0.8774</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.5997</v>
+        <v>-0.5756</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.7906</v>
+        <v>-0.7935</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.914</v>
+        <v>-0.8774</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.914</v>
+        <v>-0.8774</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>-0.914</v>
+        <v>-0.8774</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.914</v>
+        <v>-0.8774</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>44</v>
+        <v>182</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>-0.914</v>
+        <v>-0.8774</v>
       </c>
       <c r="N70" t="n">
-        <v>44</v>
+        <v>182</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Zeus</t>
+          <t>n0thing</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-0.9534</v>
+        <v>-0.913</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.6254999999999999</v>
+        <v>-0.599</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.8065</v>
+        <v>-0.8076</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.9534</v>
+        <v>-0.913</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.72</v>
+        <v>-0.913</v>
       </c>
       <c r="G71" t="n">
-        <v>-0.2334</v>
+        <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>-0.72</v>
+        <v>-0.913</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.5836</v>
+        <v>-0.913</v>
       </c>
       <c r="J71" t="n">
-        <v>-0.2334</v>
+        <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>96</v>
+        <v>44</v>
       </c>
       <c r="L71" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>-0.8169999999999999</v>
+        <v>-0.913</v>
       </c>
       <c r="N71" t="n">
-        <v>201</v>
+        <v>44</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>reltuC</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-0.9578</v>
+        <v>-0.914</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.6284</v>
+        <v>-0.5997</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.8083</v>
+        <v>-0.8080000000000001</v>
       </c>
       <c r="E72" t="n">
-        <v>-0.9578</v>
+        <v>-0.914</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.9578</v>
+        <v>-0.914</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>-0.9578</v>
+        <v>-0.914</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.9578</v>
+        <v>-0.914</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>182</v>
+        <v>44</v>
       </c>
       <c r="L72" t="n">
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>-0.9578</v>
+        <v>-0.914</v>
       </c>
       <c r="N72" t="n">
-        <v>182</v>
+        <v>44</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>SmithZz</t>
+          <t>Zeus</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-1.1164</v>
+        <v>-0.9534</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.7324000000000001</v>
+        <v>-0.6254999999999999</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.8724</v>
+        <v>-0.8237</v>
       </c>
       <c r="E73" t="n">
-        <v>-1.1164</v>
+        <v>-0.9534</v>
       </c>
       <c r="F73" t="n">
-        <v>-1.1164</v>
+        <v>-0.72</v>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>-0.2334</v>
       </c>
       <c r="H73" t="n">
-        <v>-1.1164</v>
+        <v>-0.72</v>
       </c>
       <c r="I73" t="n">
-        <v>-1.1164</v>
+        <v>-0.5836</v>
       </c>
       <c r="J73" t="n">
-        <v>0</v>
+        <v>-0.2334</v>
       </c>
       <c r="K73" t="n">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="M73" t="n">
-        <v>-1.1164</v>
+        <v>-0.8169999999999999</v>
       </c>
       <c r="N73" t="n">
-        <v>109</v>
+        <v>201</v>
       </c>
     </row>
     <row r="74">
@@ -3814,7 +3814,7 @@
         <v>-0.7399</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.8769</v>
+        <v>-0.8932</v>
       </c>
       <c r="E74" t="n">
         <v>-1.1277</v>
@@ -3860,7 +3860,7 @@
         <v>-0.867</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.9552</v>
+        <v>-0.9704</v>
       </c>
       <c r="E75" t="n">
         <v>-1.3215</v>
@@ -3906,7 +3906,7 @@
         <v>-0.9852</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.028</v>
+        <v>-1.0421</v>
       </c>
       <c r="E76" t="n">
         <v>-1.5016</v>
@@ -3952,7 +3952,7 @@
         <v>-1.0953</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.0958</v>
+        <v>-1.109</v>
       </c>
       <c r="E77" t="n">
         <v>-1.6694</v>
@@ -3998,7 +3998,7 @@
         <v>-1.1155</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.1082</v>
+        <v>-1.1213</v>
       </c>
       <c r="E78" t="n">
         <v>-1.7002</v>
@@ -4044,7 +4044,7 @@
         <v>-1.3009</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.2224</v>
+        <v>-1.2339</v>
       </c>
       <c r="E79" t="n">
         <v>-1.9828</v>
@@ -4090,7 +4090,7 @@
         <v>-1.5342</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.3661</v>
+        <v>-1.3756</v>
       </c>
       <c r="E80" t="n">
         <v>-2.3385</v>
@@ -4136,7 +4136,7 @@
         <v>-2.6694</v>
       </c>
       <c r="D81" t="n">
-        <v>-2.0651</v>
+        <v>-2.0649</v>
       </c>
       <c r="E81" t="n">
         <v>-4.0688</v>

--- a/database/event/2027/event_2027_evp_summary.xlsx
+++ b/database/event/2027/event_2027_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.8264</v>
+        <v>6.9416</v>
       </c>
       <c r="C2" t="n">
-        <v>5.1347</v>
+        <v>4.5542</v>
       </c>
       <c r="D2" t="n">
-        <v>2.6741</v>
+        <v>2.4958</v>
       </c>
       <c r="E2" t="n">
-        <v>7.8264</v>
+        <v>6.9416</v>
       </c>
       <c r="F2" t="n">
-        <v>4.3658</v>
+        <v>3.7766</v>
       </c>
       <c r="G2" t="n">
-        <v>3.4606</v>
+        <v>3.165</v>
       </c>
       <c r="H2" t="n">
-        <v>5.0043</v>
+        <v>7.8201</v>
       </c>
       <c r="I2" t="n">
-        <v>4.0561</v>
+        <v>4.0661</v>
       </c>
       <c r="J2" t="n">
-        <v>3.4606</v>
+        <v>3.165</v>
       </c>
       <c r="K2" t="n">
         <v>139</v>
@@ -529,7 +529,7 @@
         <v>123</v>
       </c>
       <c r="M2" t="n">
-        <v>7.5167</v>
+        <v>7.2311</v>
       </c>
       <c r="N2" t="n">
         <v>262</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.5703</v>
+        <v>5.2904</v>
       </c>
       <c r="C3" t="n">
-        <v>4.3106</v>
+        <v>3.4709</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1737</v>
+        <v>1.7503</v>
       </c>
       <c r="E3" t="n">
-        <v>6.5703</v>
+        <v>5.2904</v>
       </c>
       <c r="F3" t="n">
-        <v>4.3027</v>
+        <v>3.6048</v>
       </c>
       <c r="G3" t="n">
-        <v>2.2677</v>
+        <v>1.6856</v>
       </c>
       <c r="H3" t="n">
-        <v>4.7501</v>
+        <v>7.2149</v>
       </c>
       <c r="I3" t="n">
-        <v>3.8501</v>
+        <v>3.7514</v>
       </c>
       <c r="J3" t="n">
-        <v>2.2677</v>
+        <v>1.6856</v>
       </c>
       <c r="K3" t="n">
         <v>96</v>
@@ -575,7 +575,7 @@
         <v>105</v>
       </c>
       <c r="M3" t="n">
-        <v>6.1178</v>
+        <v>5.436999999999999</v>
       </c>
       <c r="N3" t="n">
         <v>201</v>
@@ -584,127 +584,127 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>flamie</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.9749</v>
+        <v>5.1813</v>
       </c>
       <c r="C4" t="n">
-        <v>3.92</v>
+        <v>3.3993</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9365</v>
+        <v>1.7011</v>
       </c>
       <c r="E4" t="n">
-        <v>5.9749</v>
+        <v>5.1813</v>
       </c>
       <c r="F4" t="n">
-        <v>3.801</v>
+        <v>2.2466</v>
       </c>
       <c r="G4" t="n">
-        <v>2.1739</v>
+        <v>2.9347</v>
       </c>
       <c r="H4" t="n">
-        <v>3.801</v>
+        <v>2.4294</v>
       </c>
       <c r="I4" t="n">
-        <v>3.0808</v>
+        <v>1.2632</v>
       </c>
       <c r="J4" t="n">
-        <v>2.1739</v>
+        <v>2.9347</v>
       </c>
       <c r="K4" t="n">
-        <v>96</v>
+        <v>139</v>
       </c>
       <c r="L4" t="n">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="M4" t="n">
-        <v>5.2547</v>
+        <v>4.1979</v>
       </c>
       <c r="N4" t="n">
-        <v>201</v>
+        <v>262</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>flamie</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.7368</v>
+        <v>5.0153</v>
       </c>
       <c r="C5" t="n">
-        <v>3.1077</v>
+        <v>3.2904</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4432</v>
+        <v>1.6261</v>
       </c>
       <c r="E5" t="n">
-        <v>4.7368</v>
+        <v>5.0153</v>
       </c>
       <c r="F5" t="n">
-        <v>1.4098</v>
+        <v>3.3364</v>
       </c>
       <c r="G5" t="n">
-        <v>3.327</v>
+        <v>1.6789</v>
       </c>
       <c r="H5" t="n">
-        <v>1.4098</v>
+        <v>6.2692</v>
       </c>
       <c r="I5" t="n">
-        <v>1.1427</v>
+        <v>3.2597</v>
       </c>
       <c r="J5" t="n">
-        <v>3.327</v>
+        <v>1.6789</v>
       </c>
       <c r="K5" t="n">
-        <v>139</v>
+        <v>96</v>
       </c>
       <c r="L5" t="n">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="M5" t="n">
-        <v>4.4697</v>
+        <v>4.9386</v>
       </c>
       <c r="N5" t="n">
-        <v>262</v>
+        <v>201</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>fnx</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.6848</v>
+        <v>4.3623</v>
       </c>
       <c r="C6" t="n">
-        <v>3.0736</v>
+        <v>2.862</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4225</v>
+        <v>1.3313</v>
       </c>
       <c r="E6" t="n">
-        <v>4.6848</v>
+        <v>4.3623</v>
       </c>
       <c r="F6" t="n">
-        <v>4.2559</v>
+        <v>1.6763</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4289</v>
+        <v>2.686</v>
       </c>
       <c r="H6" t="n">
-        <v>4.5621</v>
+        <v>1.6763</v>
       </c>
       <c r="I6" t="n">
-        <v>3.6977</v>
+        <v>0.8716</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4289</v>
+        <v>2.686</v>
       </c>
       <c r="K6" t="n">
         <v>139</v>
@@ -713,7 +713,7 @@
         <v>123</v>
       </c>
       <c r="M6" t="n">
-        <v>4.1266</v>
+        <v>3.5576</v>
       </c>
       <c r="N6" t="n">
         <v>262</v>
@@ -722,47 +722,47 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>fnx</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.8663</v>
+        <v>4.1113</v>
       </c>
       <c r="C7" t="n">
-        <v>2.5366</v>
+        <v>2.6973</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0964</v>
+        <v>1.218</v>
       </c>
       <c r="E7" t="n">
-        <v>3.8663</v>
+        <v>4.1113</v>
       </c>
       <c r="F7" t="n">
-        <v>4.3498</v>
+        <v>3.463</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.4835</v>
+        <v>0.6483</v>
       </c>
       <c r="H7" t="n">
-        <v>4.9397</v>
+        <v>6.7151</v>
       </c>
       <c r="I7" t="n">
-        <v>4.0038</v>
+        <v>3.4915</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.4835</v>
+        <v>0.6483</v>
       </c>
       <c r="K7" t="n">
-        <v>98</v>
+        <v>139</v>
       </c>
       <c r="L7" t="n">
-        <v>51</v>
+        <v>123</v>
       </c>
       <c r="M7" t="n">
-        <v>3.5203</v>
+        <v>4.1398</v>
       </c>
       <c r="N7" t="n">
-        <v>149</v>
+        <v>262</v>
       </c>
     </row>
     <row r="8">
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.8186</v>
+        <v>3.5313</v>
       </c>
       <c r="C8" t="n">
-        <v>2.5053</v>
+        <v>2.3168</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0774</v>
+        <v>0.9562</v>
       </c>
       <c r="E8" t="n">
-        <v>3.8186</v>
+        <v>3.5313</v>
       </c>
       <c r="F8" t="n">
-        <v>3.5041</v>
+        <v>3.212</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3145</v>
+        <v>0.3193</v>
       </c>
       <c r="H8" t="n">
-        <v>3.5041</v>
+        <v>5.8309</v>
       </c>
       <c r="I8" t="n">
-        <v>2.8401</v>
+        <v>3.0318</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3145</v>
+        <v>0.3193</v>
       </c>
       <c r="K8" t="n">
         <v>119</v>
@@ -805,7 +805,7 @@
         <v>69</v>
       </c>
       <c r="M8" t="n">
-        <v>3.1546</v>
+        <v>3.3511</v>
       </c>
       <c r="N8" t="n">
         <v>188</v>
@@ -814,47 +814,47 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.767</v>
+        <v>3.4461</v>
       </c>
       <c r="C9" t="n">
-        <v>2.4714</v>
+        <v>2.2609</v>
       </c>
       <c r="D9" t="n">
-        <v>1.0569</v>
+        <v>0.9177</v>
       </c>
       <c r="E9" t="n">
-        <v>3.767</v>
+        <v>3.4461</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8449</v>
+        <v>3.6988</v>
       </c>
       <c r="G9" t="n">
-        <v>2.9221</v>
+        <v>-0.2527</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8449</v>
+        <v>7.5459</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6848</v>
+        <v>3.9235</v>
       </c>
       <c r="J9" t="n">
-        <v>2.9221</v>
+        <v>-0.2527</v>
       </c>
       <c r="K9" t="n">
-        <v>139</v>
+        <v>98</v>
       </c>
       <c r="L9" t="n">
-        <v>123</v>
+        <v>51</v>
       </c>
       <c r="M9" t="n">
-        <v>3.6069</v>
+        <v>3.6708</v>
       </c>
       <c r="N9" t="n">
-        <v>262</v>
+        <v>149</v>
       </c>
     </row>
     <row r="10">
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.672</v>
+        <v>3.1599</v>
       </c>
       <c r="C10" t="n">
-        <v>2.4091</v>
+        <v>2.0731</v>
       </c>
       <c r="D10" t="n">
-        <v>1.019</v>
+        <v>0.7885</v>
       </c>
       <c r="E10" t="n">
-        <v>3.672</v>
+        <v>3.1599</v>
       </c>
       <c r="F10" t="n">
-        <v>4.0225</v>
+        <v>3.3208</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.3505</v>
+        <v>-0.1609</v>
       </c>
       <c r="H10" t="n">
-        <v>4.0225</v>
+        <v>6.214</v>
       </c>
       <c r="I10" t="n">
-        <v>3.2603</v>
+        <v>3.231</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.3505</v>
+        <v>-0.1609</v>
       </c>
       <c r="K10" t="n">
         <v>119</v>
@@ -897,7 +897,7 @@
         <v>69</v>
       </c>
       <c r="M10" t="n">
-        <v>2.9098</v>
+        <v>3.0701</v>
       </c>
       <c r="N10" t="n">
         <v>188</v>
@@ -906,277 +906,277 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>seized</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.3008</v>
+        <v>3.0046</v>
       </c>
       <c r="C11" t="n">
-        <v>2.1656</v>
+        <v>1.9712</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8711</v>
+        <v>0.7184</v>
       </c>
       <c r="E11" t="n">
-        <v>3.3008</v>
+        <v>3.0046</v>
       </c>
       <c r="F11" t="n">
-        <v>4.2932</v>
+        <v>3.3016</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.9923999999999999</v>
+        <v>-0.297</v>
       </c>
       <c r="H11" t="n">
-        <v>4.712</v>
+        <v>6.1463</v>
       </c>
       <c r="I11" t="n">
-        <v>3.8192</v>
+        <v>3.1958</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.9923999999999999</v>
+        <v>-0.297</v>
       </c>
       <c r="K11" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L11" t="n">
-        <v>105</v>
+        <v>51</v>
       </c>
       <c r="M11" t="n">
-        <v>2.8268</v>
+        <v>2.8988</v>
       </c>
       <c r="N11" t="n">
-        <v>201</v>
+        <v>149</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>jdm64</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.0847</v>
+        <v>2.9556</v>
       </c>
       <c r="C12" t="n">
-        <v>2.0238</v>
+        <v>1.9391</v>
       </c>
       <c r="D12" t="n">
-        <v>0.785</v>
+        <v>0.6963</v>
       </c>
       <c r="E12" t="n">
-        <v>3.0847</v>
+        <v>2.9556</v>
       </c>
       <c r="F12" t="n">
-        <v>3.4838</v>
+        <v>2.9556</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.3991</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>3.4838</v>
+        <v>3.1302</v>
       </c>
       <c r="I12" t="n">
-        <v>2.8237</v>
+        <v>3.1302</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.3991</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>98</v>
+        <v>182</v>
       </c>
       <c r="L12" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.4246</v>
+        <v>3.1302</v>
       </c>
       <c r="N12" t="n">
-        <v>149</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>cajunb</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.07</v>
+        <v>2.9319</v>
       </c>
       <c r="C13" t="n">
-        <v>2.0142</v>
+        <v>1.9235</v>
       </c>
       <c r="D13" t="n">
-        <v>0.7792</v>
+        <v>0.6856</v>
       </c>
       <c r="E13" t="n">
-        <v>3.07</v>
+        <v>2.9319</v>
       </c>
       <c r="F13" t="n">
-        <v>3.4691</v>
+        <v>2.9319</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.3991</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>3.4691</v>
+        <v>3.0781</v>
       </c>
       <c r="I13" t="n">
-        <v>2.8118</v>
+        <v>3.0781</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.3991</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>98</v>
+        <v>182</v>
       </c>
       <c r="L13" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.4127</v>
+        <v>3.0781</v>
       </c>
       <c r="N13" t="n">
-        <v>149</v>
+        <v>182</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>flusha</t>
+          <t>byali</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.9738</v>
+        <v>2.9243</v>
       </c>
       <c r="C14" t="n">
-        <v>1.951</v>
+        <v>1.9186</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7409</v>
+        <v>0.6822</v>
       </c>
       <c r="E14" t="n">
-        <v>2.9738</v>
+        <v>2.9243</v>
       </c>
       <c r="F14" t="n">
-        <v>2.9738</v>
+        <v>2.9243</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>2.9738</v>
+        <v>3.0616</v>
       </c>
       <c r="I14" t="n">
-        <v>2.9738</v>
+        <v>3.0616</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>157</v>
+        <v>199</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.9738</v>
+        <v>3.0616</v>
       </c>
       <c r="N14" t="n">
-        <v>157</v>
+        <v>199</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>byali</t>
+          <t>GeT_RiGhT</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.9169</v>
+        <v>2.9038</v>
       </c>
       <c r="C15" t="n">
-        <v>1.9137</v>
+        <v>1.9051</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7181999999999999</v>
+        <v>0.6729000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>2.9169</v>
+        <v>2.9038</v>
       </c>
       <c r="F15" t="n">
-        <v>2.9169</v>
+        <v>2.9038</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2.9169</v>
+        <v>3.0164</v>
       </c>
       <c r="I15" t="n">
-        <v>2.9169</v>
+        <v>3.0164</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.9169</v>
+        <v>3.0164</v>
       </c>
       <c r="N15" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>flusha</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.8249</v>
+        <v>2.8849</v>
       </c>
       <c r="C16" t="n">
-        <v>1.8533</v>
+        <v>1.8927</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6815</v>
+        <v>0.6644</v>
       </c>
       <c r="E16" t="n">
-        <v>2.8249</v>
+        <v>2.8849</v>
       </c>
       <c r="F16" t="n">
-        <v>2.8249</v>
+        <v>2.8849</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2.8249</v>
+        <v>2.9751</v>
       </c>
       <c r="I16" t="n">
-        <v>2.8249</v>
+        <v>2.9751</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.8249</v>
+        <v>2.9751</v>
       </c>
       <c r="N16" t="n">
-        <v>162</v>
+        <v>157</v>
       </c>
     </row>
     <row r="17">
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.8149</v>
+        <v>2.8845</v>
       </c>
       <c r="C17" t="n">
-        <v>1.8468</v>
+        <v>1.8925</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6775</v>
+        <v>0.6642</v>
       </c>
       <c r="E17" t="n">
-        <v>2.8149</v>
+        <v>2.8845</v>
       </c>
       <c r="F17" t="n">
-        <v>2.8149</v>
+        <v>2.8845</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>2.8149</v>
+        <v>2.9742</v>
       </c>
       <c r="I17" t="n">
-        <v>2.8149</v>
+        <v>2.9742</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>2.8149</v>
+        <v>2.9742</v>
       </c>
       <c r="N17" t="n">
         <v>199</v>
@@ -1228,93 +1228,93 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.6181</v>
+        <v>2.8839</v>
       </c>
       <c r="C18" t="n">
-        <v>1.7177</v>
+        <v>1.8921</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5991</v>
+        <v>0.6639</v>
       </c>
       <c r="E18" t="n">
-        <v>2.6181</v>
+        <v>2.8839</v>
       </c>
       <c r="F18" t="n">
-        <v>2.6181</v>
+        <v>2.8839</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>2.6181</v>
+        <v>2.9728</v>
       </c>
       <c r="I18" t="n">
-        <v>2.6181</v>
+        <v>2.9728</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>182</v>
+        <v>162</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>2.6181</v>
+        <v>2.9728</v>
       </c>
       <c r="N18" t="n">
-        <v>182</v>
+        <v>162</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>JW</t>
+          <t>seized</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.0043</v>
+        <v>2.8411</v>
       </c>
       <c r="C19" t="n">
-        <v>1.315</v>
+        <v>1.864</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3546</v>
+        <v>0.6446</v>
       </c>
       <c r="E19" t="n">
-        <v>2.0043</v>
+        <v>2.8411</v>
       </c>
       <c r="F19" t="n">
-        <v>2.0043</v>
+        <v>3.64</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>-0.7989000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>2.0043</v>
+        <v>7.3389</v>
       </c>
       <c r="I19" t="n">
-        <v>2.0043</v>
+        <v>3.8159</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>-0.7989000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>157</v>
+        <v>96</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="M19" t="n">
-        <v>2.0043</v>
+        <v>3.017</v>
       </c>
       <c r="N19" t="n">
-        <v>157</v>
+        <v>201</v>
       </c>
     </row>
     <row r="20">
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.986</v>
+        <v>2.8124</v>
       </c>
       <c r="C20" t="n">
-        <v>1.303</v>
+        <v>1.8451</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3473</v>
+        <v>0.6316000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>1.986</v>
+        <v>2.8124</v>
       </c>
       <c r="F20" t="n">
-        <v>1.986</v>
+        <v>2.8124</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.986</v>
+        <v>2.8158</v>
       </c>
       <c r="I20" t="n">
-        <v>1.986</v>
+        <v>2.8158</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.986</v>
+        <v>2.8158</v>
       </c>
       <c r="N20" t="n">
         <v>199</v>
@@ -1366,369 +1366,369 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Hiko</t>
+          <t>cajunb</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.9392</v>
+        <v>2.78</v>
       </c>
       <c r="C21" t="n">
-        <v>1.2723</v>
+        <v>1.8239</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3287</v>
+        <v>0.617</v>
       </c>
       <c r="E21" t="n">
-        <v>1.9392</v>
+        <v>2.78</v>
       </c>
       <c r="F21" t="n">
-        <v>1.9676</v>
+        <v>3.077</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0284</v>
+        <v>-0.297</v>
       </c>
       <c r="H21" t="n">
-        <v>1.9676</v>
+        <v>5.3551</v>
       </c>
       <c r="I21" t="n">
-        <v>1.5948</v>
+        <v>2.7844</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.0284</v>
+        <v>-0.297</v>
       </c>
       <c r="K21" t="n">
-        <v>119</v>
+        <v>98</v>
       </c>
       <c r="L21" t="n">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="M21" t="n">
-        <v>1.5664</v>
+        <v>2.4874</v>
       </c>
       <c r="N21" t="n">
-        <v>188</v>
+        <v>149</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>Hiko</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.9153</v>
+        <v>2.6571</v>
       </c>
       <c r="C22" t="n">
-        <v>1.2566</v>
+        <v>1.7433</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3191</v>
+        <v>0.5615</v>
       </c>
       <c r="E22" t="n">
-        <v>1.9153</v>
+        <v>2.6571</v>
       </c>
       <c r="F22" t="n">
-        <v>1.9153</v>
+        <v>2.5374</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>0.1197</v>
       </c>
       <c r="H22" t="n">
-        <v>1.9153</v>
+        <v>3.454</v>
       </c>
       <c r="I22" t="n">
-        <v>1.9153</v>
+        <v>1.7959</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>0.1197</v>
       </c>
       <c r="K22" t="n">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="M22" t="n">
-        <v>1.9153</v>
+        <v>1.9156</v>
       </c>
       <c r="N22" t="n">
-        <v>94</v>
+        <v>188</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>GeT_RiGhT</t>
+          <t>JW</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.9141</v>
+        <v>2.5652</v>
       </c>
       <c r="C23" t="n">
-        <v>1.2558</v>
+        <v>1.683</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3187</v>
+        <v>0.52</v>
       </c>
       <c r="E23" t="n">
-        <v>1.9141</v>
+        <v>2.5652</v>
       </c>
       <c r="F23" t="n">
-        <v>1.9141</v>
+        <v>2.5652</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.9141</v>
+        <v>2.5652</v>
       </c>
       <c r="I23" t="n">
-        <v>1.9141</v>
+        <v>2.5652</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>182</v>
+        <v>157</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.9141</v>
+        <v>2.5652</v>
       </c>
       <c r="N23" t="n">
-        <v>182</v>
+        <v>157</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>jdm64</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.7876</v>
+        <v>2.2563</v>
       </c>
       <c r="C24" t="n">
-        <v>1.1728</v>
+        <v>1.4803</v>
       </c>
       <c r="D24" t="n">
-        <v>0.2683</v>
+        <v>0.3806</v>
       </c>
       <c r="E24" t="n">
-        <v>1.7876</v>
+        <v>2.2563</v>
       </c>
       <c r="F24" t="n">
-        <v>1.7876</v>
+        <v>2.5281</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>-0.2718</v>
       </c>
       <c r="H24" t="n">
-        <v>1.7876</v>
+        <v>3.4213</v>
       </c>
       <c r="I24" t="n">
-        <v>1.7876</v>
+        <v>1.7789</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>-0.2718</v>
       </c>
       <c r="K24" t="n">
-        <v>182</v>
+        <v>98</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="M24" t="n">
-        <v>1.7876</v>
+        <v>1.5071</v>
       </c>
       <c r="N24" t="n">
-        <v>182</v>
+        <v>149</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.6366</v>
+        <v>2.1981</v>
       </c>
       <c r="C25" t="n">
-        <v>1.0737</v>
+        <v>1.4421</v>
       </c>
       <c r="D25" t="n">
-        <v>0.2081</v>
+        <v>0.3543</v>
       </c>
       <c r="E25" t="n">
-        <v>1.6366</v>
+        <v>2.1981</v>
       </c>
       <c r="F25" t="n">
-        <v>1.6366</v>
+        <v>2.1981</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1.6366</v>
+        <v>2.1981</v>
       </c>
       <c r="I25" t="n">
-        <v>1.6366</v>
+        <v>2.1981</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>157</v>
+        <v>94</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1.6366</v>
+        <v>2.1981</v>
       </c>
       <c r="N25" t="n">
-        <v>157</v>
+        <v>94</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>hazed</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.5981</v>
+        <v>2.0548</v>
       </c>
       <c r="C26" t="n">
-        <v>1.0485</v>
+        <v>1.3481</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1928</v>
+        <v>0.2896</v>
       </c>
       <c r="E26" t="n">
-        <v>1.5981</v>
+        <v>2.0548</v>
       </c>
       <c r="F26" t="n">
-        <v>1.5981</v>
+        <v>2.0548</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1.5981</v>
+        <v>2.0548</v>
       </c>
       <c r="I26" t="n">
-        <v>1.5981</v>
+        <v>2.0548</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>182</v>
+        <v>157</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1.5981</v>
+        <v>2.0548</v>
       </c>
       <c r="N26" t="n">
-        <v>182</v>
+        <v>157</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>hazed</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.5807</v>
+        <v>1.8918</v>
       </c>
       <c r="C27" t="n">
-        <v>1.0371</v>
+        <v>1.2412</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1858</v>
+        <v>0.216</v>
       </c>
       <c r="E27" t="n">
-        <v>1.5807</v>
+        <v>1.8918</v>
       </c>
       <c r="F27" t="n">
-        <v>1.9242</v>
+        <v>1.8918</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.3435</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1.9242</v>
+        <v>1.8918</v>
       </c>
       <c r="I27" t="n">
-        <v>1.5596</v>
+        <v>1.8918</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.3435</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>98</v>
+        <v>182</v>
       </c>
       <c r="L27" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1.2161</v>
+        <v>1.8918</v>
       </c>
       <c r="N27" t="n">
-        <v>149</v>
+        <v>182</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>f0rest</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.5698</v>
+        <v>1.7641</v>
       </c>
       <c r="C28" t="n">
-        <v>1.0299</v>
+        <v>1.1574</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1815</v>
+        <v>0.1584</v>
       </c>
       <c r="E28" t="n">
-        <v>1.5698</v>
+        <v>1.7641</v>
       </c>
       <c r="F28" t="n">
-        <v>1.5698</v>
+        <v>2.2368</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>-0.4727</v>
       </c>
       <c r="H28" t="n">
-        <v>1.5698</v>
+        <v>2.3946</v>
       </c>
       <c r="I28" t="n">
-        <v>1.5698</v>
+        <v>1.2451</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>-0.4727</v>
       </c>
       <c r="K28" t="n">
-        <v>182</v>
+        <v>119</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="M28" t="n">
-        <v>1.5698</v>
+        <v>0.7724000000000001</v>
       </c>
       <c r="N28" t="n">
-        <v>182</v>
+        <v>188</v>
       </c>
     </row>
     <row r="29">
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.4531</v>
+        <v>1.7419</v>
       </c>
       <c r="C29" t="n">
-        <v>0.9533</v>
+        <v>1.1428</v>
       </c>
       <c r="D29" t="n">
-        <v>0.135</v>
+        <v>0.1484</v>
       </c>
       <c r="E29" t="n">
-        <v>1.4531</v>
+        <v>1.7419</v>
       </c>
       <c r="F29" t="n">
-        <v>1.4531</v>
+        <v>1.7419</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1.4531</v>
+        <v>1.7419</v>
       </c>
       <c r="I29" t="n">
-        <v>1.4531</v>
+        <v>1.7419</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1.4531</v>
+        <v>1.7419</v>
       </c>
       <c r="N29" t="n">
         <v>157</v>
@@ -1780,47 +1780,47 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>f0rest</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.1278</v>
+        <v>1.6858</v>
       </c>
       <c r="C30" t="n">
-        <v>0.7399</v>
+        <v>1.106</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0054</v>
+        <v>0.123</v>
       </c>
       <c r="E30" t="n">
-        <v>1.1278</v>
+        <v>1.6858</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.7569</v>
+        <v>1.6858</v>
       </c>
       <c r="G30" t="n">
-        <v>1.8847</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.7569</v>
+        <v>1.6858</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.6135</v>
+        <v>1.6858</v>
       </c>
       <c r="J30" t="n">
-        <v>1.8847</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>139</v>
+        <v>182</v>
       </c>
       <c r="L30" t="n">
-        <v>123</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>1.2712</v>
+        <v>1.6858</v>
       </c>
       <c r="N30" t="n">
-        <v>262</v>
+        <v>182</v>
       </c>
     </row>
     <row r="31">
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.0996</v>
+        <v>1.5651</v>
       </c>
       <c r="C31" t="n">
-        <v>0.7214</v>
+        <v>1.0268</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.0058</v>
+        <v>0.06859999999999999</v>
       </c>
       <c r="E31" t="n">
-        <v>1.0996</v>
+        <v>1.5651</v>
       </c>
       <c r="F31" t="n">
-        <v>1.0996</v>
+        <v>1.5651</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1.0996</v>
+        <v>1.5651</v>
       </c>
       <c r="I31" t="n">
-        <v>1.0996</v>
+        <v>1.5651</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>1.0996</v>
+        <v>1.5651</v>
       </c>
       <c r="N31" t="n">
         <v>157</v>
@@ -1872,47 +1872,47 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>aizy</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.0227</v>
+        <v>1.5153</v>
       </c>
       <c r="C32" t="n">
-        <v>0.671</v>
+        <v>0.9942</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.0365</v>
+        <v>0.0461</v>
       </c>
       <c r="E32" t="n">
-        <v>1.0227</v>
+        <v>1.5153</v>
       </c>
       <c r="F32" t="n">
-        <v>1.0227</v>
+        <v>1.469</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>0.0463</v>
       </c>
       <c r="H32" t="n">
-        <v>1.0227</v>
+        <v>1.469</v>
       </c>
       <c r="I32" t="n">
-        <v>1.0227</v>
+        <v>0.7638</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>0.0463</v>
       </c>
       <c r="K32" t="n">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="M32" t="n">
-        <v>1.0227</v>
+        <v>0.8101</v>
       </c>
       <c r="N32" t="n">
-        <v>94</v>
+        <v>188</v>
       </c>
     </row>
     <row r="33">
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.8532999999999999</v>
+        <v>1.4181</v>
       </c>
       <c r="C33" t="n">
-        <v>0.5598</v>
+        <v>0.9304</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.104</v>
+        <v>0.0022</v>
       </c>
       <c r="E33" t="n">
-        <v>0.8532999999999999</v>
+        <v>1.4181</v>
       </c>
       <c r="F33" t="n">
-        <v>0.8532999999999999</v>
+        <v>1.4181</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.8532999999999999</v>
+        <v>1.4181</v>
       </c>
       <c r="I33" t="n">
-        <v>0.8532999999999999</v>
+        <v>1.4181</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0.8532999999999999</v>
+        <v>1.4181</v>
       </c>
       <c r="N33" t="n">
         <v>199</v>
@@ -1964,185 +1964,185 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Shara</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.707</v>
+        <v>1.1098</v>
       </c>
       <c r="C34" t="n">
-        <v>0.4638</v>
+        <v>0.7281</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.1622</v>
+        <v>-0.137</v>
       </c>
       <c r="E34" t="n">
-        <v>0.707</v>
+        <v>1.1098</v>
       </c>
       <c r="F34" t="n">
-        <v>0.707</v>
+        <v>-0.486</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>1.5958</v>
       </c>
       <c r="H34" t="n">
-        <v>0.707</v>
+        <v>-0.486</v>
       </c>
       <c r="I34" t="n">
-        <v>0.707</v>
+        <v>-0.2527</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>1.5958</v>
       </c>
       <c r="K34" t="n">
-        <v>95</v>
+        <v>139</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="M34" t="n">
-        <v>0.707</v>
+        <v>1.3431</v>
       </c>
       <c r="N34" t="n">
-        <v>95</v>
+        <v>262</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>bondik</t>
+          <t>aizy</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.6839</v>
+        <v>0.9928</v>
       </c>
       <c r="C35" t="n">
-        <v>0.4487</v>
+        <v>0.6514</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.1714</v>
+        <v>-0.1898</v>
       </c>
       <c r="E35" t="n">
-        <v>0.6839</v>
+        <v>0.9928</v>
       </c>
       <c r="F35" t="n">
-        <v>0.6839</v>
+        <v>0.9928</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0.6839</v>
+        <v>0.9928</v>
       </c>
       <c r="I35" t="n">
-        <v>0.6839</v>
+        <v>0.9928</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0.6839</v>
+        <v>0.9928</v>
       </c>
       <c r="N35" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>bondik</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.6788999999999999</v>
+        <v>0.9674</v>
       </c>
       <c r="C36" t="n">
-        <v>0.4454</v>
+        <v>0.6347</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.1734</v>
+        <v>-0.2013</v>
       </c>
       <c r="E36" t="n">
-        <v>0.6788999999999999</v>
+        <v>0.9674</v>
       </c>
       <c r="F36" t="n">
-        <v>1.4228</v>
+        <v>0.9674</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.7439</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>1.4228</v>
+        <v>0.9674</v>
       </c>
       <c r="I36" t="n">
-        <v>1.1532</v>
+        <v>0.9674</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.7439</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="L36" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0.4093</v>
+        <v>0.9674</v>
       </c>
       <c r="N36" t="n">
-        <v>188</v>
+        <v>95</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>fox</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.5286</v>
+        <v>0.9372</v>
       </c>
       <c r="C37" t="n">
-        <v>0.3468</v>
+        <v>0.6149</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.2333</v>
+        <v>-0.2149</v>
       </c>
       <c r="E37" t="n">
-        <v>0.5286</v>
+        <v>0.9372</v>
       </c>
       <c r="F37" t="n">
-        <v>0.5286</v>
+        <v>2.3035</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>-1.3663</v>
       </c>
       <c r="H37" t="n">
-        <v>0.5286</v>
+        <v>2.6297</v>
       </c>
       <c r="I37" t="n">
-        <v>0.5286</v>
+        <v>1.3673</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>-1.3663</v>
       </c>
       <c r="K37" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="M37" t="n">
-        <v>0.5286</v>
+        <v>0.0009999999999998899</v>
       </c>
       <c r="N37" t="n">
-        <v>94</v>
+        <v>201</v>
       </c>
     </row>
     <row r="38">
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.5259</v>
+        <v>0.8657</v>
       </c>
       <c r="C38" t="n">
-        <v>0.345</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.2344</v>
+        <v>-0.2472</v>
       </c>
       <c r="E38" t="n">
-        <v>0.5259</v>
+        <v>0.8657</v>
       </c>
       <c r="F38" t="n">
-        <v>0.5259</v>
+        <v>0.8657</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.5259</v>
+        <v>0.8657</v>
       </c>
       <c r="I38" t="n">
-        <v>0.5259</v>
+        <v>0.8657</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.5259</v>
+        <v>0.8657</v>
       </c>
       <c r="N38" t="n">
         <v>137</v>
@@ -2194,231 +2194,231 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>pashaBiceps</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5173</v>
+        <v>0.846</v>
       </c>
       <c r="C39" t="n">
-        <v>0.3394</v>
+        <v>0.555</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.2378</v>
+        <v>-0.2561</v>
       </c>
       <c r="E39" t="n">
-        <v>0.5173</v>
+        <v>0.846</v>
       </c>
       <c r="F39" t="n">
-        <v>0.6664</v>
+        <v>0.846</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.1491</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.6664</v>
+        <v>0.846</v>
       </c>
       <c r="I39" t="n">
-        <v>0.5401</v>
+        <v>0.846</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.1491</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>119</v>
+        <v>199</v>
       </c>
       <c r="L39" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.391</v>
+        <v>0.846</v>
       </c>
       <c r="N39" t="n">
-        <v>188</v>
+        <v>199</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>shox</t>
+          <t>Shara</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.4424</v>
+        <v>0.8387</v>
       </c>
       <c r="C40" t="n">
-        <v>0.2902</v>
+        <v>0.5503</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.2677</v>
+        <v>-0.2594</v>
       </c>
       <c r="E40" t="n">
-        <v>0.4424</v>
+        <v>0.8387</v>
       </c>
       <c r="F40" t="n">
-        <v>0.4424</v>
+        <v>0.8387</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.4424</v>
+        <v>0.8387</v>
       </c>
       <c r="I40" t="n">
-        <v>0.4424</v>
+        <v>0.8387</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0.4424</v>
+        <v>0.8387</v>
       </c>
       <c r="N40" t="n">
-        <v>109</v>
+        <v>95</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>RpK</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.4139</v>
+        <v>0.8289</v>
       </c>
       <c r="C41" t="n">
-        <v>0.2715</v>
+        <v>0.5438</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.279</v>
+        <v>-0.2638</v>
       </c>
       <c r="E41" t="n">
-        <v>0.4139</v>
+        <v>0.8289</v>
       </c>
       <c r="F41" t="n">
-        <v>0.4139</v>
+        <v>0.8289</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.4139</v>
+        <v>0.8289</v>
       </c>
       <c r="I41" t="n">
-        <v>0.4139</v>
+        <v>0.8289</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>53</v>
+        <v>109</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.4139</v>
+        <v>0.8289</v>
       </c>
       <c r="N41" t="n">
-        <v>53</v>
+        <v>109</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>RpK</t>
+          <t>fox</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.4136</v>
+        <v>0.7614</v>
       </c>
       <c r="C42" t="n">
-        <v>0.2714</v>
+        <v>0.4995</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.2791</v>
+        <v>-0.2943</v>
       </c>
       <c r="E42" t="n">
-        <v>0.4136</v>
+        <v>0.7614</v>
       </c>
       <c r="F42" t="n">
-        <v>0.4136</v>
+        <v>0.7614</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.4136</v>
+        <v>0.7614</v>
       </c>
       <c r="I42" t="n">
-        <v>0.4136</v>
+        <v>0.7614</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.4136</v>
+        <v>0.7614</v>
       </c>
       <c r="N42" t="n">
-        <v>109</v>
+        <v>94</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AdreN</t>
+          <t>shox</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.3511</v>
+        <v>0.7541</v>
       </c>
       <c r="C43" t="n">
-        <v>0.2303</v>
+        <v>0.4947</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.304</v>
+        <v>-0.2976</v>
       </c>
       <c r="E43" t="n">
-        <v>0.3511</v>
+        <v>0.7541</v>
       </c>
       <c r="F43" t="n">
-        <v>0.3511</v>
+        <v>0.7541</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.3511</v>
+        <v>0.7541</v>
       </c>
       <c r="I43" t="n">
-        <v>0.3511</v>
+        <v>0.7541</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>137</v>
+        <v>109</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.3511</v>
+        <v>0.7541</v>
       </c>
       <c r="N43" t="n">
-        <v>137</v>
+        <v>109</v>
       </c>
     </row>
     <row r="44">
@@ -2428,28 +2428,28 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.325</v>
+        <v>0.5589</v>
       </c>
       <c r="C44" t="n">
-        <v>0.2132</v>
+        <v>0.3667</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.3144</v>
+        <v>-0.3857</v>
       </c>
       <c r="E44" t="n">
-        <v>0.325</v>
+        <v>0.5589</v>
       </c>
       <c r="F44" t="n">
-        <v>0.325</v>
+        <v>0.5589</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.325</v>
+        <v>0.5589</v>
       </c>
       <c r="I44" t="n">
-        <v>0.325</v>
+        <v>0.5589</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -2461,7 +2461,7 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.325</v>
+        <v>0.5589</v>
       </c>
       <c r="N44" t="n">
         <v>109</v>
@@ -2470,369 +2470,369 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>chrisJ</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.3115</v>
+        <v>0.5247000000000001</v>
       </c>
       <c r="C45" t="n">
-        <v>0.2044</v>
+        <v>0.3442</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.3198</v>
+        <v>-0.4011</v>
       </c>
       <c r="E45" t="n">
-        <v>0.3115</v>
+        <v>0.5247000000000001</v>
       </c>
       <c r="F45" t="n">
-        <v>0.3115</v>
+        <v>0.5247000000000001</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.3115</v>
+        <v>0.5247000000000001</v>
       </c>
       <c r="I45" t="n">
-        <v>0.3115</v>
+        <v>0.5247000000000001</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>53</v>
+        <v>162</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0.3115</v>
+        <v>0.5247000000000001</v>
       </c>
       <c r="N45" t="n">
-        <v>53</v>
+        <v>162</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Xizt</t>
+          <t>markeloff</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.2931</v>
+        <v>0.511</v>
       </c>
       <c r="C46" t="n">
-        <v>0.1923</v>
+        <v>0.3353</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.3271</v>
+        <v>-0.4073</v>
       </c>
       <c r="E46" t="n">
-        <v>0.2931</v>
+        <v>0.511</v>
       </c>
       <c r="F46" t="n">
-        <v>0.2931</v>
+        <v>0.511</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.2931</v>
+        <v>0.511</v>
       </c>
       <c r="I46" t="n">
-        <v>0.2931</v>
+        <v>0.511</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>182</v>
+        <v>95</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0.2931</v>
+        <v>0.511</v>
       </c>
       <c r="N46" t="n">
-        <v>182</v>
+        <v>95</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>markeloff</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.2578</v>
+        <v>0.5001</v>
       </c>
       <c r="C47" t="n">
-        <v>0.1691</v>
+        <v>0.3281</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.3412</v>
+        <v>-0.4122</v>
       </c>
       <c r="E47" t="n">
-        <v>0.2578</v>
+        <v>0.5001</v>
       </c>
       <c r="F47" t="n">
-        <v>0.2578</v>
+        <v>0.5001</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.2578</v>
+        <v>0.5001</v>
       </c>
       <c r="I47" t="n">
-        <v>0.2578</v>
+        <v>0.5001</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>95</v>
+        <v>53</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0.2578</v>
+        <v>0.5001</v>
       </c>
       <c r="N47" t="n">
-        <v>95</v>
+        <v>53</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Spiidi</t>
+          <t>Xizt</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.2222</v>
+        <v>0.4903</v>
       </c>
       <c r="C48" t="n">
-        <v>0.1458</v>
+        <v>0.3217</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.3554</v>
+        <v>-0.4167</v>
       </c>
       <c r="E48" t="n">
-        <v>0.2222</v>
+        <v>0.4903</v>
       </c>
       <c r="F48" t="n">
-        <v>0.2222</v>
+        <v>0.4903</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.2222</v>
+        <v>0.4903</v>
       </c>
       <c r="I48" t="n">
-        <v>0.2222</v>
+        <v>0.4903</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0.2222</v>
+        <v>0.4903</v>
       </c>
       <c r="N48" t="n">
-        <v>162</v>
+        <v>182</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Dosia</t>
+          <t>Spiidi</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.2221</v>
+        <v>0.4836</v>
       </c>
       <c r="C49" t="n">
-        <v>0.1457</v>
+        <v>0.3173</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.3554</v>
+        <v>-0.4197</v>
       </c>
       <c r="E49" t="n">
-        <v>0.2221</v>
+        <v>0.4836</v>
       </c>
       <c r="F49" t="n">
-        <v>0.2221</v>
+        <v>0.4836</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.2221</v>
+        <v>0.4836</v>
       </c>
       <c r="I49" t="n">
-        <v>0.2221</v>
+        <v>0.4836</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>137</v>
+        <v>162</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0.2221</v>
+        <v>0.4836</v>
       </c>
       <c r="N49" t="n">
-        <v>137</v>
+        <v>162</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>pashaBiceps</t>
+          <t>AdreN</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.2033</v>
+        <v>0.4651</v>
       </c>
       <c r="C50" t="n">
-        <v>0.1334</v>
+        <v>0.3051</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.3629</v>
+        <v>-0.428</v>
       </c>
       <c r="E50" t="n">
-        <v>0.2033</v>
+        <v>0.4651</v>
       </c>
       <c r="F50" t="n">
-        <v>0.2033</v>
+        <v>0.4651</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0.2033</v>
+        <v>0.4651</v>
       </c>
       <c r="I50" t="n">
-        <v>0.2033</v>
+        <v>0.4651</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>199</v>
+        <v>137</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>0.2033</v>
+        <v>0.4651</v>
       </c>
       <c r="N50" t="n">
-        <v>199</v>
+        <v>137</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>DAVEY</t>
+          <t>Happy</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.1855</v>
+        <v>0.3827</v>
       </c>
       <c r="C51" t="n">
-        <v>0.1217</v>
+        <v>0.2511</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.37</v>
+        <v>-0.4652</v>
       </c>
       <c r="E51" t="n">
-        <v>0.1855</v>
+        <v>0.3827</v>
       </c>
       <c r="F51" t="n">
-        <v>0.1855</v>
+        <v>0.3827</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>0.1855</v>
+        <v>0.3827</v>
       </c>
       <c r="I51" t="n">
-        <v>0.1855</v>
+        <v>0.3827</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>0.1855</v>
+        <v>0.3827</v>
       </c>
       <c r="N51" t="n">
-        <v>40</v>
+        <v>53</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>chrisJ</t>
+          <t>DAVEY</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.132</v>
+        <v>0.3525</v>
       </c>
       <c r="C52" t="n">
-        <v>0.0866</v>
+        <v>0.2313</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.3913</v>
+        <v>-0.4789</v>
       </c>
       <c r="E52" t="n">
-        <v>0.132</v>
+        <v>0.3525</v>
       </c>
       <c r="F52" t="n">
-        <v>0.132</v>
+        <v>0.3525</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>0.132</v>
+        <v>0.3525</v>
       </c>
       <c r="I52" t="n">
-        <v>0.132</v>
+        <v>0.3525</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>162</v>
+        <v>40</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>0.132</v>
+        <v>0.3525</v>
       </c>
       <c r="N52" t="n">
-        <v>162</v>
+        <v>40</v>
       </c>
     </row>
     <row r="53">
@@ -2842,28 +2842,28 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.0658</v>
+        <v>0.3323</v>
       </c>
       <c r="C53" t="n">
-        <v>0.0432</v>
+        <v>0.218</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.4177</v>
+        <v>-0.488</v>
       </c>
       <c r="E53" t="n">
-        <v>0.0658</v>
+        <v>0.3323</v>
       </c>
       <c r="F53" t="n">
-        <v>0.0658</v>
+        <v>0.3323</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>0.0658</v>
+        <v>0.3323</v>
       </c>
       <c r="I53" t="n">
-        <v>0.0658</v>
+        <v>0.3323</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -2875,7 +2875,7 @@
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>0.0658</v>
+        <v>0.3323</v>
       </c>
       <c r="N53" t="n">
         <v>109</v>
@@ -2884,277 +2884,277 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>WorldEdit</t>
+          <t>Dosia</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.0126</v>
+        <v>0.3271</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.0083</v>
+        <v>0.2146</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.4489</v>
+        <v>-0.4903</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.0126</v>
+        <v>0.3271</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.0126</v>
+        <v>0.3271</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.0126</v>
+        <v>0.3271</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.0126</v>
+        <v>0.3271</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>95</v>
+        <v>137</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-0.0126</v>
+        <v>0.3271</v>
       </c>
       <c r="N54" t="n">
-        <v>95</v>
+        <v>137</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>NBK-</t>
+          <t>reltuC</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.0847</v>
+        <v>0.2728</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.0556</v>
+        <v>0.179</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.4777</v>
+        <v>-0.5149</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.0847</v>
+        <v>0.2728</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.0847</v>
+        <v>0.2728</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.0847</v>
+        <v>0.2728</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.0847</v>
+        <v>0.2728</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>53</v>
+        <v>182</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>-0.0847</v>
+        <v>0.2728</v>
       </c>
       <c r="N55" t="n">
-        <v>53</v>
+        <v>182</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>SmithZz</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.14</v>
+        <v>0.2695</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.0919</v>
+        <v>0.1768</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.4997</v>
+        <v>-0.5163</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.14</v>
+        <v>0.2695</v>
       </c>
       <c r="F56" t="n">
-        <v>1.5423</v>
+        <v>0.2695</v>
       </c>
       <c r="G56" t="n">
-        <v>-1.6823</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>1.5423</v>
+        <v>0.2695</v>
       </c>
       <c r="I56" t="n">
-        <v>1.2501</v>
+        <v>0.2695</v>
       </c>
       <c r="J56" t="n">
-        <v>-1.6823</v>
+        <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="L56" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>-0.4321999999999999</v>
+        <v>0.2695</v>
       </c>
       <c r="N56" t="n">
-        <v>201</v>
+        <v>109</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Skadoodle</t>
+          <t>NBK-</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.1461</v>
+        <v>0.1796</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.0959</v>
+        <v>0.1178</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.5021</v>
+        <v>-0.5569</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.1461</v>
+        <v>0.1796</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.1461</v>
+        <v>0.1796</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.1461</v>
+        <v>0.1796</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.1461</v>
+        <v>0.1796</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>-0.1461</v>
+        <v>0.1796</v>
       </c>
       <c r="N57" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>reltuC</t>
+          <t>WorldEdit</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.1753</v>
+        <v>0.1072</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.115</v>
+        <v>0.0703</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.5137</v>
+        <v>-0.5896</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.1753</v>
+        <v>0.1072</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.1753</v>
+        <v>0.1072</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.1753</v>
+        <v>0.1072</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.1753</v>
+        <v>0.1072</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>182</v>
+        <v>95</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>-0.1753</v>
+        <v>0.1072</v>
       </c>
       <c r="N58" t="n">
-        <v>182</v>
+        <v>95</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SmithZz</t>
+          <t>denis</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.1907</v>
+        <v>0.0075</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.1251</v>
+        <v>0.0049</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.5199</v>
+        <v>-0.6346000000000001</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.1907</v>
+        <v>0.0075</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.1907</v>
+        <v>0.0075</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.1907</v>
+        <v>0.0075</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.1907</v>
+        <v>0.0075</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>109</v>
+        <v>162</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>-0.1907</v>
+        <v>0.0075</v>
       </c>
       <c r="N59" t="n">
-        <v>109</v>
+        <v>162</v>
       </c>
     </row>
     <row r="60">
@@ -3164,28 +3164,28 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.2551</v>
+        <v>-0.0825</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.1674</v>
+        <v>-0.0541</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.5455</v>
+        <v>-0.6753</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.2551</v>
+        <v>-0.0825</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.2551</v>
+        <v>-0.0825</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.2551</v>
+        <v>-0.0825</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.2551</v>
+        <v>-0.0825</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -3197,7 +3197,7 @@
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>-0.2551</v>
+        <v>-0.0825</v>
       </c>
       <c r="N60" t="n">
         <v>137</v>
@@ -3206,507 +3206,507 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>DEVIL</t>
+          <t>jkaem</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.2942</v>
+        <v>-0.1524</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.193</v>
+        <v>-0.1</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.5611</v>
+        <v>-0.7068</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.2942</v>
+        <v>-0.1524</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.2942</v>
+        <v>-0.1524</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.2942</v>
+        <v>-0.1524</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.2942</v>
+        <v>-0.1524</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>53</v>
+        <v>94</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>-0.2942</v>
+        <v>-0.1524</v>
       </c>
       <c r="N61" t="n">
-        <v>53</v>
+        <v>94</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>denis</t>
+          <t>Skadoodle</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.3573</v>
+        <v>-0.155</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.2344</v>
+        <v>-0.1017</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.5863</v>
+        <v>-0.708</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.3573</v>
+        <v>-0.155</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.3573</v>
+        <v>-0.155</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.3573</v>
+        <v>-0.155</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.3573</v>
+        <v>-0.155</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>162</v>
+        <v>44</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.3573</v>
+        <v>-0.155</v>
       </c>
       <c r="N62" t="n">
-        <v>162</v>
+        <v>44</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>arya</t>
+          <t>DEVIL</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.4357</v>
+        <v>-0.1937</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.2859</v>
+        <v>-0.1271</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.6175</v>
+        <v>-0.7255</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.4357</v>
+        <v>-0.1937</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.4357</v>
+        <v>-0.1937</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.4357</v>
+        <v>-0.1937</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.4357</v>
+        <v>-0.1937</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.4357</v>
+        <v>-0.1937</v>
       </c>
       <c r="N63" t="n">
-        <v>40</v>
+        <v>53</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>shroud</t>
+          <t>arya</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.4671</v>
+        <v>-0.2246</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.3065</v>
+        <v>-0.1474</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.63</v>
+        <v>-0.7393999999999999</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.4671</v>
+        <v>-0.2246</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.4671</v>
+        <v>-0.2246</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.4671</v>
+        <v>-0.2246</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.4671</v>
+        <v>-0.2246</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>-0.4671</v>
+        <v>-0.2246</v>
       </c>
       <c r="N64" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>B1ad3</t>
+          <t>Maikelele</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.5107</v>
+        <v>-0.2324</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.3351</v>
+        <v>-0.1525</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.6474</v>
+        <v>-0.7429</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.5107</v>
+        <v>-0.2324</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.5107</v>
+        <v>-0.2324</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.5107</v>
+        <v>-0.2324</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.5107</v>
+        <v>-0.2324</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.5107</v>
+        <v>-0.2324</v>
       </c>
       <c r="N65" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Maikelele</t>
+          <t>B1ad3</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.7125</v>
+        <v>-0.2914</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.4675</v>
+        <v>-0.1912</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.7278</v>
+        <v>-0.7696</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.7125</v>
+        <v>-0.2914</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.7125</v>
+        <v>-0.2914</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.7125</v>
+        <v>-0.2914</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.7125</v>
+        <v>-0.2914</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>-0.7125</v>
+        <v>-0.2914</v>
       </c>
       <c r="N66" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>jkaem</t>
+          <t>shroud</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.7631</v>
+        <v>-0.3877</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.5007</v>
+        <v>-0.2544</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.7479</v>
+        <v>-0.8129999999999999</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.7631</v>
+        <v>-0.3877</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.7631</v>
+        <v>-0.3877</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.7631</v>
+        <v>-0.3877</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.7631</v>
+        <v>-0.3877</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>94</v>
+        <v>44</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>-0.7631</v>
+        <v>-0.3877</v>
       </c>
       <c r="N67" t="n">
-        <v>94</v>
+        <v>44</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>mou</t>
+          <t>friberg</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.8448</v>
+        <v>-0.4326</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.5543</v>
+        <v>-0.2838</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.7805</v>
+        <v>-0.8333</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.8448</v>
+        <v>-0.4326</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.8448</v>
+        <v>-0.4326</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.8448</v>
+        <v>-0.4326</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.8448</v>
+        <v>-0.4326</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>137</v>
+        <v>182</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>-0.8448</v>
+        <v>-0.4326</v>
       </c>
       <c r="N68" t="n">
-        <v>137</v>
+        <v>182</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>kennyS</t>
+          <t>Zeus</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-0.8482</v>
+        <v>-0.528</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.5565</v>
+        <v>-0.3464</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.7818000000000001</v>
+        <v>-0.8764</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.8482</v>
+        <v>-0.528</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.8482</v>
+        <v>-0.4658</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>-0.0622</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.8482</v>
+        <v>-0.4658</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.8482</v>
+        <v>-0.2422</v>
       </c>
       <c r="J69" t="n">
-        <v>0</v>
+        <v>-0.0622</v>
       </c>
       <c r="K69" t="n">
-        <v>53</v>
+        <v>96</v>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="M69" t="n">
-        <v>-0.8482</v>
+        <v>-0.3044</v>
       </c>
       <c r="N69" t="n">
-        <v>53</v>
+        <v>201</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>friberg</t>
+          <t>mou</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-0.8774</v>
+        <v>-0.5479000000000001</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.5756</v>
+        <v>-0.3595</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.7935</v>
+        <v>-0.8854</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.8774</v>
+        <v>-0.5479000000000001</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.8774</v>
+        <v>-0.5479000000000001</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>-0.8774</v>
+        <v>-0.5479000000000001</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.8774</v>
+        <v>-0.5479000000000001</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>182</v>
+        <v>137</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>-0.8774</v>
+        <v>-0.5479000000000001</v>
       </c>
       <c r="N70" t="n">
-        <v>182</v>
+        <v>137</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>n0thing</t>
+          <t>kennyS</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-0.913</v>
+        <v>-0.584</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.599</v>
+        <v>-0.3831</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.8076</v>
+        <v>-0.9016999999999999</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.913</v>
+        <v>-0.584</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.913</v>
+        <v>-0.584</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>-0.913</v>
+        <v>-0.584</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.913</v>
+        <v>-0.584</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>-0.913</v>
+        <v>-0.584</v>
       </c>
       <c r="N71" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
     </row>
     <row r="72">
@@ -3716,28 +3716,28 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-0.914</v>
+        <v>-0.6286</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.5997</v>
+        <v>-0.4124</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.8080000000000001</v>
+        <v>-0.9218</v>
       </c>
       <c r="E72" t="n">
-        <v>-0.914</v>
+        <v>-0.6286</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.914</v>
+        <v>-0.6286</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>-0.914</v>
+        <v>-0.6286</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.914</v>
+        <v>-0.6286</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -3749,7 +3749,7 @@
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>-0.914</v>
+        <v>-0.6286</v>
       </c>
       <c r="N72" t="n">
         <v>44</v>
@@ -3758,47 +3758,47 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Zeus</t>
+          <t>n0thing</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-0.9534</v>
+        <v>-0.6331</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.6254999999999999</v>
+        <v>-0.4154</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.8237</v>
+        <v>-0.9238</v>
       </c>
       <c r="E73" t="n">
-        <v>-0.9534</v>
+        <v>-0.6331</v>
       </c>
       <c r="F73" t="n">
-        <v>-0.72</v>
+        <v>-0.6331</v>
       </c>
       <c r="G73" t="n">
-        <v>-0.2334</v>
+        <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>-0.72</v>
+        <v>-0.6331</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.5836</v>
+        <v>-0.6331</v>
       </c>
       <c r="J73" t="n">
-        <v>-0.2334</v>
+        <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>96</v>
+        <v>44</v>
       </c>
       <c r="L73" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>-0.8169999999999999</v>
+        <v>-0.6331</v>
       </c>
       <c r="N73" t="n">
-        <v>201</v>
+        <v>44</v>
       </c>
     </row>
     <row r="74">
@@ -3808,28 +3808,28 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-1.1277</v>
+        <v>-0.7833</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.7399</v>
+        <v>-0.5139</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.8932</v>
+        <v>-0.9916</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.1277</v>
+        <v>-0.7833</v>
       </c>
       <c r="F74" t="n">
-        <v>-1.1277</v>
+        <v>-0.7833</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>-1.1277</v>
+        <v>-0.7833</v>
       </c>
       <c r="I74" t="n">
-        <v>-1.1277</v>
+        <v>-0.7833</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -3841,7 +3841,7 @@
         <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>-1.1277</v>
+        <v>-0.7833</v>
       </c>
       <c r="N74" t="n">
         <v>40</v>
@@ -3854,28 +3854,28 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-1.3215</v>
+        <v>-0.9145</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.867</v>
+        <v>-0.6</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.9704</v>
+        <v>-1.0509</v>
       </c>
       <c r="E75" t="n">
-        <v>-1.3215</v>
+        <v>-0.9145</v>
       </c>
       <c r="F75" t="n">
-        <v>-1.3215</v>
+        <v>-0.9145</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>-1.3215</v>
+        <v>-0.9145</v>
       </c>
       <c r="I75" t="n">
-        <v>-1.3215</v>
+        <v>-0.9145</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -3887,7 +3887,7 @@
         <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>-1.3215</v>
+        <v>-0.9145</v>
       </c>
       <c r="N75" t="n">
         <v>44</v>
@@ -3896,78 +3896,78 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>jasonR</t>
+          <t>THREAT</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-1.5016</v>
+        <v>-1.0201</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.9852</v>
+        <v>-0.6693</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.0421</v>
+        <v>-1.0985</v>
       </c>
       <c r="E76" t="n">
-        <v>-1.5016</v>
+        <v>-1.0201</v>
       </c>
       <c r="F76" t="n">
-        <v>-1.5016</v>
+        <v>-1.0201</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>-1.5016</v>
+        <v>-1.0201</v>
       </c>
       <c r="I76" t="n">
-        <v>-1.5016</v>
+        <v>-1.0201</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>40</v>
+        <v>182</v>
       </c>
       <c r="L76" t="n">
         <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>-1.5016</v>
+        <v>-1.0201</v>
       </c>
       <c r="N76" t="n">
-        <v>40</v>
+        <v>182</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>abE</t>
+          <t>jasonR</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-1.6694</v>
+        <v>-1.0261</v>
       </c>
       <c r="C77" t="n">
-        <v>-1.0953</v>
+        <v>-0.6732</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.109</v>
+        <v>-1.1012</v>
       </c>
       <c r="E77" t="n">
-        <v>-1.6694</v>
+        <v>-1.0261</v>
       </c>
       <c r="F77" t="n">
-        <v>-1.6694</v>
+        <v>-1.0261</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>-1.6694</v>
+        <v>-1.0261</v>
       </c>
       <c r="I77" t="n">
-        <v>-1.6694</v>
+        <v>-1.0261</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -3979,7 +3979,7 @@
         <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>-1.6694</v>
+        <v>-1.0261</v>
       </c>
       <c r="N77" t="n">
         <v>40</v>
@@ -3988,47 +3988,47 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>THREAT</t>
+          <t>abE</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-1.7002</v>
+        <v>-1.1499</v>
       </c>
       <c r="C78" t="n">
-        <v>-1.1155</v>
+        <v>-0.7544</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.1213</v>
+        <v>-1.1571</v>
       </c>
       <c r="E78" t="n">
-        <v>-1.7002</v>
+        <v>-1.1499</v>
       </c>
       <c r="F78" t="n">
-        <v>-1.7002</v>
+        <v>-1.1499</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>-1.7002</v>
+        <v>-1.1499</v>
       </c>
       <c r="I78" t="n">
-        <v>-1.7002</v>
+        <v>-1.1499</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>182</v>
+        <v>40</v>
       </c>
       <c r="L78" t="n">
         <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>-1.7002</v>
+        <v>-1.1499</v>
       </c>
       <c r="N78" t="n">
-        <v>182</v>
+        <v>40</v>
       </c>
     </row>
     <row r="79">
@@ -4038,28 +4038,28 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-1.9828</v>
+        <v>-1.3088</v>
       </c>
       <c r="C79" t="n">
-        <v>-1.3009</v>
+        <v>-0.8587</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.2339</v>
+        <v>-1.2289</v>
       </c>
       <c r="E79" t="n">
-        <v>-1.9828</v>
+        <v>-1.3088</v>
       </c>
       <c r="F79" t="n">
-        <v>-1.9828</v>
+        <v>-1.3088</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>-1.9828</v>
+        <v>-1.3088</v>
       </c>
       <c r="I79" t="n">
-        <v>-1.9828</v>
+        <v>-1.3088</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -4071,7 +4071,7 @@
         <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>-1.9828</v>
+        <v>-1.3088</v>
       </c>
       <c r="N79" t="n">
         <v>162</v>
@@ -4084,31 +4084,31 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-2.3385</v>
+        <v>-2.7139</v>
       </c>
       <c r="C80" t="n">
-        <v>-1.5342</v>
+        <v>-1.7805</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.3756</v>
+        <v>-1.8632</v>
       </c>
       <c r="E80" t="n">
-        <v>-2.3385</v>
+        <v>-2.7139</v>
       </c>
       <c r="F80" t="n">
-        <v>-1.7257</v>
+        <v>-2.2854</v>
       </c>
       <c r="G80" t="n">
-        <v>-0.6128</v>
+        <v>-0.4285</v>
       </c>
       <c r="H80" t="n">
-        <v>-1.7257</v>
+        <v>-2.2854</v>
       </c>
       <c r="I80" t="n">
-        <v>-1.3987</v>
+        <v>-1.1883</v>
       </c>
       <c r="J80" t="n">
-        <v>-0.6128</v>
+        <v>-0.4285</v>
       </c>
       <c r="K80" t="n">
         <v>98</v>
@@ -4117,7 +4117,7 @@
         <v>51</v>
       </c>
       <c r="M80" t="n">
-        <v>-2.0115</v>
+        <v>-1.6168</v>
       </c>
       <c r="N80" t="n">
         <v>149</v>
@@ -4130,28 +4130,28 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-4.0688</v>
+        <v>-3.3304</v>
       </c>
       <c r="C81" t="n">
-        <v>-2.6694</v>
+        <v>-2.185</v>
       </c>
       <c r="D81" t="n">
-        <v>-2.0649</v>
+        <v>-2.1415</v>
       </c>
       <c r="E81" t="n">
-        <v>-4.0688</v>
+        <v>-3.3304</v>
       </c>
       <c r="F81" t="n">
-        <v>-4.0688</v>
+        <v>-3.3304</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>-4.0688</v>
+        <v>-3.3304</v>
       </c>
       <c r="I81" t="n">
-        <v>-4.0688</v>
+        <v>-3.3304</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -4163,7 +4163,7 @@
         <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>-4.0688</v>
+        <v>-3.3304</v>
       </c>
       <c r="N81" t="n">
         <v>182</v>
@@ -4269,10 +4269,10 @@
         <v>1.16</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3265</v>
+        <v>0.3658</v>
       </c>
       <c r="J2" t="n">
-        <v>11.754</v>
+        <v>13.1688</v>
       </c>
     </row>
     <row r="3">
@@ -4309,10 +4309,10 @@
         <v>1.14</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2956</v>
+        <v>0.3274</v>
       </c>
       <c r="J3" t="n">
-        <v>10.6416</v>
+        <v>11.7864</v>
       </c>
     </row>
     <row r="4">
@@ -4349,10 +4349,10 @@
         <v>0.99</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0359</v>
+        <v>-0.0202</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.2924</v>
+        <v>-0.7272</v>
       </c>
     </row>
     <row r="5">
@@ -4389,10 +4389,10 @@
         <v>0.91</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2085</v>
+        <v>-0.1224</v>
       </c>
       <c r="J5" t="n">
-        <v>-7.506</v>
+        <v>-4.4064</v>
       </c>
     </row>
     <row r="6">
@@ -4429,10 +4429,10 @@
         <v>0.77</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4248</v>
+        <v>-0.2681</v>
       </c>
       <c r="J6" t="n">
-        <v>-15.2928</v>
+        <v>-9.6516</v>
       </c>
     </row>
     <row r="7">
@@ -4469,10 +4469,10 @@
         <v>1.4</v>
       </c>
       <c r="I7" t="n">
-        <v>1.0155</v>
+        <v>1.0052</v>
       </c>
       <c r="J7" t="n">
-        <v>36.558</v>
+        <v>36.1872</v>
       </c>
     </row>
     <row r="8">
@@ -4509,10 +4509,10 @@
         <v>1.36</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9286</v>
+        <v>0.929</v>
       </c>
       <c r="J8" t="n">
-        <v>33.4296</v>
+        <v>33.444</v>
       </c>
     </row>
     <row r="9">
@@ -4549,10 +4549,10 @@
         <v>1.16</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4059</v>
+        <v>0.4626</v>
       </c>
       <c r="J9" t="n">
-        <v>14.6124</v>
+        <v>16.6536</v>
       </c>
     </row>
     <row r="10">
@@ -4589,10 +4589,10 @@
         <v>1.05</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0835</v>
+        <v>0.1523</v>
       </c>
       <c r="J10" t="n">
-        <v>3.006</v>
+        <v>5.4828</v>
       </c>
     </row>
     <row r="11">
@@ -4629,10 +4629,10 @@
         <v>1.03</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0149</v>
+        <v>0.08450000000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5364</v>
+        <v>3.042</v>
       </c>
     </row>
     <row r="12">
@@ -4669,10 +4669,10 @@
         <v>0.97</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1193</v>
+        <v>0.1021</v>
       </c>
       <c r="J12" t="n">
-        <v>2.1474</v>
+        <v>1.8378</v>
       </c>
     </row>
     <row r="13">
@@ -4709,10 +4709,10 @@
         <v>0.67</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.3782</v>
+        <v>-0.3048</v>
       </c>
       <c r="J13" t="n">
-        <v>-6.8076</v>
+        <v>-5.4864</v>
       </c>
     </row>
     <row r="14">
@@ -4749,10 +4749,10 @@
         <v>0.53</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.626</v>
+        <v>-0.4338</v>
       </c>
       <c r="J14" t="n">
-        <v>-11.268</v>
+        <v>-7.8084</v>
       </c>
     </row>
     <row r="15">
@@ -4789,10 +4789,10 @@
         <v>0.4</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.8099</v>
+        <v>-0.5570000000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>-14.5782</v>
+        <v>-10.026</v>
       </c>
     </row>
     <row r="16">
@@ -4829,10 +4829,10 @@
         <v>0.35</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8748</v>
+        <v>-0.6052</v>
       </c>
       <c r="J16" t="n">
-        <v>-15.7464</v>
+        <v>-10.8936</v>
       </c>
     </row>
     <row r="17">
@@ -4869,10 +4869,10 @@
         <v>1.89</v>
       </c>
       <c r="I17" t="n">
-        <v>1.7725</v>
+        <v>1.5237</v>
       </c>
       <c r="J17" t="n">
-        <v>31.905</v>
+        <v>27.4266</v>
       </c>
     </row>
     <row r="18">
@@ -4909,10 +4909,10 @@
         <v>1.79</v>
       </c>
       <c r="I18" t="n">
-        <v>1.5965</v>
+        <v>1.413</v>
       </c>
       <c r="J18" t="n">
-        <v>28.737</v>
+        <v>25.434</v>
       </c>
     </row>
     <row r="19">
@@ -4949,10 +4949,10 @@
         <v>1.64</v>
       </c>
       <c r="I19" t="n">
-        <v>1.3113</v>
+        <v>1.2453</v>
       </c>
       <c r="J19" t="n">
-        <v>23.6034</v>
+        <v>22.4154</v>
       </c>
     </row>
     <row r="20">
@@ -4989,10 +4989,10 @@
         <v>1.38</v>
       </c>
       <c r="I20" t="n">
-        <v>0.7532</v>
+        <v>0.8956</v>
       </c>
       <c r="J20" t="n">
-        <v>13.5576</v>
+        <v>16.1208</v>
       </c>
     </row>
     <row r="21">
@@ -5029,10 +5029,10 @@
         <v>1.26</v>
       </c>
       <c r="I21" t="n">
-        <v>0.4982</v>
+        <v>0.6257</v>
       </c>
       <c r="J21" t="n">
-        <v>8.967599999999999</v>
+        <v>11.2626</v>
       </c>
     </row>
     <row r="22">
@@ -5069,10 +5069,10 @@
         <v>1.2</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4324</v>
+        <v>0.4277</v>
       </c>
       <c r="J22" t="n">
-        <v>14.7016</v>
+        <v>14.5418</v>
       </c>
     </row>
     <row r="23">
@@ -5109,10 +5109,10 @@
         <v>0.97</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.0156</v>
+        <v>-0.0353</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.5304</v>
+        <v>-1.2002</v>
       </c>
     </row>
     <row r="24">
@@ -5149,10 +5149,10 @@
         <v>0.8</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.3432</v>
+        <v>-0.2226</v>
       </c>
       <c r="J24" t="n">
-        <v>-11.6688</v>
+        <v>-7.5684</v>
       </c>
     </row>
     <row r="25">
@@ -5189,10 +5189,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.5042</v>
+        <v>-0.3292</v>
       </c>
       <c r="J25" t="n">
-        <v>-17.1428</v>
+        <v>-11.1928</v>
       </c>
     </row>
     <row r="26">
@@ -5229,10 +5229,10 @@
         <v>0.67</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.5314</v>
+        <v>-0.3482</v>
       </c>
       <c r="J26" t="n">
-        <v>-18.0676</v>
+        <v>-11.8388</v>
       </c>
     </row>
     <row r="27">
@@ -5269,10 +5269,10 @@
         <v>1.36</v>
       </c>
       <c r="I27" t="n">
-        <v>0.9446</v>
+        <v>0.6912</v>
       </c>
       <c r="J27" t="n">
-        <v>32.1164</v>
+        <v>23.5008</v>
       </c>
     </row>
     <row r="28">
@@ -5309,10 +5309,10 @@
         <v>1.26</v>
       </c>
       <c r="I28" t="n">
-        <v>0.7138</v>
+        <v>0.5547</v>
       </c>
       <c r="J28" t="n">
-        <v>24.2692</v>
+        <v>18.8598</v>
       </c>
     </row>
     <row r="29">
@@ -5349,10 +5349,10 @@
         <v>1.23</v>
       </c>
       <c r="I29" t="n">
-        <v>0.6387</v>
+        <v>0.5125999999999999</v>
       </c>
       <c r="J29" t="n">
-        <v>21.7158</v>
+        <v>17.4284</v>
       </c>
     </row>
     <row r="30">
@@ -5389,10 +5389,10 @@
         <v>1.17</v>
       </c>
       <c r="I30" t="n">
-        <v>0.4656</v>
+        <v>0.4273</v>
       </c>
       <c r="J30" t="n">
-        <v>15.8304</v>
+        <v>14.5282</v>
       </c>
     </row>
     <row r="31">
@@ -5429,10 +5429,10 @@
         <v>0.83</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.6496</v>
+        <v>-0.5893</v>
       </c>
       <c r="J31" t="n">
-        <v>-22.0864</v>
+        <v>-20.0362</v>
       </c>
     </row>
     <row r="32">
@@ -5469,10 +5469,10 @@
         <v>1.16</v>
       </c>
       <c r="I32" t="n">
-        <v>0.3301</v>
+        <v>0.3546</v>
       </c>
       <c r="J32" t="n">
-        <v>11.5535</v>
+        <v>12.411</v>
       </c>
     </row>
     <row r="33">
@@ -5509,10 +5509,10 @@
         <v>1.15</v>
       </c>
       <c r="I33" t="n">
-        <v>0.3148</v>
+        <v>0.3423</v>
       </c>
       <c r="J33" t="n">
-        <v>11.018</v>
+        <v>11.9805</v>
       </c>
     </row>
     <row r="34">
@@ -5549,10 +5549,10 @@
         <v>1.07</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1809</v>
+        <v>0.1873</v>
       </c>
       <c r="J34" t="n">
-        <v>6.3315</v>
+        <v>6.5555</v>
       </c>
     </row>
     <row r="35">
@@ -5589,10 +5589,10 @@
         <v>0.89</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.2397</v>
+        <v>-0.1435</v>
       </c>
       <c r="J35" t="n">
-        <v>-8.3895</v>
+        <v>-5.0225</v>
       </c>
     </row>
     <row r="36">
@@ -5629,10 +5629,10 @@
         <v>0.65</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.5815</v>
+        <v>-0.3814</v>
       </c>
       <c r="J36" t="n">
-        <v>-20.3525</v>
+        <v>-13.349</v>
       </c>
     </row>
     <row r="37">
@@ -5669,10 +5669,10 @@
         <v>1.48</v>
       </c>
       <c r="I37" t="n">
-        <v>1.2081</v>
+        <v>0.8552999999999999</v>
       </c>
       <c r="J37" t="n">
-        <v>42.2835</v>
+        <v>29.9355</v>
       </c>
     </row>
     <row r="38">
@@ -5709,10 +5709,10 @@
         <v>1.37</v>
       </c>
       <c r="I38" t="n">
-        <v>0.9781</v>
+        <v>0.7095</v>
       </c>
       <c r="J38" t="n">
-        <v>34.2335</v>
+        <v>24.8325</v>
       </c>
     </row>
     <row r="39">
@@ -5749,10 +5749,10 @@
         <v>1.08</v>
       </c>
       <c r="I39" t="n">
-        <v>0.204</v>
+        <v>0.2572</v>
       </c>
       <c r="J39" t="n">
-        <v>7.14</v>
+        <v>9.002000000000001</v>
       </c>
     </row>
     <row r="40">
@@ -5789,10 +5789,10 @@
         <v>0.97</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.2417</v>
+        <v>-0.1686</v>
       </c>
       <c r="J40" t="n">
-        <v>-8.4595</v>
+        <v>-5.901</v>
       </c>
     </row>
     <row r="41">
@@ -5829,10 +5829,10 @@
         <v>0.84</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.6183999999999999</v>
+        <v>-0.5570000000000001</v>
       </c>
       <c r="J41" t="n">
-        <v>-21.644</v>
+        <v>-19.495</v>
       </c>
     </row>
     <row r="42">
@@ -5869,10 +5869,10 @@
         <v>1.45</v>
       </c>
       <c r="I42" t="n">
-        <v>1.2162</v>
+        <v>0.8561</v>
       </c>
       <c r="J42" t="n">
-        <v>36.486</v>
+        <v>25.683</v>
       </c>
     </row>
     <row r="43">
@@ -5909,10 +5909,10 @@
         <v>1.21</v>
       </c>
       <c r="I43" t="n">
-        <v>0.6804</v>
+        <v>0.5132</v>
       </c>
       <c r="J43" t="n">
-        <v>20.412</v>
+        <v>15.396</v>
       </c>
     </row>
     <row r="44">
@@ -5949,10 +5949,10 @@
         <v>0.9</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.4071</v>
+        <v>-0.3546</v>
       </c>
       <c r="J44" t="n">
-        <v>-12.213</v>
+        <v>-10.638</v>
       </c>
     </row>
     <row r="45">
@@ -5989,10 +5989,10 @@
         <v>0.84</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.5732</v>
+        <v>-0.5214</v>
       </c>
       <c r="J45" t="n">
-        <v>-17.196</v>
+        <v>-15.642</v>
       </c>
     </row>
     <row r="46">
@@ -6029,10 +6029,10 @@
         <v>0.7</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.9114</v>
+        <v>-0.8796</v>
       </c>
       <c r="J46" t="n">
-        <v>-27.342</v>
+        <v>-26.388</v>
       </c>
     </row>
     <row r="47">
@@ -6069,10 +6069,10 @@
         <v>1.08</v>
       </c>
       <c r="I47" t="n">
-        <v>0.2078</v>
+        <v>0.2146</v>
       </c>
       <c r="J47" t="n">
-        <v>6.234</v>
+        <v>6.438</v>
       </c>
     </row>
     <row r="48">
@@ -6109,10 +6109,10 @@
         <v>0.99</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.0109</v>
+        <v>-0.0178</v>
       </c>
       <c r="J48" t="n">
-        <v>-0.327</v>
+        <v>-0.534</v>
       </c>
     </row>
     <row r="49">
@@ -6149,10 +6149,10 @@
         <v>0.95</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.1166</v>
+        <v>-0.07240000000000001</v>
       </c>
       <c r="J49" t="n">
-        <v>-3.498</v>
+        <v>-2.172</v>
       </c>
     </row>
     <row r="50">
@@ -6189,10 +6189,10 @@
         <v>0.95</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.1166</v>
+        <v>-0.07240000000000001</v>
       </c>
       <c r="J50" t="n">
-        <v>-3.498</v>
+        <v>-2.172</v>
       </c>
     </row>
     <row r="51">
@@ -6229,10 +6229,10 @@
         <v>0.84</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.3138</v>
+        <v>-0.1939</v>
       </c>
       <c r="J51" t="n">
-        <v>-9.414</v>
+        <v>-5.817</v>
       </c>
     </row>
     <row r="52">
@@ -6269,10 +6269,10 @@
         <v>1.76</v>
       </c>
       <c r="I52" t="n">
-        <v>1.6299</v>
+        <v>1.1431</v>
       </c>
       <c r="J52" t="n">
-        <v>34.2279</v>
+        <v>24.0051</v>
       </c>
     </row>
     <row r="53">
@@ -6309,10 +6309,10 @@
         <v>1.43</v>
       </c>
       <c r="I53" t="n">
-        <v>0.9838</v>
+        <v>0.7476</v>
       </c>
       <c r="J53" t="n">
-        <v>20.6598</v>
+        <v>15.6996</v>
       </c>
     </row>
     <row r="54">
@@ -6349,10 +6349,10 @@
         <v>1.39</v>
       </c>
       <c r="I54" t="n">
-        <v>0.8881</v>
+        <v>0.6986</v>
       </c>
       <c r="J54" t="n">
-        <v>18.6501</v>
+        <v>14.6706</v>
       </c>
     </row>
     <row r="55">
@@ -6389,10 +6389,10 @@
         <v>1.34</v>
       </c>
       <c r="I55" t="n">
-        <v>0.7534999999999999</v>
+        <v>0.6369</v>
       </c>
       <c r="J55" t="n">
-        <v>15.8235</v>
+        <v>13.3749</v>
       </c>
     </row>
     <row r="56">
@@ -6429,10 +6429,10 @@
         <v>0.98</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.2752</v>
+        <v>-0.1866</v>
       </c>
       <c r="J56" t="n">
-        <v>-5.7792</v>
+        <v>-3.9186</v>
       </c>
     </row>
     <row r="57">
@@ -6469,10 +6469,10 @@
         <v>0.78</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.2825</v>
+        <v>-0.2246</v>
       </c>
       <c r="J57" t="n">
-        <v>-5.9325</v>
+        <v>-4.7166</v>
       </c>
     </row>
     <row r="58">
@@ -6509,10 +6509,10 @@
         <v>0.78</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.2825</v>
+        <v>-0.2246</v>
       </c>
       <c r="J58" t="n">
-        <v>-5.9325</v>
+        <v>-4.7166</v>
       </c>
     </row>
     <row r="59">
@@ -6549,10 +6549,10 @@
         <v>0.77</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.299</v>
+        <v>-0.2346</v>
       </c>
       <c r="J59" t="n">
-        <v>-6.279</v>
+        <v>-4.9266</v>
       </c>
     </row>
     <row r="60">
@@ -6589,10 +6589,10 @@
         <v>0.75</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.3326</v>
+        <v>-0.254</v>
       </c>
       <c r="J60" t="n">
-        <v>-6.9846</v>
+        <v>-5.334</v>
       </c>
     </row>
     <row r="61">
@@ -6629,10 +6629,10 @@
         <v>0.52</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.6913</v>
+        <v>-0.4673</v>
       </c>
       <c r="J61" t="n">
-        <v>-14.5173</v>
+        <v>-9.8133</v>
       </c>
     </row>
     <row r="62">
@@ -6669,10 +6669,10 @@
         <v>1.18</v>
       </c>
       <c r="I62" t="n">
-        <v>0.3658</v>
+        <v>0.3153</v>
       </c>
       <c r="J62" t="n">
-        <v>13.1688</v>
+        <v>11.3508</v>
       </c>
     </row>
     <row r="63">
@@ -6709,10 +6709,10 @@
         <v>0.98</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.0417</v>
+        <v>-0.0339</v>
       </c>
       <c r="J63" t="n">
-        <v>-1.5012</v>
+        <v>-1.2204</v>
       </c>
     </row>
     <row r="64">
@@ -6749,10 +6749,10 @@
         <v>0.91</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.199</v>
+        <v>-0.1196</v>
       </c>
       <c r="J64" t="n">
-        <v>-7.164</v>
+        <v>-4.3056</v>
       </c>
     </row>
     <row r="65">
@@ -6789,10 +6789,10 @@
         <v>0.89</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.2343</v>
+        <v>-0.1417</v>
       </c>
       <c r="J65" t="n">
-        <v>-8.434799999999999</v>
+        <v>-5.1012</v>
       </c>
     </row>
     <row r="66">
@@ -6829,10 +6829,10 @@
         <v>0.88</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.2512</v>
+        <v>-0.1525</v>
       </c>
       <c r="J66" t="n">
-        <v>-9.043200000000001</v>
+        <v>-5.49</v>
       </c>
     </row>
     <row r="67">
@@ -6869,10 +6869,10 @@
         <v>1.33</v>
       </c>
       <c r="I67" t="n">
-        <v>0.5152</v>
+        <v>0.4445</v>
       </c>
       <c r="J67" t="n">
-        <v>18.5472</v>
+        <v>16.002</v>
       </c>
     </row>
     <row r="68">
@@ -6909,10 +6909,10 @@
         <v>1.26</v>
       </c>
       <c r="I68" t="n">
-        <v>0.4219</v>
+        <v>0.3614</v>
       </c>
       <c r="J68" t="n">
-        <v>15.1884</v>
+        <v>13.0104</v>
       </c>
     </row>
     <row r="69">
@@ -6949,10 +6949,10 @@
         <v>1.08</v>
       </c>
       <c r="I69" t="n">
-        <v>0.1214</v>
+        <v>0.1307</v>
       </c>
       <c r="J69" t="n">
-        <v>4.3704</v>
+        <v>4.7052</v>
       </c>
     </row>
     <row r="70">
@@ -6989,10 +6989,10 @@
         <v>1.04</v>
       </c>
       <c r="I70" t="n">
-        <v>0.0456</v>
+        <v>0.068</v>
       </c>
       <c r="J70" t="n">
-        <v>1.6416</v>
+        <v>2.448</v>
       </c>
     </row>
     <row r="71">
@@ -7029,10 +7029,10 @@
         <v>0.97</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.1361</v>
+        <v>-0.06370000000000001</v>
       </c>
       <c r="J71" t="n">
-        <v>-4.8996</v>
+        <v>-2.2932</v>
       </c>
     </row>
     <row r="72">
@@ -7069,10 +7069,10 @@
         <v>1.59</v>
       </c>
       <c r="I72" t="n">
-        <v>1.3472</v>
+        <v>1.2294</v>
       </c>
       <c r="J72" t="n">
-        <v>35.0272</v>
+        <v>31.9644</v>
       </c>
     </row>
     <row r="73">
@@ -7109,10 +7109,10 @@
         <v>1.4</v>
       </c>
       <c r="I73" t="n">
-        <v>0.9585</v>
+        <v>0.9801</v>
       </c>
       <c r="J73" t="n">
-        <v>24.921</v>
+        <v>25.4826</v>
       </c>
     </row>
     <row r="74">
@@ -7149,10 +7149,10 @@
         <v>1.24</v>
       </c>
       <c r="I74" t="n">
-        <v>0.5518</v>
+        <v>0.636</v>
       </c>
       <c r="J74" t="n">
-        <v>14.3468</v>
+        <v>16.536</v>
       </c>
     </row>
     <row r="75">
@@ -7189,10 +7189,10 @@
         <v>1.24</v>
       </c>
       <c r="I75" t="n">
-        <v>0.5518</v>
+        <v>0.636</v>
       </c>
       <c r="J75" t="n">
-        <v>14.3468</v>
+        <v>16.536</v>
       </c>
     </row>
     <row r="76">
@@ -7229,10 +7229,10 @@
         <v>1.07</v>
       </c>
       <c r="I76" t="n">
-        <v>0.1059</v>
+        <v>0.1892</v>
       </c>
       <c r="J76" t="n">
-        <v>2.7534</v>
+        <v>4.9192</v>
       </c>
     </row>
     <row r="77">
@@ -7269,10 +7269,10 @@
         <v>1.21</v>
       </c>
       <c r="I77" t="n">
-        <v>0.4576</v>
+        <v>0.5271</v>
       </c>
       <c r="J77" t="n">
-        <v>11.8976</v>
+        <v>13.7046</v>
       </c>
     </row>
     <row r="78">
@@ -7309,10 +7309,10 @@
         <v>0.99</v>
       </c>
       <c r="I78" t="n">
-        <v>0.0442</v>
+        <v>0.0015</v>
       </c>
       <c r="J78" t="n">
-        <v>1.1492</v>
+        <v>0.039</v>
       </c>
     </row>
     <row r="79">
@@ -7349,10 +7349,10 @@
         <v>0.77</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.379</v>
+        <v>-0.2485</v>
       </c>
       <c r="J79" t="n">
-        <v>-9.853999999999999</v>
+        <v>-6.461</v>
       </c>
     </row>
     <row r="80">
@@ -7389,10 +7389,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.4964</v>
+        <v>-0.3254</v>
       </c>
       <c r="J80" t="n">
-        <v>-12.9064</v>
+        <v>-8.4604</v>
       </c>
     </row>
     <row r="81">
@@ -7429,10 +7429,10 @@
         <v>0.53</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.7048</v>
+        <v>-0.4748</v>
       </c>
       <c r="J81" t="n">
-        <v>-18.3248</v>
+        <v>-12.3448</v>
       </c>
     </row>
     <row r="82">
@@ -7469,10 +7469,10 @@
         <v>1.27</v>
       </c>
       <c r="I82" t="n">
-        <v>0.7672</v>
+        <v>0.748</v>
       </c>
       <c r="J82" t="n">
-        <v>20.7144</v>
+        <v>20.196</v>
       </c>
     </row>
     <row r="83">
@@ -7509,10 +7509,10 @@
         <v>1.19</v>
       </c>
       <c r="I83" t="n">
-        <v>0.5676</v>
+        <v>0.5522</v>
       </c>
       <c r="J83" t="n">
-        <v>15.3252</v>
+        <v>14.9094</v>
       </c>
     </row>
     <row r="84">
@@ -7549,10 +7549,10 @@
         <v>1.11</v>
       </c>
       <c r="I84" t="n">
-        <v>0.3195</v>
+        <v>0.3472</v>
       </c>
       <c r="J84" t="n">
-        <v>8.6265</v>
+        <v>9.3744</v>
       </c>
     </row>
     <row r="85">
@@ -7589,10 +7589,10 @@
         <v>1.02</v>
       </c>
       <c r="I85" t="n">
-        <v>0.0129</v>
+        <v>0.06759999999999999</v>
       </c>
       <c r="J85" t="n">
-        <v>0.3483</v>
+        <v>1.8252</v>
       </c>
     </row>
     <row r="86">
@@ -7629,10 +7629,10 @@
         <v>1.01</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.0302</v>
+        <v>0.0267</v>
       </c>
       <c r="J86" t="n">
-        <v>-0.8154</v>
+        <v>0.7209</v>
       </c>
     </row>
     <row r="87">
@@ -7669,10 +7669,10 @@
         <v>1.25</v>
       </c>
       <c r="I87" t="n">
-        <v>0.464</v>
+        <v>0.5402</v>
       </c>
       <c r="J87" t="n">
-        <v>12.528</v>
+        <v>14.5854</v>
       </c>
     </row>
     <row r="88">
@@ -7709,10 +7709,10 @@
         <v>1</v>
       </c>
       <c r="I88" t="n">
-        <v>0.0211</v>
+        <v>0.0042</v>
       </c>
       <c r="J88" t="n">
-        <v>0.5697</v>
+        <v>0.1134</v>
       </c>
     </row>
     <row r="89">
@@ -7749,10 +7749,10 @@
         <v>0.9</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.2176</v>
+        <v>-0.1309</v>
       </c>
       <c r="J89" t="n">
-        <v>-5.8752</v>
+        <v>-3.5343</v>
       </c>
     </row>
     <row r="90">
@@ -7789,10 +7789,10 @@
         <v>0.86</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.2846</v>
+        <v>-0.174</v>
       </c>
       <c r="J90" t="n">
-        <v>-7.6842</v>
+        <v>-4.698</v>
       </c>
     </row>
     <row r="91">
@@ -7829,10 +7829,10 @@
         <v>0.84</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.3162</v>
+        <v>-0.1948</v>
       </c>
       <c r="J91" t="n">
-        <v>-8.5374</v>
+        <v>-5.2596</v>
       </c>
     </row>
     <row r="92">
@@ -7869,10 +7869,10 @@
         <v>1.27</v>
       </c>
       <c r="I92" t="n">
-        <v>0.7649</v>
+        <v>0.7466</v>
       </c>
       <c r="J92" t="n">
-        <v>22.1821</v>
+        <v>21.6514</v>
       </c>
     </row>
     <row r="93">
@@ -7909,10 +7909,10 @@
         <v>1.18</v>
       </c>
       <c r="I93" t="n">
-        <v>0.5381</v>
+        <v>0.5261</v>
       </c>
       <c r="J93" t="n">
-        <v>15.6049</v>
+        <v>15.2569</v>
       </c>
     </row>
     <row r="94">
@@ -7949,10 +7949,10 @@
         <v>1.16</v>
       </c>
       <c r="I94" t="n">
-        <v>0.4823</v>
+        <v>0.4755</v>
       </c>
       <c r="J94" t="n">
-        <v>13.9867</v>
+        <v>13.7895</v>
       </c>
     </row>
     <row r="95">
@@ -7989,10 +7989,10 @@
         <v>1.02</v>
       </c>
       <c r="I95" t="n">
-        <v>0.0108</v>
+        <v>0.06660000000000001</v>
       </c>
       <c r="J95" t="n">
-        <v>0.3132</v>
+        <v>1.9314</v>
       </c>
     </row>
     <row r="96">
@@ -8029,10 +8029,10 @@
         <v>0.99</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.151</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="J96" t="n">
-        <v>-4.379</v>
+        <v>-2.436</v>
       </c>
     </row>
     <row r="97">
@@ -8069,10 +8069,10 @@
         <v>1.66</v>
       </c>
       <c r="I97" t="n">
-        <v>0.9236</v>
+        <v>1.1071</v>
       </c>
       <c r="J97" t="n">
-        <v>26.7844</v>
+        <v>32.1059</v>
       </c>
     </row>
     <row r="98">
@@ -8109,10 +8109,10 @@
         <v>1.1</v>
       </c>
       <c r="I98" t="n">
-        <v>0.2067</v>
+        <v>0.2351</v>
       </c>
       <c r="J98" t="n">
-        <v>5.9943</v>
+        <v>6.8179</v>
       </c>
     </row>
     <row r="99">
@@ -8149,10 +8149,10 @@
         <v>0.86</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.3066</v>
+        <v>-0.1833</v>
       </c>
       <c r="J99" t="n">
-        <v>-8.891400000000001</v>
+        <v>-5.3157</v>
       </c>
     </row>
     <row r="100">
@@ -8189,10 +8189,10 @@
         <v>0.86</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.3066</v>
+        <v>-0.1833</v>
       </c>
       <c r="J100" t="n">
-        <v>-8.891400000000001</v>
+        <v>-5.3157</v>
       </c>
     </row>
     <row r="101">
@@ -8229,10 +8229,10 @@
         <v>0.78</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.4228</v>
+        <v>-0.2648</v>
       </c>
       <c r="J101" t="n">
-        <v>-12.2612</v>
+        <v>-7.6792</v>
       </c>
     </row>
     <row r="102">
@@ -8269,10 +8269,10 @@
         <v>1.82</v>
       </c>
       <c r="I102" t="n">
-        <v>1.7379</v>
+        <v>1.4877</v>
       </c>
       <c r="J102" t="n">
-        <v>38.2338</v>
+        <v>32.7294</v>
       </c>
     </row>
     <row r="103">
@@ -8309,10 +8309,10 @@
         <v>1.51</v>
       </c>
       <c r="I103" t="n">
-        <v>1.1569</v>
+        <v>1.1196</v>
       </c>
       <c r="J103" t="n">
-        <v>25.4518</v>
+        <v>24.6312</v>
       </c>
     </row>
     <row r="104">
@@ -8349,10 +8349,10 @@
         <v>1.37</v>
       </c>
       <c r="I104" t="n">
-        <v>0.8319</v>
+        <v>0.912</v>
       </c>
       <c r="J104" t="n">
-        <v>18.3018</v>
+        <v>20.064</v>
       </c>
     </row>
     <row r="105">
@@ -8389,10 +8389,10 @@
         <v>1.13</v>
       </c>
       <c r="I105" t="n">
-        <v>0.2501</v>
+        <v>0.3449</v>
       </c>
       <c r="J105" t="n">
-        <v>5.5022</v>
+        <v>7.5878</v>
       </c>
     </row>
     <row r="106">
@@ -8429,10 +8429,10 @@
         <v>1.05</v>
       </c>
       <c r="I106" t="n">
-        <v>0.0249</v>
+        <v>0.1111</v>
       </c>
       <c r="J106" t="n">
-        <v>0.5478</v>
+        <v>2.4442</v>
       </c>
     </row>
     <row r="107">
@@ -8469,10 +8469,10 @@
         <v>0.76</v>
       </c>
       <c r="I107" t="n">
-        <v>-0.3039</v>
+        <v>-0.2409</v>
       </c>
       <c r="J107" t="n">
-        <v>-6.6858</v>
+        <v>-5.2998</v>
       </c>
     </row>
     <row r="108">
@@ -8509,10 +8509,10 @@
         <v>0.74</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.3368</v>
+        <v>-0.2605</v>
       </c>
       <c r="J108" t="n">
-        <v>-7.4096</v>
+        <v>-5.731</v>
       </c>
     </row>
     <row r="109">
@@ -8549,10 +8549,10 @@
         <v>0.74</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.3368</v>
+        <v>-0.2605</v>
       </c>
       <c r="J109" t="n">
-        <v>-7.4096</v>
+        <v>-5.731</v>
       </c>
     </row>
     <row r="110">
@@ -8589,10 +8589,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.4346</v>
+        <v>-0.3062</v>
       </c>
       <c r="J110" t="n">
-        <v>-9.561199999999999</v>
+        <v>-6.7364</v>
       </c>
     </row>
     <row r="111">
@@ -8629,10 +8629,10 @@
         <v>0.57</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.6183999999999999</v>
+        <v>-0.4173</v>
       </c>
       <c r="J111" t="n">
-        <v>-13.6048</v>
+        <v>-9.1806</v>
       </c>
     </row>
     <row r="112">
@@ -8669,10 +8669,10 @@
         <v>1.45</v>
       </c>
       <c r="I112" t="n">
-        <v>1.1297</v>
+        <v>1.0812</v>
       </c>
       <c r="J112" t="n">
-        <v>29.3722</v>
+        <v>28.1112</v>
       </c>
     </row>
     <row r="113">
@@ -8709,10 +8709,10 @@
         <v>1.37</v>
       </c>
       <c r="I113" t="n">
-        <v>0.9601</v>
+        <v>0.9552</v>
       </c>
       <c r="J113" t="n">
-        <v>24.9626</v>
+        <v>24.8352</v>
       </c>
     </row>
     <row r="114">
@@ -8749,10 +8749,10 @@
         <v>1.19</v>
       </c>
       <c r="I114" t="n">
-        <v>0.519</v>
+        <v>0.5387</v>
       </c>
       <c r="J114" t="n">
-        <v>13.494</v>
+        <v>14.0062</v>
       </c>
     </row>
     <row r="115">
@@ -8789,10 +8789,10 @@
         <v>1.03</v>
       </c>
       <c r="I115" t="n">
-        <v>0.0223</v>
+        <v>0.089</v>
       </c>
       <c r="J115" t="n">
-        <v>0.5798</v>
+        <v>2.314</v>
       </c>
     </row>
     <row r="116">
@@ -8829,10 +8829,10 @@
         <v>0.87</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.5514</v>
+        <v>-0.4839</v>
       </c>
       <c r="J116" t="n">
-        <v>-14.3364</v>
+        <v>-12.5814</v>
       </c>
     </row>
     <row r="117">
@@ -8869,10 +8869,10 @@
         <v>1.26</v>
       </c>
       <c r="I117" t="n">
-        <v>0.4659</v>
+        <v>0.5455</v>
       </c>
       <c r="J117" t="n">
-        <v>12.1134</v>
+        <v>14.183</v>
       </c>
     </row>
     <row r="118">
@@ -8909,10 +8909,10 @@
         <v>1.06</v>
       </c>
       <c r="I118" t="n">
-        <v>0.1535</v>
+        <v>0.1609</v>
       </c>
       <c r="J118" t="n">
-        <v>3.991</v>
+        <v>4.1834</v>
       </c>
     </row>
     <row r="119">
@@ -8949,10 +8949,10 @@
         <v>1.02</v>
       </c>
       <c r="I119" t="n">
-        <v>0.06569999999999999</v>
+        <v>0.0654</v>
       </c>
       <c r="J119" t="n">
-        <v>1.7082</v>
+        <v>1.7004</v>
       </c>
     </row>
     <row r="120">
@@ -8989,10 +8989,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.1568</v>
+        <v>-0.0885</v>
       </c>
       <c r="J120" t="n">
-        <v>-4.0768</v>
+        <v>-2.301</v>
       </c>
     </row>
     <row r="121">
@@ -9029,10 +9029,10 @@
         <v>0.74</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.468</v>
+        <v>-0.2984</v>
       </c>
       <c r="J121" t="n">
-        <v>-12.168</v>
+        <v>-7.7584</v>
       </c>
     </row>
     <row r="122">
@@ -9069,10 +9069,10 @@
         <v>1.97</v>
       </c>
       <c r="I122" t="n">
-        <v>1.9561</v>
+        <v>1.6544</v>
       </c>
       <c r="J122" t="n">
-        <v>41.0781</v>
+        <v>34.7424</v>
       </c>
     </row>
     <row r="123">
@@ -9109,10 +9109,10 @@
         <v>1.56</v>
       </c>
       <c r="I123" t="n">
-        <v>1.2471</v>
+        <v>1.1766</v>
       </c>
       <c r="J123" t="n">
-        <v>26.1891</v>
+        <v>24.7086</v>
       </c>
     </row>
     <row r="124">
@@ -9149,10 +9149,10 @@
         <v>1.35</v>
       </c>
       <c r="I124" t="n">
-        <v>0.7665</v>
+        <v>0.8668</v>
       </c>
       <c r="J124" t="n">
-        <v>16.0965</v>
+        <v>18.2028</v>
       </c>
     </row>
     <row r="125">
@@ -9189,10 +9189,10 @@
         <v>1.25</v>
       </c>
       <c r="I125" t="n">
-        <v>0.5353</v>
+        <v>0.6411</v>
       </c>
       <c r="J125" t="n">
-        <v>11.2413</v>
+        <v>13.4631</v>
       </c>
     </row>
     <row r="126">
@@ -9229,10 +9229,10 @@
         <v>0.86</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.6269</v>
+        <v>-0.5594</v>
       </c>
       <c r="J126" t="n">
-        <v>-13.1649</v>
+        <v>-11.7474</v>
       </c>
     </row>
     <row r="127">
@@ -9269,10 +9269,10 @@
         <v>1.06</v>
       </c>
       <c r="I127" t="n">
-        <v>0.2885</v>
+        <v>0.3031</v>
       </c>
       <c r="J127" t="n">
-        <v>6.0585</v>
+        <v>6.3651</v>
       </c>
     </row>
     <row r="128">
@@ -9309,10 +9309,10 @@
         <v>0.67</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.4587</v>
+        <v>-0.3222</v>
       </c>
       <c r="J128" t="n">
-        <v>-9.6327</v>
+        <v>-6.7662</v>
       </c>
     </row>
     <row r="129">
@@ -9349,10 +9349,10 @@
         <v>0.62</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.54</v>
+        <v>-0.368</v>
       </c>
       <c r="J129" t="n">
-        <v>-11.34</v>
+        <v>-7.728</v>
       </c>
     </row>
     <row r="130">
@@ -9389,10 +9389,10 @@
         <v>0.61</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.555</v>
+        <v>-0.3773</v>
       </c>
       <c r="J130" t="n">
-        <v>-11.655</v>
+        <v>-7.9233</v>
       </c>
     </row>
     <row r="131">
@@ -9429,10 +9429,10 @@
         <v>0.46</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.7594</v>
+        <v>-0.5175999999999999</v>
       </c>
       <c r="J131" t="n">
-        <v>-15.9474</v>
+        <v>-10.8696</v>
       </c>
     </row>
     <row r="132">
@@ -9469,10 +9469,10 @@
         <v>1.4</v>
       </c>
       <c r="I132" t="n">
-        <v>1.0301</v>
+        <v>1.0128</v>
       </c>
       <c r="J132" t="n">
-        <v>25.7525</v>
+        <v>25.32</v>
       </c>
     </row>
     <row r="133">
@@ -9509,10 +9509,10 @@
         <v>1.26</v>
       </c>
       <c r="I133" t="n">
-        <v>0.7126</v>
+        <v>0.708</v>
       </c>
       <c r="J133" t="n">
-        <v>17.815</v>
+        <v>17.7</v>
       </c>
     </row>
     <row r="134">
@@ -9549,10 +9549,10 @@
         <v>1.13</v>
       </c>
       <c r="I134" t="n">
-        <v>0.339</v>
+        <v>0.3907</v>
       </c>
       <c r="J134" t="n">
-        <v>8.475</v>
+        <v>9.7675</v>
       </c>
     </row>
     <row r="135">
@@ -9589,10 +9589,10 @@
         <v>1.1</v>
       </c>
       <c r="I135" t="n">
-        <v>0.251</v>
+        <v>0.309</v>
       </c>
       <c r="J135" t="n">
-        <v>6.275</v>
+        <v>7.725</v>
       </c>
     </row>
     <row r="136">
@@ -9629,10 +9629,10 @@
         <v>0.97</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.2509</v>
+        <v>-0.1749</v>
       </c>
       <c r="J136" t="n">
-        <v>-6.2725</v>
+        <v>-4.3725</v>
       </c>
     </row>
     <row r="137">
@@ -9669,10 +9669,10 @@
         <v>1.05</v>
       </c>
       <c r="I137" t="n">
-        <v>0.1533</v>
+        <v>0.1489</v>
       </c>
       <c r="J137" t="n">
-        <v>3.8325</v>
+        <v>3.7225</v>
       </c>
     </row>
     <row r="138">
@@ -9709,10 +9709,10 @@
         <v>1.03</v>
       </c>
       <c r="I138" t="n">
-        <v>0.1116</v>
+        <v>0.1005</v>
       </c>
       <c r="J138" t="n">
-        <v>2.79</v>
+        <v>2.5125</v>
       </c>
     </row>
     <row r="139">
@@ -9749,10 +9749,10 @@
         <v>1.02</v>
       </c>
       <c r="I139" t="n">
-        <v>0.0885</v>
+        <v>0.0742</v>
       </c>
       <c r="J139" t="n">
-        <v>2.2125</v>
+        <v>1.855</v>
       </c>
     </row>
     <row r="140">
@@ -9789,10 +9789,10 @@
         <v>0.98</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.0356</v>
+        <v>-0.033</v>
       </c>
       <c r="J140" t="n">
-        <v>-0.89</v>
+        <v>-0.825</v>
       </c>
     </row>
     <row r="141">
@@ -9829,10 +9829,10 @@
         <v>0.71</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.4989</v>
+        <v>-0.3219</v>
       </c>
       <c r="J141" t="n">
-        <v>-12.4725</v>
+        <v>-8.047499999999999</v>
       </c>
     </row>
     <row r="142">
@@ -9869,10 +9869,10 @@
         <v>1.84</v>
       </c>
       <c r="I142" t="n">
-        <v>1.8302</v>
+        <v>1.5478</v>
       </c>
       <c r="J142" t="n">
-        <v>47.5852</v>
+        <v>40.2428</v>
       </c>
     </row>
     <row r="143">
@@ -9909,10 +9909,10 @@
         <v>1.45</v>
       </c>
       <c r="I143" t="n">
-        <v>1.0975</v>
+        <v>1.0673</v>
       </c>
       <c r="J143" t="n">
-        <v>28.535</v>
+        <v>27.7498</v>
       </c>
     </row>
     <row r="144">
@@ -9949,10 +9949,10 @@
         <v>1.18</v>
       </c>
       <c r="I144" t="n">
-        <v>0.4323</v>
+        <v>0.5034999999999999</v>
       </c>
       <c r="J144" t="n">
-        <v>11.2398</v>
+        <v>13.091</v>
       </c>
     </row>
     <row r="145">
@@ -9989,10 +9989,10 @@
         <v>0.9</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.4892</v>
+        <v>-0.4147</v>
       </c>
       <c r="J145" t="n">
-        <v>-12.7192</v>
+        <v>-10.7822</v>
       </c>
     </row>
     <row r="146">
@@ -10029,10 +10029,10 @@
         <v>0.86</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.5944</v>
+        <v>-0.527</v>
       </c>
       <c r="J146" t="n">
-        <v>-15.4544</v>
+        <v>-13.702</v>
       </c>
     </row>
     <row r="147">
@@ -10069,10 +10069,10 @@
         <v>1.09</v>
       </c>
       <c r="I147" t="n">
-        <v>0.2824</v>
+        <v>0.2918</v>
       </c>
       <c r="J147" t="n">
-        <v>7.3424</v>
+        <v>7.5868</v>
       </c>
     </row>
     <row r="148">
@@ -10109,10 +10109,10 @@
         <v>1.04</v>
       </c>
       <c r="I148" t="n">
-        <v>0.1906</v>
+        <v>0.174</v>
       </c>
       <c r="J148" t="n">
-        <v>4.9556</v>
+        <v>4.524</v>
       </c>
     </row>
     <row r="149">
@@ -10149,10 +10149,10 @@
         <v>0.8</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.318</v>
+        <v>-0.2169</v>
       </c>
       <c r="J149" t="n">
-        <v>-8.268000000000001</v>
+        <v>-5.6394</v>
       </c>
     </row>
     <row r="150">
@@ -10189,10 +10189,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.4896</v>
+        <v>-0.3223</v>
       </c>
       <c r="J150" t="n">
-        <v>-12.7296</v>
+        <v>-8.379799999999999</v>
       </c>
     </row>
     <row r="151">
@@ -10229,10 +10229,10 @@
         <v>0.46</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.7858000000000001</v>
+        <v>-0.5361</v>
       </c>
       <c r="J151" t="n">
-        <v>-20.4308</v>
+        <v>-13.9386</v>
       </c>
     </row>
     <row r="152">
@@ -10269,10 +10269,10 @@
         <v>0.99</v>
       </c>
       <c r="I152" t="n">
-        <v>0.0621</v>
+        <v>0.0184</v>
       </c>
       <c r="J152" t="n">
-        <v>1.5525</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="153">
@@ -10309,10 +10309,10 @@
         <v>0.83</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.241</v>
+        <v>-0.186</v>
       </c>
       <c r="J153" t="n">
-        <v>-6.025</v>
+        <v>-4.65</v>
       </c>
     </row>
     <row r="154">
@@ -10349,10 +10349,10 @@
         <v>0.73</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.4233</v>
+        <v>-0.2814</v>
       </c>
       <c r="J154" t="n">
-        <v>-10.5825</v>
+        <v>-7.035</v>
       </c>
     </row>
     <row r="155">
@@ -10389,10 +10389,10 @@
         <v>0.72</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.4385</v>
+        <v>-0.291</v>
       </c>
       <c r="J155" t="n">
-        <v>-10.9625</v>
+        <v>-7.275</v>
       </c>
     </row>
     <row r="156">
@@ -10429,10 +10429,10 @@
         <v>0.71</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.4535</v>
+        <v>-0.3005</v>
       </c>
       <c r="J156" t="n">
-        <v>-11.3375</v>
+        <v>-7.5125</v>
       </c>
     </row>
     <row r="157">
@@ -10469,10 +10469,10 @@
         <v>1.65</v>
       </c>
       <c r="I157" t="n">
-        <v>1.4537</v>
+        <v>1.2988</v>
       </c>
       <c r="J157" t="n">
-        <v>36.3425</v>
+        <v>32.47</v>
       </c>
     </row>
     <row r="158">
@@ -10509,10 +10509,10 @@
         <v>1.63</v>
       </c>
       <c r="I158" t="n">
-        <v>1.4161</v>
+        <v>1.2746</v>
       </c>
       <c r="J158" t="n">
-        <v>35.4025</v>
+        <v>31.865</v>
       </c>
     </row>
     <row r="159">
@@ -10549,10 +10549,10 @@
         <v>1.21</v>
       </c>
       <c r="I159" t="n">
-        <v>0.4701</v>
+        <v>0.5609</v>
       </c>
       <c r="J159" t="n">
-        <v>11.7525</v>
+        <v>14.0225</v>
       </c>
     </row>
     <row r="160">
@@ -10589,10 +10589,10 @@
         <v>1.11</v>
       </c>
       <c r="I160" t="n">
-        <v>0.2139</v>
+        <v>0.3017</v>
       </c>
       <c r="J160" t="n">
-        <v>5.3475</v>
+        <v>7.5425</v>
       </c>
     </row>
     <row r="161">
@@ -10629,10 +10629,10 @@
         <v>1.02</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.06370000000000001</v>
+        <v>0.0177</v>
       </c>
       <c r="J161" t="n">
-        <v>-1.5925</v>
+        <v>0.4425</v>
       </c>
     </row>
     <row r="162">
@@ -10669,10 +10669,10 @@
         <v>1.7</v>
       </c>
       <c r="I162" t="n">
-        <v>0.909</v>
+        <v>0.8263</v>
       </c>
       <c r="J162" t="n">
-        <v>22.725</v>
+        <v>20.6575</v>
       </c>
     </row>
     <row r="163">
@@ -10709,10 +10709,10 @@
         <v>1.42</v>
       </c>
       <c r="I163" t="n">
-        <v>0.5946</v>
+        <v>0.5274</v>
       </c>
       <c r="J163" t="n">
-        <v>14.865</v>
+        <v>13.185</v>
       </c>
     </row>
     <row r="164">
@@ -10749,10 +10749,10 @@
         <v>1.36</v>
       </c>
       <c r="I164" t="n">
-        <v>0.5194</v>
+        <v>0.4609</v>
       </c>
       <c r="J164" t="n">
-        <v>12.985</v>
+        <v>11.5225</v>
       </c>
     </row>
     <row r="165">
@@ -10789,10 +10789,10 @@
         <v>0.92</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.2489</v>
+        <v>-0.1369</v>
       </c>
       <c r="J165" t="n">
-        <v>-6.2225</v>
+        <v>-3.4225</v>
       </c>
     </row>
     <row r="166">
@@ -10829,10 +10829,10 @@
         <v>0.83</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.3844</v>
+        <v>-0.2338</v>
       </c>
       <c r="J166" t="n">
-        <v>-9.609999999999999</v>
+        <v>-5.845</v>
       </c>
     </row>
     <row r="167">
@@ -10869,10 +10869,10 @@
         <v>1.31</v>
       </c>
       <c r="I167" t="n">
-        <v>0.5671</v>
+        <v>0.5187</v>
       </c>
       <c r="J167" t="n">
-        <v>14.1775</v>
+        <v>12.9675</v>
       </c>
     </row>
     <row r="168">
@@ -10909,10 +10909,10 @@
         <v>0.95</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.07539999999999999</v>
+        <v>-0.0674</v>
       </c>
       <c r="J168" t="n">
-        <v>-1.885</v>
+        <v>-1.685</v>
       </c>
     </row>
     <row r="169">
@@ -10949,10 +10949,10 @@
         <v>0.82</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.3261</v>
+        <v>-0.2073</v>
       </c>
       <c r="J169" t="n">
-        <v>-8.1525</v>
+        <v>-5.1825</v>
       </c>
     </row>
     <row r="170">
@@ -10989,10 +10989,10 @@
         <v>0.75</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.4308</v>
+        <v>-0.2766</v>
       </c>
       <c r="J170" t="n">
-        <v>-10.77</v>
+        <v>-6.915</v>
       </c>
     </row>
     <row r="171">
@@ -11029,10 +11029,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.5137</v>
+        <v>-0.3342</v>
       </c>
       <c r="J171" t="n">
-        <v>-12.8425</v>
+        <v>-8.355</v>
       </c>
     </row>
     <row r="172">
@@ -11069,10 +11069,10 @@
         <v>0.97</v>
       </c>
       <c r="I172" t="n">
-        <v>0.0467</v>
+        <v>-0.0025</v>
       </c>
       <c r="J172" t="n">
-        <v>1.0741</v>
+        <v>-0.0575</v>
       </c>
     </row>
     <row r="173">
@@ -11109,10 +11109,10 @@
         <v>0.85</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.1702</v>
+        <v>-0.1518</v>
       </c>
       <c r="J173" t="n">
-        <v>-3.9146</v>
+        <v>-3.4914</v>
       </c>
     </row>
     <row r="174">
@@ -11149,10 +11149,10 @@
         <v>0.74</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.3531</v>
+        <v>-0.264</v>
       </c>
       <c r="J174" t="n">
-        <v>-8.1213</v>
+        <v>-6.072</v>
       </c>
     </row>
     <row r="175">
@@ -11189,10 +11189,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.451</v>
+        <v>-0.3092</v>
       </c>
       <c r="J175" t="n">
-        <v>-10.373</v>
+        <v>-7.1116</v>
       </c>
     </row>
     <row r="176">
@@ -11229,10 +11229,10 @@
         <v>0.37</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.8779</v>
+        <v>-0.6073</v>
       </c>
       <c r="J176" t="n">
-        <v>-20.1917</v>
+        <v>-13.9679</v>
       </c>
     </row>
     <row r="177">
@@ -11269,10 +11269,10 @@
         <v>1.65</v>
       </c>
       <c r="I177" t="n">
-        <v>1.4305</v>
+        <v>1.288</v>
       </c>
       <c r="J177" t="n">
-        <v>32.9015</v>
+        <v>29.624</v>
       </c>
     </row>
     <row r="178">
@@ -11309,10 +11309,10 @@
         <v>1.53</v>
       </c>
       <c r="I178" t="n">
-        <v>1.1976</v>
+        <v>1.1439</v>
       </c>
       <c r="J178" t="n">
-        <v>27.5448</v>
+        <v>26.3097</v>
       </c>
     </row>
     <row r="179">
@@ -11349,10 +11349,10 @@
         <v>1.44</v>
       </c>
       <c r="I179" t="n">
-        <v>1.0085</v>
+        <v>1.0319</v>
       </c>
       <c r="J179" t="n">
-        <v>23.1955</v>
+        <v>23.7337</v>
       </c>
     </row>
     <row r="180">
@@ -11389,10 +11389,10 @@
         <v>1.27</v>
       </c>
       <c r="I180" t="n">
-        <v>0.5911</v>
+        <v>0.6923</v>
       </c>
       <c r="J180" t="n">
-        <v>13.5953</v>
+        <v>15.9229</v>
       </c>
     </row>
     <row r="181">
@@ -11429,10 +11429,10 @@
         <v>0.99</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.2334</v>
+        <v>-0.1447</v>
       </c>
       <c r="J181" t="n">
-        <v>-5.3682</v>
+        <v>-3.3281</v>
       </c>
     </row>
     <row r="182">
@@ -11469,10 +11469,10 @@
         <v>1.37</v>
       </c>
       <c r="I182" t="n">
-        <v>0.5609</v>
+        <v>0.4878</v>
       </c>
       <c r="J182" t="n">
-        <v>16.2661</v>
+        <v>14.1462</v>
       </c>
     </row>
     <row r="183">
@@ -11509,10 +11509,10 @@
         <v>1.34</v>
       </c>
       <c r="I183" t="n">
-        <v>0.523</v>
+        <v>0.4532</v>
       </c>
       <c r="J183" t="n">
-        <v>15.167</v>
+        <v>13.1428</v>
       </c>
     </row>
     <row r="184">
@@ -11549,10 +11549,10 @@
         <v>1.32</v>
       </c>
       <c r="I184" t="n">
-        <v>0.4972</v>
+        <v>0.4299</v>
       </c>
       <c r="J184" t="n">
-        <v>14.4188</v>
+        <v>12.4671</v>
       </c>
     </row>
     <row r="185">
@@ -11589,10 +11589,10 @@
         <v>1.23</v>
       </c>
       <c r="I185" t="n">
-        <v>0.3738</v>
+        <v>0.3228</v>
       </c>
       <c r="J185" t="n">
-        <v>10.8402</v>
+        <v>9.3612</v>
       </c>
     </row>
     <row r="186">
@@ -11629,10 +11629,10 @@
         <v>0.5</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.7783</v>
+        <v>-0.5315</v>
       </c>
       <c r="J186" t="n">
-        <v>-22.5707</v>
+        <v>-15.4135</v>
       </c>
     </row>
     <row r="187">
@@ -11669,10 +11669,10 @@
         <v>1.21</v>
       </c>
       <c r="I187" t="n">
-        <v>0.4234</v>
+        <v>0.3701</v>
       </c>
       <c r="J187" t="n">
-        <v>12.2786</v>
+        <v>10.7329</v>
       </c>
     </row>
     <row r="188">
@@ -11709,10 +11709,10 @@
         <v>1.2</v>
       </c>
       <c r="I188" t="n">
-        <v>0.4092</v>
+        <v>0.3557</v>
       </c>
       <c r="J188" t="n">
-        <v>11.8668</v>
+        <v>10.3153</v>
       </c>
     </row>
     <row r="189">
@@ -11749,10 +11749,10 @@
         <v>0.9</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.1995</v>
+        <v>-0.1266</v>
       </c>
       <c r="J189" t="n">
-        <v>-5.7855</v>
+        <v>-3.6714</v>
       </c>
     </row>
     <row r="190">
@@ -11789,10 +11789,10 @@
         <v>0.68</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.5323</v>
+        <v>-0.3467</v>
       </c>
       <c r="J190" t="n">
-        <v>-15.4367</v>
+        <v>-10.0543</v>
       </c>
     </row>
     <row r="191">
@@ -11829,10 +11829,10 @@
         <v>0.65</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.5714</v>
+        <v>-0.3749</v>
       </c>
       <c r="J191" t="n">
-        <v>-16.5706</v>
+        <v>-10.8721</v>
       </c>
     </row>
     <row r="192">
@@ -11869,10 +11869,10 @@
         <v>1.19</v>
       </c>
       <c r="I192" t="n">
-        <v>0.3911</v>
+        <v>0.442</v>
       </c>
       <c r="J192" t="n">
-        <v>10.5597</v>
+        <v>11.934</v>
       </c>
     </row>
     <row r="193">
@@ -11909,10 +11909,10 @@
         <v>1.09</v>
       </c>
       <c r="I193" t="n">
-        <v>0.2345</v>
+        <v>0.243</v>
       </c>
       <c r="J193" t="n">
-        <v>6.3315</v>
+        <v>6.561</v>
       </c>
     </row>
     <row r="194">
@@ -11949,10 +11949,10 @@
         <v>0.88</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.2401</v>
+        <v>-0.1491</v>
       </c>
       <c r="J194" t="n">
-        <v>-6.4827</v>
+        <v>-4.0257</v>
       </c>
     </row>
     <row r="195">
@@ -11989,10 +11989,10 @@
         <v>0.85</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.2902</v>
+        <v>-0.1807</v>
       </c>
       <c r="J195" t="n">
-        <v>-7.8354</v>
+        <v>-4.8789</v>
       </c>
     </row>
     <row r="196">
@@ -12029,10 +12029,10 @@
         <v>0.68</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.5344</v>
+        <v>-0.3479</v>
       </c>
       <c r="J196" t="n">
-        <v>-14.4288</v>
+        <v>-9.3933</v>
       </c>
     </row>
     <row r="197">
@@ -12069,10 +12069,10 @@
         <v>1.37</v>
       </c>
       <c r="I197" t="n">
-        <v>0.9813</v>
+        <v>0.9683</v>
       </c>
       <c r="J197" t="n">
-        <v>26.4951</v>
+        <v>26.1441</v>
       </c>
     </row>
     <row r="198">
@@ -12109,10 +12109,10 @@
         <v>1.34</v>
       </c>
       <c r="I198" t="n">
-        <v>0.9154</v>
+        <v>0.9045</v>
       </c>
       <c r="J198" t="n">
-        <v>24.7158</v>
+        <v>24.4215</v>
       </c>
     </row>
     <row r="199">
@@ -12149,10 +12149,10 @@
         <v>1.21</v>
       </c>
       <c r="I199" t="n">
-        <v>0.6056</v>
+        <v>0.5959</v>
       </c>
       <c r="J199" t="n">
-        <v>16.3512</v>
+        <v>16.0893</v>
       </c>
     </row>
     <row r="200">
@@ -12189,10 +12189,10 @@
         <v>1.08</v>
       </c>
       <c r="I200" t="n">
-        <v>0.2076</v>
+        <v>0.2585</v>
       </c>
       <c r="J200" t="n">
-        <v>5.6052</v>
+        <v>6.9795</v>
       </c>
     </row>
     <row r="201">
@@ -12229,10 +12229,10 @@
         <v>0.71</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.9211</v>
+        <v>-0.8869</v>
       </c>
       <c r="J201" t="n">
-        <v>-24.8697</v>
+        <v>-23.9463</v>
       </c>
     </row>
     <row r="202">
@@ -12269,10 +12269,10 @@
         <v>0.96</v>
       </c>
       <c r="I202" t="n">
-        <v>-0.0397</v>
+        <v>-0.05</v>
       </c>
       <c r="J202" t="n">
-        <v>-1.0322</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="203">
@@ -12309,10 +12309,10 @@
         <v>0.93</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.0998</v>
+        <v>-0.0877</v>
       </c>
       <c r="J203" t="n">
-        <v>-2.5948</v>
+        <v>-2.2802</v>
       </c>
     </row>
     <row r="204">
@@ -12349,10 +12349,10 @@
         <v>0.91</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.138</v>
+        <v>-0.1108</v>
       </c>
       <c r="J204" t="n">
-        <v>-3.588</v>
+        <v>-2.8808</v>
       </c>
     </row>
     <row r="205">
@@ -12389,10 +12389,10 @@
         <v>0.79</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.3612</v>
+        <v>-0.2333</v>
       </c>
       <c r="J205" t="n">
-        <v>-9.3912</v>
+        <v>-6.0658</v>
       </c>
     </row>
     <row r="206">
@@ -12429,10 +12429,10 @@
         <v>0.77</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.3917</v>
+        <v>-0.2529</v>
       </c>
       <c r="J206" t="n">
-        <v>-10.1842</v>
+        <v>-6.5754</v>
       </c>
     </row>
     <row r="207">
@@ -12469,10 +12469,10 @@
         <v>1.75</v>
       </c>
       <c r="I207" t="n">
-        <v>1.6618</v>
+        <v>1.4332</v>
       </c>
       <c r="J207" t="n">
-        <v>43.2068</v>
+        <v>37.2632</v>
       </c>
     </row>
     <row r="208">
@@ -12509,10 +12509,10 @@
         <v>1.72</v>
       </c>
       <c r="I208" t="n">
-        <v>1.6078</v>
+        <v>1.397</v>
       </c>
       <c r="J208" t="n">
-        <v>41.8028</v>
+        <v>36.322</v>
       </c>
     </row>
     <row r="209">
@@ -12549,10 +12549,10 @@
         <v>1.05</v>
       </c>
       <c r="I209" t="n">
-        <v>0.0576</v>
+        <v>0.1358</v>
       </c>
       <c r="J209" t="n">
-        <v>1.4976</v>
+        <v>3.5308</v>
       </c>
     </row>
     <row r="210">
@@ -12589,10 +12589,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.3802</v>
+        <v>-0.2992</v>
       </c>
       <c r="J210" t="n">
-        <v>-9.885199999999999</v>
+        <v>-7.7792</v>
       </c>
     </row>
     <row r="211">
@@ -12629,10 +12629,10 @@
         <v>0.88</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.5483</v>
+        <v>-0.4767</v>
       </c>
       <c r="J211" t="n">
-        <v>-14.2558</v>
+        <v>-12.3942</v>
       </c>
     </row>
     <row r="212">
@@ -12669,10 +12669,10 @@
         <v>1.37</v>
       </c>
       <c r="I212" t="n">
-        <v>0.6165</v>
+        <v>0.7469</v>
       </c>
       <c r="J212" t="n">
-        <v>16.029</v>
+        <v>19.4194</v>
       </c>
     </row>
     <row r="213">
@@ -12709,10 +12709,10 @@
         <v>0.93</v>
       </c>
       <c r="I213" t="n">
-        <v>-0.1658</v>
+        <v>-0.0978</v>
       </c>
       <c r="J213" t="n">
-        <v>-4.3108</v>
+        <v>-2.5428</v>
       </c>
     </row>
     <row r="214">
@@ -12749,10 +12749,10 @@
         <v>0.88</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.2545</v>
+        <v>-0.1536</v>
       </c>
       <c r="J214" t="n">
-        <v>-6.617</v>
+        <v>-3.9936</v>
       </c>
     </row>
     <row r="215">
@@ -12789,10 +12789,10 @@
         <v>0.86</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.2871</v>
+        <v>-0.1749</v>
       </c>
       <c r="J215" t="n">
-        <v>-7.4646</v>
+        <v>-4.5474</v>
       </c>
     </row>
     <row r="216">
@@ -12829,10 +12829,10 @@
         <v>0.85</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.3029</v>
+        <v>-0.1854</v>
       </c>
       <c r="J216" t="n">
-        <v>-7.8754</v>
+        <v>-4.8204</v>
       </c>
     </row>
     <row r="217">
@@ -12869,10 +12869,10 @@
         <v>1.28</v>
       </c>
       <c r="I217" t="n">
-        <v>0.7771</v>
+        <v>0.7637</v>
       </c>
       <c r="J217" t="n">
-        <v>20.2046</v>
+        <v>19.8562</v>
       </c>
     </row>
     <row r="218">
@@ -12909,10 +12909,10 @@
         <v>1.19</v>
       </c>
       <c r="I218" t="n">
-        <v>0.5511</v>
+        <v>0.5461</v>
       </c>
       <c r="J218" t="n">
-        <v>14.3286</v>
+        <v>14.1986</v>
       </c>
     </row>
     <row r="219">
@@ -12949,10 +12949,10 @@
         <v>1.19</v>
       </c>
       <c r="I219" t="n">
-        <v>0.5511</v>
+        <v>0.5461</v>
       </c>
       <c r="J219" t="n">
-        <v>14.3286</v>
+        <v>14.1986</v>
       </c>
     </row>
     <row r="220">
@@ -12989,10 +12989,10 @@
         <v>1.07</v>
       </c>
       <c r="I220" t="n">
-        <v>0.1748</v>
+        <v>0.2284</v>
       </c>
       <c r="J220" t="n">
-        <v>4.5448</v>
+        <v>5.9384</v>
       </c>
     </row>
     <row r="221">
@@ -13029,10 +13029,10 @@
         <v>0.99</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.1598</v>
+        <v>-0.0892</v>
       </c>
       <c r="J221" t="n">
-        <v>-4.1548</v>
+        <v>-2.3192</v>
       </c>
     </row>
     <row r="222">
@@ -13069,10 +13069,10 @@
         <v>0.89</v>
       </c>
       <c r="I222" t="n">
-        <v>-0.0728</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="J222" t="n">
-        <v>-1.6016</v>
+        <v>-1.936</v>
       </c>
     </row>
     <row r="223">
@@ -13109,10 +13109,10 @@
         <v>0.78</v>
       </c>
       <c r="I223" t="n">
-        <v>-0.2512</v>
+        <v>-0.2122</v>
       </c>
       <c r="J223" t="n">
-        <v>-5.5264</v>
+        <v>-4.6684</v>
       </c>
     </row>
     <row r="224">
@@ -13149,10 +13149,10 @@
         <v>0.65</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.4777</v>
+        <v>-0.3374</v>
       </c>
       <c r="J224" t="n">
-        <v>-10.5094</v>
+        <v>-7.4228</v>
       </c>
     </row>
     <row r="225">
@@ -13189,10 +13189,10 @@
         <v>0.57</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.6039</v>
+        <v>-0.4108</v>
       </c>
       <c r="J225" t="n">
-        <v>-13.2858</v>
+        <v>-9.037599999999999</v>
       </c>
     </row>
     <row r="226">
@@ -13229,10 +13229,10 @@
         <v>0.42</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.8048</v>
+        <v>-0.5516</v>
       </c>
       <c r="J226" t="n">
-        <v>-17.7056</v>
+        <v>-12.1352</v>
       </c>
     </row>
     <row r="227">
@@ -13269,10 +13269,10 @@
         <v>1.56</v>
       </c>
       <c r="I227" t="n">
-        <v>1.2232</v>
+        <v>1.1695</v>
       </c>
       <c r="J227" t="n">
-        <v>26.9104</v>
+        <v>25.729</v>
       </c>
     </row>
     <row r="228">
@@ -13309,10 +13309,10 @@
         <v>1.5</v>
       </c>
       <c r="I228" t="n">
-        <v>1.098</v>
+        <v>1.0984</v>
       </c>
       <c r="J228" t="n">
-        <v>24.156</v>
+        <v>24.1648</v>
       </c>
     </row>
     <row r="229">
@@ -13349,10 +13349,10 @@
         <v>1.5</v>
       </c>
       <c r="I229" t="n">
-        <v>1.098</v>
+        <v>1.0984</v>
       </c>
       <c r="J229" t="n">
-        <v>24.156</v>
+        <v>24.1648</v>
       </c>
     </row>
     <row r="230">
@@ -13389,10 +13389,10 @@
         <v>1.49</v>
       </c>
       <c r="I230" t="n">
-        <v>1.0761</v>
+        <v>1.0865</v>
       </c>
       <c r="J230" t="n">
-        <v>23.6742</v>
+        <v>23.903</v>
       </c>
     </row>
     <row r="231">
@@ -13429,10 +13429,10 @@
         <v>1.19</v>
       </c>
       <c r="I231" t="n">
-        <v>0.3773</v>
+        <v>0.485</v>
       </c>
       <c r="J231" t="n">
-        <v>8.300599999999999</v>
+        <v>10.67</v>
       </c>
     </row>
     <row r="232">
@@ -13469,10 +13469,10 @@
         <v>1.38</v>
       </c>
       <c r="I232" t="n">
-        <v>0.6699000000000001</v>
+        <v>0.8248</v>
       </c>
       <c r="J232" t="n">
-        <v>14.0679</v>
+        <v>17.3208</v>
       </c>
     </row>
     <row r="233">
@@ -13509,10 +13509,10 @@
         <v>1.06</v>
       </c>
       <c r="I233" t="n">
-        <v>0.209</v>
+        <v>0.2017</v>
       </c>
       <c r="J233" t="n">
-        <v>4.389</v>
+        <v>4.2357</v>
       </c>
     </row>
     <row r="234">
@@ -13549,10 +13549,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.5042</v>
+        <v>-0.3292</v>
       </c>
       <c r="J234" t="n">
-        <v>-10.5882</v>
+        <v>-6.9132</v>
       </c>
     </row>
     <row r="235">
@@ -13589,10 +13589,10 @@
         <v>0.63</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.5842000000000001</v>
+        <v>-0.3858</v>
       </c>
       <c r="J235" t="n">
-        <v>-12.2682</v>
+        <v>-8.101800000000001</v>
       </c>
     </row>
     <row r="236">
@@ -13629,10 +13629,10 @@
         <v>0.57</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.6606</v>
+        <v>-0.4415</v>
       </c>
       <c r="J236" t="n">
-        <v>-13.8726</v>
+        <v>-9.2715</v>
       </c>
     </row>
     <row r="237">
@@ -13669,10 +13669,10 @@
         <v>1.68</v>
       </c>
       <c r="I237" t="n">
-        <v>1.5049</v>
+        <v>1.3326</v>
       </c>
       <c r="J237" t="n">
-        <v>31.6029</v>
+        <v>27.9846</v>
       </c>
     </row>
     <row r="238">
@@ -13709,10 +13709,10 @@
         <v>1.38</v>
       </c>
       <c r="I238" t="n">
-        <v>0.8978</v>
+        <v>0.9376</v>
       </c>
       <c r="J238" t="n">
-        <v>18.8538</v>
+        <v>19.6896</v>
       </c>
     </row>
     <row r="239">
@@ -13749,10 +13749,10 @@
         <v>1.36</v>
       </c>
       <c r="I239" t="n">
-        <v>0.8499</v>
+        <v>0.8966</v>
       </c>
       <c r="J239" t="n">
-        <v>17.8479</v>
+        <v>18.8286</v>
       </c>
     </row>
     <row r="240">
@@ -13789,10 +13789,10 @@
         <v>1.18</v>
       </c>
       <c r="I240" t="n">
-        <v>0.3916</v>
+        <v>0.4844</v>
       </c>
       <c r="J240" t="n">
-        <v>8.223599999999999</v>
+        <v>10.1724</v>
       </c>
     </row>
     <row r="241">
@@ -13829,10 +13829,10 @@
         <v>1.07</v>
       </c>
       <c r="I241" t="n">
-        <v>0.0977</v>
+        <v>0.1832</v>
       </c>
       <c r="J241" t="n">
-        <v>2.0517</v>
+        <v>3.8472</v>
       </c>
     </row>
     <row r="242">
@@ -13869,10 +13869,10 @@
         <v>1.5</v>
       </c>
       <c r="I242" t="n">
-        <v>0.6956</v>
+        <v>0.6187</v>
       </c>
       <c r="J242" t="n">
-        <v>19.4768</v>
+        <v>17.3236</v>
       </c>
     </row>
     <row r="243">
@@ -13909,10 +13909,10 @@
         <v>1.27</v>
       </c>
       <c r="I243" t="n">
-        <v>0.4046</v>
+        <v>0.3614</v>
       </c>
       <c r="J243" t="n">
-        <v>11.3288</v>
+        <v>10.1192</v>
       </c>
     </row>
     <row r="244">
@@ -13949,10 +13949,10 @@
         <v>1.17</v>
       </c>
       <c r="I244" t="n">
-        <v>0.2404</v>
+        <v>0.2429</v>
       </c>
       <c r="J244" t="n">
-        <v>6.7312</v>
+        <v>6.8012</v>
       </c>
     </row>
     <row r="245">
@@ -13989,10 +13989,10 @@
         <v>1.11</v>
       </c>
       <c r="I245" t="n">
-        <v>0.1456</v>
+        <v>0.1634</v>
       </c>
       <c r="J245" t="n">
-        <v>4.0768</v>
+        <v>4.5752</v>
       </c>
     </row>
     <row r="246">
@@ -14029,10 +14029,10 @@
         <v>1.07</v>
       </c>
       <c r="I246" t="n">
-        <v>0.0785</v>
+        <v>0.1052</v>
       </c>
       <c r="J246" t="n">
-        <v>2.198</v>
+        <v>2.9456</v>
       </c>
     </row>
     <row r="247">
@@ -14069,10 +14069,10 @@
         <v>1.33</v>
       </c>
       <c r="I247" t="n">
-        <v>0.5868</v>
+        <v>0.5396</v>
       </c>
       <c r="J247" t="n">
-        <v>16.4304</v>
+        <v>15.1088</v>
       </c>
     </row>
     <row r="248">
@@ -14109,10 +14109,10 @@
         <v>1.08</v>
       </c>
       <c r="I248" t="n">
-        <v>0.224</v>
+        <v>0.1739</v>
       </c>
       <c r="J248" t="n">
-        <v>6.272</v>
+        <v>4.8692</v>
       </c>
     </row>
     <row r="249">
@@ -14149,10 +14149,10 @@
         <v>0.92</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.1509</v>
+        <v>-0.1041</v>
       </c>
       <c r="J249" t="n">
-        <v>-4.2252</v>
+        <v>-2.9148</v>
       </c>
     </row>
     <row r="250">
@@ -14189,10 +14189,10 @@
         <v>0.7</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.504</v>
+        <v>-0.3267</v>
       </c>
       <c r="J250" t="n">
-        <v>-14.112</v>
+        <v>-9.147600000000001</v>
       </c>
     </row>
     <row r="251">
@@ -14229,10 +14229,10 @@
         <v>0.57</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.6701</v>
+        <v>-0.448</v>
       </c>
       <c r="J251" t="n">
-        <v>-18.7628</v>
+        <v>-12.544</v>
       </c>
     </row>
     <row r="252">
@@ -14269,10 +14269,10 @@
         <v>1.27</v>
       </c>
       <c r="I252" t="n">
-        <v>0.5102</v>
+        <v>0.5996</v>
       </c>
       <c r="J252" t="n">
-        <v>12.755</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="253">
@@ -14309,10 +14309,10 @@
         <v>1.19</v>
       </c>
       <c r="I253" t="n">
-        <v>0.3992</v>
+        <v>0.4508</v>
       </c>
       <c r="J253" t="n">
-        <v>9.98</v>
+        <v>11.27</v>
       </c>
     </row>
     <row r="254">
@@ -14349,10 +14349,10 @@
         <v>0.98</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.0147</v>
+        <v>-0.0283</v>
       </c>
       <c r="J254" t="n">
-        <v>-0.3675</v>
+        <v>-0.7075</v>
       </c>
     </row>
     <row r="255">
@@ -14389,10 +14389,10 @@
         <v>0.68</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.5298</v>
+        <v>-0.3452</v>
       </c>
       <c r="J255" t="n">
-        <v>-13.245</v>
+        <v>-8.630000000000001</v>
       </c>
     </row>
     <row r="256">
@@ -14429,10 +14429,10 @@
         <v>0.46</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.7999000000000001</v>
+        <v>-0.5471</v>
       </c>
       <c r="J256" t="n">
-        <v>-19.9975</v>
+        <v>-13.6775</v>
       </c>
     </row>
     <row r="257">
@@ -14469,10 +14469,10 @@
         <v>1.54</v>
       </c>
       <c r="I257" t="n">
-        <v>1.3103</v>
+        <v>1.1972</v>
       </c>
       <c r="J257" t="n">
-        <v>32.7575</v>
+        <v>29.93</v>
       </c>
     </row>
     <row r="258">
@@ -14509,10 +14509,10 @@
         <v>1.33</v>
       </c>
       <c r="I258" t="n">
-        <v>0.8713</v>
+        <v>0.8678</v>
       </c>
       <c r="J258" t="n">
-        <v>21.7825</v>
+        <v>21.695</v>
       </c>
     </row>
     <row r="259">
@@ -14549,10 +14549,10 @@
         <v>1.05</v>
       </c>
       <c r="I259" t="n">
-        <v>0.09130000000000001</v>
+        <v>0.1567</v>
       </c>
       <c r="J259" t="n">
-        <v>2.2825</v>
+        <v>3.9175</v>
       </c>
     </row>
     <row r="260">
@@ -14589,10 +14589,10 @@
         <v>1.03</v>
       </c>
       <c r="I260" t="n">
-        <v>0.0223</v>
+        <v>0.089</v>
       </c>
       <c r="J260" t="n">
-        <v>0.5575</v>
+        <v>2.225</v>
       </c>
     </row>
     <row r="261">
@@ -14629,10 +14629,10 @@
         <v>0.96</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.2894</v>
+        <v>-0.2125</v>
       </c>
       <c r="J261" t="n">
-        <v>-7.235</v>
+        <v>-5.3125</v>
       </c>
     </row>
     <row r="262">
@@ -14669,10 +14669,10 @@
         <v>1.7</v>
       </c>
       <c r="I262" t="n">
-        <v>1.4889</v>
+        <v>1.3321</v>
       </c>
       <c r="J262" t="n">
-        <v>29.778</v>
+        <v>26.642</v>
       </c>
     </row>
     <row r="263">
@@ -14709,10 +14709,10 @@
         <v>1.59</v>
       </c>
       <c r="I263" t="n">
-        <v>1.2793</v>
+        <v>1.2037</v>
       </c>
       <c r="J263" t="n">
-        <v>25.586</v>
+        <v>24.074</v>
       </c>
     </row>
     <row r="264">
@@ -14749,10 +14749,10 @@
         <v>1.55</v>
       </c>
       <c r="I264" t="n">
-        <v>1.1989</v>
+        <v>1.1566</v>
       </c>
       <c r="J264" t="n">
-        <v>23.978</v>
+        <v>23.132</v>
       </c>
     </row>
     <row r="265">
@@ -14789,10 +14789,10 @@
         <v>1.23</v>
       </c>
       <c r="I265" t="n">
-        <v>0.4687</v>
+        <v>0.5814</v>
       </c>
       <c r="J265" t="n">
-        <v>9.374000000000001</v>
+        <v>11.628</v>
       </c>
     </row>
     <row r="266">
@@ -14829,10 +14829,10 @@
         <v>1.21</v>
       </c>
       <c r="I266" t="n">
-        <v>0.4222</v>
+        <v>0.5329</v>
       </c>
       <c r="J266" t="n">
-        <v>8.444000000000001</v>
+        <v>10.658</v>
       </c>
     </row>
     <row r="267">
@@ -14869,10 +14869,10 @@
         <v>0.79</v>
       </c>
       <c r="I267" t="n">
-        <v>-0.2237</v>
+        <v>-0.1955</v>
       </c>
       <c r="J267" t="n">
-        <v>-4.474</v>
+        <v>-3.91</v>
       </c>
     </row>
     <row r="268">
@@ -14909,10 +14909,10 @@
         <v>0.75</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.2863</v>
+        <v>-0.2379</v>
       </c>
       <c r="J268" t="n">
-        <v>-5.726</v>
+        <v>-4.758</v>
       </c>
     </row>
     <row r="269">
@@ -14949,10 +14949,10 @@
         <v>0.63</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.4962</v>
+        <v>-0.3523</v>
       </c>
       <c r="J269" t="n">
-        <v>-9.923999999999999</v>
+        <v>-7.046</v>
       </c>
     </row>
     <row r="270">
@@ -14989,10 +14989,10 @@
         <v>0.57</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.5941</v>
+        <v>-0.407</v>
       </c>
       <c r="J270" t="n">
-        <v>-11.882</v>
+        <v>-8.140000000000001</v>
       </c>
     </row>
     <row r="271">
@@ -15029,10 +15029,10 @@
         <v>0.46</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.7474</v>
+        <v>-0.5102</v>
       </c>
       <c r="J271" t="n">
-        <v>-14.948</v>
+        <v>-10.204</v>
       </c>
     </row>
     <row r="272">
@@ -15069,10 +15069,10 @@
         <v>1.08</v>
       </c>
       <c r="I272" t="n">
-        <v>0.2872</v>
+        <v>0.2972</v>
       </c>
       <c r="J272" t="n">
-        <v>7.18</v>
+        <v>7.43</v>
       </c>
     </row>
     <row r="273">
@@ -15109,10 +15109,10 @@
         <v>0.75</v>
       </c>
       <c r="I273" t="n">
-        <v>-0.3732</v>
+        <v>-0.2586</v>
       </c>
       <c r="J273" t="n">
-        <v>-9.33</v>
+        <v>-6.465</v>
       </c>
     </row>
     <row r="274">
@@ -15149,10 +15149,10 @@
         <v>0.72</v>
       </c>
       <c r="I274" t="n">
-        <v>-0.424</v>
+        <v>-0.2866</v>
       </c>
       <c r="J274" t="n">
-        <v>-10.6</v>
+        <v>-7.165</v>
       </c>
     </row>
     <row r="275">
@@ -15189,10 +15189,10 @@
         <v>0.66</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.5145</v>
+        <v>-0.3431</v>
       </c>
       <c r="J275" t="n">
-        <v>-12.8625</v>
+        <v>-8.577500000000001</v>
       </c>
     </row>
     <row r="276">
@@ -15229,10 +15229,10 @@
         <v>0.61</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.5843</v>
+        <v>-0.39</v>
       </c>
       <c r="J276" t="n">
-        <v>-14.6075</v>
+        <v>-9.75</v>
       </c>
     </row>
     <row r="277">
@@ -15269,10 +15269,10 @@
         <v>1.47</v>
       </c>
       <c r="I277" t="n">
-        <v>1.1516</v>
+        <v>1.0984</v>
       </c>
       <c r="J277" t="n">
-        <v>28.79</v>
+        <v>27.46</v>
       </c>
     </row>
     <row r="278">
@@ -15309,10 +15309,10 @@
         <v>1.42</v>
       </c>
       <c r="I278" t="n">
-        <v>1.0478</v>
+        <v>1.0317</v>
       </c>
       <c r="J278" t="n">
-        <v>26.195</v>
+        <v>25.7925</v>
       </c>
     </row>
     <row r="279">
@@ -15349,10 +15349,10 @@
         <v>1.21</v>
       </c>
       <c r="I279" t="n">
-        <v>0.5326</v>
+        <v>0.5812</v>
       </c>
       <c r="J279" t="n">
-        <v>13.315</v>
+        <v>14.53</v>
       </c>
     </row>
     <row r="280">
@@ -15389,10 +15389,10 @@
         <v>1.12</v>
       </c>
       <c r="I280" t="n">
-        <v>0.2833</v>
+        <v>0.3533</v>
       </c>
       <c r="J280" t="n">
-        <v>7.0825</v>
+        <v>8.8325</v>
       </c>
     </row>
     <row r="281">
@@ -15429,10 +15429,10 @@
         <v>0.88</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.5359</v>
+        <v>-0.4654</v>
       </c>
       <c r="J281" t="n">
-        <v>-13.3975</v>
+        <v>-11.635</v>
       </c>
     </row>
     <row r="282">
@@ -15469,10 +15469,10 @@
         <v>1.42</v>
       </c>
       <c r="I282" t="n">
-        <v>1.0672</v>
+        <v>1.0408</v>
       </c>
       <c r="J282" t="n">
-        <v>43.7552</v>
+        <v>42.6728</v>
       </c>
     </row>
     <row r="283">
@@ -15509,10 +15509,10 @@
         <v>1.24</v>
       </c>
       <c r="I283" t="n">
-        <v>0.6563</v>
+        <v>0.6581</v>
       </c>
       <c r="J283" t="n">
-        <v>26.9083</v>
+        <v>26.9821</v>
       </c>
     </row>
     <row r="284">
@@ -15549,10 +15549,10 @@
         <v>1.24</v>
       </c>
       <c r="I284" t="n">
-        <v>0.6563</v>
+        <v>0.6581</v>
       </c>
       <c r="J284" t="n">
-        <v>26.9083</v>
+        <v>26.9821</v>
       </c>
     </row>
     <row r="285">
@@ -15589,10 +15589,10 @@
         <v>1.22</v>
       </c>
       <c r="I285" t="n">
-        <v>0.6042</v>
+        <v>0.6105</v>
       </c>
       <c r="J285" t="n">
-        <v>24.7722</v>
+        <v>25.0305</v>
       </c>
     </row>
     <row r="286">
@@ -15629,10 +15629,10 @@
         <v>0.79</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.7491</v>
+        <v>-0.6965</v>
       </c>
       <c r="J286" t="n">
-        <v>-30.7131</v>
+        <v>-28.5565</v>
       </c>
     </row>
     <row r="287">
@@ -15669,10 +15669,10 @@
         <v>1.07</v>
       </c>
       <c r="I287" t="n">
-        <v>0.1944</v>
+        <v>0.1962</v>
       </c>
       <c r="J287" t="n">
-        <v>7.9704</v>
+        <v>8.0442</v>
       </c>
     </row>
     <row r="288">
@@ -15709,10 +15709,10 @@
         <v>1.02</v>
       </c>
       <c r="I288" t="n">
-        <v>0.092</v>
+        <v>0.076</v>
       </c>
       <c r="J288" t="n">
-        <v>3.772</v>
+        <v>3.116</v>
       </c>
     </row>
     <row r="289">
@@ -15749,10 +15749,10 @@
         <v>1</v>
       </c>
       <c r="I289" t="n">
-        <v>0.0309</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="J289" t="n">
-        <v>1.2669</v>
+        <v>0.3362</v>
       </c>
     </row>
     <row r="290">
@@ -15789,10 +15789,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.131</v>
+        <v>-0.0835</v>
       </c>
       <c r="J290" t="n">
-        <v>-5.371</v>
+        <v>-3.4235</v>
       </c>
     </row>
     <row r="291">
@@ -15829,10 +15829,10 @@
         <v>0.72</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.4837</v>
+        <v>-0.3113</v>
       </c>
       <c r="J291" t="n">
-        <v>-19.8317</v>
+        <v>-12.7633</v>
       </c>
     </row>
     <row r="292">
@@ -15869,10 +15869,10 @@
         <v>0.77</v>
       </c>
       <c r="I292" t="n">
-        <v>-0.2767</v>
+        <v>-0.2268</v>
       </c>
       <c r="J292" t="n">
-        <v>-5.8107</v>
+        <v>-4.7628</v>
       </c>
     </row>
     <row r="293">
@@ -15909,10 +15909,10 @@
         <v>0.73</v>
       </c>
       <c r="I293" t="n">
-        <v>-0.341</v>
+        <v>-0.2668</v>
       </c>
       <c r="J293" t="n">
-        <v>-7.161</v>
+        <v>-5.6028</v>
       </c>
     </row>
     <row r="294">
@@ -15949,10 +15949,10 @@
         <v>0.72</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.3575</v>
+        <v>-0.2764</v>
       </c>
       <c r="J294" t="n">
-        <v>-7.5075</v>
+        <v>-5.8044</v>
       </c>
     </row>
     <row r="295">
@@ -15989,10 +15989,10 @@
         <v>0.67</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.4554</v>
+        <v>-0.3217</v>
       </c>
       <c r="J295" t="n">
-        <v>-9.5634</v>
+        <v>-6.7557</v>
       </c>
     </row>
     <row r="296">
@@ -16029,10 +16029,10 @@
         <v>0.51</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.6932</v>
+        <v>-0.4701</v>
       </c>
       <c r="J296" t="n">
-        <v>-14.5572</v>
+        <v>-9.8721</v>
       </c>
     </row>
     <row r="297">
@@ -16069,10 +16069,10 @@
         <v>2.36</v>
       </c>
       <c r="I297" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J297" t="n">
-        <v>43.2453</v>
+        <v>38.5098</v>
       </c>
     </row>
     <row r="298">
@@ -16109,10 +16109,10 @@
         <v>1.68</v>
       </c>
       <c r="I298" t="n">
-        <v>1.4406</v>
+        <v>1.3047</v>
       </c>
       <c r="J298" t="n">
-        <v>30.2526</v>
+        <v>27.3987</v>
       </c>
     </row>
     <row r="299">
@@ -16149,10 +16149,10 @@
         <v>1.61</v>
       </c>
       <c r="I299" t="n">
-        <v>1.3064</v>
+        <v>1.2236</v>
       </c>
       <c r="J299" t="n">
-        <v>27.4344</v>
+        <v>25.6956</v>
       </c>
     </row>
     <row r="300">
@@ -16189,10 +16189,10 @@
         <v>0.96</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.3663</v>
+        <v>-0.2791</v>
       </c>
       <c r="J300" t="n">
-        <v>-7.6923</v>
+        <v>-5.8611</v>
       </c>
     </row>
     <row r="301">
@@ -16229,10 +16229,10 @@
         <v>0.8</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.7829</v>
+        <v>-0.7317</v>
       </c>
       <c r="J301" t="n">
-        <v>-16.4409</v>
+        <v>-15.3657</v>
       </c>
     </row>
     <row r="302">
@@ -16269,10 +16269,10 @@
         <v>0.93</v>
       </c>
       <c r="I302" t="n">
-        <v>0.0242</v>
+        <v>-0.0169</v>
       </c>
       <c r="J302" t="n">
-        <v>0.4598</v>
+        <v>-0.3211</v>
       </c>
     </row>
     <row r="303">
@@ -16309,10 +16309,10 @@
         <v>0.71</v>
       </c>
       <c r="I303" t="n">
-        <v>-0.3327</v>
+        <v>-0.2717</v>
       </c>
       <c r="J303" t="n">
-        <v>-6.3213</v>
+        <v>-5.1623</v>
       </c>
     </row>
     <row r="304">
@@ -16349,10 +16349,10 @@
         <v>0.61</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.5072</v>
+        <v>-0.3665</v>
       </c>
       <c r="J304" t="n">
-        <v>-9.636799999999999</v>
+        <v>-6.9635</v>
       </c>
     </row>
     <row r="305">
@@ -16389,10 +16389,10 @@
         <v>0.54</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.6254</v>
+        <v>-0.4298</v>
       </c>
       <c r="J305" t="n">
-        <v>-11.8826</v>
+        <v>-8.1662</v>
       </c>
     </row>
     <row r="306">
@@ -16429,10 +16429,10 @@
         <v>0.27</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.9792</v>
+        <v>-0.6866</v>
       </c>
       <c r="J306" t="n">
-        <v>-18.6048</v>
+        <v>-13.0454</v>
       </c>
     </row>
     <row r="307">
@@ -16469,10 +16469,10 @@
         <v>2.09</v>
       </c>
       <c r="I307" t="n">
-        <v>2.0305</v>
+        <v>1.7468</v>
       </c>
       <c r="J307" t="n">
-        <v>38.5795</v>
+        <v>33.1892</v>
       </c>
     </row>
     <row r="308">
@@ -16509,10 +16509,10 @@
         <v>1.96</v>
       </c>
       <c r="I308" t="n">
-        <v>1.8938</v>
+        <v>1.605</v>
       </c>
       <c r="J308" t="n">
-        <v>35.9822</v>
+        <v>30.495</v>
       </c>
     </row>
     <row r="309">
@@ -16549,10 +16549,10 @@
         <v>1.47</v>
       </c>
       <c r="I309" t="n">
-        <v>0.9477</v>
+        <v>1.0525</v>
       </c>
       <c r="J309" t="n">
-        <v>18.0063</v>
+        <v>19.9975</v>
       </c>
     </row>
     <row r="310">
@@ -16589,10 +16589,10 @@
         <v>1.22</v>
       </c>
       <c r="I310" t="n">
-        <v>0.4149</v>
+        <v>0.5349</v>
       </c>
       <c r="J310" t="n">
-        <v>7.8831</v>
+        <v>10.1631</v>
       </c>
     </row>
     <row r="311">
@@ -16629,10 +16629,10 @@
         <v>1.1</v>
       </c>
       <c r="I311" t="n">
-        <v>0.1236</v>
+        <v>0.2229</v>
       </c>
       <c r="J311" t="n">
-        <v>2.3484</v>
+        <v>4.2351</v>
       </c>
     </row>
     <row r="312">
@@ -16669,10 +16669,10 @@
         <v>1.28</v>
       </c>
       <c r="I312" t="n">
-        <v>0.476</v>
+        <v>0.5638</v>
       </c>
       <c r="J312" t="n">
-        <v>13.804</v>
+        <v>16.3502</v>
       </c>
     </row>
     <row r="313">
@@ -16709,10 +16709,10 @@
         <v>1.26</v>
       </c>
       <c r="I313" t="n">
-        <v>0.4491</v>
+        <v>0.5291</v>
       </c>
       <c r="J313" t="n">
-        <v>13.0239</v>
+        <v>15.3439</v>
       </c>
     </row>
     <row r="314">
@@ -16749,10 +16749,10 @@
         <v>1.22</v>
       </c>
       <c r="I314" t="n">
-        <v>0.3936</v>
+        <v>0.4588</v>
       </c>
       <c r="J314" t="n">
-        <v>11.4144</v>
+        <v>13.3052</v>
       </c>
     </row>
     <row r="315">
@@ -16789,10 +16789,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.1732</v>
+        <v>-0.09379999999999999</v>
       </c>
       <c r="J315" t="n">
-        <v>-5.0228</v>
+        <v>-2.7202</v>
       </c>
     </row>
     <row r="316">
@@ -16829,10 +16829,10 @@
         <v>0.57</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.6887</v>
+        <v>-0.4617</v>
       </c>
       <c r="J316" t="n">
-        <v>-19.9723</v>
+        <v>-13.3893</v>
       </c>
     </row>
     <row r="317">
@@ -16869,10 +16869,10 @@
         <v>1.67</v>
       </c>
       <c r="I317" t="n">
-        <v>1.6004</v>
+        <v>1.3906</v>
       </c>
       <c r="J317" t="n">
-        <v>46.4116</v>
+        <v>40.3274</v>
       </c>
     </row>
     <row r="318">
@@ -16909,10 +16909,10 @@
         <v>1.02</v>
       </c>
       <c r="I318" t="n">
-        <v>0.0248</v>
+        <v>0.0731</v>
       </c>
       <c r="J318" t="n">
-        <v>0.7192</v>
+        <v>2.1199</v>
       </c>
     </row>
     <row r="319">
@@ -16949,10 +16949,10 @@
         <v>0.99</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.1385</v>
+        <v>-0.0772</v>
       </c>
       <c r="J319" t="n">
-        <v>-4.0165</v>
+        <v>-2.2388</v>
       </c>
     </row>
     <row r="320">
@@ -16989,10 +16989,10 @@
         <v>0.98</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.1815</v>
+        <v>-0.1182</v>
       </c>
       <c r="J320" t="n">
-        <v>-5.2635</v>
+        <v>-3.4278</v>
       </c>
     </row>
     <row r="321">
@@ -17029,10 +17029,10 @@
         <v>0.83</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.6279</v>
+        <v>-0.5704</v>
       </c>
       <c r="J321" t="n">
-        <v>-18.2091</v>
+        <v>-16.5416</v>
       </c>
     </row>
     <row r="322">
@@ -17069,10 +17069,10 @@
         <v>1.66</v>
       </c>
       <c r="I322" t="n">
-        <v>1.4081</v>
+        <v>1.2834</v>
       </c>
       <c r="J322" t="n">
-        <v>26.7539</v>
+        <v>24.3846</v>
       </c>
     </row>
     <row r="323">
@@ -17109,10 +17109,10 @@
         <v>1.65</v>
       </c>
       <c r="I323" t="n">
-        <v>1.3892</v>
+        <v>1.2718</v>
       </c>
       <c r="J323" t="n">
-        <v>26.3948</v>
+        <v>24.1642</v>
       </c>
     </row>
     <row r="324">
@@ -17149,10 +17149,10 @@
         <v>1.42</v>
       </c>
       <c r="I324" t="n">
-        <v>0.8866000000000001</v>
+        <v>0.9922</v>
       </c>
       <c r="J324" t="n">
-        <v>16.8454</v>
+        <v>18.8518</v>
       </c>
     </row>
     <row r="325">
@@ -17189,10 +17189,10 @@
         <v>1.35</v>
       </c>
       <c r="I325" t="n">
-        <v>0.7323</v>
+        <v>0.8536</v>
       </c>
       <c r="J325" t="n">
-        <v>13.9137</v>
+        <v>16.2184</v>
       </c>
     </row>
     <row r="326">
@@ -17229,10 +17229,10 @@
         <v>1.27</v>
       </c>
       <c r="I326" t="n">
-        <v>0.5553</v>
+        <v>0.6731</v>
       </c>
       <c r="J326" t="n">
-        <v>10.5507</v>
+        <v>12.7889</v>
       </c>
     </row>
     <row r="327">
@@ -17269,10 +17269,10 @@
         <v>1.01</v>
       </c>
       <c r="I327" t="n">
-        <v>0.2187</v>
+        <v>0.2208</v>
       </c>
       <c r="J327" t="n">
-        <v>4.1553</v>
+        <v>4.1952</v>
       </c>
     </row>
     <row r="328">
@@ -17309,10 +17309,10 @@
         <v>0.72</v>
       </c>
       <c r="I328" t="n">
-        <v>-0.3183</v>
+        <v>-0.262</v>
       </c>
       <c r="J328" t="n">
-        <v>-6.0477</v>
+        <v>-4.978</v>
       </c>
     </row>
     <row r="329">
@@ -17349,10 +17349,10 @@
         <v>0.54</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.6264</v>
+        <v>-0.4302</v>
       </c>
       <c r="J329" t="n">
-        <v>-11.9016</v>
+        <v>-8.1738</v>
       </c>
     </row>
     <row r="330">
@@ -17389,10 +17389,10 @@
         <v>0.46</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.7393</v>
+        <v>-0.5054</v>
       </c>
       <c r="J330" t="n">
-        <v>-14.0467</v>
+        <v>-9.602600000000001</v>
       </c>
     </row>
     <row r="331">
@@ -17429,10 +17429,10 @@
         <v>0.34</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.8942</v>
+        <v>-0.6198</v>
       </c>
       <c r="J331" t="n">
-        <v>-16.9898</v>
+        <v>-11.7762</v>
       </c>
     </row>
     <row r="332">
@@ -17469,10 +17469,10 @@
         <v>1.37</v>
       </c>
       <c r="I332" t="n">
-        <v>0.5775</v>
+        <v>0.701</v>
       </c>
       <c r="J332" t="n">
-        <v>34.0725</v>
+        <v>41.359</v>
       </c>
     </row>
     <row r="333">
@@ -17509,10 +17509,10 @@
         <v>1.22</v>
       </c>
       <c r="I333" t="n">
-        <v>0.3785</v>
+        <v>0.4475</v>
       </c>
       <c r="J333" t="n">
-        <v>22.3315</v>
+        <v>26.4025</v>
       </c>
     </row>
     <row r="334">
@@ -17549,10 +17549,10 @@
         <v>1.07</v>
       </c>
       <c r="I334" t="n">
-        <v>0.118</v>
+        <v>0.1686</v>
       </c>
       <c r="J334" t="n">
-        <v>6.962</v>
+        <v>9.9474</v>
       </c>
     </row>
     <row r="335">
@@ -17589,10 +17589,10 @@
         <v>0.92</v>
       </c>
       <c r="I335" t="n">
-        <v>-0.2204</v>
+        <v>-0.1222</v>
       </c>
       <c r="J335" t="n">
-        <v>-13.0036</v>
+        <v>-7.2098</v>
       </c>
     </row>
     <row r="336">
@@ -17629,10 +17629,10 @@
         <v>0.91</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.2373</v>
+        <v>-0.1337</v>
       </c>
       <c r="J336" t="n">
-        <v>-14.0007</v>
+        <v>-7.8883</v>
       </c>
     </row>
     <row r="337">
@@ -17669,10 +17669,10 @@
         <v>1.32</v>
       </c>
       <c r="I337" t="n">
-        <v>0.9238</v>
+        <v>0.8986</v>
       </c>
       <c r="J337" t="n">
-        <v>54.5042</v>
+        <v>53.0174</v>
       </c>
     </row>
     <row r="338">
@@ -17709,10 +17709,10 @@
         <v>1.15</v>
       </c>
       <c r="I338" t="n">
-        <v>0.5084</v>
+        <v>0.4714</v>
       </c>
       <c r="J338" t="n">
-        <v>29.9956</v>
+        <v>27.8126</v>
       </c>
     </row>
     <row r="339">
@@ -17749,10 +17749,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I339" t="n">
-        <v>-0.2972</v>
+        <v>-0.2416</v>
       </c>
       <c r="J339" t="n">
-        <v>-17.5348</v>
+        <v>-14.2544</v>
       </c>
     </row>
     <row r="340">
@@ -17789,10 +17789,10 @@
         <v>0.91</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.3903</v>
+        <v>-0.3329</v>
       </c>
       <c r="J340" t="n">
-        <v>-23.0277</v>
+        <v>-19.6411</v>
       </c>
     </row>
     <row r="341">
@@ -17829,10 +17829,10 @@
         <v>0.91</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.3903</v>
+        <v>-0.3329</v>
       </c>
       <c r="J341" t="n">
-        <v>-23.0277</v>
+        <v>-19.6411</v>
       </c>
     </row>
     <row r="342">
@@ -17869,10 +17869,10 @@
         <v>2</v>
       </c>
       <c r="I342" t="n">
-        <v>1.9507</v>
+        <v>1.6536</v>
       </c>
       <c r="J342" t="n">
-        <v>33.1619</v>
+        <v>28.1112</v>
       </c>
     </row>
     <row r="343">
@@ -17909,10 +17909,10 @@
         <v>1.67</v>
       </c>
       <c r="I343" t="n">
-        <v>1.3942</v>
+        <v>1.2846</v>
       </c>
       <c r="J343" t="n">
-        <v>23.7014</v>
+        <v>21.8382</v>
       </c>
     </row>
     <row r="344">
@@ -17949,10 +17949,10 @@
         <v>1.53</v>
       </c>
       <c r="I344" t="n">
-        <v>1.0898</v>
+        <v>1.1257</v>
       </c>
       <c r="J344" t="n">
-        <v>18.5266</v>
+        <v>19.1369</v>
       </c>
     </row>
     <row r="345">
@@ -17989,10 +17989,10 @@
         <v>1.39</v>
       </c>
       <c r="I345" t="n">
-        <v>0.79</v>
+        <v>0.9252</v>
       </c>
       <c r="J345" t="n">
-        <v>13.43</v>
+        <v>15.7284</v>
       </c>
     </row>
     <row r="346">
@@ -18029,10 +18029,10 @@
         <v>1.13</v>
       </c>
       <c r="I346" t="n">
-        <v>0.2062</v>
+        <v>0.3102</v>
       </c>
       <c r="J346" t="n">
-        <v>3.5054</v>
+        <v>5.2734</v>
       </c>
     </row>
     <row r="347">
@@ -18069,10 +18069,10 @@
         <v>1.1</v>
       </c>
       <c r="I347" t="n">
-        <v>0.3838</v>
+        <v>0.4428</v>
       </c>
       <c r="J347" t="n">
-        <v>6.5246</v>
+        <v>7.5276</v>
       </c>
     </row>
     <row r="348">
@@ -18109,10 +18109,10 @@
         <v>0.75</v>
       </c>
       <c r="I348" t="n">
-        <v>-0.2841</v>
+        <v>-0.2369</v>
       </c>
       <c r="J348" t="n">
-        <v>-4.8297</v>
+        <v>-4.0273</v>
       </c>
     </row>
     <row r="349">
@@ -18149,10 +18149,10 @@
         <v>0.66</v>
       </c>
       <c r="I349" t="n">
-        <v>-0.4289</v>
+        <v>-0.3256</v>
       </c>
       <c r="J349" t="n">
-        <v>-7.2913</v>
+        <v>-5.5352</v>
       </c>
     </row>
     <row r="350">
@@ -18189,10 +18189,10 @@
         <v>0.44</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.7725</v>
+        <v>-0.5284</v>
       </c>
       <c r="J350" t="n">
-        <v>-13.1325</v>
+        <v>-8.982799999999999</v>
       </c>
     </row>
     <row r="351">
@@ -18229,10 +18229,10 @@
         <v>0.23</v>
       </c>
       <c r="I351" t="n">
-        <v>-1.0297</v>
+        <v>-0.7278</v>
       </c>
       <c r="J351" t="n">
-        <v>-17.5049</v>
+        <v>-12.3726</v>
       </c>
     </row>
     <row r="352">
@@ -18269,10 +18269,10 @@
         <v>1.35</v>
       </c>
       <c r="I352" t="n">
-        <v>0.8988</v>
+        <v>0.903</v>
       </c>
       <c r="J352" t="n">
-        <v>22.47</v>
+        <v>22.575</v>
       </c>
     </row>
     <row r="353">
@@ -18309,10 +18309,10 @@
         <v>1.35</v>
       </c>
       <c r="I353" t="n">
-        <v>0.8988</v>
+        <v>0.903</v>
       </c>
       <c r="J353" t="n">
-        <v>22.47</v>
+        <v>22.575</v>
       </c>
     </row>
     <row r="354">
@@ -18349,10 +18349,10 @@
         <v>1.27</v>
       </c>
       <c r="I354" t="n">
-        <v>0.7108</v>
+        <v>0.7208</v>
       </c>
       <c r="J354" t="n">
-        <v>17.77</v>
+        <v>18.02</v>
       </c>
     </row>
     <row r="355">
@@ -18389,10 +18389,10 @@
         <v>1.13</v>
       </c>
       <c r="I355" t="n">
-        <v>0.3142</v>
+        <v>0.3816</v>
       </c>
       <c r="J355" t="n">
-        <v>7.855</v>
+        <v>9.539999999999999</v>
       </c>
     </row>
     <row r="356">
@@ -18429,10 +18429,10 @@
         <v>0.97</v>
       </c>
       <c r="I356" t="n">
-        <v>-0.2657</v>
+        <v>-0.1855</v>
       </c>
       <c r="J356" t="n">
-        <v>-6.6425</v>
+        <v>-4.6375</v>
       </c>
     </row>
     <row r="357">
@@ -18469,10 +18469,10 @@
         <v>0.9</v>
       </c>
       <c r="I357" t="n">
-        <v>-0.1344</v>
+        <v>-0.116</v>
       </c>
       <c r="J357" t="n">
-        <v>-3.36</v>
+        <v>-2.9</v>
       </c>
     </row>
     <row r="358">
@@ -18509,10 +18509,10 @@
         <v>0.88</v>
       </c>
       <c r="I358" t="n">
-        <v>-0.1703</v>
+        <v>-0.1381</v>
       </c>
       <c r="J358" t="n">
-        <v>-4.2575</v>
+        <v>-3.4525</v>
       </c>
     </row>
     <row r="359">
@@ -18549,10 +18549,10 @@
         <v>0.82</v>
       </c>
       <c r="I359" t="n">
-        <v>-0.2886</v>
+        <v>-0.1988</v>
       </c>
       <c r="J359" t="n">
-        <v>-7.215</v>
+        <v>-4.97</v>
       </c>
     </row>
     <row r="360">
@@ -18589,10 +18589,10 @@
         <v>0.79</v>
       </c>
       <c r="I360" t="n">
-        <v>-0.3423</v>
+        <v>-0.2279</v>
       </c>
       <c r="J360" t="n">
-        <v>-8.557499999999999</v>
+        <v>-5.6975</v>
       </c>
     </row>
     <row r="361">
@@ -18629,10 +18629,10 @@
         <v>0.75</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.4058</v>
+        <v>-0.2666</v>
       </c>
       <c r="J361" t="n">
-        <v>-10.145</v>
+        <v>-6.665</v>
       </c>
     </row>
     <row r="362">
@@ -18669,10 +18669,10 @@
         <v>1.57</v>
       </c>
       <c r="I362" t="n">
-        <v>1.3568</v>
+        <v>1.2288</v>
       </c>
       <c r="J362" t="n">
-        <v>35.2768</v>
+        <v>31.9488</v>
       </c>
     </row>
     <row r="363">
@@ -18709,10 +18709,10 @@
         <v>1.52</v>
       </c>
       <c r="I363" t="n">
-        <v>1.2591</v>
+        <v>1.1655</v>
       </c>
       <c r="J363" t="n">
-        <v>32.7366</v>
+        <v>30.303</v>
       </c>
     </row>
     <row r="364">
@@ -18749,10 +18749,10 @@
         <v>1.31</v>
       </c>
       <c r="I364" t="n">
-        <v>0.8119</v>
+        <v>0.8148</v>
       </c>
       <c r="J364" t="n">
-        <v>21.1094</v>
+        <v>21.1848</v>
       </c>
     </row>
     <row r="365">
@@ -18789,10 +18789,10 @@
         <v>0.84</v>
       </c>
       <c r="I365" t="n">
-        <v>-0.6345</v>
+        <v>-0.5715</v>
       </c>
       <c r="J365" t="n">
-        <v>-16.497</v>
+        <v>-14.859</v>
       </c>
     </row>
     <row r="366">
@@ -18829,10 +18829,10 @@
         <v>0.79</v>
       </c>
       <c r="I366" t="n">
-        <v>-0.7549</v>
+        <v>-0.7022</v>
       </c>
       <c r="J366" t="n">
-        <v>-19.6274</v>
+        <v>-18.2572</v>
       </c>
     </row>
     <row r="367">
@@ -18869,10 +18869,10 @@
         <v>1.07</v>
       </c>
       <c r="I367" t="n">
-        <v>0.1936</v>
+        <v>0.1957</v>
       </c>
       <c r="J367" t="n">
-        <v>5.0336</v>
+        <v>5.0882</v>
       </c>
     </row>
     <row r="368">
@@ -18909,10 +18909,10 @@
         <v>1.05</v>
       </c>
       <c r="I368" t="n">
-        <v>0.1557</v>
+        <v>0.1505</v>
       </c>
       <c r="J368" t="n">
-        <v>4.0482</v>
+        <v>3.913</v>
       </c>
     </row>
     <row r="369">
@@ -18949,10 +18949,10 @@
         <v>0.9</v>
       </c>
       <c r="I369" t="n">
-        <v>-0.2106</v>
+        <v>-0.129</v>
       </c>
       <c r="J369" t="n">
-        <v>-5.4756</v>
+        <v>-3.354</v>
       </c>
     </row>
     <row r="370">
@@ -18989,10 +18989,10 @@
         <v>0.89</v>
       </c>
       <c r="I370" t="n">
-        <v>-0.2283</v>
+        <v>-0.1399</v>
       </c>
       <c r="J370" t="n">
-        <v>-5.9358</v>
+        <v>-3.6374</v>
       </c>
     </row>
     <row r="371">
@@ -19029,10 +19029,10 @@
         <v>0.85</v>
       </c>
       <c r="I371" t="n">
-        <v>-0.2949</v>
+        <v>-0.1824</v>
       </c>
       <c r="J371" t="n">
-        <v>-7.6674</v>
+        <v>-4.7424</v>
       </c>
     </row>
     <row r="372">
@@ -19069,10 +19069,10 @@
         <v>0.95</v>
       </c>
       <c r="I372" t="n">
-        <v>-0.0621</v>
+        <v>-0.06370000000000001</v>
       </c>
       <c r="J372" t="n">
-        <v>-1.4904</v>
+        <v>-1.5288</v>
       </c>
     </row>
     <row r="373">
@@ -19109,10 +19109,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I373" t="n">
-        <v>-0.08210000000000001</v>
+        <v>-0.0761</v>
       </c>
       <c r="J373" t="n">
-        <v>-1.9704</v>
+        <v>-1.8264</v>
       </c>
     </row>
     <row r="374">
@@ -19149,10 +19149,10 @@
         <v>0.92</v>
       </c>
       <c r="I374" t="n">
-        <v>-0.121</v>
+        <v>-0.0999</v>
       </c>
       <c r="J374" t="n">
-        <v>-2.904</v>
+        <v>-2.3976</v>
       </c>
     </row>
     <row r="375">
@@ -19189,10 +19189,10 @@
         <v>0.9</v>
       </c>
       <c r="I375" t="n">
-        <v>-0.1595</v>
+        <v>-0.1223</v>
       </c>
       <c r="J375" t="n">
-        <v>-3.828</v>
+        <v>-2.9352</v>
       </c>
     </row>
     <row r="376">
@@ -19229,10 +19229,10 @@
         <v>0.67</v>
       </c>
       <c r="I376" t="n">
-        <v>-0.5338000000000001</v>
+        <v>-0.3495</v>
       </c>
       <c r="J376" t="n">
-        <v>-12.8112</v>
+        <v>-8.388</v>
       </c>
     </row>
     <row r="377">
@@ -19269,10 +19269,10 @@
         <v>1.74</v>
       </c>
       <c r="I377" t="n">
-        <v>1.6411</v>
+        <v>1.4195</v>
       </c>
       <c r="J377" t="n">
-        <v>39.3864</v>
+        <v>34.068</v>
       </c>
     </row>
     <row r="378">
@@ -19309,10 +19309,10 @@
         <v>1.36</v>
       </c>
       <c r="I378" t="n">
-        <v>0.8879</v>
+        <v>0.9088000000000001</v>
       </c>
       <c r="J378" t="n">
-        <v>21.3096</v>
+        <v>21.8112</v>
       </c>
     </row>
     <row r="379">
@@ -19349,10 +19349,10 @@
         <v>1.26</v>
       </c>
       <c r="I379" t="n">
-        <v>0.6257</v>
+        <v>0.6883</v>
       </c>
       <c r="J379" t="n">
-        <v>15.0168</v>
+        <v>16.5192</v>
       </c>
     </row>
     <row r="380">
@@ -19389,10 +19389,10 @@
         <v>1.24</v>
       </c>
       <c r="I380" t="n">
-        <v>0.5721000000000001</v>
+        <v>0.6424</v>
       </c>
       <c r="J380" t="n">
-        <v>13.7304</v>
+        <v>15.4176</v>
       </c>
     </row>
     <row r="381">
@@ -19429,10 +19429,10 @@
         <v>0.77</v>
       </c>
       <c r="I381" t="n">
-        <v>-0.8156</v>
+        <v>-0.7681</v>
       </c>
       <c r="J381" t="n">
-        <v>-19.5744</v>
+        <v>-18.4344</v>
       </c>
     </row>
     <row r="382">
@@ -19469,10 +19469,10 @@
         <v>1.66</v>
       </c>
       <c r="I382" t="n">
-        <v>1.409</v>
+        <v>1.2838</v>
       </c>
       <c r="J382" t="n">
-        <v>29.589</v>
+        <v>26.9598</v>
       </c>
     </row>
     <row r="383">
@@ -19509,10 +19509,10 @@
         <v>1.62</v>
       </c>
       <c r="I383" t="n">
-        <v>1.3324</v>
+        <v>1.2372</v>
       </c>
       <c r="J383" t="n">
-        <v>27.9804</v>
+        <v>25.9812</v>
       </c>
     </row>
     <row r="384">
@@ -19549,10 +19549,10 @@
         <v>1.48</v>
       </c>
       <c r="I384" t="n">
-        <v>1.0389</v>
+        <v>1.073</v>
       </c>
       <c r="J384" t="n">
-        <v>21.8169</v>
+        <v>22.533</v>
       </c>
     </row>
     <row r="385">
@@ -19589,10 +19589,10 @@
         <v>1.43</v>
       </c>
       <c r="I385" t="n">
-        <v>0.9103</v>
+        <v>1.0082</v>
       </c>
       <c r="J385" t="n">
-        <v>19.1163</v>
+        <v>21.1722</v>
       </c>
     </row>
     <row r="386">
@@ -19629,10 +19629,10 @@
         <v>1.15</v>
       </c>
       <c r="I386" t="n">
-        <v>0.2745</v>
+        <v>0.3785</v>
       </c>
       <c r="J386" t="n">
-        <v>5.7645</v>
+        <v>7.9485</v>
       </c>
     </row>
     <row r="387">
@@ -19669,10 +19669,10 @@
         <v>1.18</v>
       </c>
       <c r="I387" t="n">
-        <v>0.5038</v>
+        <v>0.6145</v>
       </c>
       <c r="J387" t="n">
-        <v>10.5798</v>
+        <v>12.9045</v>
       </c>
     </row>
     <row r="388">
@@ -19709,10 +19709,10 @@
         <v>0.63</v>
       </c>
       <c r="I388" t="n">
-        <v>-0.5013</v>
+        <v>-0.3531</v>
       </c>
       <c r="J388" t="n">
-        <v>-10.5273</v>
+        <v>-7.4151</v>
       </c>
     </row>
     <row r="389">
@@ -19749,10 +19749,10 @@
         <v>0.53</v>
       </c>
       <c r="I389" t="n">
-        <v>-0.6544</v>
+        <v>-0.4454</v>
       </c>
       <c r="J389" t="n">
-        <v>-13.7424</v>
+        <v>-9.353400000000001</v>
       </c>
     </row>
     <row r="390">
@@ -19789,10 +19789,10 @@
         <v>0.45</v>
       </c>
       <c r="I390" t="n">
-        <v>-0.7623</v>
+        <v>-0.5207000000000001</v>
       </c>
       <c r="J390" t="n">
-        <v>-16.0083</v>
+        <v>-10.9347</v>
       </c>
     </row>
     <row r="391">
@@ -19829,10 +19829,10 @@
         <v>0.44</v>
       </c>
       <c r="I391" t="n">
-        <v>-0.7752</v>
+        <v>-0.5301</v>
       </c>
       <c r="J391" t="n">
-        <v>-16.2792</v>
+        <v>-11.1321</v>
       </c>
     </row>
     <row r="392">
@@ -19869,10 +19869,10 @@
         <v>1.26</v>
       </c>
       <c r="I392" t="n">
-        <v>0.4946</v>
+        <v>0.5786</v>
       </c>
       <c r="J392" t="n">
-        <v>13.3542</v>
+        <v>15.6222</v>
       </c>
     </row>
     <row r="393">
@@ -19909,10 +19909,10 @@
         <v>1.04</v>
       </c>
       <c r="I393" t="n">
-        <v>0.1477</v>
+        <v>0.135</v>
       </c>
       <c r="J393" t="n">
-        <v>3.9879</v>
+        <v>3.645</v>
       </c>
     </row>
     <row r="394">
@@ -19949,10 +19949,10 @@
         <v>0.93</v>
       </c>
       <c r="I394" t="n">
-        <v>-0.1279</v>
+        <v>-0.09320000000000001</v>
       </c>
       <c r="J394" t="n">
-        <v>-3.4533</v>
+        <v>-2.5164</v>
       </c>
     </row>
     <row r="395">
@@ -19989,10 +19989,10 @@
         <v>0.86</v>
       </c>
       <c r="I395" t="n">
-        <v>-0.2678</v>
+        <v>-0.1685</v>
       </c>
       <c r="J395" t="n">
-        <v>-7.2306</v>
+        <v>-4.5495</v>
       </c>
     </row>
     <row r="396">
@@ -20029,10 +20029,10 @@
         <v>0.52</v>
       </c>
       <c r="I396" t="n">
-        <v>-0.7306</v>
+        <v>-0.4937</v>
       </c>
       <c r="J396" t="n">
-        <v>-19.7262</v>
+        <v>-13.3299</v>
       </c>
     </row>
     <row r="397">
@@ -20069,10 +20069,10 @@
         <v>1.44</v>
       </c>
       <c r="I397" t="n">
-        <v>1.1141</v>
+        <v>1.0706</v>
       </c>
       <c r="J397" t="n">
-        <v>30.0807</v>
+        <v>28.9062</v>
       </c>
     </row>
     <row r="398">
@@ -20109,10 +20109,10 @@
         <v>1.38</v>
       </c>
       <c r="I398" t="n">
-        <v>0.9871</v>
+        <v>0.9778</v>
       </c>
       <c r="J398" t="n">
-        <v>26.6517</v>
+        <v>26.4006</v>
       </c>
     </row>
     <row r="399">
@@ -20149,10 +20149,10 @@
         <v>1.05</v>
       </c>
       <c r="I399" t="n">
-        <v>0.0958</v>
+        <v>0.1592</v>
       </c>
       <c r="J399" t="n">
-        <v>2.5866</v>
+        <v>4.2984</v>
       </c>
     </row>
     <row r="400">
@@ -20189,10 +20189,10 @@
         <v>1.04</v>
       </c>
       <c r="I400" t="n">
-        <v>0.062</v>
+        <v>0.1262</v>
       </c>
       <c r="J400" t="n">
-        <v>1.674</v>
+        <v>3.4074</v>
       </c>
     </row>
     <row r="401">
@@ -20229,10 +20229,10 @@
         <v>0.95</v>
       </c>
       <c r="I401" t="n">
-        <v>-0.3189</v>
+        <v>-0.2433</v>
       </c>
       <c r="J401" t="n">
-        <v>-8.610300000000001</v>
+        <v>-6.5691</v>
       </c>
     </row>
     <row r="402">
@@ -20269,10 +20269,10 @@
         <v>1.25</v>
       </c>
       <c r="I402" t="n">
-        <v>0.7484</v>
+        <v>0.718</v>
       </c>
       <c r="J402" t="n">
-        <v>21.7036</v>
+        <v>20.822</v>
       </c>
     </row>
     <row r="403">
@@ -20309,10 +20309,10 @@
         <v>1.19</v>
       </c>
       <c r="I403" t="n">
-        <v>0.5995</v>
+        <v>0.5676</v>
       </c>
       <c r="J403" t="n">
-        <v>17.3855</v>
+        <v>16.4604</v>
       </c>
     </row>
     <row r="404">
@@ -20349,10 +20349,10 @@
         <v>1.11</v>
       </c>
       <c r="I404" t="n">
-        <v>0.3766</v>
+        <v>0.3561</v>
       </c>
       <c r="J404" t="n">
-        <v>10.9214</v>
+        <v>10.3269</v>
       </c>
     </row>
     <row r="405">
@@ -20389,10 +20389,10 @@
         <v>0.98</v>
       </c>
       <c r="I405" t="n">
-        <v>-0.167</v>
+        <v>-0.1108</v>
       </c>
       <c r="J405" t="n">
-        <v>-4.843</v>
+        <v>-3.2132</v>
       </c>
     </row>
     <row r="406">
@@ -20429,10 +20429,10 @@
         <v>0.82</v>
       </c>
       <c r="I406" t="n">
-        <v>-0.6435999999999999</v>
+        <v>-0.5891999999999999</v>
       </c>
       <c r="J406" t="n">
-        <v>-18.6644</v>
+        <v>-17.0868</v>
       </c>
     </row>
     <row r="407">
@@ -20469,10 +20469,10 @@
         <v>1.33</v>
       </c>
       <c r="I407" t="n">
-        <v>0.5503</v>
+        <v>0.659</v>
       </c>
       <c r="J407" t="n">
-        <v>15.9587</v>
+        <v>19.111</v>
       </c>
     </row>
     <row r="408">
@@ -20509,10 +20509,10 @@
         <v>1.23</v>
       </c>
       <c r="I408" t="n">
-        <v>0.4172</v>
+        <v>0.4848</v>
       </c>
       <c r="J408" t="n">
-        <v>12.0988</v>
+        <v>14.0592</v>
       </c>
     </row>
     <row r="409">
@@ -20549,10 +20549,10 @@
         <v>1.05</v>
       </c>
       <c r="I409" t="n">
-        <v>0.1228</v>
+        <v>0.1346</v>
       </c>
       <c r="J409" t="n">
-        <v>3.5612</v>
+        <v>3.9034</v>
       </c>
     </row>
     <row r="410">
@@ -20589,10 +20589,10 @@
         <v>0.89</v>
       </c>
       <c r="I410" t="n">
-        <v>-0.2523</v>
+        <v>-0.1482</v>
       </c>
       <c r="J410" t="n">
-        <v>-7.3167</v>
+        <v>-4.2978</v>
       </c>
     </row>
     <row r="411">
@@ -20629,10 +20629,10 @@
         <v>0.63</v>
       </c>
       <c r="I411" t="n">
-        <v>-0.613</v>
+        <v>-0.4044</v>
       </c>
       <c r="J411" t="n">
-        <v>-17.777</v>
+        <v>-11.7276</v>
       </c>
     </row>
     <row r="412">
@@ -20669,10 +20669,10 @@
         <v>1.45</v>
       </c>
       <c r="I412" t="n">
-        <v>1.2071</v>
+        <v>1.1241</v>
       </c>
       <c r="J412" t="n">
-        <v>43.4556</v>
+        <v>40.4676</v>
       </c>
     </row>
     <row r="413">
@@ -20709,10 +20709,10 @@
         <v>1.28</v>
       </c>
       <c r="I413" t="n">
-        <v>0.8385</v>
+        <v>0.8064</v>
       </c>
       <c r="J413" t="n">
-        <v>30.186</v>
+        <v>29.0304</v>
       </c>
     </row>
     <row r="414">
@@ -20749,10 +20749,10 @@
         <v>0.88</v>
       </c>
       <c r="I414" t="n">
-        <v>-0.472</v>
+        <v>-0.4163</v>
       </c>
       <c r="J414" t="n">
-        <v>-16.992</v>
+        <v>-14.9868</v>
       </c>
     </row>
     <row r="415">
@@ -20789,10 +20789,10 @@
         <v>0.82</v>
       </c>
       <c r="I415" t="n">
-        <v>-0.6312</v>
+        <v>-0.5794</v>
       </c>
       <c r="J415" t="n">
-        <v>-22.7232</v>
+        <v>-20.8584</v>
       </c>
     </row>
     <row r="416">
@@ -20829,10 +20829,10 @@
         <v>0.75</v>
       </c>
       <c r="I416" t="n">
-        <v>-0.8015</v>
+        <v>-0.7597</v>
       </c>
       <c r="J416" t="n">
-        <v>-28.854</v>
+        <v>-27.3492</v>
       </c>
     </row>
     <row r="417">
@@ -20869,10 +20869,10 @@
         <v>1.66</v>
       </c>
       <c r="I417" t="n">
-        <v>0.9043</v>
+        <v>1.0896</v>
       </c>
       <c r="J417" t="n">
-        <v>32.5548</v>
+        <v>39.2256</v>
       </c>
     </row>
     <row r="418">
@@ -20909,10 +20909,10 @@
         <v>1.19</v>
       </c>
       <c r="I418" t="n">
-        <v>0.3285</v>
+        <v>0.3912</v>
       </c>
       <c r="J418" t="n">
-        <v>11.826</v>
+        <v>14.0832</v>
       </c>
     </row>
     <row r="419">
@@ -20949,10 +20949,10 @@
         <v>0.97</v>
       </c>
       <c r="I419" t="n">
-        <v>-0.1306</v>
+        <v>-0.0614</v>
       </c>
       <c r="J419" t="n">
-        <v>-4.7016</v>
+        <v>-2.2104</v>
       </c>
     </row>
     <row r="420">
@@ -20989,10 +20989,10 @@
         <v>0.89</v>
       </c>
       <c r="I420" t="n">
-        <v>-0.2734</v>
+        <v>-0.1577</v>
       </c>
       <c r="J420" t="n">
-        <v>-9.8424</v>
+        <v>-5.6772</v>
       </c>
     </row>
     <row r="421">
@@ -21029,10 +21029,10 @@
         <v>0.86</v>
       </c>
       <c r="I421" t="n">
-        <v>-0.3197</v>
+        <v>-0.19</v>
       </c>
       <c r="J421" t="n">
-        <v>-11.5092</v>
+        <v>-6.84</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/2027/event_2027_evp_summary.xlsx
+++ b/database/event/2027/event_2027_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.9416</v>
+        <v>6.8902</v>
       </c>
       <c r="C2" t="n">
-        <v>4.5542</v>
+        <v>4.5205</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4958</v>
+        <v>2.5124</v>
       </c>
       <c r="E2" t="n">
-        <v>6.9416</v>
+        <v>6.8902</v>
       </c>
       <c r="F2" t="n">
-        <v>3.7766</v>
+        <v>3.685</v>
       </c>
       <c r="G2" t="n">
-        <v>3.165</v>
+        <v>3.2052</v>
       </c>
       <c r="H2" t="n">
-        <v>7.8201</v>
+        <v>7.264</v>
       </c>
       <c r="I2" t="n">
-        <v>4.0661</v>
+        <v>3.9225</v>
       </c>
       <c r="J2" t="n">
-        <v>3.165</v>
+        <v>3.2052</v>
       </c>
       <c r="K2" t="n">
         <v>139</v>
@@ -529,7 +529,7 @@
         <v>123</v>
       </c>
       <c r="M2" t="n">
-        <v>7.2311</v>
+        <v>7.1277</v>
       </c>
       <c r="N2" t="n">
         <v>262</v>
@@ -538,93 +538,93 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Edward</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.2904</v>
+        <v>5.3445</v>
       </c>
       <c r="C3" t="n">
-        <v>3.4709</v>
+        <v>3.5064</v>
       </c>
       <c r="D3" t="n">
-        <v>1.7503</v>
+        <v>1.8087</v>
       </c>
       <c r="E3" t="n">
-        <v>5.2904</v>
+        <v>5.3445</v>
       </c>
       <c r="F3" t="n">
-        <v>3.6048</v>
+        <v>2.1929</v>
       </c>
       <c r="G3" t="n">
-        <v>1.6856</v>
+        <v>3.1516</v>
       </c>
       <c r="H3" t="n">
-        <v>7.2149</v>
+        <v>2.341</v>
       </c>
       <c r="I3" t="n">
-        <v>3.7514</v>
+        <v>1.2641</v>
       </c>
       <c r="J3" t="n">
-        <v>1.6856</v>
+        <v>3.1516</v>
       </c>
       <c r="K3" t="n">
-        <v>96</v>
+        <v>139</v>
       </c>
       <c r="L3" t="n">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="M3" t="n">
-        <v>5.436999999999999</v>
+        <v>4.4157</v>
       </c>
       <c r="N3" t="n">
-        <v>201</v>
+        <v>262</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>Edward</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.1813</v>
+        <v>5.3005</v>
       </c>
       <c r="C4" t="n">
-        <v>3.3993</v>
+        <v>3.4775</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7011</v>
+        <v>1.7887</v>
       </c>
       <c r="E4" t="n">
-        <v>5.1813</v>
+        <v>5.3005</v>
       </c>
       <c r="F4" t="n">
-        <v>2.2466</v>
+        <v>3.5148</v>
       </c>
       <c r="G4" t="n">
-        <v>2.9347</v>
+        <v>1.7857</v>
       </c>
       <c r="H4" t="n">
-        <v>2.4294</v>
+        <v>6.7023</v>
       </c>
       <c r="I4" t="n">
-        <v>1.2632</v>
+        <v>3.6192</v>
       </c>
       <c r="J4" t="n">
-        <v>2.9347</v>
+        <v>1.7857</v>
       </c>
       <c r="K4" t="n">
-        <v>139</v>
+        <v>96</v>
       </c>
       <c r="L4" t="n">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="M4" t="n">
-        <v>4.1979</v>
+        <v>5.4049</v>
       </c>
       <c r="N4" t="n">
-        <v>262</v>
+        <v>201</v>
       </c>
     </row>
     <row r="5">
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.0153</v>
+        <v>5.0562</v>
       </c>
       <c r="C5" t="n">
-        <v>3.2904</v>
+        <v>3.3173</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6261</v>
+        <v>1.6775</v>
       </c>
       <c r="E5" t="n">
-        <v>5.0153</v>
+        <v>5.0562</v>
       </c>
       <c r="F5" t="n">
-        <v>3.3364</v>
+        <v>3.2368</v>
       </c>
       <c r="G5" t="n">
-        <v>1.6789</v>
+        <v>1.8194</v>
       </c>
       <c r="H5" t="n">
-        <v>6.2692</v>
+        <v>5.7851</v>
       </c>
       <c r="I5" t="n">
-        <v>3.2597</v>
+        <v>3.1239</v>
       </c>
       <c r="J5" t="n">
-        <v>1.6789</v>
+        <v>1.8194</v>
       </c>
       <c r="K5" t="n">
         <v>96</v>
@@ -667,7 +667,7 @@
         <v>105</v>
       </c>
       <c r="M5" t="n">
-        <v>4.9386</v>
+        <v>4.9433</v>
       </c>
       <c r="N5" t="n">
         <v>201</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.3623</v>
+        <v>4.419</v>
       </c>
       <c r="C6" t="n">
-        <v>2.862</v>
+        <v>2.8992</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3313</v>
+        <v>1.3874</v>
       </c>
       <c r="E6" t="n">
-        <v>4.3623</v>
+        <v>4.419</v>
       </c>
       <c r="F6" t="n">
-        <v>1.6763</v>
+        <v>1.6019</v>
       </c>
       <c r="G6" t="n">
-        <v>2.686</v>
+        <v>2.8171</v>
       </c>
       <c r="H6" t="n">
-        <v>1.6763</v>
+        <v>1.6019</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8716</v>
+        <v>0.865</v>
       </c>
       <c r="J6" t="n">
-        <v>2.686</v>
+        <v>2.8171</v>
       </c>
       <c r="K6" t="n">
         <v>139</v>
@@ -713,7 +713,7 @@
         <v>123</v>
       </c>
       <c r="M6" t="n">
-        <v>3.5576</v>
+        <v>3.6821</v>
       </c>
       <c r="N6" t="n">
         <v>262</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.1113</v>
+        <v>4.2896</v>
       </c>
       <c r="C7" t="n">
-        <v>2.6973</v>
+        <v>2.8143</v>
       </c>
       <c r="D7" t="n">
-        <v>1.218</v>
+        <v>1.3285</v>
       </c>
       <c r="E7" t="n">
-        <v>4.1113</v>
+        <v>4.2896</v>
       </c>
       <c r="F7" t="n">
-        <v>3.463</v>
+        <v>3.552</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6483</v>
+        <v>0.7376</v>
       </c>
       <c r="H7" t="n">
-        <v>6.7151</v>
+        <v>6.8251</v>
       </c>
       <c r="I7" t="n">
-        <v>3.4915</v>
+        <v>3.6855</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6483</v>
+        <v>0.7376</v>
       </c>
       <c r="K7" t="n">
         <v>139</v>
@@ -759,7 +759,7 @@
         <v>123</v>
       </c>
       <c r="M7" t="n">
-        <v>4.1398</v>
+        <v>4.4231</v>
       </c>
       <c r="N7" t="n">
         <v>262</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.5313</v>
+        <v>3.4558</v>
       </c>
       <c r="C8" t="n">
-        <v>2.3168</v>
+        <v>2.2673</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9562</v>
+        <v>0.9489</v>
       </c>
       <c r="E8" t="n">
-        <v>3.5313</v>
+        <v>3.4558</v>
       </c>
       <c r="F8" t="n">
-        <v>3.212</v>
+        <v>3.1352</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3193</v>
+        <v>0.3206</v>
       </c>
       <c r="H8" t="n">
-        <v>5.8309</v>
+        <v>5.4501</v>
       </c>
       <c r="I8" t="n">
-        <v>3.0318</v>
+        <v>2.943</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3193</v>
+        <v>0.3206</v>
       </c>
       <c r="K8" t="n">
         <v>119</v>
@@ -805,7 +805,7 @@
         <v>69</v>
       </c>
       <c r="M8" t="n">
-        <v>3.3511</v>
+        <v>3.2636</v>
       </c>
       <c r="N8" t="n">
         <v>188</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.4461</v>
+        <v>3.3443</v>
       </c>
       <c r="C9" t="n">
-        <v>2.2609</v>
+        <v>2.1941</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9177</v>
+        <v>0.8982</v>
       </c>
       <c r="E9" t="n">
-        <v>3.4461</v>
+        <v>3.3443</v>
       </c>
       <c r="F9" t="n">
-        <v>3.6988</v>
+        <v>3.6039</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.2527</v>
+        <v>-0.2596</v>
       </c>
       <c r="H9" t="n">
-        <v>7.5459</v>
+        <v>6.9964</v>
       </c>
       <c r="I9" t="n">
-        <v>3.9235</v>
+        <v>3.778</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.2527</v>
+        <v>-0.2596</v>
       </c>
       <c r="K9" t="n">
         <v>98</v>
@@ -851,7 +851,7 @@
         <v>51</v>
       </c>
       <c r="M9" t="n">
-        <v>3.6708</v>
+        <v>3.5184</v>
       </c>
       <c r="N9" t="n">
         <v>149</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.1599</v>
+        <v>3.0574</v>
       </c>
       <c r="C10" t="n">
-        <v>2.0731</v>
+        <v>2.0059</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7885</v>
+        <v>0.7675999999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>3.1599</v>
+        <v>3.0574</v>
       </c>
       <c r="F10" t="n">
-        <v>3.3208</v>
+        <v>3.2253</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.1609</v>
+        <v>-0.1679</v>
       </c>
       <c r="H10" t="n">
-        <v>6.214</v>
+        <v>5.7473</v>
       </c>
       <c r="I10" t="n">
-        <v>3.231</v>
+        <v>3.1035</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.1609</v>
+        <v>-0.1679</v>
       </c>
       <c r="K10" t="n">
         <v>119</v>
@@ -897,7 +897,7 @@
         <v>69</v>
       </c>
       <c r="M10" t="n">
-        <v>3.0701</v>
+        <v>2.9356</v>
       </c>
       <c r="N10" t="n">
         <v>188</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.0046</v>
+        <v>2.9163</v>
       </c>
       <c r="C11" t="n">
-        <v>1.9712</v>
+        <v>1.9133</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7184</v>
+        <v>0.7034</v>
       </c>
       <c r="E11" t="n">
-        <v>3.0046</v>
+        <v>2.9163</v>
       </c>
       <c r="F11" t="n">
-        <v>3.3016</v>
+        <v>3.2453</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.297</v>
+        <v>-0.329</v>
       </c>
       <c r="H11" t="n">
-        <v>6.1463</v>
+        <v>5.8132</v>
       </c>
       <c r="I11" t="n">
-        <v>3.1958</v>
+        <v>3.1391</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.297</v>
+        <v>-0.329</v>
       </c>
       <c r="K11" t="n">
         <v>98</v>
@@ -943,7 +943,7 @@
         <v>51</v>
       </c>
       <c r="M11" t="n">
-        <v>2.8988</v>
+        <v>2.8101</v>
       </c>
       <c r="N11" t="n">
         <v>149</v>
@@ -952,93 +952,93 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>jdm64</t>
+          <t>seized</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.9556</v>
+        <v>2.8981</v>
       </c>
       <c r="C12" t="n">
-        <v>1.9391</v>
+        <v>1.9014</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6963</v>
+        <v>0.6951000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>2.9556</v>
+        <v>2.8981</v>
       </c>
       <c r="F12" t="n">
-        <v>2.9556</v>
+        <v>3.5859</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>-0.6878</v>
       </c>
       <c r="H12" t="n">
-        <v>3.1302</v>
+        <v>6.9371</v>
       </c>
       <c r="I12" t="n">
-        <v>3.1302</v>
+        <v>3.746</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>-0.6878</v>
       </c>
       <c r="K12" t="n">
-        <v>182</v>
+        <v>96</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="M12" t="n">
-        <v>3.1302</v>
+        <v>3.0582</v>
       </c>
       <c r="N12" t="n">
-        <v>182</v>
+        <v>201</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>cajunb</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.9319</v>
+        <v>2.6953</v>
       </c>
       <c r="C13" t="n">
-        <v>1.9235</v>
+        <v>1.7683</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6856</v>
+        <v>0.6028</v>
       </c>
       <c r="E13" t="n">
-        <v>2.9319</v>
+        <v>2.6953</v>
       </c>
       <c r="F13" t="n">
-        <v>2.9319</v>
+        <v>3.0243</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>-0.329</v>
       </c>
       <c r="H13" t="n">
-        <v>3.0781</v>
+        <v>5.084</v>
       </c>
       <c r="I13" t="n">
-        <v>3.0781</v>
+        <v>2.7453</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>-0.329</v>
       </c>
       <c r="K13" t="n">
-        <v>182</v>
+        <v>98</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="M13" t="n">
-        <v>3.0781</v>
+        <v>2.4163</v>
       </c>
       <c r="N13" t="n">
-        <v>182</v>
+        <v>149</v>
       </c>
     </row>
     <row r="14">
@@ -1048,28 +1048,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.9243</v>
+        <v>2.636</v>
       </c>
       <c r="C14" t="n">
-        <v>1.9186</v>
+        <v>1.7294</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6822</v>
+        <v>0.5758</v>
       </c>
       <c r="E14" t="n">
-        <v>2.9243</v>
+        <v>2.636</v>
       </c>
       <c r="F14" t="n">
-        <v>2.9243</v>
+        <v>2.636</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>3.0616</v>
+        <v>3.0444</v>
       </c>
       <c r="I14" t="n">
-        <v>3.0616</v>
+        <v>3.0444</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.0616</v>
+        <v>3.0444</v>
       </c>
       <c r="N14" t="n">
         <v>199</v>
@@ -1090,32 +1090,32 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GeT_RiGhT</t>
+          <t>jdm64</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.9038</v>
+        <v>2.6136</v>
       </c>
       <c r="C15" t="n">
-        <v>1.9051</v>
+        <v>1.7147</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6729000000000001</v>
+        <v>0.5656</v>
       </c>
       <c r="E15" t="n">
-        <v>2.9038</v>
+        <v>2.6136</v>
       </c>
       <c r="F15" t="n">
-        <v>2.9038</v>
+        <v>2.6136</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>3.0164</v>
+        <v>2.9954</v>
       </c>
       <c r="I15" t="n">
-        <v>3.0164</v>
+        <v>2.9954</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.0164</v>
+        <v>2.9954</v>
       </c>
       <c r="N15" t="n">
         <v>182</v>
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.8849</v>
+        <v>2.5835</v>
       </c>
       <c r="C16" t="n">
-        <v>1.8927</v>
+        <v>1.695</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6644</v>
+        <v>0.5518999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>2.8849</v>
+        <v>2.5835</v>
       </c>
       <c r="F16" t="n">
-        <v>2.8849</v>
+        <v>2.5835</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2.9751</v>
+        <v>2.9296</v>
       </c>
       <c r="I16" t="n">
-        <v>2.9751</v>
+        <v>2.9296</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.9751</v>
+        <v>2.9296</v>
       </c>
       <c r="N16" t="n">
         <v>157</v>
@@ -1182,277 +1182,277 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>Hiko</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.8845</v>
+        <v>2.5766</v>
       </c>
       <c r="C17" t="n">
-        <v>1.8925</v>
+        <v>1.6904</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6642</v>
+        <v>0.5487</v>
       </c>
       <c r="E17" t="n">
-        <v>2.8845</v>
+        <v>2.5766</v>
       </c>
       <c r="F17" t="n">
-        <v>2.8845</v>
+        <v>2.4667</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>0.1099</v>
       </c>
       <c r="H17" t="n">
-        <v>2.9742</v>
+        <v>3.2443</v>
       </c>
       <c r="I17" t="n">
-        <v>2.9742</v>
+        <v>1.7519</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>0.1099</v>
       </c>
       <c r="K17" t="n">
-        <v>199</v>
+        <v>119</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="M17" t="n">
-        <v>2.9742</v>
+        <v>1.8618</v>
       </c>
       <c r="N17" t="n">
-        <v>199</v>
+        <v>188</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.8839</v>
+        <v>2.5736</v>
       </c>
       <c r="C18" t="n">
-        <v>1.8921</v>
+        <v>1.6885</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6639</v>
+        <v>0.5474</v>
       </c>
       <c r="E18" t="n">
-        <v>2.8839</v>
+        <v>2.5736</v>
       </c>
       <c r="F18" t="n">
-        <v>2.8839</v>
+        <v>2.5736</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>2.9728</v>
+        <v>2.9078</v>
       </c>
       <c r="I18" t="n">
-        <v>2.9728</v>
+        <v>2.9078</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>2.9728</v>
+        <v>2.9078</v>
       </c>
       <c r="N18" t="n">
-        <v>162</v>
+        <v>182</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>seized</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.8411</v>
+        <v>2.5636</v>
       </c>
       <c r="C19" t="n">
-        <v>1.864</v>
+        <v>1.6819</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6446</v>
+        <v>0.5427999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>2.8411</v>
+        <v>2.5636</v>
       </c>
       <c r="F19" t="n">
-        <v>3.64</v>
+        <v>2.5636</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.7989000000000001</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>7.3389</v>
+        <v>2.886</v>
       </c>
       <c r="I19" t="n">
-        <v>3.8159</v>
+        <v>2.886</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.7989000000000001</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>96</v>
+        <v>199</v>
       </c>
       <c r="L19" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.017</v>
+        <v>2.886</v>
       </c>
       <c r="N19" t="n">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>NEO</t>
+          <t>GeT_RiGhT</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.8124</v>
+        <v>2.5386</v>
       </c>
       <c r="C20" t="n">
-        <v>1.8451</v>
+        <v>1.6655</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6316000000000001</v>
+        <v>0.5314</v>
       </c>
       <c r="E20" t="n">
-        <v>2.8124</v>
+        <v>2.5386</v>
       </c>
       <c r="F20" t="n">
-        <v>2.8124</v>
+        <v>2.5386</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>2.8158</v>
+        <v>2.8313</v>
       </c>
       <c r="I20" t="n">
-        <v>2.8158</v>
+        <v>2.8313</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>2.8158</v>
+        <v>2.8313</v>
       </c>
       <c r="N20" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>cajunb</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.78</v>
+        <v>2.5378</v>
       </c>
       <c r="C21" t="n">
-        <v>1.8239</v>
+        <v>1.665</v>
       </c>
       <c r="D21" t="n">
-        <v>0.617</v>
+        <v>0.5311</v>
       </c>
       <c r="E21" t="n">
-        <v>2.78</v>
+        <v>2.5378</v>
       </c>
       <c r="F21" t="n">
-        <v>3.077</v>
+        <v>2.5378</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.297</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>5.3551</v>
+        <v>2.8296</v>
       </c>
       <c r="I21" t="n">
-        <v>2.7844</v>
+        <v>2.8296</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.297</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>98</v>
+        <v>162</v>
       </c>
       <c r="L21" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>2.4874</v>
+        <v>2.8296</v>
       </c>
       <c r="N21" t="n">
-        <v>149</v>
+        <v>162</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Hiko</t>
+          <t>NEO</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.6571</v>
+        <v>2.4596</v>
       </c>
       <c r="C22" t="n">
-        <v>1.7433</v>
+        <v>1.6137</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5615</v>
+        <v>0.4955</v>
       </c>
       <c r="E22" t="n">
-        <v>2.6571</v>
+        <v>2.4596</v>
       </c>
       <c r="F22" t="n">
-        <v>2.5374</v>
+        <v>2.4596</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1197</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>3.454</v>
+        <v>2.6584</v>
       </c>
       <c r="I22" t="n">
-        <v>1.7959</v>
+        <v>2.6584</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1197</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>119</v>
+        <v>199</v>
       </c>
       <c r="L22" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.9156</v>
+        <v>2.6584</v>
       </c>
       <c r="N22" t="n">
-        <v>188</v>
+        <v>199</v>
       </c>
     </row>
     <row r="23">
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.5652</v>
+        <v>2.3811</v>
       </c>
       <c r="C23" t="n">
-        <v>1.683</v>
+        <v>1.5622</v>
       </c>
       <c r="D23" t="n">
-        <v>0.52</v>
+        <v>0.4597</v>
       </c>
       <c r="E23" t="n">
-        <v>2.5652</v>
+        <v>2.3811</v>
       </c>
       <c r="F23" t="n">
-        <v>2.5652</v>
+        <v>2.3811</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>2.5652</v>
+        <v>2.4866</v>
       </c>
       <c r="I23" t="n">
-        <v>2.5652</v>
+        <v>2.4866</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>2.5652</v>
+        <v>2.4866</v>
       </c>
       <c r="N23" t="n">
         <v>157</v>
@@ -1508,31 +1508,31 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.2563</v>
+        <v>2.1439</v>
       </c>
       <c r="C24" t="n">
-        <v>1.4803</v>
+        <v>1.4066</v>
       </c>
       <c r="D24" t="n">
-        <v>0.3806</v>
+        <v>0.3517</v>
       </c>
       <c r="E24" t="n">
-        <v>2.2563</v>
+        <v>2.1439</v>
       </c>
       <c r="F24" t="n">
-        <v>2.5281</v>
+        <v>2.4415</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.2718</v>
+        <v>-0.2976</v>
       </c>
       <c r="H24" t="n">
-        <v>3.4213</v>
+        <v>3.1613</v>
       </c>
       <c r="I24" t="n">
-        <v>1.7789</v>
+        <v>1.7071</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.2718</v>
+        <v>-0.2976</v>
       </c>
       <c r="K24" t="n">
         <v>98</v>
@@ -1541,7 +1541,7 @@
         <v>51</v>
       </c>
       <c r="M24" t="n">
-        <v>1.5071</v>
+        <v>1.4095</v>
       </c>
       <c r="N24" t="n">
         <v>149</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.1981</v>
+        <v>2.1087</v>
       </c>
       <c r="C25" t="n">
-        <v>1.4421</v>
+        <v>1.3835</v>
       </c>
       <c r="D25" t="n">
-        <v>0.3543</v>
+        <v>0.3357</v>
       </c>
       <c r="E25" t="n">
-        <v>2.1981</v>
+        <v>2.1087</v>
       </c>
       <c r="F25" t="n">
-        <v>2.1981</v>
+        <v>2.1087</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>2.1981</v>
+        <v>2.1087</v>
       </c>
       <c r="I25" t="n">
-        <v>2.1981</v>
+        <v>2.1087</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>2.1981</v>
+        <v>2.1087</v>
       </c>
       <c r="N25" t="n">
         <v>94</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.0548</v>
+        <v>1.9382</v>
       </c>
       <c r="C26" t="n">
-        <v>1.3481</v>
+        <v>1.2716</v>
       </c>
       <c r="D26" t="n">
-        <v>0.2896</v>
+        <v>0.2581</v>
       </c>
       <c r="E26" t="n">
-        <v>2.0548</v>
+        <v>1.9382</v>
       </c>
       <c r="F26" t="n">
-        <v>2.0548</v>
+        <v>1.9382</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>2.0548</v>
+        <v>1.9382</v>
       </c>
       <c r="I26" t="n">
-        <v>2.0548</v>
+        <v>1.9382</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>2.0548</v>
+        <v>1.9382</v>
       </c>
       <c r="N26" t="n">
         <v>157</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.8918</v>
+        <v>1.7844</v>
       </c>
       <c r="C27" t="n">
-        <v>1.2412</v>
+        <v>1.1707</v>
       </c>
       <c r="D27" t="n">
-        <v>0.216</v>
+        <v>0.1881</v>
       </c>
       <c r="E27" t="n">
-        <v>1.8918</v>
+        <v>1.7844</v>
       </c>
       <c r="F27" t="n">
-        <v>1.8918</v>
+        <v>1.7844</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1.8918</v>
+        <v>1.7844</v>
       </c>
       <c r="I27" t="n">
-        <v>1.8918</v>
+        <v>1.7844</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1.8918</v>
+        <v>1.7844</v>
       </c>
       <c r="N27" t="n">
         <v>182</v>
@@ -1692,31 +1692,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.7641</v>
+        <v>1.6829</v>
       </c>
       <c r="C28" t="n">
-        <v>1.1574</v>
+        <v>1.1041</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1584</v>
+        <v>0.1419</v>
       </c>
       <c r="E28" t="n">
-        <v>1.7641</v>
+        <v>1.6829</v>
       </c>
       <c r="F28" t="n">
-        <v>2.2368</v>
+        <v>2.1836</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.4727</v>
+        <v>-0.5007</v>
       </c>
       <c r="H28" t="n">
-        <v>2.3946</v>
+        <v>2.3104</v>
       </c>
       <c r="I28" t="n">
-        <v>1.2451</v>
+        <v>1.2476</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.4727</v>
+        <v>-0.5007</v>
       </c>
       <c r="K28" t="n">
         <v>119</v>
@@ -1725,7 +1725,7 @@
         <v>69</v>
       </c>
       <c r="M28" t="n">
-        <v>0.7724000000000001</v>
+        <v>0.7469</v>
       </c>
       <c r="N28" t="n">
         <v>188</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.7419</v>
+        <v>1.6557</v>
       </c>
       <c r="C29" t="n">
-        <v>1.1428</v>
+        <v>1.0863</v>
       </c>
       <c r="D29" t="n">
-        <v>0.1484</v>
+        <v>0.1295</v>
       </c>
       <c r="E29" t="n">
-        <v>1.7419</v>
+        <v>1.6557</v>
       </c>
       <c r="F29" t="n">
-        <v>1.7419</v>
+        <v>1.6557</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1.7419</v>
+        <v>1.6557</v>
       </c>
       <c r="I29" t="n">
-        <v>1.7419</v>
+        <v>1.6557</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1.7419</v>
+        <v>1.6557</v>
       </c>
       <c r="N29" t="n">
         <v>157</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.6858</v>
+        <v>1.6256</v>
       </c>
       <c r="C30" t="n">
-        <v>1.106</v>
+        <v>1.0665</v>
       </c>
       <c r="D30" t="n">
-        <v>0.123</v>
+        <v>0.1158</v>
       </c>
       <c r="E30" t="n">
-        <v>1.6858</v>
+        <v>1.6256</v>
       </c>
       <c r="F30" t="n">
-        <v>1.6858</v>
+        <v>1.6256</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1.6858</v>
+        <v>1.6256</v>
       </c>
       <c r="I30" t="n">
-        <v>1.6858</v>
+        <v>1.6256</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>1.6858</v>
+        <v>1.6256</v>
       </c>
       <c r="N30" t="n">
         <v>182</v>
@@ -1826,277 +1826,277 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>olofmeister</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.5651</v>
+        <v>1.542</v>
       </c>
       <c r="C31" t="n">
-        <v>1.0268</v>
+        <v>1.0117</v>
       </c>
       <c r="D31" t="n">
-        <v>0.06859999999999999</v>
+        <v>0.07770000000000001</v>
       </c>
       <c r="E31" t="n">
-        <v>1.5651</v>
+        <v>1.542</v>
       </c>
       <c r="F31" t="n">
-        <v>1.5651</v>
+        <v>1.4693</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>0.0727</v>
       </c>
       <c r="H31" t="n">
-        <v>1.5651</v>
+        <v>1.4693</v>
       </c>
       <c r="I31" t="n">
-        <v>1.5651</v>
+        <v>0.7934</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>0.0727</v>
       </c>
       <c r="K31" t="n">
-        <v>157</v>
+        <v>119</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="M31" t="n">
-        <v>1.5651</v>
+        <v>0.8661</v>
       </c>
       <c r="N31" t="n">
-        <v>157</v>
+        <v>188</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>olofmeister</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.5153</v>
+        <v>1.4773</v>
       </c>
       <c r="C32" t="n">
-        <v>0.9942</v>
+        <v>0.9692</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0461</v>
+        <v>0.0483</v>
       </c>
       <c r="E32" t="n">
-        <v>1.5153</v>
+        <v>1.4773</v>
       </c>
       <c r="F32" t="n">
-        <v>1.469</v>
+        <v>1.4773</v>
       </c>
       <c r="G32" t="n">
-        <v>0.0463</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>1.469</v>
+        <v>1.4773</v>
       </c>
       <c r="I32" t="n">
-        <v>0.7638</v>
+        <v>1.4773</v>
       </c>
       <c r="J32" t="n">
-        <v>0.0463</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>119</v>
+        <v>157</v>
       </c>
       <c r="L32" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0.8101</v>
+        <v>1.4773</v>
       </c>
       <c r="N32" t="n">
-        <v>188</v>
+        <v>157</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>TaZ</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.4181</v>
+        <v>1.4313</v>
       </c>
       <c r="C33" t="n">
-        <v>0.9304</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0022</v>
+        <v>0.0274</v>
       </c>
       <c r="E33" t="n">
-        <v>1.4181</v>
+        <v>1.4313</v>
       </c>
       <c r="F33" t="n">
-        <v>1.4181</v>
+        <v>-0.3717</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>1.803</v>
       </c>
       <c r="H33" t="n">
-        <v>1.4181</v>
+        <v>-0.3717</v>
       </c>
       <c r="I33" t="n">
-        <v>1.4181</v>
+        <v>-0.2007</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>1.803</v>
       </c>
       <c r="K33" t="n">
-        <v>199</v>
+        <v>139</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="M33" t="n">
-        <v>1.4181</v>
+        <v>1.6023</v>
       </c>
       <c r="N33" t="n">
-        <v>199</v>
+        <v>262</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>TaZ</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.1098</v>
+        <v>1.3451</v>
       </c>
       <c r="C34" t="n">
-        <v>0.7281</v>
+        <v>0.8825</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.137</v>
+        <v>-0.0119</v>
       </c>
       <c r="E34" t="n">
-        <v>1.1098</v>
+        <v>1.3451</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.486</v>
+        <v>1.3451</v>
       </c>
       <c r="G34" t="n">
-        <v>1.5958</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.486</v>
+        <v>1.3451</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.2527</v>
+        <v>1.3451</v>
       </c>
       <c r="J34" t="n">
-        <v>1.5958</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>139</v>
+        <v>199</v>
       </c>
       <c r="L34" t="n">
-        <v>123</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>1.3431</v>
+        <v>1.3451</v>
       </c>
       <c r="N34" t="n">
-        <v>262</v>
+        <v>199</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>aizy</t>
+          <t>bondik</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.9928</v>
+        <v>0.9288</v>
       </c>
       <c r="C35" t="n">
-        <v>0.6514</v>
+        <v>0.6094000000000001</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.1898</v>
+        <v>-0.2014</v>
       </c>
       <c r="E35" t="n">
-        <v>0.9928</v>
+        <v>0.9288</v>
       </c>
       <c r="F35" t="n">
-        <v>0.9928</v>
+        <v>0.9288</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0.9928</v>
+        <v>0.9288</v>
       </c>
       <c r="I35" t="n">
-        <v>0.9928</v>
+        <v>0.9288</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0.9928</v>
+        <v>0.9288</v>
       </c>
       <c r="N35" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>bondik</t>
+          <t>aizy</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.9674</v>
+        <v>0.9241</v>
       </c>
       <c r="C36" t="n">
-        <v>0.6347</v>
+        <v>0.6063</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.2013</v>
+        <v>-0.2035</v>
       </c>
       <c r="E36" t="n">
-        <v>0.9674</v>
+        <v>0.9241</v>
       </c>
       <c r="F36" t="n">
-        <v>0.9674</v>
+        <v>0.9241</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.9674</v>
+        <v>0.9241</v>
       </c>
       <c r="I36" t="n">
-        <v>0.9674</v>
+        <v>0.9241</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0.9674</v>
+        <v>0.9241</v>
       </c>
       <c r="N36" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="37">
@@ -2106,31 +2106,31 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.9372</v>
+        <v>0.9053</v>
       </c>
       <c r="C37" t="n">
-        <v>0.6149</v>
+        <v>0.5939</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.2149</v>
+        <v>-0.2121</v>
       </c>
       <c r="E37" t="n">
-        <v>0.9372</v>
+        <v>0.9053</v>
       </c>
       <c r="F37" t="n">
-        <v>2.3035</v>
+        <v>2.2627</v>
       </c>
       <c r="G37" t="n">
-        <v>-1.3663</v>
+        <v>-1.3574</v>
       </c>
       <c r="H37" t="n">
-        <v>2.6297</v>
+        <v>2.5713</v>
       </c>
       <c r="I37" t="n">
-        <v>1.3673</v>
+        <v>1.3885</v>
       </c>
       <c r="J37" t="n">
-        <v>-1.3663</v>
+        <v>-1.3574</v>
       </c>
       <c r="K37" t="n">
         <v>96</v>
@@ -2139,7 +2139,7 @@
         <v>105</v>
       </c>
       <c r="M37" t="n">
-        <v>0.0009999999999998899</v>
+        <v>0.03110000000000013</v>
       </c>
       <c r="N37" t="n">
         <v>201</v>
@@ -2148,47 +2148,47 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>wayLander</t>
+          <t>Shara</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.8657</v>
+        <v>0.8428</v>
       </c>
       <c r="C38" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.5528999999999999</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.2472</v>
+        <v>-0.2405</v>
       </c>
       <c r="E38" t="n">
-        <v>0.8657</v>
+        <v>0.8428</v>
       </c>
       <c r="F38" t="n">
-        <v>0.8657</v>
+        <v>0.8428</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.8657</v>
+        <v>0.8428</v>
       </c>
       <c r="I38" t="n">
-        <v>0.8657</v>
+        <v>0.8428</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>137</v>
+        <v>95</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.8657</v>
+        <v>0.8428</v>
       </c>
       <c r="N38" t="n">
-        <v>137</v>
+        <v>95</v>
       </c>
     </row>
     <row r="39">
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.846</v>
+        <v>0.8099</v>
       </c>
       <c r="C39" t="n">
-        <v>0.555</v>
+        <v>0.5314</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.2561</v>
+        <v>-0.2555</v>
       </c>
       <c r="E39" t="n">
-        <v>0.846</v>
+        <v>0.8099</v>
       </c>
       <c r="F39" t="n">
-        <v>0.846</v>
+        <v>0.8099</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.846</v>
+        <v>0.8099</v>
       </c>
       <c r="I39" t="n">
-        <v>0.846</v>
+        <v>0.8099</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.846</v>
+        <v>0.8099</v>
       </c>
       <c r="N39" t="n">
         <v>199</v>
@@ -2240,47 +2240,47 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Shara</t>
+          <t>wayLander</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.8387</v>
+        <v>0.7968</v>
       </c>
       <c r="C40" t="n">
-        <v>0.5503</v>
+        <v>0.5228</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.2594</v>
+        <v>-0.2615</v>
       </c>
       <c r="E40" t="n">
-        <v>0.8387</v>
+        <v>0.7968</v>
       </c>
       <c r="F40" t="n">
-        <v>0.8387</v>
+        <v>0.7968</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.8387</v>
+        <v>0.7968</v>
       </c>
       <c r="I40" t="n">
-        <v>0.8387</v>
+        <v>0.7968</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>95</v>
+        <v>137</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0.8387</v>
+        <v>0.7968</v>
       </c>
       <c r="N40" t="n">
-        <v>95</v>
+        <v>137</v>
       </c>
     </row>
     <row r="41">
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.8289</v>
+        <v>0.7622</v>
       </c>
       <c r="C41" t="n">
-        <v>0.5438</v>
+        <v>0.5001</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.2638</v>
+        <v>-0.2772</v>
       </c>
       <c r="E41" t="n">
-        <v>0.8289</v>
+        <v>0.7622</v>
       </c>
       <c r="F41" t="n">
-        <v>0.8289</v>
+        <v>0.7622</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.8289</v>
+        <v>0.7622</v>
       </c>
       <c r="I41" t="n">
-        <v>0.8289</v>
+        <v>0.7622</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.8289</v>
+        <v>0.7622</v>
       </c>
       <c r="N41" t="n">
         <v>109</v>
@@ -2336,28 +2336,28 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.7614</v>
+        <v>0.68</v>
       </c>
       <c r="C42" t="n">
-        <v>0.4995</v>
+        <v>0.4461</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.2943</v>
+        <v>-0.3147</v>
       </c>
       <c r="E42" t="n">
-        <v>0.7614</v>
+        <v>0.68</v>
       </c>
       <c r="F42" t="n">
-        <v>0.7614</v>
+        <v>0.68</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.7614</v>
+        <v>0.68</v>
       </c>
       <c r="I42" t="n">
-        <v>0.7614</v>
+        <v>0.68</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -2369,7 +2369,7 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.7614</v>
+        <v>0.68</v>
       </c>
       <c r="N42" t="n">
         <v>94</v>
@@ -2382,28 +2382,28 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.7541</v>
+        <v>0.6796</v>
       </c>
       <c r="C43" t="n">
-        <v>0.4947</v>
+        <v>0.4459</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.2976</v>
+        <v>-0.3148</v>
       </c>
       <c r="E43" t="n">
-        <v>0.7541</v>
+        <v>0.6796</v>
       </c>
       <c r="F43" t="n">
-        <v>0.7541</v>
+        <v>0.6796</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.7541</v>
+        <v>0.6796</v>
       </c>
       <c r="I43" t="n">
-        <v>0.7541</v>
+        <v>0.6796</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -2415,7 +2415,7 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.7541</v>
+        <v>0.6796</v>
       </c>
       <c r="N43" t="n">
         <v>109</v>
@@ -2428,28 +2428,28 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.5589</v>
+        <v>0.5271</v>
       </c>
       <c r="C44" t="n">
-        <v>0.3667</v>
+        <v>0.3458</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.3857</v>
+        <v>-0.3843</v>
       </c>
       <c r="E44" t="n">
-        <v>0.5589</v>
+        <v>0.5271</v>
       </c>
       <c r="F44" t="n">
-        <v>0.5589</v>
+        <v>0.5271</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.5589</v>
+        <v>0.5271</v>
       </c>
       <c r="I44" t="n">
-        <v>0.5589</v>
+        <v>0.5271</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -2461,7 +2461,7 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.5589</v>
+        <v>0.5271</v>
       </c>
       <c r="N44" t="n">
         <v>109</v>
@@ -2474,28 +2474,28 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.5247000000000001</v>
+        <v>0.4942</v>
       </c>
       <c r="C45" t="n">
-        <v>0.3442</v>
+        <v>0.3242</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.4011</v>
+        <v>-0.3992</v>
       </c>
       <c r="E45" t="n">
-        <v>0.5247000000000001</v>
+        <v>0.4942</v>
       </c>
       <c r="F45" t="n">
-        <v>0.5247000000000001</v>
+        <v>0.4942</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.5247000000000001</v>
+        <v>0.4942</v>
       </c>
       <c r="I45" t="n">
-        <v>0.5247000000000001</v>
+        <v>0.4942</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -2507,7 +2507,7 @@
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0.5247000000000001</v>
+        <v>0.4942</v>
       </c>
       <c r="N45" t="n">
         <v>162</v>
@@ -2516,139 +2516,139 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>markeloff</t>
+          <t>Xizt</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.511</v>
+        <v>0.4886</v>
       </c>
       <c r="C46" t="n">
-        <v>0.3353</v>
+        <v>0.3206</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.4073</v>
+        <v>-0.4018</v>
       </c>
       <c r="E46" t="n">
-        <v>0.511</v>
+        <v>0.4886</v>
       </c>
       <c r="F46" t="n">
-        <v>0.511</v>
+        <v>0.4886</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.511</v>
+        <v>0.4886</v>
       </c>
       <c r="I46" t="n">
-        <v>0.511</v>
+        <v>0.4886</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>95</v>
+        <v>182</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0.511</v>
+        <v>0.4886</v>
       </c>
       <c r="N46" t="n">
-        <v>95</v>
+        <v>182</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>markeloff</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.5001</v>
+        <v>0.4785</v>
       </c>
       <c r="C47" t="n">
-        <v>0.3281</v>
+        <v>0.3139</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.4122</v>
+        <v>-0.4064</v>
       </c>
       <c r="E47" t="n">
-        <v>0.5001</v>
+        <v>0.4785</v>
       </c>
       <c r="F47" t="n">
-        <v>0.5001</v>
+        <v>0.4785</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.5001</v>
+        <v>0.4785</v>
       </c>
       <c r="I47" t="n">
-        <v>0.5001</v>
+        <v>0.4785</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>53</v>
+        <v>95</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0.5001</v>
+        <v>0.4785</v>
       </c>
       <c r="N47" t="n">
-        <v>53</v>
+        <v>95</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Xizt</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.4903</v>
+        <v>0.4754</v>
       </c>
       <c r="C48" t="n">
-        <v>0.3217</v>
+        <v>0.3119</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.4167</v>
+        <v>-0.4078</v>
       </c>
       <c r="E48" t="n">
-        <v>0.4903</v>
+        <v>0.4754</v>
       </c>
       <c r="F48" t="n">
-        <v>0.4903</v>
+        <v>0.4754</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.4903</v>
+        <v>0.4754</v>
       </c>
       <c r="I48" t="n">
-        <v>0.4903</v>
+        <v>0.4754</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>182</v>
+        <v>53</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0.4903</v>
+        <v>0.4754</v>
       </c>
       <c r="N48" t="n">
-        <v>182</v>
+        <v>53</v>
       </c>
     </row>
     <row r="49">
@@ -2658,28 +2658,28 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.4836</v>
+        <v>0.4721</v>
       </c>
       <c r="C49" t="n">
-        <v>0.3173</v>
+        <v>0.3097</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.4197</v>
+        <v>-0.4093</v>
       </c>
       <c r="E49" t="n">
-        <v>0.4836</v>
+        <v>0.4721</v>
       </c>
       <c r="F49" t="n">
-        <v>0.4836</v>
+        <v>0.4721</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.4836</v>
+        <v>0.4721</v>
       </c>
       <c r="I49" t="n">
-        <v>0.4836</v>
+        <v>0.4721</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -2691,7 +2691,7 @@
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0.4836</v>
+        <v>0.4721</v>
       </c>
       <c r="N49" t="n">
         <v>162</v>
@@ -2704,28 +2704,28 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.4651</v>
+        <v>0.4598</v>
       </c>
       <c r="C50" t="n">
-        <v>0.3051</v>
+        <v>0.3017</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.428</v>
+        <v>-0.4149</v>
       </c>
       <c r="E50" t="n">
-        <v>0.4651</v>
+        <v>0.4598</v>
       </c>
       <c r="F50" t="n">
-        <v>0.4651</v>
+        <v>0.4598</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0.4651</v>
+        <v>0.4598</v>
       </c>
       <c r="I50" t="n">
-        <v>0.4651</v>
+        <v>0.4598</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -2737,7 +2737,7 @@
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>0.4651</v>
+        <v>0.4598</v>
       </c>
       <c r="N50" t="n">
         <v>137</v>
@@ -2750,28 +2750,28 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.3827</v>
+        <v>0.3656</v>
       </c>
       <c r="C51" t="n">
-        <v>0.2511</v>
+        <v>0.2399</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.4652</v>
+        <v>-0.4578</v>
       </c>
       <c r="E51" t="n">
-        <v>0.3827</v>
+        <v>0.3656</v>
       </c>
       <c r="F51" t="n">
-        <v>0.3827</v>
+        <v>0.3656</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>0.3827</v>
+        <v>0.3656</v>
       </c>
       <c r="I51" t="n">
-        <v>0.3827</v>
+        <v>0.3656</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -2783,7 +2783,7 @@
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>0.3827</v>
+        <v>0.3656</v>
       </c>
       <c r="N51" t="n">
         <v>53</v>
@@ -2792,231 +2792,231 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>DAVEY</t>
+          <t>SmithZz</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.3525</v>
+        <v>0.3217</v>
       </c>
       <c r="C52" t="n">
-        <v>0.2313</v>
+        <v>0.2111</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.4789</v>
+        <v>-0.4778</v>
       </c>
       <c r="E52" t="n">
-        <v>0.3525</v>
+        <v>0.3217</v>
       </c>
       <c r="F52" t="n">
-        <v>0.3525</v>
+        <v>0.3217</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>0.3525</v>
+        <v>0.3217</v>
       </c>
       <c r="I52" t="n">
-        <v>0.3525</v>
+        <v>0.3217</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>40</v>
+        <v>109</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>0.3525</v>
+        <v>0.3217</v>
       </c>
       <c r="N52" t="n">
-        <v>40</v>
+        <v>109</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ScreaM</t>
+          <t>Dosia</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.3323</v>
+        <v>0.3136</v>
       </c>
       <c r="C53" t="n">
-        <v>0.218</v>
+        <v>0.2057</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.488</v>
+        <v>-0.4814</v>
       </c>
       <c r="E53" t="n">
-        <v>0.3323</v>
+        <v>0.3136</v>
       </c>
       <c r="F53" t="n">
-        <v>0.3323</v>
+        <v>0.3136</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>0.3323</v>
+        <v>0.3136</v>
       </c>
       <c r="I53" t="n">
-        <v>0.3323</v>
+        <v>0.3136</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>109</v>
+        <v>137</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>0.3323</v>
+        <v>0.3136</v>
       </c>
       <c r="N53" t="n">
-        <v>109</v>
+        <v>137</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Dosia</t>
+          <t>ScreaM</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.3271</v>
+        <v>0.3046</v>
       </c>
       <c r="C54" t="n">
-        <v>0.2146</v>
+        <v>0.1998</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.4903</v>
+        <v>-0.4855</v>
       </c>
       <c r="E54" t="n">
-        <v>0.3271</v>
+        <v>0.3046</v>
       </c>
       <c r="F54" t="n">
-        <v>0.3271</v>
+        <v>0.3046</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>0.3271</v>
+        <v>0.3046</v>
       </c>
       <c r="I54" t="n">
-        <v>0.3271</v>
+        <v>0.3046</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>137</v>
+        <v>109</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>0.3271</v>
+        <v>0.3046</v>
       </c>
       <c r="N54" t="n">
-        <v>137</v>
+        <v>109</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>reltuC</t>
+          <t>DAVEY</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.2728</v>
+        <v>0.2706</v>
       </c>
       <c r="C55" t="n">
-        <v>0.179</v>
+        <v>0.1775</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.5149</v>
+        <v>-0.501</v>
       </c>
       <c r="E55" t="n">
-        <v>0.2728</v>
+        <v>0.2706</v>
       </c>
       <c r="F55" t="n">
-        <v>0.2728</v>
+        <v>0.2706</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>0.2728</v>
+        <v>0.2706</v>
       </c>
       <c r="I55" t="n">
-        <v>0.2728</v>
+        <v>0.2706</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>182</v>
+        <v>40</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>0.2728</v>
+        <v>0.2706</v>
       </c>
       <c r="N55" t="n">
-        <v>182</v>
+        <v>40</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SmithZz</t>
+          <t>reltuC</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.2695</v>
+        <v>0.2212</v>
       </c>
       <c r="C56" t="n">
-        <v>0.1768</v>
+        <v>0.1451</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.5163</v>
+        <v>-0.5235</v>
       </c>
       <c r="E56" t="n">
-        <v>0.2695</v>
+        <v>0.2212</v>
       </c>
       <c r="F56" t="n">
-        <v>0.2695</v>
+        <v>0.2212</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>0.2695</v>
+        <v>0.2212</v>
       </c>
       <c r="I56" t="n">
-        <v>0.2695</v>
+        <v>0.2212</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>109</v>
+        <v>182</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>0.2695</v>
+        <v>0.2212</v>
       </c>
       <c r="N56" t="n">
-        <v>109</v>
+        <v>182</v>
       </c>
     </row>
     <row r="57">
@@ -3026,28 +3026,28 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.1796</v>
+        <v>0.1571</v>
       </c>
       <c r="C57" t="n">
-        <v>0.1178</v>
+        <v>0.1031</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.5569</v>
+        <v>-0.5527</v>
       </c>
       <c r="E57" t="n">
-        <v>0.1796</v>
+        <v>0.1571</v>
       </c>
       <c r="F57" t="n">
-        <v>0.1796</v>
+        <v>0.1571</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>0.1796</v>
+        <v>0.1571</v>
       </c>
       <c r="I57" t="n">
-        <v>0.1796</v>
+        <v>0.1571</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -3059,7 +3059,7 @@
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>0.1796</v>
+        <v>0.1571</v>
       </c>
       <c r="N57" t="n">
         <v>53</v>
@@ -3072,28 +3072,28 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.1072</v>
+        <v>0.1139</v>
       </c>
       <c r="C58" t="n">
-        <v>0.0703</v>
+        <v>0.0747</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.5896</v>
+        <v>-0.5724</v>
       </c>
       <c r="E58" t="n">
-        <v>0.1072</v>
+        <v>0.1139</v>
       </c>
       <c r="F58" t="n">
-        <v>0.1072</v>
+        <v>0.1139</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>0.1072</v>
+        <v>0.1139</v>
       </c>
       <c r="I58" t="n">
-        <v>0.1072</v>
+        <v>0.1139</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -3105,7 +3105,7 @@
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>0.1072</v>
+        <v>0.1139</v>
       </c>
       <c r="N58" t="n">
         <v>95</v>
@@ -3118,28 +3118,28 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.0075</v>
+        <v>0.0162</v>
       </c>
       <c r="C59" t="n">
-        <v>0.0049</v>
+        <v>0.0106</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.6346000000000001</v>
+        <v>-0.6168</v>
       </c>
       <c r="E59" t="n">
-        <v>0.0075</v>
+        <v>0.0162</v>
       </c>
       <c r="F59" t="n">
-        <v>0.0075</v>
+        <v>0.0162</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>0.0075</v>
+        <v>0.0162</v>
       </c>
       <c r="I59" t="n">
-        <v>0.0075</v>
+        <v>0.0162</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -3151,7 +3151,7 @@
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>0.0075</v>
+        <v>0.0162</v>
       </c>
       <c r="N59" t="n">
         <v>162</v>
@@ -3164,28 +3164,28 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.0825</v>
+        <v>-0.1061</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.0541</v>
+        <v>-0.0696</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.6753</v>
+        <v>-0.6725</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.0825</v>
+        <v>-0.1061</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.0825</v>
+        <v>-0.1061</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.0825</v>
+        <v>-0.1061</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.0825</v>
+        <v>-0.1061</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -3197,7 +3197,7 @@
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>-0.0825</v>
+        <v>-0.1061</v>
       </c>
       <c r="N60" t="n">
         <v>137</v>
@@ -3206,139 +3206,139 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>jkaem</t>
+          <t>Skadoodle</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.1524</v>
+        <v>-0.202</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.1</v>
+        <v>-0.1325</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.7068</v>
+        <v>-0.7161999999999999</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.1524</v>
+        <v>-0.202</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.1524</v>
+        <v>-0.202</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.1524</v>
+        <v>-0.202</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.1524</v>
+        <v>-0.202</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>94</v>
+        <v>44</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>-0.1524</v>
+        <v>-0.202</v>
       </c>
       <c r="N61" t="n">
-        <v>94</v>
+        <v>44</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Skadoodle</t>
+          <t>DEVIL</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.155</v>
+        <v>-0.2181</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.1017</v>
+        <v>-0.1431</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.708</v>
+        <v>-0.7235</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.155</v>
+        <v>-0.2181</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.155</v>
+        <v>-0.2181</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.155</v>
+        <v>-0.2181</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.155</v>
+        <v>-0.2181</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.155</v>
+        <v>-0.2181</v>
       </c>
       <c r="N62" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>DEVIL</t>
+          <t>jkaem</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.1937</v>
+        <v>-0.2304</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.1271</v>
+        <v>-0.1512</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.7255</v>
+        <v>-0.7291</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.1937</v>
+        <v>-0.2304</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.1937</v>
+        <v>-0.2304</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.1937</v>
+        <v>-0.2304</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.1937</v>
+        <v>-0.2304</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>53</v>
+        <v>94</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.1937</v>
+        <v>-0.2304</v>
       </c>
       <c r="N63" t="n">
-        <v>53</v>
+        <v>94</v>
       </c>
     </row>
     <row r="64">
@@ -3348,28 +3348,28 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.2246</v>
+        <v>-0.2823</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.1474</v>
+        <v>-0.1852</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.7393999999999999</v>
+        <v>-0.7527</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.2246</v>
+        <v>-0.2823</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.2246</v>
+        <v>-0.2823</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.2246</v>
+        <v>-0.2823</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.2246</v>
+        <v>-0.2823</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -3381,7 +3381,7 @@
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>-0.2246</v>
+        <v>-0.2823</v>
       </c>
       <c r="N64" t="n">
         <v>40</v>
@@ -3394,28 +3394,28 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.2324</v>
+        <v>-0.2857</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.1525</v>
+        <v>-0.1874</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.7429</v>
+        <v>-0.7543</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.2324</v>
+        <v>-0.2857</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.2324</v>
+        <v>-0.2857</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.2324</v>
+        <v>-0.2857</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.2324</v>
+        <v>-0.2857</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -3427,7 +3427,7 @@
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.2324</v>
+        <v>-0.2857</v>
       </c>
       <c r="N65" t="n">
         <v>94</v>
@@ -3440,28 +3440,28 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.2914</v>
+        <v>-0.3116</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.1912</v>
+        <v>-0.2044</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.7696</v>
+        <v>-0.766</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.2914</v>
+        <v>-0.3116</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.2914</v>
+        <v>-0.3116</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.2914</v>
+        <v>-0.3116</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.2914</v>
+        <v>-0.3116</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -3473,7 +3473,7 @@
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>-0.2914</v>
+        <v>-0.3116</v>
       </c>
       <c r="N66" t="n">
         <v>95</v>
@@ -3482,139 +3482,139 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>shroud</t>
+          <t>Zeus</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.3877</v>
+        <v>-0.3272</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.2544</v>
+        <v>-0.2147</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.8129999999999999</v>
+        <v>-0.7732</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.3877</v>
+        <v>-0.3272</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.3877</v>
+        <v>-0.365</v>
       </c>
       <c r="G67" t="n">
-        <v>0</v>
+        <v>0.0378</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.3877</v>
+        <v>-0.365</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.3877</v>
+        <v>-0.1971</v>
       </c>
       <c r="J67" t="n">
-        <v>0</v>
+        <v>0.0378</v>
       </c>
       <c r="K67" t="n">
-        <v>44</v>
+        <v>96</v>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="M67" t="n">
-        <v>-0.3877</v>
+        <v>-0.1593</v>
       </c>
       <c r="N67" t="n">
-        <v>44</v>
+        <v>201</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>friberg</t>
+          <t>shroud</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.4326</v>
+        <v>-0.4288</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.2838</v>
+        <v>-0.2813</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.8333</v>
+        <v>-0.8194</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.4326</v>
+        <v>-0.4288</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.4326</v>
+        <v>-0.4288</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.4326</v>
+        <v>-0.4288</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.4326</v>
+        <v>-0.4288</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>182</v>
+        <v>44</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>-0.4326</v>
+        <v>-0.4288</v>
       </c>
       <c r="N68" t="n">
-        <v>182</v>
+        <v>44</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Zeus</t>
+          <t>friberg</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-0.528</v>
+        <v>-0.4709</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.3464</v>
+        <v>-0.3089</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.8764</v>
+        <v>-0.8386</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.528</v>
+        <v>-0.4709</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.4658</v>
+        <v>-0.4709</v>
       </c>
       <c r="G69" t="n">
-        <v>-0.0622</v>
+        <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.4658</v>
+        <v>-0.4709</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.2422</v>
+        <v>-0.4709</v>
       </c>
       <c r="J69" t="n">
-        <v>-0.0622</v>
+        <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>96</v>
+        <v>182</v>
       </c>
       <c r="L69" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>-0.3044</v>
+        <v>-0.4709</v>
       </c>
       <c r="N69" t="n">
-        <v>201</v>
+        <v>182</v>
       </c>
     </row>
     <row r="70">
@@ -3624,28 +3624,28 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-0.5479000000000001</v>
+        <v>-0.5281</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.3595</v>
+        <v>-0.3465</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.8854</v>
+        <v>-0.8646</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.5479000000000001</v>
+        <v>-0.5281</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.5479000000000001</v>
+        <v>-0.5281</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>-0.5479000000000001</v>
+        <v>-0.5281</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.5479000000000001</v>
+        <v>-0.5281</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -3657,7 +3657,7 @@
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>-0.5479000000000001</v>
+        <v>-0.5281</v>
       </c>
       <c r="N70" t="n">
         <v>137</v>
@@ -3670,28 +3670,28 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-0.584</v>
+        <v>-0.6052</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.3831</v>
+        <v>-0.3971</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.9016999999999999</v>
+        <v>-0.8997000000000001</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.584</v>
+        <v>-0.6052</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.584</v>
+        <v>-0.6052</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>-0.584</v>
+        <v>-0.6052</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.584</v>
+        <v>-0.6052</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -3703,7 +3703,7 @@
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>-0.584</v>
+        <v>-0.6052</v>
       </c>
       <c r="N71" t="n">
         <v>53</v>
@@ -3716,28 +3716,28 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-0.6286</v>
+        <v>-0.6636</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.4124</v>
+        <v>-0.4354</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.9218</v>
+        <v>-0.9263</v>
       </c>
       <c r="E72" t="n">
-        <v>-0.6286</v>
+        <v>-0.6636</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.6286</v>
+        <v>-0.6636</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>-0.6286</v>
+        <v>-0.6636</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.6286</v>
+        <v>-0.6636</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -3749,7 +3749,7 @@
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>-0.6286</v>
+        <v>-0.6636</v>
       </c>
       <c r="N72" t="n">
         <v>44</v>
@@ -3762,28 +3762,28 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-0.6331</v>
+        <v>-0.6706</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.4154</v>
+        <v>-0.44</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.9238</v>
+        <v>-0.9295</v>
       </c>
       <c r="E73" t="n">
-        <v>-0.6331</v>
+        <v>-0.6706</v>
       </c>
       <c r="F73" t="n">
-        <v>-0.6331</v>
+        <v>-0.6706</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>-0.6331</v>
+        <v>-0.6706</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.6331</v>
+        <v>-0.6706</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -3795,7 +3795,7 @@
         <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>-0.6331</v>
+        <v>-0.6706</v>
       </c>
       <c r="N73" t="n">
         <v>44</v>
@@ -3808,28 +3808,28 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-0.7833</v>
+        <v>-0.8199</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.5139</v>
+        <v>-0.5379</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.9916</v>
+        <v>-0.9974</v>
       </c>
       <c r="E74" t="n">
-        <v>-0.7833</v>
+        <v>-0.8199</v>
       </c>
       <c r="F74" t="n">
-        <v>-0.7833</v>
+        <v>-0.8199</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>-0.7833</v>
+        <v>-0.8199</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.7833</v>
+        <v>-0.8199</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -3841,7 +3841,7 @@
         <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>-0.7833</v>
+        <v>-0.8199</v>
       </c>
       <c r="N74" t="n">
         <v>40</v>
@@ -3854,28 +3854,28 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-0.9145</v>
+        <v>-0.9302</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.6</v>
+        <v>-0.6103</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.0509</v>
+        <v>-1.0476</v>
       </c>
       <c r="E75" t="n">
-        <v>-0.9145</v>
+        <v>-0.9302</v>
       </c>
       <c r="F75" t="n">
-        <v>-0.9145</v>
+        <v>-0.9302</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>-0.9145</v>
+        <v>-0.9302</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.9145</v>
+        <v>-0.9302</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -3887,7 +3887,7 @@
         <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>-0.9145</v>
+        <v>-0.9302</v>
       </c>
       <c r="N75" t="n">
         <v>44</v>
@@ -3896,93 +3896,93 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>THREAT</t>
+          <t>jasonR</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-1.0201</v>
+        <v>-1.0481</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.6693</v>
+        <v>-0.6876</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.0985</v>
+        <v>-1.1013</v>
       </c>
       <c r="E76" t="n">
-        <v>-1.0201</v>
+        <v>-1.0481</v>
       </c>
       <c r="F76" t="n">
-        <v>-1.0201</v>
+        <v>-1.0481</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>-1.0201</v>
+        <v>-1.0481</v>
       </c>
       <c r="I76" t="n">
-        <v>-1.0201</v>
+        <v>-1.0481</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>182</v>
+        <v>40</v>
       </c>
       <c r="L76" t="n">
         <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>-1.0201</v>
+        <v>-1.0481</v>
       </c>
       <c r="N76" t="n">
-        <v>182</v>
+        <v>40</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>jasonR</t>
+          <t>THREAT</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-1.0261</v>
+        <v>-1.0766</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.6732</v>
+        <v>-0.7063</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.1012</v>
+        <v>-1.1143</v>
       </c>
       <c r="E77" t="n">
-        <v>-1.0261</v>
+        <v>-1.0766</v>
       </c>
       <c r="F77" t="n">
-        <v>-1.0261</v>
+        <v>-1.0766</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>-1.0261</v>
+        <v>-1.0766</v>
       </c>
       <c r="I77" t="n">
-        <v>-1.0261</v>
+        <v>-1.0766</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>40</v>
+        <v>182</v>
       </c>
       <c r="L77" t="n">
         <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>-1.0261</v>
+        <v>-1.0766</v>
       </c>
       <c r="N77" t="n">
-        <v>40</v>
+        <v>182</v>
       </c>
     </row>
     <row r="78">
@@ -3992,28 +3992,28 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-1.1499</v>
+        <v>-1.1625</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.7544</v>
+        <v>-0.7627</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.1571</v>
+        <v>-1.1534</v>
       </c>
       <c r="E78" t="n">
-        <v>-1.1499</v>
+        <v>-1.1625</v>
       </c>
       <c r="F78" t="n">
-        <v>-1.1499</v>
+        <v>-1.1625</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>-1.1499</v>
+        <v>-1.1625</v>
       </c>
       <c r="I78" t="n">
-        <v>-1.1499</v>
+        <v>-1.1625</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -4025,7 +4025,7 @@
         <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>-1.1499</v>
+        <v>-1.1625</v>
       </c>
       <c r="N78" t="n">
         <v>40</v>
@@ -4038,28 +4038,28 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-1.3088</v>
+        <v>-1.3084</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.8587</v>
+        <v>-0.8584000000000001</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.2289</v>
+        <v>-1.2198</v>
       </c>
       <c r="E79" t="n">
-        <v>-1.3088</v>
+        <v>-1.3084</v>
       </c>
       <c r="F79" t="n">
-        <v>-1.3088</v>
+        <v>-1.3084</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>-1.3088</v>
+        <v>-1.3084</v>
       </c>
       <c r="I79" t="n">
-        <v>-1.3088</v>
+        <v>-1.3084</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -4071,7 +4071,7 @@
         <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>-1.3088</v>
+        <v>-1.3084</v>
       </c>
       <c r="N79" t="n">
         <v>162</v>
@@ -4084,31 +4084,31 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-2.7139</v>
+        <v>-2.4509</v>
       </c>
       <c r="C80" t="n">
-        <v>-1.7805</v>
+        <v>-1.608</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.8632</v>
+        <v>-1.7399</v>
       </c>
       <c r="E80" t="n">
-        <v>-2.7139</v>
+        <v>-2.4509</v>
       </c>
       <c r="F80" t="n">
-        <v>-2.2854</v>
+        <v>-1.9871</v>
       </c>
       <c r="G80" t="n">
-        <v>-0.4285</v>
+        <v>-0.4638</v>
       </c>
       <c r="H80" t="n">
-        <v>-2.2854</v>
+        <v>-1.9871</v>
       </c>
       <c r="I80" t="n">
-        <v>-1.1883</v>
+        <v>-1.073</v>
       </c>
       <c r="J80" t="n">
-        <v>-0.4285</v>
+        <v>-0.4638</v>
       </c>
       <c r="K80" t="n">
         <v>98</v>
@@ -4117,7 +4117,7 @@
         <v>51</v>
       </c>
       <c r="M80" t="n">
-        <v>-1.6168</v>
+        <v>-1.5368</v>
       </c>
       <c r="N80" t="n">
         <v>149</v>
@@ -4130,28 +4130,28 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-3.3304</v>
+        <v>-3.2177</v>
       </c>
       <c r="C81" t="n">
-        <v>-2.185</v>
+        <v>-2.1111</v>
       </c>
       <c r="D81" t="n">
-        <v>-2.1415</v>
+        <v>-2.089</v>
       </c>
       <c r="E81" t="n">
-        <v>-3.3304</v>
+        <v>-3.2177</v>
       </c>
       <c r="F81" t="n">
-        <v>-3.3304</v>
+        <v>-3.2177</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>-3.3304</v>
+        <v>-3.2177</v>
       </c>
       <c r="I81" t="n">
-        <v>-3.3304</v>
+        <v>-3.2177</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -4163,7 +4163,7 @@
         <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>-3.3304</v>
+        <v>-3.2177</v>
       </c>
       <c r="N81" t="n">
         <v>182</v>
@@ -4269,10 +4269,10 @@
         <v>1.16</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3658</v>
+        <v>0.3654</v>
       </c>
       <c r="J2" t="n">
-        <v>13.1688</v>
+        <v>13.1544</v>
       </c>
     </row>
     <row r="3">
@@ -4309,10 +4309,10 @@
         <v>1.14</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3274</v>
+        <v>0.3293</v>
       </c>
       <c r="J3" t="n">
-        <v>11.7864</v>
+        <v>11.8548</v>
       </c>
     </row>
     <row r="4">
@@ -4349,10 +4349,10 @@
         <v>0.99</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0202</v>
+        <v>-0.0249</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.7272</v>
+        <v>-0.8964</v>
       </c>
     </row>
     <row r="5">
@@ -4389,10 +4389,10 @@
         <v>0.91</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1224</v>
+        <v>-0.1349</v>
       </c>
       <c r="J5" t="n">
-        <v>-4.4064</v>
+        <v>-4.8564</v>
       </c>
     </row>
     <row r="6">
@@ -4429,10 +4429,10 @@
         <v>0.77</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2681</v>
+        <v>-0.2812</v>
       </c>
       <c r="J6" t="n">
-        <v>-9.6516</v>
+        <v>-10.1232</v>
       </c>
     </row>
     <row r="7">
@@ -4469,10 +4469,10 @@
         <v>1.4</v>
       </c>
       <c r="I7" t="n">
-        <v>1.0052</v>
+        <v>0.9503</v>
       </c>
       <c r="J7" t="n">
-        <v>36.1872</v>
+        <v>34.2108</v>
       </c>
     </row>
     <row r="8">
@@ -4509,10 +4509,10 @@
         <v>1.36</v>
       </c>
       <c r="I8" t="n">
-        <v>0.929</v>
+        <v>0.8725000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>33.444</v>
+        <v>31.41</v>
       </c>
     </row>
     <row r="9">
@@ -4549,10 +4549,10 @@
         <v>1.16</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4626</v>
+        <v>0.4568</v>
       </c>
       <c r="J9" t="n">
-        <v>16.6536</v>
+        <v>16.4448</v>
       </c>
     </row>
     <row r="10">
@@ -4589,10 +4589,10 @@
         <v>1.05</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1523</v>
+        <v>0.1695</v>
       </c>
       <c r="J10" t="n">
-        <v>5.4828</v>
+        <v>6.102</v>
       </c>
     </row>
     <row r="11">
@@ -4629,10 +4629,10 @@
         <v>1.03</v>
       </c>
       <c r="I11" t="n">
-        <v>0.08450000000000001</v>
+        <v>0.1041</v>
       </c>
       <c r="J11" t="n">
-        <v>3.042</v>
+        <v>3.7476</v>
       </c>
     </row>
     <row r="12">
@@ -4669,10 +4669,10 @@
         <v>0.97</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1021</v>
+        <v>0.0426</v>
       </c>
       <c r="J12" t="n">
-        <v>1.8378</v>
+        <v>0.7668</v>
       </c>
     </row>
     <row r="13">
@@ -4709,10 +4709,10 @@
         <v>0.67</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.3048</v>
+        <v>-0.3287</v>
       </c>
       <c r="J13" t="n">
-        <v>-5.4864</v>
+        <v>-5.9166</v>
       </c>
     </row>
     <row r="14">
@@ -4749,10 +4749,10 @@
         <v>0.53</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.4338</v>
+        <v>-0.4514</v>
       </c>
       <c r="J14" t="n">
-        <v>-7.8084</v>
+        <v>-8.1252</v>
       </c>
     </row>
     <row r="15">
@@ -4789,10 +4789,10 @@
         <v>0.4</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.5570000000000001</v>
+        <v>-0.5659</v>
       </c>
       <c r="J15" t="n">
-        <v>-10.026</v>
+        <v>-10.1862</v>
       </c>
     </row>
     <row r="16">
@@ -4829,10 +4829,10 @@
         <v>0.35</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6052</v>
+        <v>-0.6102</v>
       </c>
       <c r="J16" t="n">
-        <v>-10.8936</v>
+        <v>-10.9836</v>
       </c>
     </row>
     <row r="17">
@@ -4869,10 +4869,10 @@
         <v>1.89</v>
       </c>
       <c r="I17" t="n">
-        <v>1.5237</v>
+        <v>1.6649</v>
       </c>
       <c r="J17" t="n">
-        <v>27.4266</v>
+        <v>29.9682</v>
       </c>
     </row>
     <row r="18">
@@ -4909,10 +4909,10 @@
         <v>1.79</v>
       </c>
       <c r="I18" t="n">
-        <v>1.413</v>
+        <v>1.5392</v>
       </c>
       <c r="J18" t="n">
-        <v>25.434</v>
+        <v>27.7056</v>
       </c>
     </row>
     <row r="19">
@@ -4949,10 +4949,10 @@
         <v>1.64</v>
       </c>
       <c r="I19" t="n">
-        <v>1.2453</v>
+        <v>1.3079</v>
       </c>
       <c r="J19" t="n">
-        <v>22.4154</v>
+        <v>23.5422</v>
       </c>
     </row>
     <row r="20">
@@ -4989,10 +4989,10 @@
         <v>1.38</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8956</v>
+        <v>0.8568</v>
       </c>
       <c r="J20" t="n">
-        <v>16.1208</v>
+        <v>15.4224</v>
       </c>
     </row>
     <row r="21">
@@ -5029,10 +5029,10 @@
         <v>1.26</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6257</v>
+        <v>0.6193</v>
       </c>
       <c r="J21" t="n">
-        <v>11.2626</v>
+        <v>11.1474</v>
       </c>
     </row>
     <row r="22">
@@ -5069,10 +5069,10 @@
         <v>1.2</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4277</v>
+        <v>0.4643</v>
       </c>
       <c r="J22" t="n">
-        <v>14.5418</v>
+        <v>15.7862</v>
       </c>
     </row>
     <row r="23">
@@ -5109,10 +5109,10 @@
         <v>0.97</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.0353</v>
+        <v>-0.047</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.2002</v>
+        <v>-1.598</v>
       </c>
     </row>
     <row r="24">
@@ -5149,10 +5149,10 @@
         <v>0.8</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.2226</v>
+        <v>-0.2397</v>
       </c>
       <c r="J24" t="n">
-        <v>-7.5684</v>
+        <v>-8.149800000000001</v>
       </c>
     </row>
     <row r="25">
@@ -5189,10 +5189,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3292</v>
+        <v>-0.3439</v>
       </c>
       <c r="J25" t="n">
-        <v>-11.1928</v>
+        <v>-11.6926</v>
       </c>
     </row>
     <row r="26">
@@ -5229,10 +5229,10 @@
         <v>0.67</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.3482</v>
+        <v>-0.3622</v>
       </c>
       <c r="J26" t="n">
-        <v>-11.8388</v>
+        <v>-12.3148</v>
       </c>
     </row>
     <row r="27">
@@ -5269,10 +5269,10 @@
         <v>1.36</v>
       </c>
       <c r="I27" t="n">
-        <v>0.6912</v>
+        <v>0.7647</v>
       </c>
       <c r="J27" t="n">
-        <v>23.5008</v>
+        <v>25.9998</v>
       </c>
     </row>
     <row r="28">
@@ -5309,10 +5309,10 @@
         <v>1.26</v>
       </c>
       <c r="I28" t="n">
-        <v>0.5547</v>
+        <v>0.6145</v>
       </c>
       <c r="J28" t="n">
-        <v>18.8598</v>
+        <v>20.893</v>
       </c>
     </row>
     <row r="29">
@@ -5349,10 +5349,10 @@
         <v>1.23</v>
       </c>
       <c r="I29" t="n">
-        <v>0.5125999999999999</v>
+        <v>0.5676</v>
       </c>
       <c r="J29" t="n">
-        <v>17.4284</v>
+        <v>19.2984</v>
       </c>
     </row>
     <row r="30">
@@ -5389,10 +5389,10 @@
         <v>1.17</v>
       </c>
       <c r="I30" t="n">
-        <v>0.4273</v>
+        <v>0.4711</v>
       </c>
       <c r="J30" t="n">
-        <v>14.5282</v>
+        <v>16.0174</v>
       </c>
     </row>
     <row r="31">
@@ -5429,10 +5429,10 @@
         <v>0.83</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.5893</v>
+        <v>-0.5501</v>
       </c>
       <c r="J31" t="n">
-        <v>-20.0362</v>
+        <v>-18.7034</v>
       </c>
     </row>
     <row r="32">
@@ -5469,10 +5469,10 @@
         <v>1.16</v>
       </c>
       <c r="I32" t="n">
-        <v>0.3546</v>
+        <v>0.3676</v>
       </c>
       <c r="J32" t="n">
-        <v>12.411</v>
+        <v>12.866</v>
       </c>
     </row>
     <row r="33">
@@ -5509,10 +5509,10 @@
         <v>1.15</v>
       </c>
       <c r="I33" t="n">
-        <v>0.3423</v>
+        <v>0.3496</v>
       </c>
       <c r="J33" t="n">
-        <v>11.9805</v>
+        <v>12.236</v>
       </c>
     </row>
     <row r="34">
@@ -5549,10 +5549,10 @@
         <v>1.07</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1873</v>
+        <v>0.1943</v>
       </c>
       <c r="J34" t="n">
-        <v>6.5555</v>
+        <v>6.8005</v>
       </c>
     </row>
     <row r="35">
@@ -5589,10 +5589,10 @@
         <v>0.89</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1435</v>
+        <v>-0.1568</v>
       </c>
       <c r="J35" t="n">
-        <v>-5.0225</v>
+        <v>-5.488</v>
       </c>
     </row>
     <row r="36">
@@ -5629,10 +5629,10 @@
         <v>0.65</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.3814</v>
+        <v>-0.3916</v>
       </c>
       <c r="J36" t="n">
-        <v>-13.349</v>
+        <v>-13.706</v>
       </c>
     </row>
     <row r="37">
@@ -5669,10 +5669,10 @@
         <v>1.48</v>
       </c>
       <c r="I37" t="n">
-        <v>0.8552999999999999</v>
+        <v>0.9411</v>
       </c>
       <c r="J37" t="n">
-        <v>29.9355</v>
+        <v>32.9385</v>
       </c>
     </row>
     <row r="38">
@@ -5709,10 +5709,10 @@
         <v>1.37</v>
       </c>
       <c r="I38" t="n">
-        <v>0.7095</v>
+        <v>0.7836</v>
       </c>
       <c r="J38" t="n">
-        <v>24.8325</v>
+        <v>27.426</v>
       </c>
     </row>
     <row r="39">
@@ -5749,10 +5749,10 @@
         <v>1.08</v>
       </c>
       <c r="I39" t="n">
-        <v>0.2572</v>
+        <v>0.2652</v>
       </c>
       <c r="J39" t="n">
-        <v>9.002000000000001</v>
+        <v>9.282</v>
       </c>
     </row>
     <row r="40">
@@ -5789,10 +5789,10 @@
         <v>0.97</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.1686</v>
+        <v>-0.1622</v>
       </c>
       <c r="J40" t="n">
-        <v>-5.901</v>
+        <v>-5.677</v>
       </c>
     </row>
     <row r="41">
@@ -5829,10 +5829,10 @@
         <v>0.84</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.5570000000000001</v>
+        <v>-0.5223</v>
       </c>
       <c r="J41" t="n">
-        <v>-19.495</v>
+        <v>-18.2805</v>
       </c>
     </row>
     <row r="42">
@@ -5869,10 +5869,10 @@
         <v>1.45</v>
       </c>
       <c r="I42" t="n">
-        <v>0.8561</v>
+        <v>0.9344</v>
       </c>
       <c r="J42" t="n">
-        <v>25.683</v>
+        <v>28.032</v>
       </c>
     </row>
     <row r="43">
@@ -5909,10 +5909,10 @@
         <v>1.21</v>
       </c>
       <c r="I43" t="n">
-        <v>0.5132</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="J43" t="n">
-        <v>15.396</v>
+        <v>16.83</v>
       </c>
     </row>
     <row r="44">
@@ -5949,10 +5949,10 @@
         <v>0.9</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.3546</v>
+        <v>-0.346</v>
       </c>
       <c r="J44" t="n">
-        <v>-10.638</v>
+        <v>-10.38</v>
       </c>
     </row>
     <row r="45">
@@ -5989,10 +5989,10 @@
         <v>0.84</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.5214</v>
+        <v>-0.4973</v>
       </c>
       <c r="J45" t="n">
-        <v>-15.642</v>
+        <v>-14.919</v>
       </c>
     </row>
     <row r="46">
@@ -6029,10 +6029,10 @@
         <v>0.7</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.8796</v>
+        <v>-0.8132</v>
       </c>
       <c r="J46" t="n">
-        <v>-26.388</v>
+        <v>-24.396</v>
       </c>
     </row>
     <row r="47">
@@ -6069,10 +6069,10 @@
         <v>1.08</v>
       </c>
       <c r="I47" t="n">
-        <v>0.2146</v>
+        <v>0.2194</v>
       </c>
       <c r="J47" t="n">
-        <v>6.438</v>
+        <v>6.582</v>
       </c>
     </row>
     <row r="48">
@@ -6109,10 +6109,10 @@
         <v>0.99</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.0178</v>
+        <v>-0.0232</v>
       </c>
       <c r="J48" t="n">
-        <v>-0.534</v>
+        <v>-0.696</v>
       </c>
     </row>
     <row r="49">
@@ -6149,10 +6149,10 @@
         <v>0.95</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.07240000000000001</v>
+        <v>-0.0834</v>
       </c>
       <c r="J49" t="n">
-        <v>-2.172</v>
+        <v>-2.502</v>
       </c>
     </row>
     <row r="50">
@@ -6189,10 +6189,10 @@
         <v>0.95</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.07240000000000001</v>
+        <v>-0.0834</v>
       </c>
       <c r="J50" t="n">
-        <v>-2.172</v>
+        <v>-2.502</v>
       </c>
     </row>
     <row r="51">
@@ -6229,10 +6229,10 @@
         <v>0.84</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.1939</v>
+        <v>-0.2084</v>
       </c>
       <c r="J51" t="n">
-        <v>-5.817</v>
+        <v>-6.252</v>
       </c>
     </row>
     <row r="52">
@@ -6269,10 +6269,10 @@
         <v>1.76</v>
       </c>
       <c r="I52" t="n">
-        <v>1.1431</v>
+        <v>1.2578</v>
       </c>
       <c r="J52" t="n">
-        <v>24.0051</v>
+        <v>26.4138</v>
       </c>
     </row>
     <row r="53">
@@ -6309,10 +6309,10 @@
         <v>1.43</v>
       </c>
       <c r="I53" t="n">
-        <v>0.7476</v>
+        <v>0.8336</v>
       </c>
       <c r="J53" t="n">
-        <v>15.6996</v>
+        <v>17.5056</v>
       </c>
     </row>
     <row r="54">
@@ -6349,10 +6349,10 @@
         <v>1.39</v>
       </c>
       <c r="I54" t="n">
-        <v>0.6986</v>
+        <v>0.7799</v>
       </c>
       <c r="J54" t="n">
-        <v>14.6706</v>
+        <v>16.3779</v>
       </c>
     </row>
     <row r="55">
@@ -6389,10 +6389,10 @@
         <v>1.34</v>
       </c>
       <c r="I55" t="n">
-        <v>0.6369</v>
+        <v>0.7117</v>
       </c>
       <c r="J55" t="n">
-        <v>13.3749</v>
+        <v>14.9457</v>
       </c>
     </row>
     <row r="56">
@@ -6429,10 +6429,10 @@
         <v>0.98</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.1866</v>
+        <v>-0.1643</v>
       </c>
       <c r="J56" t="n">
-        <v>-3.9186</v>
+        <v>-3.4503</v>
       </c>
     </row>
     <row r="57">
@@ -6469,10 +6469,10 @@
         <v>0.78</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.2246</v>
+        <v>-0.2456</v>
       </c>
       <c r="J57" t="n">
-        <v>-4.7166</v>
+        <v>-5.1576</v>
       </c>
     </row>
     <row r="58">
@@ -6509,10 +6509,10 @@
         <v>0.78</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.2246</v>
+        <v>-0.2456</v>
       </c>
       <c r="J58" t="n">
-        <v>-4.7166</v>
+        <v>-5.1576</v>
       </c>
     </row>
     <row r="59">
@@ -6549,10 +6549,10 @@
         <v>0.77</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.2346</v>
+        <v>-0.2554</v>
       </c>
       <c r="J59" t="n">
-        <v>-4.9266</v>
+        <v>-5.3634</v>
       </c>
     </row>
     <row r="60">
@@ -6589,10 +6589,10 @@
         <v>0.75</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.254</v>
+        <v>-0.2744</v>
       </c>
       <c r="J60" t="n">
-        <v>-5.334</v>
+        <v>-5.7624</v>
       </c>
     </row>
     <row r="61">
@@ -6629,10 +6629,10 @@
         <v>0.52</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.4673</v>
+        <v>-0.479</v>
       </c>
       <c r="J61" t="n">
-        <v>-9.8133</v>
+        <v>-10.059</v>
       </c>
     </row>
     <row r="62">
@@ -6669,10 +6669,10 @@
         <v>1.18</v>
       </c>
       <c r="I62" t="n">
-        <v>0.3153</v>
+        <v>0.3187</v>
       </c>
       <c r="J62" t="n">
-        <v>11.3508</v>
+        <v>11.4732</v>
       </c>
     </row>
     <row r="63">
@@ -6709,10 +6709,10 @@
         <v>0.98</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.0339</v>
+        <v>-0.0411</v>
       </c>
       <c r="J63" t="n">
-        <v>-1.2204</v>
+        <v>-1.4796</v>
       </c>
     </row>
     <row r="64">
@@ -6749,10 +6749,10 @@
         <v>0.91</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.1196</v>
+        <v>-0.1328</v>
       </c>
       <c r="J64" t="n">
-        <v>-4.3056</v>
+        <v>-4.7808</v>
       </c>
     </row>
     <row r="65">
@@ -6789,10 +6789,10 @@
         <v>0.89</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.1417</v>
+        <v>-0.1555</v>
       </c>
       <c r="J65" t="n">
-        <v>-5.1012</v>
+        <v>-5.598</v>
       </c>
     </row>
     <row r="66">
@@ -6829,10 +6829,10 @@
         <v>0.88</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.1525</v>
+        <v>-0.1665</v>
       </c>
       <c r="J66" t="n">
-        <v>-5.49</v>
+        <v>-5.994</v>
       </c>
     </row>
     <row r="67">
@@ -6869,10 +6869,10 @@
         <v>1.33</v>
       </c>
       <c r="I67" t="n">
-        <v>0.4445</v>
+        <v>0.4544</v>
       </c>
       <c r="J67" t="n">
-        <v>16.002</v>
+        <v>16.3584</v>
       </c>
     </row>
     <row r="68">
@@ -6909,10 +6909,10 @@
         <v>1.26</v>
       </c>
       <c r="I68" t="n">
-        <v>0.3614</v>
+        <v>0.375</v>
       </c>
       <c r="J68" t="n">
-        <v>13.0104</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="69">
@@ -6949,10 +6949,10 @@
         <v>1.08</v>
       </c>
       <c r="I69" t="n">
-        <v>0.1307</v>
+        <v>0.1465</v>
       </c>
       <c r="J69" t="n">
-        <v>4.7052</v>
+        <v>5.274</v>
       </c>
     </row>
     <row r="70">
@@ -6989,10 +6989,10 @@
         <v>1.04</v>
       </c>
       <c r="I70" t="n">
-        <v>0.068</v>
+        <v>0.08169999999999999</v>
       </c>
       <c r="J70" t="n">
-        <v>2.448</v>
+        <v>2.9412</v>
       </c>
     </row>
     <row r="71">
@@ -7029,10 +7029,10 @@
         <v>0.97</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.06370000000000001</v>
+        <v>-0.0687</v>
       </c>
       <c r="J71" t="n">
-        <v>-2.2932</v>
+        <v>-2.4732</v>
       </c>
     </row>
     <row r="72">
@@ -7069,10 +7069,10 @@
         <v>1.59</v>
       </c>
       <c r="I72" t="n">
-        <v>1.2294</v>
+        <v>1.2031</v>
       </c>
       <c r="J72" t="n">
-        <v>31.9644</v>
+        <v>31.2806</v>
       </c>
     </row>
     <row r="73">
@@ -7109,10 +7109,10 @@
         <v>1.4</v>
       </c>
       <c r="I73" t="n">
-        <v>0.9801</v>
+        <v>0.9275</v>
       </c>
       <c r="J73" t="n">
-        <v>25.4826</v>
+        <v>24.115</v>
       </c>
     </row>
     <row r="74">
@@ -7149,10 +7149,10 @@
         <v>1.24</v>
       </c>
       <c r="I74" t="n">
-        <v>0.636</v>
+        <v>0.6173</v>
       </c>
       <c r="J74" t="n">
-        <v>16.536</v>
+        <v>16.0498</v>
       </c>
     </row>
     <row r="75">
@@ -7189,10 +7189,10 @@
         <v>1.24</v>
       </c>
       <c r="I75" t="n">
-        <v>0.636</v>
+        <v>0.6173</v>
       </c>
       <c r="J75" t="n">
-        <v>16.536</v>
+        <v>16.0498</v>
       </c>
     </row>
     <row r="76">
@@ -7229,10 +7229,10 @@
         <v>1.07</v>
       </c>
       <c r="I76" t="n">
-        <v>0.1892</v>
+        <v>0.2107</v>
       </c>
       <c r="J76" t="n">
-        <v>4.9192</v>
+        <v>5.4782</v>
       </c>
     </row>
     <row r="77">
@@ -7269,10 +7269,10 @@
         <v>1.21</v>
       </c>
       <c r="I77" t="n">
-        <v>0.5271</v>
+        <v>0.5023</v>
       </c>
       <c r="J77" t="n">
-        <v>13.7046</v>
+        <v>13.0598</v>
       </c>
     </row>
     <row r="78">
@@ -7309,10 +7309,10 @@
         <v>0.99</v>
       </c>
       <c r="I78" t="n">
-        <v>0.0015</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="J78" t="n">
-        <v>0.039</v>
+        <v>-0.2288</v>
       </c>
     </row>
     <row r="79">
@@ -7349,10 +7349,10 @@
         <v>0.77</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.2485</v>
+        <v>-0.266</v>
       </c>
       <c r="J79" t="n">
-        <v>-6.461</v>
+        <v>-6.916</v>
       </c>
     </row>
     <row r="80">
@@ -7389,10 +7389,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.3254</v>
+        <v>-0.3409</v>
       </c>
       <c r="J80" t="n">
-        <v>-8.4604</v>
+        <v>-8.8634</v>
       </c>
     </row>
     <row r="81">
@@ -7429,10 +7429,10 @@
         <v>0.53</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.4748</v>
+        <v>-0.4835</v>
       </c>
       <c r="J81" t="n">
-        <v>-12.3448</v>
+        <v>-12.571</v>
       </c>
     </row>
     <row r="82">
@@ -7469,10 +7469,10 @@
         <v>1.27</v>
       </c>
       <c r="I82" t="n">
-        <v>0.748</v>
+        <v>0.7083</v>
       </c>
       <c r="J82" t="n">
-        <v>20.196</v>
+        <v>19.1241</v>
       </c>
     </row>
     <row r="83">
@@ -7509,10 +7509,10 @@
         <v>1.19</v>
       </c>
       <c r="I83" t="n">
-        <v>0.5522</v>
+        <v>0.5345</v>
       </c>
       <c r="J83" t="n">
-        <v>14.9094</v>
+        <v>14.4315</v>
       </c>
     </row>
     <row r="84">
@@ -7549,10 +7549,10 @@
         <v>1.11</v>
       </c>
       <c r="I84" t="n">
-        <v>0.3472</v>
+        <v>0.3475</v>
       </c>
       <c r="J84" t="n">
-        <v>9.3744</v>
+        <v>9.3825</v>
       </c>
     </row>
     <row r="85">
@@ -7589,10 +7589,10 @@
         <v>1.02</v>
       </c>
       <c r="I85" t="n">
-        <v>0.06759999999999999</v>
+        <v>0.08169999999999999</v>
       </c>
       <c r="J85" t="n">
-        <v>1.8252</v>
+        <v>2.2059</v>
       </c>
     </row>
     <row r="86">
@@ -7629,10 +7629,10 @@
         <v>1.01</v>
       </c>
       <c r="I86" t="n">
-        <v>0.0267</v>
+        <v>0.0404</v>
       </c>
       <c r="J86" t="n">
-        <v>0.7209</v>
+        <v>1.0908</v>
       </c>
     </row>
     <row r="87">
@@ -7669,10 +7669,10 @@
         <v>1.25</v>
       </c>
       <c r="I87" t="n">
-        <v>0.5402</v>
+        <v>0.5253</v>
       </c>
       <c r="J87" t="n">
-        <v>14.5854</v>
+        <v>14.1831</v>
       </c>
     </row>
     <row r="88">
@@ -7709,10 +7709,10 @@
         <v>1</v>
       </c>
       <c r="I88" t="n">
-        <v>0.0042</v>
+        <v>0.003</v>
       </c>
       <c r="J88" t="n">
-        <v>0.1134</v>
+        <v>0.081</v>
       </c>
     </row>
     <row r="89">
@@ -7749,10 +7749,10 @@
         <v>0.9</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.1309</v>
+        <v>-0.1444</v>
       </c>
       <c r="J89" t="n">
-        <v>-3.5343</v>
+        <v>-3.8988</v>
       </c>
     </row>
     <row r="90">
@@ -7789,10 +7789,10 @@
         <v>0.86</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.174</v>
+        <v>-0.1882</v>
       </c>
       <c r="J90" t="n">
-        <v>-4.698</v>
+        <v>-5.0814</v>
       </c>
     </row>
     <row r="91">
@@ -7829,10 +7829,10 @@
         <v>0.84</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.1948</v>
+        <v>-0.2092</v>
       </c>
       <c r="J91" t="n">
-        <v>-5.2596</v>
+        <v>-5.6484</v>
       </c>
     </row>
     <row r="92">
@@ -7869,10 +7869,10 @@
         <v>1.27</v>
       </c>
       <c r="I92" t="n">
-        <v>0.7466</v>
+        <v>0.7073</v>
       </c>
       <c r="J92" t="n">
-        <v>21.6514</v>
+        <v>20.5117</v>
       </c>
     </row>
     <row r="93">
@@ -7909,10 +7909,10 @@
         <v>1.18</v>
       </c>
       <c r="I93" t="n">
-        <v>0.5261</v>
+        <v>0.5112</v>
       </c>
       <c r="J93" t="n">
-        <v>15.2569</v>
+        <v>14.8248</v>
       </c>
     </row>
     <row r="94">
@@ -7949,10 +7949,10 @@
         <v>1.16</v>
       </c>
       <c r="I94" t="n">
-        <v>0.4755</v>
+        <v>0.4655</v>
       </c>
       <c r="J94" t="n">
-        <v>13.7895</v>
+        <v>13.4995</v>
       </c>
     </row>
     <row r="95">
@@ -7989,10 +7989,10 @@
         <v>1.02</v>
       </c>
       <c r="I95" t="n">
-        <v>0.06660000000000001</v>
+        <v>0.081</v>
       </c>
       <c r="J95" t="n">
-        <v>1.9314</v>
+        <v>2.349</v>
       </c>
     </row>
     <row r="96">
@@ -8029,10 +8029,10 @@
         <v>0.99</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.08400000000000001</v>
+        <v>-0.0798</v>
       </c>
       <c r="J96" t="n">
-        <v>-2.436</v>
+        <v>-2.3142</v>
       </c>
     </row>
     <row r="97">
@@ -8069,10 +8069,10 @@
         <v>1.66</v>
       </c>
       <c r="I97" t="n">
-        <v>1.1071</v>
+        <v>1.0773</v>
       </c>
       <c r="J97" t="n">
-        <v>32.1059</v>
+        <v>31.2417</v>
       </c>
     </row>
     <row r="98">
@@ -8109,10 +8109,10 @@
         <v>1.1</v>
       </c>
       <c r="I98" t="n">
-        <v>0.2351</v>
+        <v>0.2443</v>
       </c>
       <c r="J98" t="n">
-        <v>6.8179</v>
+        <v>7.0847</v>
       </c>
     </row>
     <row r="99">
@@ -8149,10 +8149,10 @@
         <v>0.86</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.1833</v>
+        <v>-0.1955</v>
       </c>
       <c r="J99" t="n">
-        <v>-5.3157</v>
+        <v>-5.6695</v>
       </c>
     </row>
     <row r="100">
@@ -8189,10 +8189,10 @@
         <v>0.86</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.1833</v>
+        <v>-0.1955</v>
       </c>
       <c r="J100" t="n">
-        <v>-5.3157</v>
+        <v>-5.6695</v>
       </c>
     </row>
     <row r="101">
@@ -8229,10 +8229,10 @@
         <v>0.78</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.2648</v>
+        <v>-0.2767</v>
       </c>
       <c r="J101" t="n">
-        <v>-7.6792</v>
+        <v>-8.0243</v>
       </c>
     </row>
     <row r="102">
@@ -8269,10 +8269,10 @@
         <v>1.82</v>
       </c>
       <c r="I102" t="n">
-        <v>1.4877</v>
+        <v>1.4796</v>
       </c>
       <c r="J102" t="n">
-        <v>32.7294</v>
+        <v>32.5512</v>
       </c>
     </row>
     <row r="103">
@@ -8309,10 +8309,10 @@
         <v>1.51</v>
       </c>
       <c r="I103" t="n">
-        <v>1.1196</v>
+        <v>1.0875</v>
       </c>
       <c r="J103" t="n">
-        <v>24.6312</v>
+        <v>23.925</v>
       </c>
     </row>
     <row r="104">
@@ -8349,10 +8349,10 @@
         <v>1.37</v>
       </c>
       <c r="I104" t="n">
-        <v>0.912</v>
+        <v>0.8643</v>
       </c>
       <c r="J104" t="n">
-        <v>20.064</v>
+        <v>19.0146</v>
       </c>
     </row>
     <row r="105">
@@ -8389,10 +8389,10 @@
         <v>1.13</v>
       </c>
       <c r="I105" t="n">
-        <v>0.3449</v>
+        <v>0.3581</v>
       </c>
       <c r="J105" t="n">
-        <v>7.5878</v>
+        <v>7.8782</v>
       </c>
     </row>
     <row r="106">
@@ -8429,10 +8429,10 @@
         <v>1.05</v>
       </c>
       <c r="I106" t="n">
-        <v>0.1111</v>
+        <v>0.1407</v>
       </c>
       <c r="J106" t="n">
-        <v>2.4442</v>
+        <v>3.0954</v>
       </c>
     </row>
     <row r="107">
@@ -8469,10 +8469,10 @@
         <v>0.76</v>
       </c>
       <c r="I107" t="n">
-        <v>-0.2409</v>
+        <v>-0.2623</v>
       </c>
       <c r="J107" t="n">
-        <v>-5.2998</v>
+        <v>-5.7706</v>
       </c>
     </row>
     <row r="108">
@@ -8509,10 +8509,10 @@
         <v>0.74</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.2605</v>
+        <v>-0.2815</v>
       </c>
       <c r="J108" t="n">
-        <v>-5.731</v>
+        <v>-6.193</v>
       </c>
     </row>
     <row r="109">
@@ -8549,10 +8549,10 @@
         <v>0.74</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.2605</v>
+        <v>-0.2815</v>
       </c>
       <c r="J109" t="n">
-        <v>-5.731</v>
+        <v>-6.193</v>
       </c>
     </row>
     <row r="110">
@@ -8589,10 +8589,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.3062</v>
+        <v>-0.3261</v>
       </c>
       <c r="J110" t="n">
-        <v>-6.7364</v>
+        <v>-7.1742</v>
       </c>
     </row>
     <row r="111">
@@ -8629,10 +8629,10 @@
         <v>0.57</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.4173</v>
+        <v>-0.4324</v>
       </c>
       <c r="J111" t="n">
-        <v>-9.1806</v>
+        <v>-9.5128</v>
       </c>
     </row>
     <row r="112">
@@ -8669,10 +8669,10 @@
         <v>1.45</v>
       </c>
       <c r="I112" t="n">
-        <v>1.0812</v>
+        <v>1.0367</v>
       </c>
       <c r="J112" t="n">
-        <v>28.1112</v>
+        <v>26.9542</v>
       </c>
     </row>
     <row r="113">
@@ -8709,10 +8709,10 @@
         <v>1.37</v>
       </c>
       <c r="I113" t="n">
-        <v>0.9552</v>
+        <v>0.8963</v>
       </c>
       <c r="J113" t="n">
-        <v>24.8352</v>
+        <v>23.3038</v>
       </c>
     </row>
     <row r="114">
@@ -8749,10 +8749,10 @@
         <v>1.19</v>
       </c>
       <c r="I114" t="n">
-        <v>0.5387</v>
+        <v>0.5253</v>
       </c>
       <c r="J114" t="n">
-        <v>14.0062</v>
+        <v>13.6578</v>
       </c>
     </row>
     <row r="115">
@@ -8789,10 +8789,10 @@
         <v>1.03</v>
       </c>
       <c r="I115" t="n">
-        <v>0.089</v>
+        <v>0.1073</v>
       </c>
       <c r="J115" t="n">
-        <v>2.314</v>
+        <v>2.7898</v>
       </c>
     </row>
     <row r="116">
@@ -8829,10 +8829,10 @@
         <v>0.87</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.4839</v>
+        <v>-0.4545</v>
       </c>
       <c r="J116" t="n">
-        <v>-12.5814</v>
+        <v>-11.817</v>
       </c>
     </row>
     <row r="117">
@@ -8869,10 +8869,10 @@
         <v>1.26</v>
       </c>
       <c r="I117" t="n">
-        <v>0.5455</v>
+        <v>0.5323</v>
       </c>
       <c r="J117" t="n">
-        <v>14.183</v>
+        <v>13.8398</v>
       </c>
     </row>
     <row r="118">
@@ -8909,10 +8909,10 @@
         <v>1.06</v>
       </c>
       <c r="I118" t="n">
-        <v>0.1609</v>
+        <v>0.1695</v>
       </c>
       <c r="J118" t="n">
-        <v>4.1834</v>
+        <v>4.407</v>
       </c>
     </row>
     <row r="119">
@@ -8949,10 +8949,10 @@
         <v>1.02</v>
       </c>
       <c r="I119" t="n">
-        <v>0.0654</v>
+        <v>0.073</v>
       </c>
       <c r="J119" t="n">
-        <v>1.7004</v>
+        <v>1.898</v>
       </c>
     </row>
     <row r="120">
@@ -8989,10 +8989,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.0885</v>
+        <v>-0.0993</v>
       </c>
       <c r="J120" t="n">
-        <v>-2.301</v>
+        <v>-2.5818</v>
       </c>
     </row>
     <row r="121">
@@ -9029,10 +9029,10 @@
         <v>0.74</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.2984</v>
+        <v>-0.3108</v>
       </c>
       <c r="J121" t="n">
-        <v>-7.7584</v>
+        <v>-8.0808</v>
       </c>
     </row>
     <row r="122">
@@ -9069,10 +9069,10 @@
         <v>1.97</v>
       </c>
       <c r="I122" t="n">
-        <v>1.6544</v>
+        <v>1.6552</v>
       </c>
       <c r="J122" t="n">
-        <v>34.7424</v>
+        <v>34.7592</v>
       </c>
     </row>
     <row r="123">
@@ -9109,10 +9109,10 @@
         <v>1.56</v>
       </c>
       <c r="I123" t="n">
-        <v>1.1766</v>
+        <v>1.1497</v>
       </c>
       <c r="J123" t="n">
-        <v>24.7086</v>
+        <v>24.1437</v>
       </c>
     </row>
     <row r="124">
@@ -9149,10 +9149,10 @@
         <v>1.35</v>
       </c>
       <c r="I124" t="n">
-        <v>0.8668</v>
+        <v>0.8248</v>
       </c>
       <c r="J124" t="n">
-        <v>18.2028</v>
+        <v>17.3208</v>
       </c>
     </row>
     <row r="125">
@@ -9189,10 +9189,10 @@
         <v>1.25</v>
       </c>
       <c r="I125" t="n">
-        <v>0.6411</v>
+        <v>0.6254999999999999</v>
       </c>
       <c r="J125" t="n">
-        <v>13.4631</v>
+        <v>13.1355</v>
       </c>
     </row>
     <row r="126">
@@ -9229,10 +9229,10 @@
         <v>0.86</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.5594</v>
+        <v>-0.5133</v>
       </c>
       <c r="J126" t="n">
-        <v>-11.7474</v>
+        <v>-10.7793</v>
       </c>
     </row>
     <row r="127">
@@ -9269,10 +9269,10 @@
         <v>1.06</v>
       </c>
       <c r="I127" t="n">
-        <v>0.3031</v>
+        <v>0.2741</v>
       </c>
       <c r="J127" t="n">
-        <v>6.3651</v>
+        <v>5.7561</v>
       </c>
     </row>
     <row r="128">
@@ -9309,10 +9309,10 @@
         <v>0.67</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.3222</v>
+        <v>-0.3421</v>
       </c>
       <c r="J128" t="n">
-        <v>-6.7662</v>
+        <v>-7.1841</v>
       </c>
     </row>
     <row r="129">
@@ -9349,10 +9349,10 @@
         <v>0.62</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.368</v>
+        <v>-0.3861</v>
       </c>
       <c r="J129" t="n">
-        <v>-7.728</v>
+        <v>-8.1081</v>
       </c>
     </row>
     <row r="130">
@@ -9389,10 +9389,10 @@
         <v>0.61</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.3773</v>
+        <v>-0.3949</v>
       </c>
       <c r="J130" t="n">
-        <v>-7.9233</v>
+        <v>-8.292899999999999</v>
       </c>
     </row>
     <row r="131">
@@ -9429,10 +9429,10 @@
         <v>0.46</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.5175999999999999</v>
+        <v>-0.527</v>
       </c>
       <c r="J131" t="n">
-        <v>-10.8696</v>
+        <v>-11.067</v>
       </c>
     </row>
     <row r="132">
@@ -9469,10 +9469,10 @@
         <v>1.4</v>
       </c>
       <c r="I132" t="n">
-        <v>1.0128</v>
+        <v>0.9556</v>
       </c>
       <c r="J132" t="n">
-        <v>25.32</v>
+        <v>23.89</v>
       </c>
     </row>
     <row r="133">
@@ -9509,10 +9509,10 @@
         <v>1.26</v>
       </c>
       <c r="I133" t="n">
-        <v>0.708</v>
+        <v>0.6761</v>
       </c>
       <c r="J133" t="n">
-        <v>17.7</v>
+        <v>16.9025</v>
       </c>
     </row>
     <row r="134">
@@ -9549,10 +9549,10 @@
         <v>1.13</v>
       </c>
       <c r="I134" t="n">
-        <v>0.3907</v>
+        <v>0.3899</v>
       </c>
       <c r="J134" t="n">
-        <v>9.7675</v>
+        <v>9.7475</v>
       </c>
     </row>
     <row r="135">
@@ -9589,10 +9589,10 @@
         <v>1.1</v>
       </c>
       <c r="I135" t="n">
-        <v>0.309</v>
+        <v>0.3147</v>
       </c>
       <c r="J135" t="n">
-        <v>7.725</v>
+        <v>7.8675</v>
       </c>
     </row>
     <row r="136">
@@ -9629,10 +9629,10 @@
         <v>0.97</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.1749</v>
+        <v>-0.1665</v>
       </c>
       <c r="J136" t="n">
-        <v>-4.3725</v>
+        <v>-4.1625</v>
       </c>
     </row>
     <row r="137">
@@ -9669,10 +9669,10 @@
         <v>1.05</v>
       </c>
       <c r="I137" t="n">
-        <v>0.1489</v>
+        <v>0.1548</v>
       </c>
       <c r="J137" t="n">
-        <v>3.7225</v>
+        <v>3.87</v>
       </c>
     </row>
     <row r="138">
@@ -9709,10 +9709,10 @@
         <v>1.03</v>
       </c>
       <c r="I138" t="n">
-        <v>0.1005</v>
+        <v>0.1062</v>
       </c>
       <c r="J138" t="n">
-        <v>2.5125</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="139">
@@ -9749,10 +9749,10 @@
         <v>1.02</v>
       </c>
       <c r="I139" t="n">
-        <v>0.0742</v>
+        <v>0.07920000000000001</v>
       </c>
       <c r="J139" t="n">
-        <v>1.855</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="140">
@@ -9789,10 +9789,10 @@
         <v>0.98</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.033</v>
+        <v>-0.0405</v>
       </c>
       <c r="J140" t="n">
-        <v>-0.825</v>
+        <v>-1.0125</v>
       </c>
     </row>
     <row r="141">
@@ -9829,10 +9829,10 @@
         <v>0.71</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.3219</v>
+        <v>-0.3346</v>
       </c>
       <c r="J141" t="n">
-        <v>-8.047499999999999</v>
+        <v>-8.365</v>
       </c>
     </row>
     <row r="142">
@@ -9869,10 +9869,10 @@
         <v>1.84</v>
       </c>
       <c r="I142" t="n">
-        <v>1.5478</v>
+        <v>1.5368</v>
       </c>
       <c r="J142" t="n">
-        <v>40.2428</v>
+        <v>39.9568</v>
       </c>
     </row>
     <row r="143">
@@ -9909,10 +9909,10 @@
         <v>1.45</v>
       </c>
       <c r="I143" t="n">
-        <v>1.0673</v>
+        <v>1.0232</v>
       </c>
       <c r="J143" t="n">
-        <v>27.7498</v>
+        <v>26.6032</v>
       </c>
     </row>
     <row r="144">
@@ -9949,10 +9949,10 @@
         <v>1.18</v>
       </c>
       <c r="I144" t="n">
-        <v>0.5034999999999999</v>
+        <v>0.4959</v>
       </c>
       <c r="J144" t="n">
-        <v>13.091</v>
+        <v>12.8934</v>
       </c>
     </row>
     <row r="145">
@@ -9989,10 +9989,10 @@
         <v>0.9</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.4147</v>
+        <v>-0.388</v>
       </c>
       <c r="J145" t="n">
-        <v>-10.7822</v>
+        <v>-10.088</v>
       </c>
     </row>
     <row r="146">
@@ -10029,10 +10029,10 @@
         <v>0.86</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.527</v>
+        <v>-0.4904</v>
       </c>
       <c r="J146" t="n">
-        <v>-13.702</v>
+        <v>-12.7504</v>
       </c>
     </row>
     <row r="147">
@@ -10069,10 +10069,10 @@
         <v>1.09</v>
       </c>
       <c r="I147" t="n">
-        <v>0.2918</v>
+        <v>0.281</v>
       </c>
       <c r="J147" t="n">
-        <v>7.5868</v>
+        <v>7.306</v>
       </c>
     </row>
     <row r="148">
@@ -10109,10 +10109,10 @@
         <v>1.04</v>
       </c>
       <c r="I148" t="n">
-        <v>0.174</v>
+        <v>0.1668</v>
       </c>
       <c r="J148" t="n">
-        <v>4.524</v>
+        <v>4.3368</v>
       </c>
     </row>
     <row r="149">
@@ -10149,10 +10149,10 @@
         <v>0.8</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.2169</v>
+        <v>-0.2353</v>
       </c>
       <c r="J149" t="n">
-        <v>-5.6394</v>
+        <v>-6.1178</v>
       </c>
     </row>
     <row r="150">
@@ -10189,10 +10189,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.3223</v>
+        <v>-0.3385</v>
       </c>
       <c r="J150" t="n">
-        <v>-8.379799999999999</v>
+        <v>-8.801</v>
       </c>
     </row>
     <row r="151">
@@ -10229,10 +10229,10 @@
         <v>0.46</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.5361</v>
+        <v>-0.5416</v>
       </c>
       <c r="J151" t="n">
-        <v>-13.9386</v>
+        <v>-14.0816</v>
       </c>
     </row>
     <row r="152">
@@ -10269,10 +10269,10 @@
         <v>0.99</v>
       </c>
       <c r="I152" t="n">
-        <v>0.0184</v>
+        <v>-0.0016</v>
       </c>
       <c r="J152" t="n">
-        <v>0.46</v>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="153">
@@ -10309,10 +10309,10 @@
         <v>0.83</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.186</v>
+        <v>-0.2048</v>
       </c>
       <c r="J153" t="n">
-        <v>-4.65</v>
+        <v>-5.12</v>
       </c>
     </row>
     <row r="154">
@@ -10349,10 +10349,10 @@
         <v>0.73</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.2814</v>
+        <v>-0.2994</v>
       </c>
       <c r="J154" t="n">
-        <v>-7.035</v>
+        <v>-7.485</v>
       </c>
     </row>
     <row r="155">
@@ -10389,10 +10389,10 @@
         <v>0.72</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.291</v>
+        <v>-0.3087</v>
       </c>
       <c r="J155" t="n">
-        <v>-7.275</v>
+        <v>-7.7175</v>
       </c>
     </row>
     <row r="156">
@@ -10429,10 +10429,10 @@
         <v>0.71</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.3005</v>
+        <v>-0.3179</v>
       </c>
       <c r="J156" t="n">
-        <v>-7.5125</v>
+        <v>-7.9475</v>
       </c>
     </row>
     <row r="157">
@@ -10469,10 +10469,10 @@
         <v>1.65</v>
       </c>
       <c r="I157" t="n">
-        <v>1.2988</v>
+        <v>1.2776</v>
       </c>
       <c r="J157" t="n">
-        <v>32.47</v>
+        <v>31.94</v>
       </c>
     </row>
     <row r="158">
@@ -10509,10 +10509,10 @@
         <v>1.63</v>
       </c>
       <c r="I158" t="n">
-        <v>1.2746</v>
+        <v>1.252</v>
       </c>
       <c r="J158" t="n">
-        <v>31.865</v>
+        <v>31.3</v>
       </c>
     </row>
     <row r="159">
@@ -10549,10 +10549,10 @@
         <v>1.21</v>
       </c>
       <c r="I159" t="n">
-        <v>0.5609</v>
+        <v>0.5508999999999999</v>
       </c>
       <c r="J159" t="n">
-        <v>14.0225</v>
+        <v>13.7725</v>
       </c>
     </row>
     <row r="160">
@@ -10589,10 +10589,10 @@
         <v>1.11</v>
       </c>
       <c r="I160" t="n">
-        <v>0.3017</v>
+        <v>0.316</v>
       </c>
       <c r="J160" t="n">
-        <v>7.5425</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="161">
@@ -10629,10 +10629,10 @@
         <v>1.02</v>
       </c>
       <c r="I161" t="n">
-        <v>0.0177</v>
+        <v>0.0469</v>
       </c>
       <c r="J161" t="n">
-        <v>0.4425</v>
+        <v>1.1725</v>
       </c>
     </row>
     <row r="162">
@@ -10669,10 +10669,10 @@
         <v>1.7</v>
       </c>
       <c r="I162" t="n">
-        <v>0.8263</v>
+        <v>0.8142</v>
       </c>
       <c r="J162" t="n">
-        <v>20.6575</v>
+        <v>20.355</v>
       </c>
     </row>
     <row r="163">
@@ -10709,10 +10709,10 @@
         <v>1.42</v>
       </c>
       <c r="I163" t="n">
-        <v>0.5274</v>
+        <v>0.5364</v>
       </c>
       <c r="J163" t="n">
-        <v>13.185</v>
+        <v>13.41</v>
       </c>
     </row>
     <row r="164">
@@ -10749,10 +10749,10 @@
         <v>1.36</v>
       </c>
       <c r="I164" t="n">
-        <v>0.4609</v>
+        <v>0.4734</v>
       </c>
       <c r="J164" t="n">
-        <v>11.5225</v>
+        <v>11.835</v>
       </c>
     </row>
     <row r="165">
@@ -10789,10 +10789,10 @@
         <v>0.92</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.1369</v>
+        <v>-0.1433</v>
       </c>
       <c r="J165" t="n">
-        <v>-3.4225</v>
+        <v>-3.5825</v>
       </c>
     </row>
     <row r="166">
@@ -10829,10 +10829,10 @@
         <v>0.83</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.2338</v>
+        <v>-0.2419</v>
       </c>
       <c r="J166" t="n">
-        <v>-5.845</v>
+        <v>-6.0475</v>
       </c>
     </row>
     <row r="167">
@@ -10869,10 +10869,10 @@
         <v>1.31</v>
       </c>
       <c r="I167" t="n">
-        <v>0.5187</v>
+        <v>0.5053</v>
       </c>
       <c r="J167" t="n">
-        <v>12.9675</v>
+        <v>12.6325</v>
       </c>
     </row>
     <row r="168">
@@ -10909,10 +10909,10 @@
         <v>0.95</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.0674</v>
+        <v>-0.0796</v>
       </c>
       <c r="J168" t="n">
-        <v>-1.685</v>
+        <v>-1.99</v>
       </c>
     </row>
     <row r="169">
@@ -10949,10 +10949,10 @@
         <v>0.82</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.2073</v>
+        <v>-0.2234</v>
       </c>
       <c r="J169" t="n">
-        <v>-5.1825</v>
+        <v>-5.585</v>
       </c>
     </row>
     <row r="170">
@@ -10989,10 +10989,10 @@
         <v>0.75</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.2766</v>
+        <v>-0.2918</v>
       </c>
       <c r="J170" t="n">
-        <v>-6.915</v>
+        <v>-7.295</v>
       </c>
     </row>
     <row r="171">
@@ -11029,10 +11029,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.3342</v>
+        <v>-0.3478</v>
       </c>
       <c r="J171" t="n">
-        <v>-8.355</v>
+        <v>-8.695</v>
       </c>
     </row>
     <row r="172">
@@ -11069,10 +11069,10 @@
         <v>0.97</v>
       </c>
       <c r="I172" t="n">
-        <v>-0.0025</v>
+        <v>-0.0212</v>
       </c>
       <c r="J172" t="n">
-        <v>-0.0575</v>
+        <v>-0.4876</v>
       </c>
     </row>
     <row r="173">
@@ -11109,10 +11109,10 @@
         <v>0.85</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.1518</v>
+        <v>-0.1736</v>
       </c>
       <c r="J173" t="n">
-        <v>-3.4914</v>
+        <v>-3.9928</v>
       </c>
     </row>
     <row r="174">
@@ -11149,10 +11149,10 @@
         <v>0.74</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.264</v>
+        <v>-0.2841</v>
       </c>
       <c r="J174" t="n">
-        <v>-6.072</v>
+        <v>-6.5343</v>
       </c>
     </row>
     <row r="175">
@@ -11189,10 +11189,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.3092</v>
+        <v>-0.3284</v>
       </c>
       <c r="J175" t="n">
-        <v>-7.1116</v>
+        <v>-7.5532</v>
       </c>
     </row>
     <row r="176">
@@ -11229,10 +11229,10 @@
         <v>0.37</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.6073</v>
+        <v>-0.6094000000000001</v>
       </c>
       <c r="J176" t="n">
-        <v>-13.9679</v>
+        <v>-14.0162</v>
       </c>
     </row>
     <row r="177">
@@ -11269,10 +11269,10 @@
         <v>1.65</v>
       </c>
       <c r="I177" t="n">
-        <v>1.288</v>
+        <v>1.2682</v>
       </c>
       <c r="J177" t="n">
-        <v>29.624</v>
+        <v>29.1686</v>
       </c>
     </row>
     <row r="178">
@@ -11309,10 +11309,10 @@
         <v>1.53</v>
       </c>
       <c r="I178" t="n">
-        <v>1.1439</v>
+        <v>1.1138</v>
       </c>
       <c r="J178" t="n">
-        <v>26.3097</v>
+        <v>25.6174</v>
       </c>
     </row>
     <row r="179">
@@ -11349,10 +11349,10 @@
         <v>1.44</v>
       </c>
       <c r="I179" t="n">
-        <v>1.0319</v>
+        <v>0.9866</v>
       </c>
       <c r="J179" t="n">
-        <v>23.7337</v>
+        <v>22.6918</v>
       </c>
     </row>
     <row r="180">
@@ -11389,10 +11389,10 @@
         <v>1.27</v>
       </c>
       <c r="I180" t="n">
-        <v>0.6923</v>
+        <v>0.6701</v>
       </c>
       <c r="J180" t="n">
-        <v>15.9229</v>
+        <v>15.4123</v>
       </c>
     </row>
     <row r="181">
@@ -11429,10 +11429,10 @@
         <v>0.99</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.1447</v>
+        <v>-0.1222</v>
       </c>
       <c r="J181" t="n">
-        <v>-3.3281</v>
+        <v>-2.8106</v>
       </c>
     </row>
     <row r="182">
@@ -11469,10 +11469,10 @@
         <v>1.37</v>
       </c>
       <c r="I182" t="n">
-        <v>0.4878</v>
+        <v>0.496</v>
       </c>
       <c r="J182" t="n">
-        <v>14.1462</v>
+        <v>14.384</v>
       </c>
     </row>
     <row r="183">
@@ -11509,10 +11509,10 @@
         <v>1.34</v>
       </c>
       <c r="I183" t="n">
-        <v>0.4532</v>
+        <v>0.4632</v>
       </c>
       <c r="J183" t="n">
-        <v>13.1428</v>
+        <v>13.4328</v>
       </c>
     </row>
     <row r="184">
@@ -11549,10 +11549,10 @@
         <v>1.32</v>
       </c>
       <c r="I184" t="n">
-        <v>0.4299</v>
+        <v>0.441</v>
       </c>
       <c r="J184" t="n">
-        <v>12.4671</v>
+        <v>12.789</v>
       </c>
     </row>
     <row r="185">
@@ -11589,10 +11589,10 @@
         <v>1.23</v>
       </c>
       <c r="I185" t="n">
-        <v>0.3228</v>
+        <v>0.3381</v>
       </c>
       <c r="J185" t="n">
-        <v>9.3612</v>
+        <v>9.8049</v>
       </c>
     </row>
     <row r="186">
@@ -11629,10 +11629,10 @@
         <v>0.5</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.5315</v>
+        <v>-0.5326</v>
       </c>
       <c r="J186" t="n">
-        <v>-15.4135</v>
+        <v>-15.4454</v>
       </c>
     </row>
     <row r="187">
@@ -11669,10 +11669,10 @@
         <v>1.21</v>
       </c>
       <c r="I187" t="n">
-        <v>0.3701</v>
+        <v>0.3683</v>
       </c>
       <c r="J187" t="n">
-        <v>10.7329</v>
+        <v>10.6807</v>
       </c>
     </row>
     <row r="188">
@@ -11709,10 +11709,10 @@
         <v>1.2</v>
       </c>
       <c r="I188" t="n">
-        <v>0.3557</v>
+        <v>0.3547</v>
       </c>
       <c r="J188" t="n">
-        <v>10.3153</v>
+        <v>10.2863</v>
       </c>
     </row>
     <row r="189">
@@ -11749,10 +11749,10 @@
         <v>0.9</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.1266</v>
+        <v>-0.141</v>
       </c>
       <c r="J189" t="n">
-        <v>-3.6714</v>
+        <v>-4.089</v>
       </c>
     </row>
     <row r="190">
@@ -11789,10 +11789,10 @@
         <v>0.68</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.3467</v>
+        <v>-0.3593</v>
       </c>
       <c r="J190" t="n">
-        <v>-10.0543</v>
+        <v>-10.4197</v>
       </c>
     </row>
     <row r="191">
@@ -11829,10 +11829,10 @@
         <v>0.65</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.3749</v>
+        <v>-0.3865</v>
       </c>
       <c r="J191" t="n">
-        <v>-10.8721</v>
+        <v>-11.2085</v>
       </c>
     </row>
     <row r="192">
@@ -11869,10 +11869,10 @@
         <v>1.19</v>
       </c>
       <c r="I192" t="n">
-        <v>0.442</v>
+        <v>0.4325</v>
       </c>
       <c r="J192" t="n">
-        <v>11.934</v>
+        <v>11.6775</v>
       </c>
     </row>
     <row r="193">
@@ -11909,10 +11909,10 @@
         <v>1.09</v>
       </c>
       <c r="I193" t="n">
-        <v>0.243</v>
+        <v>0.2452</v>
       </c>
       <c r="J193" t="n">
-        <v>6.561</v>
+        <v>6.6204</v>
       </c>
     </row>
     <row r="194">
@@ -11949,10 +11949,10 @@
         <v>0.88</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.1491</v>
+        <v>-0.1639</v>
       </c>
       <c r="J194" t="n">
-        <v>-4.0257</v>
+        <v>-4.4253</v>
       </c>
     </row>
     <row r="195">
@@ -11989,10 +11989,10 @@
         <v>0.85</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.1807</v>
+        <v>-0.1959</v>
       </c>
       <c r="J195" t="n">
-        <v>-4.8789</v>
+        <v>-5.2893</v>
       </c>
     </row>
     <row r="196">
@@ -12029,10 +12029,10 @@
         <v>0.68</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.3479</v>
+        <v>-0.3603</v>
       </c>
       <c r="J196" t="n">
-        <v>-9.3933</v>
+        <v>-9.7281</v>
       </c>
     </row>
     <row r="197">
@@ -12069,10 +12069,10 @@
         <v>1.37</v>
       </c>
       <c r="I197" t="n">
-        <v>0.9683</v>
+        <v>0.9067</v>
       </c>
       <c r="J197" t="n">
-        <v>26.1441</v>
+        <v>24.4809</v>
       </c>
     </row>
     <row r="198">
@@ -12109,10 +12109,10 @@
         <v>1.34</v>
       </c>
       <c r="I198" t="n">
-        <v>0.9045</v>
+        <v>0.8469</v>
       </c>
       <c r="J198" t="n">
-        <v>24.4215</v>
+        <v>22.8663</v>
       </c>
     </row>
     <row r="199">
@@ -12149,10 +12149,10 @@
         <v>1.21</v>
       </c>
       <c r="I199" t="n">
-        <v>0.5959</v>
+        <v>0.5748</v>
       </c>
       <c r="J199" t="n">
-        <v>16.0893</v>
+        <v>15.5196</v>
       </c>
     </row>
     <row r="200">
@@ -12189,10 +12189,10 @@
         <v>1.08</v>
       </c>
       <c r="I200" t="n">
-        <v>0.2585</v>
+        <v>0.2661</v>
       </c>
       <c r="J200" t="n">
-        <v>6.9795</v>
+        <v>7.1847</v>
       </c>
     </row>
     <row r="201">
@@ -12229,10 +12229,10 @@
         <v>0.71</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.8869</v>
+        <v>-0.8143</v>
       </c>
       <c r="J201" t="n">
-        <v>-23.9463</v>
+        <v>-21.9861</v>
       </c>
     </row>
     <row r="202">
@@ -12269,10 +12269,10 @@
         <v>0.96</v>
       </c>
       <c r="I202" t="n">
-        <v>-0.05</v>
+        <v>-0.0624</v>
       </c>
       <c r="J202" t="n">
-        <v>-1.3</v>
+        <v>-1.6224</v>
       </c>
     </row>
     <row r="203">
@@ -12309,10 +12309,10 @@
         <v>0.93</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.0877</v>
+        <v>-0.1021</v>
       </c>
       <c r="J203" t="n">
-        <v>-2.2802</v>
+        <v>-2.6546</v>
       </c>
     </row>
     <row r="204">
@@ -12349,10 +12349,10 @@
         <v>0.91</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.1108</v>
+        <v>-0.1261</v>
       </c>
       <c r="J204" t="n">
-        <v>-2.8808</v>
+        <v>-3.2786</v>
       </c>
     </row>
     <row r="205">
@@ -12389,10 +12389,10 @@
         <v>0.79</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.2333</v>
+        <v>-0.25</v>
       </c>
       <c r="J205" t="n">
-        <v>-6.0658</v>
+        <v>-6.5</v>
       </c>
     </row>
     <row r="206">
@@ -12429,10 +12429,10 @@
         <v>0.77</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.2529</v>
+        <v>-0.2694</v>
       </c>
       <c r="J206" t="n">
-        <v>-6.5754</v>
+        <v>-7.0044</v>
       </c>
     </row>
     <row r="207">
@@ -12469,10 +12469,10 @@
         <v>1.75</v>
       </c>
       <c r="I207" t="n">
-        <v>1.4332</v>
+        <v>1.4175</v>
       </c>
       <c r="J207" t="n">
-        <v>37.2632</v>
+        <v>36.855</v>
       </c>
     </row>
     <row r="208">
@@ -12509,10 +12509,10 @@
         <v>1.72</v>
       </c>
       <c r="I208" t="n">
-        <v>1.397</v>
+        <v>1.3793</v>
       </c>
       <c r="J208" t="n">
-        <v>36.322</v>
+        <v>35.8618</v>
       </c>
     </row>
     <row r="209">
@@ -12549,10 +12549,10 @@
         <v>1.05</v>
       </c>
       <c r="I209" t="n">
-        <v>0.1358</v>
+        <v>0.158</v>
       </c>
       <c r="J209" t="n">
-        <v>3.5308</v>
+        <v>4.108</v>
       </c>
     </row>
     <row r="210">
@@ -12589,10 +12589,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.2992</v>
+        <v>-0.2794</v>
       </c>
       <c r="J210" t="n">
-        <v>-7.7792</v>
+        <v>-7.2644</v>
       </c>
     </row>
     <row r="211">
@@ -12629,10 +12629,10 @@
         <v>0.88</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.4767</v>
+        <v>-0.4437</v>
       </c>
       <c r="J211" t="n">
-        <v>-12.3942</v>
+        <v>-11.5362</v>
       </c>
     </row>
     <row r="212">
@@ -12669,10 +12669,10 @@
         <v>1.37</v>
       </c>
       <c r="I212" t="n">
-        <v>0.7469</v>
+        <v>0.713</v>
       </c>
       <c r="J212" t="n">
-        <v>19.4194</v>
+        <v>18.538</v>
       </c>
     </row>
     <row r="213">
@@ -12709,10 +12709,10 @@
         <v>0.93</v>
       </c>
       <c r="I213" t="n">
-        <v>-0.0978</v>
+        <v>-0.1098</v>
       </c>
       <c r="J213" t="n">
-        <v>-2.5428</v>
+        <v>-2.8548</v>
       </c>
     </row>
     <row r="214">
@@ -12749,10 +12749,10 @@
         <v>0.88</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.1536</v>
+        <v>-0.1674</v>
       </c>
       <c r="J214" t="n">
-        <v>-3.9936</v>
+        <v>-4.3524</v>
       </c>
     </row>
     <row r="215">
@@ -12789,10 +12789,10 @@
         <v>0.86</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.1749</v>
+        <v>-0.1889</v>
       </c>
       <c r="J215" t="n">
-        <v>-4.5474</v>
+        <v>-4.9114</v>
       </c>
     </row>
     <row r="216">
@@ -12829,10 +12829,10 @@
         <v>0.85</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.1854</v>
+        <v>-0.1995</v>
       </c>
       <c r="J216" t="n">
-        <v>-4.8204</v>
+        <v>-5.187</v>
       </c>
     </row>
     <row r="217">
@@ -12869,10 +12869,10 @@
         <v>1.28</v>
       </c>
       <c r="I217" t="n">
-        <v>0.7637</v>
+        <v>0.7236</v>
       </c>
       <c r="J217" t="n">
-        <v>19.8562</v>
+        <v>18.8136</v>
       </c>
     </row>
     <row r="218">
@@ -12909,10 +12909,10 @@
         <v>1.19</v>
       </c>
       <c r="I218" t="n">
-        <v>0.5461</v>
+        <v>0.5303</v>
       </c>
       <c r="J218" t="n">
-        <v>14.1986</v>
+        <v>13.7878</v>
       </c>
     </row>
     <row r="219">
@@ -12949,10 +12949,10 @@
         <v>1.19</v>
       </c>
       <c r="I219" t="n">
-        <v>0.5461</v>
+        <v>0.5303</v>
       </c>
       <c r="J219" t="n">
-        <v>14.1986</v>
+        <v>13.7878</v>
       </c>
     </row>
     <row r="220">
@@ -12989,10 +12989,10 @@
         <v>1.07</v>
       </c>
       <c r="I220" t="n">
-        <v>0.2284</v>
+        <v>0.238</v>
       </c>
       <c r="J220" t="n">
-        <v>5.9384</v>
+        <v>6.188</v>
       </c>
     </row>
     <row r="221">
@@ -13029,10 +13029,10 @@
         <v>0.99</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.0892</v>
+        <v>-0.0834</v>
       </c>
       <c r="J221" t="n">
-        <v>-2.3192</v>
+        <v>-2.1684</v>
       </c>
     </row>
     <row r="222">
@@ -13069,10 +13069,10 @@
         <v>0.89</v>
       </c>
       <c r="I222" t="n">
-        <v>-0.08799999999999999</v>
+        <v>-0.1138</v>
       </c>
       <c r="J222" t="n">
-        <v>-1.936</v>
+        <v>-2.5036</v>
       </c>
     </row>
     <row r="223">
@@ -13109,10 +13109,10 @@
         <v>0.78</v>
       </c>
       <c r="I223" t="n">
-        <v>-0.2122</v>
+        <v>-0.236</v>
       </c>
       <c r="J223" t="n">
-        <v>-4.6684</v>
+        <v>-5.192</v>
       </c>
     </row>
     <row r="224">
@@ -13149,10 +13149,10 @@
         <v>0.65</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.3374</v>
+        <v>-0.3573</v>
       </c>
       <c r="J224" t="n">
-        <v>-7.4228</v>
+        <v>-7.8606</v>
       </c>
     </row>
     <row r="225">
@@ -13189,10 +13189,10 @@
         <v>0.57</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.4108</v>
+        <v>-0.4274</v>
       </c>
       <c r="J225" t="n">
-        <v>-9.037599999999999</v>
+        <v>-9.402799999999999</v>
       </c>
     </row>
     <row r="226">
@@ -13229,10 +13229,10 @@
         <v>0.42</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.5516</v>
+        <v>-0.5591</v>
       </c>
       <c r="J226" t="n">
-        <v>-12.1352</v>
+        <v>-12.3002</v>
       </c>
     </row>
     <row r="227">
@@ -13269,10 +13269,10 @@
         <v>1.56</v>
       </c>
       <c r="I227" t="n">
-        <v>1.1695</v>
+        <v>1.1435</v>
       </c>
       <c r="J227" t="n">
-        <v>25.729</v>
+        <v>25.157</v>
       </c>
     </row>
     <row r="228">
@@ -13309,10 +13309,10 @@
         <v>1.5</v>
       </c>
       <c r="I228" t="n">
-        <v>1.0984</v>
+        <v>1.0662</v>
       </c>
       <c r="J228" t="n">
-        <v>24.1648</v>
+        <v>23.4564</v>
       </c>
     </row>
     <row r="229">
@@ -13349,10 +13349,10 @@
         <v>1.5</v>
       </c>
       <c r="I229" t="n">
-        <v>1.0984</v>
+        <v>1.0662</v>
       </c>
       <c r="J229" t="n">
-        <v>24.1648</v>
+        <v>23.4564</v>
       </c>
     </row>
     <row r="230">
@@ -13389,10 +13389,10 @@
         <v>1.49</v>
       </c>
       <c r="I230" t="n">
-        <v>1.0865</v>
+        <v>1.0528</v>
       </c>
       <c r="J230" t="n">
-        <v>23.903</v>
+        <v>23.1616</v>
       </c>
     </row>
     <row r="231">
@@ -13429,10 +13429,10 @@
         <v>1.19</v>
       </c>
       <c r="I231" t="n">
-        <v>0.485</v>
+        <v>0.4882</v>
       </c>
       <c r="J231" t="n">
-        <v>10.67</v>
+        <v>10.7404</v>
       </c>
     </row>
     <row r="232">
@@ -13469,10 +13469,10 @@
         <v>1.38</v>
       </c>
       <c r="I232" t="n">
-        <v>0.8248</v>
+        <v>0.7734</v>
       </c>
       <c r="J232" t="n">
-        <v>17.3208</v>
+        <v>16.2414</v>
       </c>
     </row>
     <row r="233">
@@ -13509,10 +13509,10 @@
         <v>1.06</v>
       </c>
       <c r="I233" t="n">
-        <v>0.2017</v>
+        <v>0.1992</v>
       </c>
       <c r="J233" t="n">
-        <v>4.2357</v>
+        <v>4.1832</v>
       </c>
     </row>
     <row r="234">
@@ -13549,10 +13549,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.3292</v>
+        <v>-0.3439</v>
       </c>
       <c r="J234" t="n">
-        <v>-6.9132</v>
+        <v>-7.2219</v>
       </c>
     </row>
     <row r="235">
@@ -13589,10 +13589,10 @@
         <v>0.63</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.3858</v>
+        <v>-0.3983</v>
       </c>
       <c r="J235" t="n">
-        <v>-8.101800000000001</v>
+        <v>-8.3643</v>
       </c>
     </row>
     <row r="236">
@@ -13629,10 +13629,10 @@
         <v>0.57</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.4415</v>
+        <v>-0.4514</v>
       </c>
       <c r="J236" t="n">
-        <v>-9.2715</v>
+        <v>-9.4794</v>
       </c>
     </row>
     <row r="237">
@@ -13669,10 +13669,10 @@
         <v>1.68</v>
       </c>
       <c r="I237" t="n">
-        <v>1.3326</v>
+        <v>1.3139</v>
       </c>
       <c r="J237" t="n">
-        <v>27.9846</v>
+        <v>27.5919</v>
       </c>
     </row>
     <row r="238">
@@ -13709,10 +13709,10 @@
         <v>1.38</v>
       </c>
       <c r="I238" t="n">
-        <v>0.9376</v>
+        <v>0.8868</v>
       </c>
       <c r="J238" t="n">
-        <v>19.6896</v>
+        <v>18.6228</v>
       </c>
     </row>
     <row r="239">
@@ -13749,10 +13749,10 @@
         <v>1.36</v>
       </c>
       <c r="I239" t="n">
-        <v>0.8966</v>
+        <v>0.8494</v>
       </c>
       <c r="J239" t="n">
-        <v>18.8286</v>
+        <v>17.8374</v>
       </c>
     </row>
     <row r="240">
@@ -13789,10 +13789,10 @@
         <v>1.18</v>
       </c>
       <c r="I240" t="n">
-        <v>0.4844</v>
+        <v>0.4827</v>
       </c>
       <c r="J240" t="n">
-        <v>10.1724</v>
+        <v>10.1367</v>
       </c>
     </row>
     <row r="241">
@@ -13829,10 +13829,10 @@
         <v>1.07</v>
       </c>
       <c r="I241" t="n">
-        <v>0.1832</v>
+        <v>0.2066</v>
       </c>
       <c r="J241" t="n">
-        <v>3.8472</v>
+        <v>4.3386</v>
       </c>
     </row>
     <row r="242">
@@ -13869,10 +13869,10 @@
         <v>1.5</v>
       </c>
       <c r="I242" t="n">
-        <v>0.6187</v>
+        <v>0.6214</v>
       </c>
       <c r="J242" t="n">
-        <v>17.3236</v>
+        <v>17.3992</v>
       </c>
     </row>
     <row r="243">
@@ -13909,10 +13909,10 @@
         <v>1.27</v>
       </c>
       <c r="I243" t="n">
-        <v>0.3614</v>
+        <v>0.3774</v>
       </c>
       <c r="J243" t="n">
-        <v>10.1192</v>
+        <v>10.5672</v>
       </c>
     </row>
     <row r="244">
@@ -13949,10 +13949,10 @@
         <v>1.17</v>
       </c>
       <c r="I244" t="n">
-        <v>0.2429</v>
+        <v>0.2613</v>
       </c>
       <c r="J244" t="n">
-        <v>6.8012</v>
+        <v>7.3164</v>
       </c>
     </row>
     <row r="245">
@@ -13989,10 +13989,10 @@
         <v>1.11</v>
       </c>
       <c r="I245" t="n">
-        <v>0.1634</v>
+        <v>0.1822</v>
       </c>
       <c r="J245" t="n">
-        <v>4.5752</v>
+        <v>5.1016</v>
       </c>
     </row>
     <row r="246">
@@ -14029,10 +14029,10 @@
         <v>1.07</v>
       </c>
       <c r="I246" t="n">
-        <v>0.1052</v>
+        <v>0.1232</v>
       </c>
       <c r="J246" t="n">
-        <v>2.9456</v>
+        <v>3.4496</v>
       </c>
     </row>
     <row r="247">
@@ -14069,10 +14069,10 @@
         <v>1.33</v>
       </c>
       <c r="I247" t="n">
-        <v>0.5396</v>
+        <v>0.5256999999999999</v>
       </c>
       <c r="J247" t="n">
-        <v>15.1088</v>
+        <v>14.7196</v>
       </c>
     </row>
     <row r="248">
@@ -14109,10 +14109,10 @@
         <v>1.08</v>
       </c>
       <c r="I248" t="n">
-        <v>0.1739</v>
+        <v>0.1791</v>
       </c>
       <c r="J248" t="n">
-        <v>4.8692</v>
+        <v>5.0148</v>
       </c>
     </row>
     <row r="249">
@@ -14149,10 +14149,10 @@
         <v>0.92</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.1041</v>
+        <v>-0.1179</v>
       </c>
       <c r="J249" t="n">
-        <v>-2.9148</v>
+        <v>-3.3012</v>
       </c>
     </row>
     <row r="250">
@@ -14189,10 +14189,10 @@
         <v>0.7</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.3267</v>
+        <v>-0.3402</v>
       </c>
       <c r="J250" t="n">
-        <v>-9.147600000000001</v>
+        <v>-9.525600000000001</v>
       </c>
     </row>
     <row r="251">
@@ -14229,10 +14229,10 @@
         <v>0.57</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.448</v>
+        <v>-0.4565</v>
       </c>
       <c r="J251" t="n">
-        <v>-12.544</v>
+        <v>-12.782</v>
       </c>
     </row>
     <row r="252">
@@ -14269,10 +14269,10 @@
         <v>1.27</v>
       </c>
       <c r="I252" t="n">
-        <v>0.5996</v>
+        <v>0.5754</v>
       </c>
       <c r="J252" t="n">
-        <v>14.99</v>
+        <v>14.385</v>
       </c>
     </row>
     <row r="253">
@@ -14309,10 +14309,10 @@
         <v>1.19</v>
       </c>
       <c r="I253" t="n">
-        <v>0.4508</v>
+        <v>0.439</v>
       </c>
       <c r="J253" t="n">
-        <v>11.27</v>
+        <v>10.975</v>
       </c>
     </row>
     <row r="254">
@@ -14349,10 +14349,10 @@
         <v>0.98</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.0283</v>
+        <v>-0.0369</v>
       </c>
       <c r="J254" t="n">
-        <v>-0.7075</v>
+        <v>-0.9225</v>
       </c>
     </row>
     <row r="255">
@@ -14389,10 +14389,10 @@
         <v>0.68</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.3452</v>
+        <v>-0.3582</v>
       </c>
       <c r="J255" t="n">
-        <v>-8.630000000000001</v>
+        <v>-8.955</v>
       </c>
     </row>
     <row r="256">
@@ -14429,10 +14429,10 @@
         <v>0.46</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.5471</v>
+        <v>-0.5503</v>
       </c>
       <c r="J256" t="n">
-        <v>-13.6775</v>
+        <v>-13.7575</v>
       </c>
     </row>
     <row r="257">
@@ -14469,10 +14469,10 @@
         <v>1.54</v>
       </c>
       <c r="I257" t="n">
-        <v>1.1972</v>
+        <v>1.1631</v>
       </c>
       <c r="J257" t="n">
-        <v>29.93</v>
+        <v>29.0775</v>
       </c>
     </row>
     <row r="258">
@@ -14509,10 +14509,10 @@
         <v>1.33</v>
       </c>
       <c r="I258" t="n">
-        <v>0.8678</v>
+        <v>0.8171</v>
       </c>
       <c r="J258" t="n">
-        <v>21.695</v>
+        <v>20.4275</v>
       </c>
     </row>
     <row r="259">
@@ -14549,10 +14549,10 @@
         <v>1.05</v>
       </c>
       <c r="I259" t="n">
-        <v>0.1567</v>
+        <v>0.1726</v>
       </c>
       <c r="J259" t="n">
-        <v>3.9175</v>
+        <v>4.315</v>
       </c>
     </row>
     <row r="260">
@@ -14589,10 +14589,10 @@
         <v>1.03</v>
       </c>
       <c r="I260" t="n">
-        <v>0.089</v>
+        <v>0.1073</v>
       </c>
       <c r="J260" t="n">
-        <v>2.225</v>
+        <v>2.6825</v>
       </c>
     </row>
     <row r="261">
@@ -14629,10 +14629,10 @@
         <v>0.96</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.2125</v>
+        <v>-0.2022</v>
       </c>
       <c r="J261" t="n">
-        <v>-5.3125</v>
+        <v>-5.055</v>
       </c>
     </row>
     <row r="262">
@@ -14669,10 +14669,10 @@
         <v>1.7</v>
       </c>
       <c r="I262" t="n">
-        <v>1.3321</v>
+        <v>1.3179</v>
       </c>
       <c r="J262" t="n">
-        <v>26.642</v>
+        <v>26.358</v>
       </c>
     </row>
     <row r="263">
@@ -14709,10 +14709,10 @@
         <v>1.59</v>
       </c>
       <c r="I263" t="n">
-        <v>1.2037</v>
+        <v>1.1806</v>
       </c>
       <c r="J263" t="n">
-        <v>24.074</v>
+        <v>23.612</v>
       </c>
     </row>
     <row r="264">
@@ -14749,10 +14749,10 @@
         <v>1.55</v>
       </c>
       <c r="I264" t="n">
-        <v>1.1566</v>
+        <v>1.1298</v>
       </c>
       <c r="J264" t="n">
-        <v>23.132</v>
+        <v>22.596</v>
       </c>
     </row>
     <row r="265">
@@ -14789,10 +14789,10 @@
         <v>1.23</v>
       </c>
       <c r="I265" t="n">
-        <v>0.5814</v>
+        <v>0.5748</v>
       </c>
       <c r="J265" t="n">
-        <v>11.628</v>
+        <v>11.496</v>
       </c>
     </row>
     <row r="266">
@@ -14829,10 +14829,10 @@
         <v>1.21</v>
       </c>
       <c r="I266" t="n">
-        <v>0.5329</v>
+        <v>0.5314</v>
       </c>
       <c r="J266" t="n">
-        <v>10.658</v>
+        <v>10.628</v>
       </c>
     </row>
     <row r="267">
@@ -14869,10 +14869,10 @@
         <v>0.79</v>
       </c>
       <c r="I267" t="n">
-        <v>-0.1955</v>
+        <v>-0.2209</v>
       </c>
       <c r="J267" t="n">
-        <v>-3.91</v>
+        <v>-4.418</v>
       </c>
     </row>
     <row r="268">
@@ -14909,10 +14909,10 @@
         <v>0.75</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.2379</v>
+        <v>-0.262</v>
       </c>
       <c r="J268" t="n">
-        <v>-4.758</v>
+        <v>-5.24</v>
       </c>
     </row>
     <row r="269">
@@ -14949,10 +14949,10 @@
         <v>0.63</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.3523</v>
+        <v>-0.3723</v>
       </c>
       <c r="J269" t="n">
-        <v>-7.046</v>
+        <v>-7.446</v>
       </c>
     </row>
     <row r="270">
@@ -14989,10 +14989,10 @@
         <v>0.57</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.407</v>
+        <v>-0.4244</v>
       </c>
       <c r="J270" t="n">
-        <v>-8.140000000000001</v>
+        <v>-8.488</v>
       </c>
     </row>
     <row r="271">
@@ -15029,10 +15029,10 @@
         <v>0.46</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.5102</v>
+        <v>-0.5211</v>
       </c>
       <c r="J271" t="n">
-        <v>-10.204</v>
+        <v>-10.422</v>
       </c>
     </row>
     <row r="272">
@@ -15069,10 +15069,10 @@
         <v>1.08</v>
       </c>
       <c r="I272" t="n">
-        <v>0.2972</v>
+        <v>0.2801</v>
       </c>
       <c r="J272" t="n">
-        <v>7.43</v>
+        <v>7.0025</v>
       </c>
     </row>
     <row r="273">
@@ -15109,10 +15109,10 @@
         <v>0.75</v>
       </c>
       <c r="I273" t="n">
-        <v>-0.2586</v>
+        <v>-0.2779</v>
       </c>
       <c r="J273" t="n">
-        <v>-6.465</v>
+        <v>-6.9475</v>
       </c>
     </row>
     <row r="274">
@@ -15149,10 +15149,10 @@
         <v>0.72</v>
       </c>
       <c r="I274" t="n">
-        <v>-0.2866</v>
+        <v>-0.3053</v>
       </c>
       <c r="J274" t="n">
-        <v>-7.165</v>
+        <v>-7.6325</v>
       </c>
     </row>
     <row r="275">
@@ -15189,10 +15189,10 @@
         <v>0.66</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.3431</v>
+        <v>-0.3599</v>
       </c>
       <c r="J275" t="n">
-        <v>-8.577500000000001</v>
+        <v>-8.9975</v>
       </c>
     </row>
     <row r="276">
@@ -15229,10 +15229,10 @@
         <v>0.61</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.39</v>
+        <v>-0.4048</v>
       </c>
       <c r="J276" t="n">
-        <v>-9.75</v>
+        <v>-10.12</v>
       </c>
     </row>
     <row r="277">
@@ -15269,10 +15269,10 @@
         <v>1.47</v>
       </c>
       <c r="I277" t="n">
-        <v>1.0984</v>
+        <v>1.0582</v>
       </c>
       <c r="J277" t="n">
-        <v>27.46</v>
+        <v>26.455</v>
       </c>
     </row>
     <row r="278">
@@ -15309,10 +15309,10 @@
         <v>1.42</v>
       </c>
       <c r="I278" t="n">
-        <v>1.0317</v>
+        <v>0.9797</v>
       </c>
       <c r="J278" t="n">
-        <v>25.7925</v>
+        <v>24.4925</v>
       </c>
     </row>
     <row r="279">
@@ -15349,10 +15349,10 @@
         <v>1.21</v>
       </c>
       <c r="I279" t="n">
-        <v>0.5812</v>
+        <v>0.5648</v>
       </c>
       <c r="J279" t="n">
-        <v>14.53</v>
+        <v>14.12</v>
       </c>
     </row>
     <row r="280">
@@ -15389,10 +15389,10 @@
         <v>1.12</v>
       </c>
       <c r="I280" t="n">
-        <v>0.3533</v>
+        <v>0.358</v>
       </c>
       <c r="J280" t="n">
-        <v>8.8325</v>
+        <v>8.949999999999999</v>
       </c>
     </row>
     <row r="281">
@@ -15429,10 +15429,10 @@
         <v>0.88</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.4654</v>
+        <v>-0.4358</v>
       </c>
       <c r="J281" t="n">
-        <v>-11.635</v>
+        <v>-10.895</v>
       </c>
     </row>
     <row r="282">
@@ -15469,10 +15469,10 @@
         <v>1.42</v>
       </c>
       <c r="I282" t="n">
-        <v>1.0408</v>
+        <v>0.9883999999999999</v>
       </c>
       <c r="J282" t="n">
-        <v>42.6728</v>
+        <v>40.5244</v>
       </c>
     </row>
     <row r="283">
@@ -15509,10 +15509,10 @@
         <v>1.24</v>
       </c>
       <c r="I283" t="n">
-        <v>0.6581</v>
+        <v>0.6323</v>
       </c>
       <c r="J283" t="n">
-        <v>26.9821</v>
+        <v>25.9243</v>
       </c>
     </row>
     <row r="284">
@@ -15549,10 +15549,10 @@
         <v>1.24</v>
       </c>
       <c r="I284" t="n">
-        <v>0.6581</v>
+        <v>0.6323</v>
       </c>
       <c r="J284" t="n">
-        <v>26.9821</v>
+        <v>25.9243</v>
       </c>
     </row>
     <row r="285">
@@ -15589,10 +15589,10 @@
         <v>1.22</v>
       </c>
       <c r="I285" t="n">
-        <v>0.6105</v>
+        <v>0.5899</v>
       </c>
       <c r="J285" t="n">
-        <v>25.0305</v>
+        <v>24.1859</v>
       </c>
     </row>
     <row r="286">
@@ -15629,10 +15629,10 @@
         <v>0.79</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.6965</v>
+        <v>-0.6452</v>
       </c>
       <c r="J286" t="n">
-        <v>-28.5565</v>
+        <v>-26.4532</v>
       </c>
     </row>
     <row r="287">
@@ -15669,10 +15669,10 @@
         <v>1.07</v>
       </c>
       <c r="I287" t="n">
-        <v>0.1962</v>
+        <v>0.2008</v>
       </c>
       <c r="J287" t="n">
-        <v>8.0442</v>
+        <v>8.232799999999999</v>
       </c>
     </row>
     <row r="288">
@@ -15709,10 +15709,10 @@
         <v>1.02</v>
       </c>
       <c r="I288" t="n">
-        <v>0.076</v>
+        <v>0.0805</v>
       </c>
       <c r="J288" t="n">
-        <v>3.116</v>
+        <v>3.3005</v>
       </c>
     </row>
     <row r="289">
@@ -15749,10 +15749,10 @@
         <v>1</v>
       </c>
       <c r="I289" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.0058</v>
       </c>
       <c r="J289" t="n">
-        <v>0.3362</v>
+        <v>0.2378</v>
       </c>
     </row>
     <row r="290">
@@ -15789,10 +15789,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.0835</v>
+        <v>-0.0955</v>
       </c>
       <c r="J290" t="n">
-        <v>-3.4235</v>
+        <v>-3.9155</v>
       </c>
     </row>
     <row r="291">
@@ -15829,10 +15829,10 @@
         <v>0.72</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.3113</v>
+        <v>-0.3246</v>
       </c>
       <c r="J291" t="n">
-        <v>-12.7633</v>
+        <v>-13.3086</v>
       </c>
     </row>
     <row r="292">
@@ -15869,10 +15869,10 @@
         <v>0.77</v>
       </c>
       <c r="I292" t="n">
-        <v>-0.2268</v>
+        <v>-0.2494</v>
       </c>
       <c r="J292" t="n">
-        <v>-4.7628</v>
+        <v>-5.2374</v>
       </c>
     </row>
     <row r="293">
@@ -15909,10 +15909,10 @@
         <v>0.73</v>
       </c>
       <c r="I293" t="n">
-        <v>-0.2668</v>
+        <v>-0.2882</v>
       </c>
       <c r="J293" t="n">
-        <v>-5.6028</v>
+        <v>-6.0522</v>
       </c>
     </row>
     <row r="294">
@@ -15949,10 +15949,10 @@
         <v>0.72</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.2764</v>
+        <v>-0.2976</v>
       </c>
       <c r="J294" t="n">
-        <v>-5.8044</v>
+        <v>-6.2496</v>
       </c>
     </row>
     <row r="295">
@@ -15989,10 +15989,10 @@
         <v>0.67</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.3217</v>
+        <v>-0.3417</v>
       </c>
       <c r="J295" t="n">
-        <v>-6.7557</v>
+        <v>-7.1757</v>
       </c>
     </row>
     <row r="296">
@@ -16029,10 +16029,10 @@
         <v>0.51</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.4701</v>
+        <v>-0.4826</v>
       </c>
       <c r="J296" t="n">
-        <v>-9.8721</v>
+        <v>-10.1346</v>
       </c>
     </row>
     <row r="297">
@@ -16069,10 +16069,10 @@
         <v>2.36</v>
       </c>
       <c r="I297" t="n">
-        <v>1.8338</v>
+        <v>1.9372</v>
       </c>
       <c r="J297" t="n">
-        <v>38.5098</v>
+        <v>40.6812</v>
       </c>
     </row>
     <row r="298">
@@ -16109,10 +16109,10 @@
         <v>1.68</v>
       </c>
       <c r="I298" t="n">
-        <v>1.3047</v>
+        <v>1.2895</v>
       </c>
       <c r="J298" t="n">
-        <v>27.3987</v>
+        <v>27.0795</v>
       </c>
     </row>
     <row r="299">
@@ -16149,10 +16149,10 @@
         <v>1.61</v>
       </c>
       <c r="I299" t="n">
-        <v>1.2236</v>
+        <v>1.2026</v>
       </c>
       <c r="J299" t="n">
-        <v>25.6956</v>
+        <v>25.2546</v>
       </c>
     </row>
     <row r="300">
@@ -16189,10 +16189,10 @@
         <v>0.96</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.2791</v>
+        <v>-0.249</v>
       </c>
       <c r="J300" t="n">
-        <v>-5.8611</v>
+        <v>-5.229</v>
       </c>
     </row>
     <row r="301">
@@ -16229,10 +16229,10 @@
         <v>0.8</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.7317</v>
+        <v>-0.6654</v>
       </c>
       <c r="J301" t="n">
-        <v>-15.3657</v>
+        <v>-13.9734</v>
       </c>
     </row>
     <row r="302">
@@ -16269,10 +16269,10 @@
         <v>0.93</v>
       </c>
       <c r="I302" t="n">
-        <v>-0.0169</v>
+        <v>-0.0465</v>
       </c>
       <c r="J302" t="n">
-        <v>-0.3211</v>
+        <v>-0.8835</v>
       </c>
     </row>
     <row r="303">
@@ -16309,10 +16309,10 @@
         <v>0.71</v>
       </c>
       <c r="I303" t="n">
-        <v>-0.2717</v>
+        <v>-0.2958</v>
       </c>
       <c r="J303" t="n">
-        <v>-5.1623</v>
+        <v>-5.6202</v>
       </c>
     </row>
     <row r="304">
@@ -16349,10 +16349,10 @@
         <v>0.61</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.3665</v>
+        <v>-0.3866</v>
       </c>
       <c r="J304" t="n">
-        <v>-6.9635</v>
+        <v>-7.3454</v>
       </c>
     </row>
     <row r="305">
@@ -16389,10 +16389,10 @@
         <v>0.54</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.4298</v>
+        <v>-0.4467</v>
       </c>
       <c r="J305" t="n">
-        <v>-8.1662</v>
+        <v>-8.487299999999999</v>
       </c>
     </row>
     <row r="306">
@@ -16429,10 +16429,10 @@
         <v>0.27</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.6866</v>
+        <v>-0.6843</v>
       </c>
       <c r="J306" t="n">
-        <v>-13.0454</v>
+        <v>-13.0017</v>
       </c>
     </row>
     <row r="307">
@@ -16469,10 +16469,10 @@
         <v>2.09</v>
       </c>
       <c r="I307" t="n">
-        <v>1.7468</v>
+        <v>1.7581</v>
       </c>
       <c r="J307" t="n">
-        <v>33.1892</v>
+        <v>33.4039</v>
       </c>
     </row>
     <row r="308">
@@ -16509,10 +16509,10 @@
         <v>1.96</v>
       </c>
       <c r="I308" t="n">
-        <v>1.605</v>
+        <v>1.6097</v>
       </c>
       <c r="J308" t="n">
-        <v>30.495</v>
+        <v>30.5843</v>
       </c>
     </row>
     <row r="309">
@@ -16549,10 +16549,10 @@
         <v>1.47</v>
       </c>
       <c r="I309" t="n">
-        <v>1.0525</v>
+        <v>1.0154</v>
       </c>
       <c r="J309" t="n">
-        <v>19.9975</v>
+        <v>19.2926</v>
       </c>
     </row>
     <row r="310">
@@ -16589,10 +16589,10 @@
         <v>1.22</v>
       </c>
       <c r="I310" t="n">
-        <v>0.5349</v>
+        <v>0.5375</v>
       </c>
       <c r="J310" t="n">
-        <v>10.1631</v>
+        <v>10.2125</v>
       </c>
     </row>
     <row r="311">
@@ -16629,10 +16629,10 @@
         <v>1.1</v>
       </c>
       <c r="I311" t="n">
-        <v>0.2229</v>
+        <v>0.2545</v>
       </c>
       <c r="J311" t="n">
-        <v>4.2351</v>
+        <v>4.8355</v>
       </c>
     </row>
     <row r="312">
@@ -16669,10 +16669,10 @@
         <v>1.28</v>
       </c>
       <c r="I312" t="n">
-        <v>0.5638</v>
+        <v>0.5521</v>
       </c>
       <c r="J312" t="n">
-        <v>16.3502</v>
+        <v>16.0109</v>
       </c>
     </row>
     <row r="313">
@@ -16709,10 +16709,10 @@
         <v>1.26</v>
       </c>
       <c r="I313" t="n">
-        <v>0.5291</v>
+        <v>0.5203</v>
       </c>
       <c r="J313" t="n">
-        <v>15.3439</v>
+        <v>15.0887</v>
       </c>
     </row>
     <row r="314">
@@ -16749,10 +16749,10 @@
         <v>1.22</v>
       </c>
       <c r="I314" t="n">
-        <v>0.4588</v>
+        <v>0.4555</v>
       </c>
       <c r="J314" t="n">
-        <v>13.3052</v>
+        <v>13.2095</v>
       </c>
     </row>
     <row r="315">
@@ -16789,10 +16789,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.09379999999999999</v>
+        <v>-0.1034</v>
       </c>
       <c r="J315" t="n">
-        <v>-2.7202</v>
+        <v>-2.9986</v>
       </c>
     </row>
     <row r="316">
@@ -16829,10 +16829,10 @@
         <v>0.57</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.4617</v>
+        <v>-0.4673</v>
       </c>
       <c r="J316" t="n">
-        <v>-13.3893</v>
+        <v>-13.5517</v>
       </c>
     </row>
     <row r="317">
@@ -16869,10 +16869,10 @@
         <v>1.67</v>
       </c>
       <c r="I317" t="n">
-        <v>1.3906</v>
+        <v>1.3634</v>
       </c>
       <c r="J317" t="n">
-        <v>40.3274</v>
+        <v>39.5386</v>
       </c>
     </row>
     <row r="318">
@@ -16909,10 +16909,10 @@
         <v>1.02</v>
       </c>
       <c r="I318" t="n">
-        <v>0.0731</v>
+        <v>0.08550000000000001</v>
       </c>
       <c r="J318" t="n">
-        <v>2.1199</v>
+        <v>2.4795</v>
       </c>
     </row>
     <row r="319">
@@ -16949,10 +16949,10 @@
         <v>0.99</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.0772</v>
+        <v>-0.075</v>
       </c>
       <c r="J319" t="n">
-        <v>-2.2388</v>
+        <v>-2.175</v>
       </c>
     </row>
     <row r="320">
@@ -16989,10 +16989,10 @@
         <v>0.98</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.1182</v>
+        <v>-0.1164</v>
       </c>
       <c r="J320" t="n">
-        <v>-3.4278</v>
+        <v>-3.3756</v>
       </c>
     </row>
     <row r="321">
@@ -17029,10 +17029,10 @@
         <v>0.83</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.5704</v>
+        <v>-0.5369</v>
       </c>
       <c r="J321" t="n">
-        <v>-16.5416</v>
+        <v>-15.5701</v>
       </c>
     </row>
     <row r="322">
@@ -17069,10 +17069,10 @@
         <v>1.66</v>
       </c>
       <c r="I322" t="n">
-        <v>1.2834</v>
+        <v>1.2664</v>
       </c>
       <c r="J322" t="n">
-        <v>24.3846</v>
+        <v>24.0616</v>
       </c>
     </row>
     <row r="323">
@@ -17109,10 +17109,10 @@
         <v>1.65</v>
       </c>
       <c r="I323" t="n">
-        <v>1.2718</v>
+        <v>1.254</v>
       </c>
       <c r="J323" t="n">
-        <v>24.1642</v>
+        <v>23.826</v>
       </c>
     </row>
     <row r="324">
@@ -17149,10 +17149,10 @@
         <v>1.42</v>
       </c>
       <c r="I324" t="n">
-        <v>0.9922</v>
+        <v>0.9451000000000001</v>
       </c>
       <c r="J324" t="n">
-        <v>18.8518</v>
+        <v>17.9569</v>
       </c>
     </row>
     <row r="325">
@@ -17189,10 +17189,10 @@
         <v>1.35</v>
       </c>
       <c r="I325" t="n">
-        <v>0.8536</v>
+        <v>0.8157</v>
       </c>
       <c r="J325" t="n">
-        <v>16.2184</v>
+        <v>15.4983</v>
       </c>
     </row>
     <row r="326">
@@ -17229,10 +17229,10 @@
         <v>1.27</v>
       </c>
       <c r="I326" t="n">
-        <v>0.6731</v>
+        <v>0.6568000000000001</v>
       </c>
       <c r="J326" t="n">
-        <v>12.7889</v>
+        <v>12.4792</v>
       </c>
     </row>
     <row r="327">
@@ -17269,10 +17269,10 @@
         <v>1.01</v>
       </c>
       <c r="I327" t="n">
-        <v>0.2208</v>
+        <v>0.1781</v>
       </c>
       <c r="J327" t="n">
-        <v>4.1952</v>
+        <v>3.3839</v>
       </c>
     </row>
     <row r="328">
@@ -17309,10 +17309,10 @@
         <v>0.72</v>
       </c>
       <c r="I328" t="n">
-        <v>-0.262</v>
+        <v>-0.2864</v>
       </c>
       <c r="J328" t="n">
-        <v>-4.978</v>
+        <v>-5.4416</v>
       </c>
     </row>
     <row r="329">
@@ -17349,10 +17349,10 @@
         <v>0.54</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.4302</v>
+        <v>-0.447</v>
       </c>
       <c r="J329" t="n">
-        <v>-8.1738</v>
+        <v>-8.493</v>
       </c>
     </row>
     <row r="330">
@@ -17389,10 +17389,10 @@
         <v>0.46</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.5054</v>
+        <v>-0.5174</v>
       </c>
       <c r="J330" t="n">
-        <v>-9.602600000000001</v>
+        <v>-9.8306</v>
       </c>
     </row>
     <row r="331">
@@ -17429,10 +17429,10 @@
         <v>0.34</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.6198</v>
+        <v>-0.623</v>
       </c>
       <c r="J331" t="n">
-        <v>-11.7762</v>
+        <v>-11.837</v>
       </c>
     </row>
     <row r="332">
@@ -17469,10 +17469,10 @@
         <v>1.37</v>
       </c>
       <c r="I332" t="n">
-        <v>0.701</v>
+        <v>0.6792</v>
       </c>
       <c r="J332" t="n">
-        <v>41.359</v>
+        <v>40.0728</v>
       </c>
     </row>
     <row r="333">
@@ -17509,10 +17509,10 @@
         <v>1.22</v>
       </c>
       <c r="I333" t="n">
-        <v>0.4475</v>
+        <v>0.4473</v>
       </c>
       <c r="J333" t="n">
-        <v>26.4025</v>
+        <v>26.3907</v>
       </c>
     </row>
     <row r="334">
@@ -17549,10 +17549,10 @@
         <v>1.07</v>
       </c>
       <c r="I334" t="n">
-        <v>0.1686</v>
+        <v>0.1809</v>
       </c>
       <c r="J334" t="n">
-        <v>9.9474</v>
+        <v>10.6731</v>
       </c>
     </row>
     <row r="335">
@@ -17589,10 +17589,10 @@
         <v>0.92</v>
       </c>
       <c r="I335" t="n">
-        <v>-0.1222</v>
+        <v>-0.1318</v>
       </c>
       <c r="J335" t="n">
-        <v>-7.2098</v>
+        <v>-7.7762</v>
       </c>
     </row>
     <row r="336">
@@ -17629,10 +17629,10 @@
         <v>0.91</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.1337</v>
+        <v>-0.1437</v>
       </c>
       <c r="J336" t="n">
-        <v>-7.8883</v>
+        <v>-8.478300000000001</v>
       </c>
     </row>
     <row r="337">
@@ -17669,10 +17669,10 @@
         <v>1.32</v>
       </c>
       <c r="I337" t="n">
-        <v>0.8986</v>
+        <v>0.8347</v>
       </c>
       <c r="J337" t="n">
-        <v>53.0174</v>
+        <v>49.2473</v>
       </c>
     </row>
     <row r="338">
@@ -17709,10 +17709,10 @@
         <v>1.15</v>
       </c>
       <c r="I338" t="n">
-        <v>0.4714</v>
+        <v>0.457</v>
       </c>
       <c r="J338" t="n">
-        <v>27.8126</v>
+        <v>26.963</v>
       </c>
     </row>
     <row r="339">
@@ -17749,10 +17749,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I339" t="n">
-        <v>-0.2416</v>
+        <v>-0.2391</v>
       </c>
       <c r="J339" t="n">
-        <v>-14.2544</v>
+        <v>-14.1069</v>
       </c>
     </row>
     <row r="340">
@@ -17789,10 +17789,10 @@
         <v>0.91</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.3329</v>
+        <v>-0.3242</v>
       </c>
       <c r="J340" t="n">
-        <v>-19.6411</v>
+        <v>-19.1278</v>
       </c>
     </row>
     <row r="341">
@@ -17829,10 +17829,10 @@
         <v>0.91</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.3329</v>
+        <v>-0.3242</v>
       </c>
       <c r="J341" t="n">
-        <v>-19.6411</v>
+        <v>-19.1278</v>
       </c>
     </row>
     <row r="342">
@@ -17869,10 +17869,10 @@
         <v>2</v>
       </c>
       <c r="I342" t="n">
-        <v>1.6536</v>
+        <v>1.6599</v>
       </c>
       <c r="J342" t="n">
-        <v>28.1112</v>
+        <v>28.2183</v>
       </c>
     </row>
     <row r="343">
@@ -17909,10 +17909,10 @@
         <v>1.67</v>
       </c>
       <c r="I343" t="n">
-        <v>1.2846</v>
+        <v>1.2697</v>
       </c>
       <c r="J343" t="n">
-        <v>21.8382</v>
+        <v>21.5849</v>
       </c>
     </row>
     <row r="344">
@@ -17949,10 +17949,10 @@
         <v>1.53</v>
       </c>
       <c r="I344" t="n">
-        <v>1.1257</v>
+        <v>1.0981</v>
       </c>
       <c r="J344" t="n">
-        <v>19.1369</v>
+        <v>18.6677</v>
       </c>
     </row>
     <row r="345">
@@ -17989,10 +17989,10 @@
         <v>1.39</v>
       </c>
       <c r="I345" t="n">
-        <v>0.9252</v>
+        <v>0.8819</v>
       </c>
       <c r="J345" t="n">
-        <v>15.7284</v>
+        <v>14.9923</v>
       </c>
     </row>
     <row r="346">
@@ -18029,10 +18029,10 @@
         <v>1.13</v>
       </c>
       <c r="I346" t="n">
-        <v>0.3102</v>
+        <v>0.3338</v>
       </c>
       <c r="J346" t="n">
-        <v>5.2734</v>
+        <v>5.6746</v>
       </c>
     </row>
     <row r="347">
@@ -18069,10 +18069,10 @@
         <v>1.1</v>
       </c>
       <c r="I347" t="n">
-        <v>0.4428</v>
+        <v>0.3976</v>
       </c>
       <c r="J347" t="n">
-        <v>7.5276</v>
+        <v>6.7592</v>
       </c>
     </row>
     <row r="348">
@@ -18109,10 +18109,10 @@
         <v>0.75</v>
       </c>
       <c r="I348" t="n">
-        <v>-0.2369</v>
+        <v>-0.2612</v>
       </c>
       <c r="J348" t="n">
-        <v>-4.0273</v>
+        <v>-4.4404</v>
       </c>
     </row>
     <row r="349">
@@ -18149,10 +18149,10 @@
         <v>0.66</v>
       </c>
       <c r="I349" t="n">
-        <v>-0.3256</v>
+        <v>-0.3465</v>
       </c>
       <c r="J349" t="n">
-        <v>-5.5352</v>
+        <v>-5.8905</v>
       </c>
     </row>
     <row r="350">
@@ -18189,10 +18189,10 @@
         <v>0.44</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.5284</v>
+        <v>-0.5381</v>
       </c>
       <c r="J350" t="n">
-        <v>-8.982799999999999</v>
+        <v>-9.1477</v>
       </c>
     </row>
     <row r="351">
@@ -18229,10 +18229,10 @@
         <v>0.23</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.7278</v>
+        <v>-0.7215</v>
       </c>
       <c r="J351" t="n">
-        <v>-12.3726</v>
+        <v>-12.2655</v>
       </c>
     </row>
     <row r="352">
@@ -18269,10 +18269,10 @@
         <v>1.35</v>
       </c>
       <c r="I352" t="n">
-        <v>0.903</v>
+        <v>0.8498</v>
       </c>
       <c r="J352" t="n">
-        <v>22.575</v>
+        <v>21.245</v>
       </c>
     </row>
     <row r="353">
@@ -18309,10 +18309,10 @@
         <v>1.35</v>
       </c>
       <c r="I353" t="n">
-        <v>0.903</v>
+        <v>0.8498</v>
       </c>
       <c r="J353" t="n">
-        <v>22.575</v>
+        <v>21.245</v>
       </c>
     </row>
     <row r="354">
@@ -18349,10 +18349,10 @@
         <v>1.27</v>
       </c>
       <c r="I354" t="n">
-        <v>0.7208</v>
+        <v>0.6895</v>
       </c>
       <c r="J354" t="n">
-        <v>18.02</v>
+        <v>17.2375</v>
       </c>
     </row>
     <row r="355">
@@ -18389,10 +18389,10 @@
         <v>1.13</v>
       </c>
       <c r="I355" t="n">
-        <v>0.3816</v>
+        <v>0.3836</v>
       </c>
       <c r="J355" t="n">
-        <v>9.539999999999999</v>
+        <v>9.59</v>
       </c>
     </row>
     <row r="356">
@@ -18429,10 +18429,10 @@
         <v>0.97</v>
       </c>
       <c r="I356" t="n">
-        <v>-0.1855</v>
+        <v>-0.174</v>
       </c>
       <c r="J356" t="n">
-        <v>-4.6375</v>
+        <v>-4.35</v>
       </c>
     </row>
     <row r="357">
@@ -18469,10 +18469,10 @@
         <v>0.9</v>
       </c>
       <c r="I357" t="n">
-        <v>-0.116</v>
+        <v>-0.133</v>
       </c>
       <c r="J357" t="n">
-        <v>-2.9</v>
+        <v>-3.325</v>
       </c>
     </row>
     <row r="358">
@@ -18509,10 +18509,10 @@
         <v>0.88</v>
       </c>
       <c r="I358" t="n">
-        <v>-0.1381</v>
+        <v>-0.1555</v>
       </c>
       <c r="J358" t="n">
-        <v>-3.4525</v>
+        <v>-3.8875</v>
       </c>
     </row>
     <row r="359">
@@ -18549,10 +18549,10 @@
         <v>0.82</v>
       </c>
       <c r="I359" t="n">
-        <v>-0.1988</v>
+        <v>-0.2169</v>
       </c>
       <c r="J359" t="n">
-        <v>-4.97</v>
+        <v>-5.4225</v>
       </c>
     </row>
     <row r="360">
@@ -18589,10 +18589,10 @@
         <v>0.79</v>
       </c>
       <c r="I360" t="n">
-        <v>-0.2279</v>
+        <v>-0.2459</v>
       </c>
       <c r="J360" t="n">
-        <v>-5.6975</v>
+        <v>-6.1475</v>
       </c>
     </row>
     <row r="361">
@@ -18629,10 +18629,10 @@
         <v>0.75</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.2666</v>
+        <v>-0.284</v>
       </c>
       <c r="J361" t="n">
-        <v>-6.665</v>
+        <v>-7.1</v>
       </c>
     </row>
     <row r="362">
@@ -18669,10 +18669,10 @@
         <v>1.57</v>
       </c>
       <c r="I362" t="n">
-        <v>1.2288</v>
+        <v>1.198</v>
       </c>
       <c r="J362" t="n">
-        <v>31.9488</v>
+        <v>31.148</v>
       </c>
     </row>
     <row r="363">
@@ -18709,10 +18709,10 @@
         <v>1.52</v>
       </c>
       <c r="I363" t="n">
-        <v>1.1655</v>
+        <v>1.1303</v>
       </c>
       <c r="J363" t="n">
-        <v>30.303</v>
+        <v>29.3878</v>
       </c>
     </row>
     <row r="364">
@@ -18749,10 +18749,10 @@
         <v>1.31</v>
       </c>
       <c r="I364" t="n">
-        <v>0.8148</v>
+        <v>0.772</v>
       </c>
       <c r="J364" t="n">
-        <v>21.1848</v>
+        <v>20.072</v>
       </c>
     </row>
     <row r="365">
@@ -18789,10 +18789,10 @@
         <v>0.84</v>
       </c>
       <c r="I365" t="n">
-        <v>-0.5715</v>
+        <v>-0.5325</v>
       </c>
       <c r="J365" t="n">
-        <v>-14.859</v>
+        <v>-13.845</v>
       </c>
     </row>
     <row r="366">
@@ -18829,10 +18829,10 @@
         <v>0.79</v>
       </c>
       <c r="I366" t="n">
-        <v>-0.7022</v>
+        <v>-0.6492</v>
       </c>
       <c r="J366" t="n">
-        <v>-18.2572</v>
+        <v>-16.8792</v>
       </c>
     </row>
     <row r="367">
@@ -18869,10 +18869,10 @@
         <v>1.07</v>
       </c>
       <c r="I367" t="n">
-        <v>0.1957</v>
+        <v>0.2003</v>
       </c>
       <c r="J367" t="n">
-        <v>5.0882</v>
+        <v>5.2078</v>
       </c>
     </row>
     <row r="368">
@@ -18909,10 +18909,10 @@
         <v>1.05</v>
       </c>
       <c r="I368" t="n">
-        <v>0.1505</v>
+        <v>0.1559</v>
       </c>
       <c r="J368" t="n">
-        <v>3.913</v>
+        <v>4.0534</v>
       </c>
     </row>
     <row r="369">
@@ -18949,10 +18949,10 @@
         <v>0.9</v>
       </c>
       <c r="I369" t="n">
-        <v>-0.129</v>
+        <v>-0.1429</v>
       </c>
       <c r="J369" t="n">
-        <v>-3.354</v>
+        <v>-3.7154</v>
       </c>
     </row>
     <row r="370">
@@ -18989,10 +18989,10 @@
         <v>0.89</v>
       </c>
       <c r="I370" t="n">
-        <v>-0.1399</v>
+        <v>-0.1541</v>
       </c>
       <c r="J370" t="n">
-        <v>-3.6374</v>
+        <v>-4.0066</v>
       </c>
     </row>
     <row r="371">
@@ -19029,10 +19029,10 @@
         <v>0.85</v>
       </c>
       <c r="I371" t="n">
-        <v>-0.1824</v>
+        <v>-0.1971</v>
       </c>
       <c r="J371" t="n">
-        <v>-4.7424</v>
+        <v>-5.1246</v>
       </c>
     </row>
     <row r="372">
@@ -19069,10 +19069,10 @@
         <v>0.95</v>
       </c>
       <c r="I372" t="n">
-        <v>-0.06370000000000001</v>
+        <v>-0.0767</v>
       </c>
       <c r="J372" t="n">
-        <v>-1.5288</v>
+        <v>-1.8408</v>
       </c>
     </row>
     <row r="373">
@@ -19109,10 +19109,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I373" t="n">
-        <v>-0.0761</v>
+        <v>-0.08989999999999999</v>
       </c>
       <c r="J373" t="n">
-        <v>-1.8264</v>
+        <v>-2.1576</v>
       </c>
     </row>
     <row r="374">
@@ -19149,10 +19149,10 @@
         <v>0.92</v>
       </c>
       <c r="I374" t="n">
-        <v>-0.0999</v>
+        <v>-0.1147</v>
       </c>
       <c r="J374" t="n">
-        <v>-2.3976</v>
+        <v>-2.7528</v>
       </c>
     </row>
     <row r="375">
@@ -19189,10 +19189,10 @@
         <v>0.9</v>
       </c>
       <c r="I375" t="n">
-        <v>-0.1223</v>
+        <v>-0.1379</v>
       </c>
       <c r="J375" t="n">
-        <v>-2.9352</v>
+        <v>-3.3096</v>
       </c>
     </row>
     <row r="376">
@@ -19229,10 +19229,10 @@
         <v>0.67</v>
       </c>
       <c r="I376" t="n">
-        <v>-0.3495</v>
+        <v>-0.3632</v>
       </c>
       <c r="J376" t="n">
-        <v>-8.388</v>
+        <v>-8.716799999999999</v>
       </c>
     </row>
     <row r="377">
@@ -19269,10 +19269,10 @@
         <v>1.74</v>
       </c>
       <c r="I377" t="n">
-        <v>1.4195</v>
+        <v>1.4033</v>
       </c>
       <c r="J377" t="n">
-        <v>34.068</v>
+        <v>33.6792</v>
       </c>
     </row>
     <row r="378">
@@ -19309,10 +19309,10 @@
         <v>1.36</v>
       </c>
       <c r="I378" t="n">
-        <v>0.9088000000000001</v>
+        <v>0.8579</v>
       </c>
       <c r="J378" t="n">
-        <v>21.8112</v>
+        <v>20.5896</v>
       </c>
     </row>
     <row r="379">
@@ -19349,10 +19349,10 @@
         <v>1.26</v>
       </c>
       <c r="I379" t="n">
-        <v>0.6883</v>
+        <v>0.6626</v>
       </c>
       <c r="J379" t="n">
-        <v>16.5192</v>
+        <v>15.9024</v>
       </c>
     </row>
     <row r="380">
@@ -19389,10 +19389,10 @@
         <v>1.24</v>
       </c>
       <c r="I380" t="n">
-        <v>0.6424</v>
+        <v>0.6217</v>
       </c>
       <c r="J380" t="n">
-        <v>15.4176</v>
+        <v>14.9208</v>
       </c>
     </row>
     <row r="381">
@@ -19429,10 +19429,10 @@
         <v>0.77</v>
       </c>
       <c r="I381" t="n">
-        <v>-0.7681</v>
+        <v>-0.7048</v>
       </c>
       <c r="J381" t="n">
-        <v>-18.4344</v>
+        <v>-16.9152</v>
       </c>
     </row>
     <row r="382">
@@ -19469,10 +19469,10 @@
         <v>1.66</v>
       </c>
       <c r="I382" t="n">
-        <v>1.2838</v>
+        <v>1.2667</v>
       </c>
       <c r="J382" t="n">
-        <v>26.9598</v>
+        <v>26.6007</v>
       </c>
     </row>
     <row r="383">
@@ -19509,10 +19509,10 @@
         <v>1.62</v>
       </c>
       <c r="I383" t="n">
-        <v>1.2372</v>
+        <v>1.2168</v>
       </c>
       <c r="J383" t="n">
-        <v>25.9812</v>
+        <v>25.5528</v>
       </c>
     </row>
     <row r="384">
@@ -19549,10 +19549,10 @@
         <v>1.48</v>
       </c>
       <c r="I384" t="n">
-        <v>1.073</v>
+        <v>1.0375</v>
       </c>
       <c r="J384" t="n">
-        <v>22.533</v>
+        <v>21.7875</v>
       </c>
     </row>
     <row r="385">
@@ -19589,10 +19589,10 @@
         <v>1.43</v>
       </c>
       <c r="I385" t="n">
-        <v>1.0082</v>
+        <v>0.9622000000000001</v>
       </c>
       <c r="J385" t="n">
-        <v>21.1722</v>
+        <v>20.2062</v>
       </c>
     </row>
     <row r="386">
@@ -19629,10 +19629,10 @@
         <v>1.15</v>
       </c>
       <c r="I386" t="n">
-        <v>0.3785</v>
+        <v>0.3928</v>
       </c>
       <c r="J386" t="n">
-        <v>7.9485</v>
+        <v>8.248799999999999</v>
       </c>
     </row>
     <row r="387">
@@ -19669,10 +19669,10 @@
         <v>1.18</v>
       </c>
       <c r="I387" t="n">
-        <v>0.6145</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="J387" t="n">
-        <v>12.9045</v>
+        <v>11.697</v>
       </c>
     </row>
     <row r="388">
@@ -19709,10 +19709,10 @@
         <v>0.63</v>
       </c>
       <c r="I388" t="n">
-        <v>-0.3531</v>
+        <v>-0.3729</v>
       </c>
       <c r="J388" t="n">
-        <v>-7.4151</v>
+        <v>-7.8309</v>
       </c>
     </row>
     <row r="389">
@@ -19749,10 +19749,10 @@
         <v>0.53</v>
       </c>
       <c r="I389" t="n">
-        <v>-0.4454</v>
+        <v>-0.4604</v>
       </c>
       <c r="J389" t="n">
-        <v>-9.353400000000001</v>
+        <v>-9.6684</v>
       </c>
     </row>
     <row r="390">
@@ -19789,10 +19789,10 @@
         <v>0.45</v>
       </c>
       <c r="I390" t="n">
-        <v>-0.5207000000000001</v>
+        <v>-0.5306999999999999</v>
       </c>
       <c r="J390" t="n">
-        <v>-10.9347</v>
+        <v>-11.1447</v>
       </c>
     </row>
     <row r="391">
@@ -19829,10 +19829,10 @@
         <v>0.44</v>
       </c>
       <c r="I391" t="n">
-        <v>-0.5301</v>
+        <v>-0.5395</v>
       </c>
       <c r="J391" t="n">
-        <v>-11.1321</v>
+        <v>-11.3295</v>
       </c>
     </row>
     <row r="392">
@@ -19869,10 +19869,10 @@
         <v>1.26</v>
       </c>
       <c r="I392" t="n">
-        <v>0.5786</v>
+        <v>0.5567</v>
       </c>
       <c r="J392" t="n">
-        <v>15.6222</v>
+        <v>15.0309</v>
       </c>
     </row>
     <row r="393">
@@ -19909,10 +19909,10 @@
         <v>1.04</v>
       </c>
       <c r="I393" t="n">
-        <v>0.135</v>
+        <v>0.1383</v>
       </c>
       <c r="J393" t="n">
-        <v>3.645</v>
+        <v>3.7341</v>
       </c>
     </row>
     <row r="394">
@@ -19949,10 +19949,10 @@
         <v>0.93</v>
       </c>
       <c r="I394" t="n">
-        <v>-0.09320000000000001</v>
+        <v>-0.1063</v>
       </c>
       <c r="J394" t="n">
-        <v>-2.5164</v>
+        <v>-2.8701</v>
       </c>
     </row>
     <row r="395">
@@ -19989,10 +19989,10 @@
         <v>0.86</v>
       </c>
       <c r="I395" t="n">
-        <v>-0.1685</v>
+        <v>-0.1839</v>
       </c>
       <c r="J395" t="n">
-        <v>-4.5495</v>
+        <v>-4.9653</v>
       </c>
     </row>
     <row r="396">
@@ -20029,10 +20029,10 @@
         <v>0.52</v>
       </c>
       <c r="I396" t="n">
-        <v>-0.4937</v>
+        <v>-0.4999</v>
       </c>
       <c r="J396" t="n">
-        <v>-13.3299</v>
+        <v>-13.4973</v>
       </c>
     </row>
     <row r="397">
@@ -20069,10 +20069,10 @@
         <v>1.44</v>
       </c>
       <c r="I397" t="n">
-        <v>1.0706</v>
+        <v>1.0235</v>
       </c>
       <c r="J397" t="n">
-        <v>28.9062</v>
+        <v>27.6345</v>
       </c>
     </row>
     <row r="398">
@@ -20109,10 +20109,10 @@
         <v>1.38</v>
       </c>
       <c r="I398" t="n">
-        <v>0.9778</v>
+        <v>0.9182</v>
       </c>
       <c r="J398" t="n">
-        <v>26.4006</v>
+        <v>24.7914</v>
       </c>
     </row>
     <row r="399">
@@ -20149,10 +20149,10 @@
         <v>1.05</v>
       </c>
       <c r="I399" t="n">
-        <v>0.1592</v>
+        <v>0.1743</v>
       </c>
       <c r="J399" t="n">
-        <v>4.2984</v>
+        <v>4.7061</v>
       </c>
     </row>
     <row r="400">
@@ -20189,10 +20189,10 @@
         <v>1.04</v>
       </c>
       <c r="I400" t="n">
-        <v>0.1262</v>
+        <v>0.1426</v>
       </c>
       <c r="J400" t="n">
-        <v>3.4074</v>
+        <v>3.8502</v>
       </c>
     </row>
     <row r="401">
@@ -20229,10 +20229,10 @@
         <v>0.95</v>
       </c>
       <c r="I401" t="n">
-        <v>-0.2433</v>
+        <v>-0.2323</v>
       </c>
       <c r="J401" t="n">
-        <v>-6.5691</v>
+        <v>-6.2721</v>
       </c>
     </row>
     <row r="402">
@@ -20269,10 +20269,10 @@
         <v>1.25</v>
       </c>
       <c r="I402" t="n">
-        <v>0.718</v>
+        <v>0.6785</v>
       </c>
       <c r="J402" t="n">
-        <v>20.822</v>
+        <v>19.6765</v>
       </c>
     </row>
     <row r="403">
@@ -20309,10 +20309,10 @@
         <v>1.19</v>
       </c>
       <c r="I403" t="n">
-        <v>0.5676</v>
+        <v>0.5451</v>
       </c>
       <c r="J403" t="n">
-        <v>16.4604</v>
+        <v>15.8079</v>
       </c>
     </row>
     <row r="404">
@@ -20349,10 +20349,10 @@
         <v>1.11</v>
       </c>
       <c r="I404" t="n">
-        <v>0.3561</v>
+        <v>0.3534</v>
       </c>
       <c r="J404" t="n">
-        <v>10.3269</v>
+        <v>10.2486</v>
       </c>
     </row>
     <row r="405">
@@ -20389,10 +20389,10 @@
         <v>0.98</v>
       </c>
       <c r="I405" t="n">
-        <v>-0.1108</v>
+        <v>-0.1113</v>
       </c>
       <c r="J405" t="n">
-        <v>-3.2132</v>
+        <v>-3.2277</v>
       </c>
     </row>
     <row r="406">
@@ -20429,10 +20429,10 @@
         <v>0.82</v>
       </c>
       <c r="I406" t="n">
-        <v>-0.5891999999999999</v>
+        <v>-0.5551</v>
       </c>
       <c r="J406" t="n">
-        <v>-17.0868</v>
+        <v>-16.0979</v>
       </c>
     </row>
     <row r="407">
@@ -20469,10 +20469,10 @@
         <v>1.33</v>
       </c>
       <c r="I407" t="n">
-        <v>0.659</v>
+        <v>0.637</v>
       </c>
       <c r="J407" t="n">
-        <v>19.111</v>
+        <v>18.473</v>
       </c>
     </row>
     <row r="408">
@@ -20509,10 +20509,10 @@
         <v>1.23</v>
       </c>
       <c r="I408" t="n">
-        <v>0.4848</v>
+        <v>0.478</v>
       </c>
       <c r="J408" t="n">
-        <v>14.0592</v>
+        <v>13.862</v>
       </c>
     </row>
     <row r="409">
@@ -20549,10 +20549,10 @@
         <v>1.05</v>
       </c>
       <c r="I409" t="n">
-        <v>0.1346</v>
+        <v>0.1445</v>
       </c>
       <c r="J409" t="n">
-        <v>3.9034</v>
+        <v>4.1905</v>
       </c>
     </row>
     <row r="410">
@@ -20589,10 +20589,10 @@
         <v>0.89</v>
       </c>
       <c r="I410" t="n">
-        <v>-0.1482</v>
+        <v>-0.1605</v>
       </c>
       <c r="J410" t="n">
-        <v>-4.2978</v>
+        <v>-4.6545</v>
       </c>
     </row>
     <row r="411">
@@ -20629,10 +20629,10 @@
         <v>0.63</v>
       </c>
       <c r="I411" t="n">
-        <v>-0.4044</v>
+        <v>-0.413</v>
       </c>
       <c r="J411" t="n">
-        <v>-11.7276</v>
+        <v>-11.977</v>
       </c>
     </row>
     <row r="412">
@@ -20669,10 +20669,10 @@
         <v>1.45</v>
       </c>
       <c r="I412" t="n">
-        <v>1.1241</v>
+        <v>1.0764</v>
       </c>
       <c r="J412" t="n">
-        <v>40.4676</v>
+        <v>38.7504</v>
       </c>
     </row>
     <row r="413">
@@ -20709,10 +20709,10 @@
         <v>1.28</v>
       </c>
       <c r="I413" t="n">
-        <v>0.8064</v>
+        <v>0.7534999999999999</v>
       </c>
       <c r="J413" t="n">
-        <v>29.0304</v>
+        <v>27.126</v>
       </c>
     </row>
     <row r="414">
@@ -20749,10 +20749,10 @@
         <v>0.88</v>
       </c>
       <c r="I414" t="n">
-        <v>-0.4163</v>
+        <v>-0.4013</v>
       </c>
       <c r="J414" t="n">
-        <v>-14.9868</v>
+        <v>-14.4468</v>
       </c>
     </row>
     <row r="415">
@@ -20789,10 +20789,10 @@
         <v>0.82</v>
       </c>
       <c r="I415" t="n">
-        <v>-0.5794</v>
+        <v>-0.5483</v>
       </c>
       <c r="J415" t="n">
-        <v>-20.8584</v>
+        <v>-19.7388</v>
       </c>
     </row>
     <row r="416">
@@ -20829,10 +20829,10 @@
         <v>0.75</v>
       </c>
       <c r="I416" t="n">
-        <v>-0.7597</v>
+        <v>-0.7078</v>
       </c>
       <c r="J416" t="n">
-        <v>-27.3492</v>
+        <v>-25.4808</v>
       </c>
     </row>
     <row r="417">
@@ -20869,10 +20869,10 @@
         <v>1.66</v>
       </c>
       <c r="I417" t="n">
-        <v>1.0896</v>
+        <v>1.0606</v>
       </c>
       <c r="J417" t="n">
-        <v>39.2256</v>
+        <v>38.1816</v>
       </c>
     </row>
     <row r="418">
@@ -20909,10 +20909,10 @@
         <v>1.19</v>
       </c>
       <c r="I418" t="n">
-        <v>0.3912</v>
+        <v>0.3955</v>
       </c>
       <c r="J418" t="n">
-        <v>14.0832</v>
+        <v>14.238</v>
       </c>
     </row>
     <row r="419">
@@ -20949,10 +20949,10 @@
         <v>0.97</v>
       </c>
       <c r="I419" t="n">
-        <v>-0.0614</v>
+        <v>-0.067</v>
       </c>
       <c r="J419" t="n">
-        <v>-2.2104</v>
+        <v>-2.412</v>
       </c>
     </row>
     <row r="420">
@@ -20989,10 +20989,10 @@
         <v>0.89</v>
       </c>
       <c r="I420" t="n">
-        <v>-0.1577</v>
+        <v>-0.1679</v>
       </c>
       <c r="J420" t="n">
-        <v>-5.6772</v>
+        <v>-6.0444</v>
       </c>
     </row>
     <row r="421">
@@ -21029,10 +21029,10 @@
         <v>0.86</v>
       </c>
       <c r="I421" t="n">
-        <v>-0.19</v>
+        <v>-0.2007</v>
       </c>
       <c r="J421" t="n">
-        <v>-6.84</v>
+        <v>-7.2252</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/2027/event_2027_evp_summary.xlsx
+++ b/database/event/2027/event_2027_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.8902</v>
+        <v>6.7047</v>
       </c>
       <c r="C2" t="n">
-        <v>4.5205</v>
+        <v>4.3988</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5124</v>
+        <v>2.4485</v>
       </c>
       <c r="E2" t="n">
-        <v>6.8902</v>
+        <v>6.7047</v>
       </c>
       <c r="F2" t="n">
-        <v>3.685</v>
+        <v>3.5449</v>
       </c>
       <c r="G2" t="n">
-        <v>3.2052</v>
+        <v>3.1598</v>
       </c>
       <c r="H2" t="n">
-        <v>7.264</v>
+        <v>6.8666</v>
       </c>
       <c r="I2" t="n">
-        <v>3.9225</v>
+        <v>3.8554</v>
       </c>
       <c r="J2" t="n">
-        <v>3.2052</v>
+        <v>3.1598</v>
       </c>
       <c r="K2" t="n">
         <v>139</v>
@@ -529,7 +529,7 @@
         <v>123</v>
       </c>
       <c r="M2" t="n">
-        <v>7.1277</v>
+        <v>7.0152</v>
       </c>
       <c r="N2" t="n">
         <v>262</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.3445</v>
+        <v>5.4043</v>
       </c>
       <c r="C3" t="n">
-        <v>3.5064</v>
+        <v>3.5456</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8087</v>
+        <v>1.8561</v>
       </c>
       <c r="E3" t="n">
-        <v>5.3445</v>
+        <v>5.4043</v>
       </c>
       <c r="F3" t="n">
-        <v>2.1929</v>
+        <v>2.3048</v>
       </c>
       <c r="G3" t="n">
-        <v>3.1516</v>
+        <v>3.0995</v>
       </c>
       <c r="H3" t="n">
-        <v>2.341</v>
+        <v>2.3048</v>
       </c>
       <c r="I3" t="n">
-        <v>1.2641</v>
+        <v>1.2941</v>
       </c>
       <c r="J3" t="n">
-        <v>3.1516</v>
+        <v>3.0995</v>
       </c>
       <c r="K3" t="n">
         <v>139</v>
@@ -575,7 +575,7 @@
         <v>123</v>
       </c>
       <c r="M3" t="n">
-        <v>4.4157</v>
+        <v>4.3936</v>
       </c>
       <c r="N3" t="n">
         <v>262</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.3005</v>
+        <v>5.225</v>
       </c>
       <c r="C4" t="n">
-        <v>3.4775</v>
+        <v>3.428</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7887</v>
+        <v>1.7744</v>
       </c>
       <c r="E4" t="n">
-        <v>5.3005</v>
+        <v>5.225</v>
       </c>
       <c r="F4" t="n">
-        <v>3.5148</v>
+        <v>3.4128</v>
       </c>
       <c r="G4" t="n">
-        <v>1.7857</v>
+        <v>1.8122</v>
       </c>
       <c r="H4" t="n">
-        <v>6.7023</v>
+        <v>6.3704</v>
       </c>
       <c r="I4" t="n">
-        <v>3.6192</v>
+        <v>3.5768</v>
       </c>
       <c r="J4" t="n">
-        <v>1.7857</v>
+        <v>1.8122</v>
       </c>
       <c r="K4" t="n">
         <v>96</v>
@@ -621,7 +621,7 @@
         <v>105</v>
       </c>
       <c r="M4" t="n">
-        <v>5.4049</v>
+        <v>5.389</v>
       </c>
       <c r="N4" t="n">
         <v>201</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.0562</v>
+        <v>4.9259</v>
       </c>
       <c r="C5" t="n">
-        <v>3.3173</v>
+        <v>3.2318</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6775</v>
+        <v>1.6382</v>
       </c>
       <c r="E5" t="n">
-        <v>5.0562</v>
+        <v>4.9259</v>
       </c>
       <c r="F5" t="n">
-        <v>3.2368</v>
+        <v>3.1616</v>
       </c>
       <c r="G5" t="n">
-        <v>1.8194</v>
+        <v>1.7643</v>
       </c>
       <c r="H5" t="n">
-        <v>5.7851</v>
+        <v>5.4274</v>
       </c>
       <c r="I5" t="n">
-        <v>3.1239</v>
+        <v>3.0473</v>
       </c>
       <c r="J5" t="n">
-        <v>1.8194</v>
+        <v>1.7643</v>
       </c>
       <c r="K5" t="n">
         <v>96</v>
@@ -667,7 +667,7 @@
         <v>105</v>
       </c>
       <c r="M5" t="n">
-        <v>4.9433</v>
+        <v>4.8116</v>
       </c>
       <c r="N5" t="n">
         <v>201</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.419</v>
+        <v>4.2818</v>
       </c>
       <c r="C6" t="n">
-        <v>2.8992</v>
+        <v>2.8092</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3874</v>
+        <v>1.3448</v>
       </c>
       <c r="E6" t="n">
-        <v>4.419</v>
+        <v>4.2818</v>
       </c>
       <c r="F6" t="n">
-        <v>1.6019</v>
+        <v>1.4288</v>
       </c>
       <c r="G6" t="n">
-        <v>2.8171</v>
+        <v>2.853</v>
       </c>
       <c r="H6" t="n">
-        <v>1.6019</v>
+        <v>1.4288</v>
       </c>
       <c r="I6" t="n">
-        <v>0.865</v>
+        <v>0.8022</v>
       </c>
       <c r="J6" t="n">
-        <v>2.8171</v>
+        <v>2.853</v>
       </c>
       <c r="K6" t="n">
         <v>139</v>
@@ -713,7 +713,7 @@
         <v>123</v>
       </c>
       <c r="M6" t="n">
-        <v>3.6821</v>
+        <v>3.6552</v>
       </c>
       <c r="N6" t="n">
         <v>262</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.2896</v>
+        <v>4.1696</v>
       </c>
       <c r="C7" t="n">
-        <v>2.8143</v>
+        <v>2.7356</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3285</v>
+        <v>1.2937</v>
       </c>
       <c r="E7" t="n">
-        <v>4.2896</v>
+        <v>4.1696</v>
       </c>
       <c r="F7" t="n">
-        <v>3.552</v>
+        <v>3.4658</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7376</v>
+        <v>0.7038</v>
       </c>
       <c r="H7" t="n">
-        <v>6.8251</v>
+        <v>6.5696</v>
       </c>
       <c r="I7" t="n">
-        <v>3.6855</v>
+        <v>3.6886</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7376</v>
+        <v>0.7038</v>
       </c>
       <c r="K7" t="n">
         <v>139</v>
@@ -759,7 +759,7 @@
         <v>123</v>
       </c>
       <c r="M7" t="n">
-        <v>4.4231</v>
+        <v>4.3924</v>
       </c>
       <c r="N7" t="n">
         <v>262</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.4558</v>
+        <v>3.4014</v>
       </c>
       <c r="C8" t="n">
-        <v>2.2673</v>
+        <v>2.2316</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9489</v>
+        <v>0.9437</v>
       </c>
       <c r="E8" t="n">
-        <v>3.4558</v>
+        <v>3.4014</v>
       </c>
       <c r="F8" t="n">
-        <v>3.1352</v>
+        <v>3.1262</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3206</v>
+        <v>0.2752</v>
       </c>
       <c r="H8" t="n">
-        <v>5.4501</v>
+        <v>5.2945</v>
       </c>
       <c r="I8" t="n">
-        <v>2.943</v>
+        <v>2.9727</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3206</v>
+        <v>0.2752</v>
       </c>
       <c r="K8" t="n">
         <v>119</v>
@@ -805,7 +805,7 @@
         <v>69</v>
       </c>
       <c r="M8" t="n">
-        <v>3.2636</v>
+        <v>3.2479</v>
       </c>
       <c r="N8" t="n">
         <v>188</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.3443</v>
+        <v>3.1995</v>
       </c>
       <c r="C9" t="n">
-        <v>2.1941</v>
+        <v>2.0991</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8982</v>
+        <v>0.8517</v>
       </c>
       <c r="E9" t="n">
-        <v>3.3443</v>
+        <v>3.1995</v>
       </c>
       <c r="F9" t="n">
-        <v>3.6039</v>
+        <v>3.4986</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.2596</v>
+        <v>-0.2991</v>
       </c>
       <c r="H9" t="n">
-        <v>6.9964</v>
+        <v>6.6924</v>
       </c>
       <c r="I9" t="n">
-        <v>3.778</v>
+        <v>3.7576</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.2596</v>
+        <v>-0.2991</v>
       </c>
       <c r="K9" t="n">
         <v>98</v>
@@ -851,7 +851,7 @@
         <v>51</v>
       </c>
       <c r="M9" t="n">
-        <v>3.5184</v>
+        <v>3.4585</v>
       </c>
       <c r="N9" t="n">
         <v>149</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.0574</v>
+        <v>2.9587</v>
       </c>
       <c r="C10" t="n">
-        <v>2.0059</v>
+        <v>1.9411</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7675999999999999</v>
+        <v>0.742</v>
       </c>
       <c r="E10" t="n">
-        <v>3.0574</v>
+        <v>2.9587</v>
       </c>
       <c r="F10" t="n">
-        <v>3.2253</v>
+        <v>3.1528</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.1679</v>
+        <v>-0.1941</v>
       </c>
       <c r="H10" t="n">
-        <v>5.7473</v>
+        <v>5.3944</v>
       </c>
       <c r="I10" t="n">
-        <v>3.1035</v>
+        <v>3.0288</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.1679</v>
+        <v>-0.1941</v>
       </c>
       <c r="K10" t="n">
         <v>119</v>
@@ -897,7 +897,7 @@
         <v>69</v>
       </c>
       <c r="M10" t="n">
-        <v>2.9356</v>
+        <v>2.8347</v>
       </c>
       <c r="N10" t="n">
         <v>188</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.9163</v>
+        <v>2.9439</v>
       </c>
       <c r="C11" t="n">
-        <v>1.9133</v>
+        <v>1.9314</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7034</v>
+        <v>0.7353</v>
       </c>
       <c r="E11" t="n">
-        <v>2.9163</v>
+        <v>2.9439</v>
       </c>
       <c r="F11" t="n">
-        <v>3.2453</v>
+        <v>3.2432</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.329</v>
+        <v>-0.2993</v>
       </c>
       <c r="H11" t="n">
-        <v>5.8132</v>
+        <v>5.7337</v>
       </c>
       <c r="I11" t="n">
-        <v>3.1391</v>
+        <v>3.2193</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.329</v>
+        <v>-0.2993</v>
       </c>
       <c r="K11" t="n">
         <v>98</v>
@@ -943,7 +943,7 @@
         <v>51</v>
       </c>
       <c r="M11" t="n">
-        <v>2.8101</v>
+        <v>2.92</v>
       </c>
       <c r="N11" t="n">
         <v>149</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.8981</v>
+        <v>2.8399</v>
       </c>
       <c r="C12" t="n">
-        <v>1.9014</v>
+        <v>1.8632</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6951000000000001</v>
+        <v>0.6879</v>
       </c>
       <c r="E12" t="n">
-        <v>2.8981</v>
+        <v>2.8399</v>
       </c>
       <c r="F12" t="n">
-        <v>3.5859</v>
+        <v>3.488</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.6878</v>
+        <v>-0.6481</v>
       </c>
       <c r="H12" t="n">
-        <v>6.9371</v>
+        <v>6.6527</v>
       </c>
       <c r="I12" t="n">
-        <v>3.746</v>
+        <v>3.7353</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.6878</v>
+        <v>-0.6481</v>
       </c>
       <c r="K12" t="n">
         <v>96</v>
@@ -989,7 +989,7 @@
         <v>105</v>
       </c>
       <c r="M12" t="n">
-        <v>3.0582</v>
+        <v>3.0872</v>
       </c>
       <c r="N12" t="n">
         <v>201</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.6953</v>
+        <v>2.7066</v>
       </c>
       <c r="C13" t="n">
-        <v>1.7683</v>
+        <v>1.7757</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6028</v>
+        <v>0.6272</v>
       </c>
       <c r="E13" t="n">
-        <v>2.6953</v>
+        <v>2.7066</v>
       </c>
       <c r="F13" t="n">
-        <v>3.0243</v>
+        <v>3.0059</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.329</v>
+        <v>-0.2993</v>
       </c>
       <c r="H13" t="n">
-        <v>5.084</v>
+        <v>4.843</v>
       </c>
       <c r="I13" t="n">
-        <v>2.7453</v>
+        <v>2.7192</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.329</v>
+        <v>-0.2993</v>
       </c>
       <c r="K13" t="n">
         <v>98</v>
@@ -1035,7 +1035,7 @@
         <v>51</v>
       </c>
       <c r="M13" t="n">
-        <v>2.4163</v>
+        <v>2.4199</v>
       </c>
       <c r="N13" t="n">
         <v>149</v>
@@ -1048,28 +1048,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.636</v>
+        <v>2.6069</v>
       </c>
       <c r="C14" t="n">
-        <v>1.7294</v>
+        <v>1.7103</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5758</v>
+        <v>0.5818</v>
       </c>
       <c r="E14" t="n">
-        <v>2.636</v>
+        <v>2.6069</v>
       </c>
       <c r="F14" t="n">
-        <v>2.636</v>
+        <v>2.6069</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>3.0444</v>
+        <v>3.024</v>
       </c>
       <c r="I14" t="n">
-        <v>3.0444</v>
+        <v>3.024</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.0444</v>
+        <v>3.024</v>
       </c>
       <c r="N14" t="n">
         <v>199</v>
@@ -1090,369 +1090,369 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>jdm64</t>
+          <t>Hiko</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.6136</v>
+        <v>2.5801</v>
       </c>
       <c r="C15" t="n">
-        <v>1.7147</v>
+        <v>1.6927</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5656</v>
+        <v>0.5696</v>
       </c>
       <c r="E15" t="n">
-        <v>2.6136</v>
+        <v>2.5801</v>
       </c>
       <c r="F15" t="n">
-        <v>2.6136</v>
+        <v>2.5049</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>0.0752</v>
       </c>
       <c r="H15" t="n">
-        <v>2.9954</v>
+        <v>2.9621</v>
       </c>
       <c r="I15" t="n">
-        <v>2.9954</v>
+        <v>1.6631</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>0.0752</v>
       </c>
       <c r="K15" t="n">
-        <v>182</v>
+        <v>119</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="M15" t="n">
-        <v>2.9954</v>
+        <v>1.7383</v>
       </c>
       <c r="N15" t="n">
-        <v>182</v>
+        <v>188</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>flusha</t>
+          <t>jdm64</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.5835</v>
+        <v>2.5781</v>
       </c>
       <c r="C16" t="n">
-        <v>1.695</v>
+        <v>1.6914</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5518999999999999</v>
+        <v>0.5687</v>
       </c>
       <c r="E16" t="n">
-        <v>2.5835</v>
+        <v>2.5781</v>
       </c>
       <c r="F16" t="n">
-        <v>2.5835</v>
+        <v>2.5781</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2.9296</v>
+        <v>2.9582</v>
       </c>
       <c r="I16" t="n">
-        <v>2.9296</v>
+        <v>2.9582</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>157</v>
+        <v>182</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.9296</v>
+        <v>2.9582</v>
       </c>
       <c r="N16" t="n">
-        <v>157</v>
+        <v>182</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Hiko</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.5766</v>
+        <v>2.5524</v>
       </c>
       <c r="C17" t="n">
-        <v>1.6904</v>
+        <v>1.6746</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5487</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>2.5766</v>
+        <v>2.5524</v>
       </c>
       <c r="F17" t="n">
-        <v>2.4667</v>
+        <v>2.5524</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1099</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>3.2443</v>
+        <v>2.8993</v>
       </c>
       <c r="I17" t="n">
-        <v>1.7519</v>
+        <v>2.8993</v>
       </c>
       <c r="J17" t="n">
-        <v>0.1099</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>119</v>
+        <v>182</v>
       </c>
       <c r="L17" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.8618</v>
+        <v>2.8993</v>
       </c>
       <c r="N17" t="n">
-        <v>188</v>
+        <v>182</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.5736</v>
+        <v>2.5413</v>
       </c>
       <c r="C18" t="n">
-        <v>1.6885</v>
+        <v>1.6673</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5474</v>
+        <v>0.5518999999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>2.5736</v>
+        <v>2.5413</v>
       </c>
       <c r="F18" t="n">
-        <v>2.5736</v>
+        <v>2.5413</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>2.9078</v>
+        <v>2.8738</v>
       </c>
       <c r="I18" t="n">
-        <v>2.9078</v>
+        <v>2.8738</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>182</v>
+        <v>199</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>2.9078</v>
+        <v>2.8738</v>
       </c>
       <c r="N18" t="n">
-        <v>182</v>
+        <v>199</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>GeT_RiGhT</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.5636</v>
+        <v>2.5211</v>
       </c>
       <c r="C19" t="n">
-        <v>1.6819</v>
+        <v>1.654</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5427999999999999</v>
+        <v>0.5427</v>
       </c>
       <c r="E19" t="n">
-        <v>2.5636</v>
+        <v>2.5211</v>
       </c>
       <c r="F19" t="n">
-        <v>2.5636</v>
+        <v>2.5211</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>2.886</v>
+        <v>2.8275</v>
       </c>
       <c r="I19" t="n">
-        <v>2.886</v>
+        <v>2.8275</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>2.886</v>
+        <v>2.8275</v>
       </c>
       <c r="N19" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>GeT_RiGhT</t>
+          <t>flusha</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.5386</v>
+        <v>2.4974</v>
       </c>
       <c r="C20" t="n">
-        <v>1.6655</v>
+        <v>1.6385</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5314</v>
+        <v>0.5319</v>
       </c>
       <c r="E20" t="n">
-        <v>2.5386</v>
+        <v>2.4974</v>
       </c>
       <c r="F20" t="n">
-        <v>2.5386</v>
+        <v>2.4974</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>2.8313</v>
+        <v>2.7732</v>
       </c>
       <c r="I20" t="n">
-        <v>2.8313</v>
+        <v>2.7732</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>182</v>
+        <v>157</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>2.8313</v>
+        <v>2.7732</v>
       </c>
       <c r="N20" t="n">
-        <v>182</v>
+        <v>157</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>NEO</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.5378</v>
+        <v>2.4578</v>
       </c>
       <c r="C21" t="n">
-        <v>1.665</v>
+        <v>1.6125</v>
       </c>
       <c r="D21" t="n">
-        <v>0.5311</v>
+        <v>0.5139</v>
       </c>
       <c r="E21" t="n">
-        <v>2.5378</v>
+        <v>2.4578</v>
       </c>
       <c r="F21" t="n">
-        <v>2.5378</v>
+        <v>2.4578</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>2.8296</v>
+        <v>2.6824</v>
       </c>
       <c r="I21" t="n">
-        <v>2.8296</v>
+        <v>2.6824</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>162</v>
+        <v>199</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>2.8296</v>
+        <v>2.6824</v>
       </c>
       <c r="N21" t="n">
-        <v>162</v>
+        <v>199</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>NEO</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.4596</v>
+        <v>2.4345</v>
       </c>
       <c r="C22" t="n">
-        <v>1.6137</v>
+        <v>1.5972</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4955</v>
+        <v>0.5032</v>
       </c>
       <c r="E22" t="n">
-        <v>2.4596</v>
+        <v>2.4345</v>
       </c>
       <c r="F22" t="n">
-        <v>2.4596</v>
+        <v>2.4345</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>2.6584</v>
+        <v>2.6289</v>
       </c>
       <c r="I22" t="n">
-        <v>2.6584</v>
+        <v>2.6289</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>199</v>
+        <v>162</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>2.6584</v>
+        <v>2.6289</v>
       </c>
       <c r="N22" t="n">
-        <v>199</v>
+        <v>162</v>
       </c>
     </row>
     <row r="23">
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.3811</v>
+        <v>2.3206</v>
       </c>
       <c r="C23" t="n">
-        <v>1.5622</v>
+        <v>1.5225</v>
       </c>
       <c r="D23" t="n">
-        <v>0.4597</v>
+        <v>0.4514</v>
       </c>
       <c r="E23" t="n">
-        <v>2.3811</v>
+        <v>2.3206</v>
       </c>
       <c r="F23" t="n">
-        <v>2.3811</v>
+        <v>2.3206</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>2.4866</v>
+        <v>2.3679</v>
       </c>
       <c r="I23" t="n">
-        <v>2.4866</v>
+        <v>2.3679</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>2.4866</v>
+        <v>2.3679</v>
       </c>
       <c r="N23" t="n">
         <v>157</v>
@@ -1508,31 +1508,31 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.1439</v>
+        <v>2.2344</v>
       </c>
       <c r="C24" t="n">
-        <v>1.4066</v>
+        <v>1.4659</v>
       </c>
       <c r="D24" t="n">
-        <v>0.3517</v>
+        <v>0.4121</v>
       </c>
       <c r="E24" t="n">
-        <v>2.1439</v>
+        <v>2.2344</v>
       </c>
       <c r="F24" t="n">
-        <v>2.4415</v>
+        <v>2.5111</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.2976</v>
+        <v>-0.2767</v>
       </c>
       <c r="H24" t="n">
-        <v>3.1613</v>
+        <v>2.985</v>
       </c>
       <c r="I24" t="n">
-        <v>1.7071</v>
+        <v>1.676</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.2976</v>
+        <v>-0.2767</v>
       </c>
       <c r="K24" t="n">
         <v>98</v>
@@ -1541,7 +1541,7 @@
         <v>51</v>
       </c>
       <c r="M24" t="n">
-        <v>1.4095</v>
+        <v>1.3993</v>
       </c>
       <c r="N24" t="n">
         <v>149</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.1087</v>
+        <v>2.0206</v>
       </c>
       <c r="C25" t="n">
-        <v>1.3835</v>
+        <v>1.3257</v>
       </c>
       <c r="D25" t="n">
-        <v>0.3357</v>
+        <v>0.3147</v>
       </c>
       <c r="E25" t="n">
-        <v>2.1087</v>
+        <v>2.0206</v>
       </c>
       <c r="F25" t="n">
-        <v>2.1087</v>
+        <v>2.0206</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>2.1087</v>
+        <v>2.0206</v>
       </c>
       <c r="I25" t="n">
-        <v>2.1087</v>
+        <v>2.0206</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>2.1087</v>
+        <v>2.0206</v>
       </c>
       <c r="N25" t="n">
         <v>94</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.9382</v>
+        <v>1.9291</v>
       </c>
       <c r="C26" t="n">
-        <v>1.2716</v>
+        <v>1.2656</v>
       </c>
       <c r="D26" t="n">
-        <v>0.2581</v>
+        <v>0.273</v>
       </c>
       <c r="E26" t="n">
-        <v>1.9382</v>
+        <v>1.9291</v>
       </c>
       <c r="F26" t="n">
-        <v>1.9382</v>
+        <v>1.9291</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1.9382</v>
+        <v>1.9291</v>
       </c>
       <c r="I26" t="n">
-        <v>1.9382</v>
+        <v>1.9291</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1.9382</v>
+        <v>1.9291</v>
       </c>
       <c r="N26" t="n">
         <v>157</v>
@@ -1642,139 +1642,139 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>hazed</t>
+          <t>dennis</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.7844</v>
+        <v>1.7092</v>
       </c>
       <c r="C27" t="n">
-        <v>1.1707</v>
+        <v>1.1214</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1881</v>
+        <v>0.1728</v>
       </c>
       <c r="E27" t="n">
-        <v>1.7844</v>
+        <v>1.7092</v>
       </c>
       <c r="F27" t="n">
-        <v>1.7844</v>
+        <v>1.7092</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1.7844</v>
+        <v>1.7092</v>
       </c>
       <c r="I27" t="n">
-        <v>1.7844</v>
+        <v>1.7092</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>182</v>
+        <v>157</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1.7844</v>
+        <v>1.7092</v>
       </c>
       <c r="N27" t="n">
-        <v>182</v>
+        <v>157</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>hazed</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.6829</v>
+        <v>1.6942</v>
       </c>
       <c r="C28" t="n">
-        <v>1.1041</v>
+        <v>1.1115</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1419</v>
+        <v>0.166</v>
       </c>
       <c r="E28" t="n">
-        <v>1.6829</v>
+        <v>1.6942</v>
       </c>
       <c r="F28" t="n">
-        <v>2.1836</v>
+        <v>1.6942</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.5007</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>2.3104</v>
+        <v>1.6942</v>
       </c>
       <c r="I28" t="n">
-        <v>1.2476</v>
+        <v>1.6942</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.5007</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>119</v>
+        <v>182</v>
       </c>
       <c r="L28" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.7469</v>
+        <v>1.6942</v>
       </c>
       <c r="N28" t="n">
-        <v>188</v>
+        <v>182</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>dennis</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.6557</v>
+        <v>1.6919</v>
       </c>
       <c r="C29" t="n">
-        <v>1.0863</v>
+        <v>1.11</v>
       </c>
       <c r="D29" t="n">
-        <v>0.1295</v>
+        <v>0.165</v>
       </c>
       <c r="E29" t="n">
-        <v>1.6557</v>
+        <v>1.6919</v>
       </c>
       <c r="F29" t="n">
-        <v>1.6557</v>
+        <v>2.1572</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>-0.4653</v>
       </c>
       <c r="H29" t="n">
-        <v>1.6557</v>
+        <v>2.1572</v>
       </c>
       <c r="I29" t="n">
-        <v>1.6557</v>
+        <v>1.2112</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>-0.4653</v>
       </c>
       <c r="K29" t="n">
-        <v>157</v>
+        <v>119</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="M29" t="n">
-        <v>1.6557</v>
+        <v>0.7459</v>
       </c>
       <c r="N29" t="n">
-        <v>157</v>
+        <v>188</v>
       </c>
     </row>
     <row r="30">
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.6256</v>
+        <v>1.563</v>
       </c>
       <c r="C30" t="n">
-        <v>1.0665</v>
+        <v>1.0254</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1158</v>
+        <v>0.1062</v>
       </c>
       <c r="E30" t="n">
-        <v>1.6256</v>
+        <v>1.563</v>
       </c>
       <c r="F30" t="n">
-        <v>1.6256</v>
+        <v>1.563</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1.6256</v>
+        <v>1.563</v>
       </c>
       <c r="I30" t="n">
-        <v>1.6256</v>
+        <v>1.563</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>1.6256</v>
+        <v>1.563</v>
       </c>
       <c r="N30" t="n">
         <v>182</v>
@@ -1826,47 +1826,47 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.542</v>
+        <v>1.5337</v>
       </c>
       <c r="C31" t="n">
-        <v>1.0117</v>
+        <v>1.0062</v>
       </c>
       <c r="D31" t="n">
-        <v>0.07770000000000001</v>
+        <v>0.0929</v>
       </c>
       <c r="E31" t="n">
-        <v>1.542</v>
+        <v>1.5337</v>
       </c>
       <c r="F31" t="n">
-        <v>1.4693</v>
+        <v>-0.3113</v>
       </c>
       <c r="G31" t="n">
-        <v>0.0727</v>
+        <v>1.845</v>
       </c>
       <c r="H31" t="n">
-        <v>1.4693</v>
+        <v>-0.3113</v>
       </c>
       <c r="I31" t="n">
-        <v>0.7934</v>
+        <v>-0.1748</v>
       </c>
       <c r="J31" t="n">
-        <v>0.0727</v>
+        <v>1.845</v>
       </c>
       <c r="K31" t="n">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="L31" t="n">
-        <v>69</v>
+        <v>123</v>
       </c>
       <c r="M31" t="n">
-        <v>0.8661</v>
+        <v>1.6702</v>
       </c>
       <c r="N31" t="n">
-        <v>188</v>
+        <v>262</v>
       </c>
     </row>
     <row r="32">
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.4773</v>
+        <v>1.522</v>
       </c>
       <c r="C32" t="n">
-        <v>0.9692</v>
+        <v>0.9985000000000001</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0483</v>
+        <v>0.0876</v>
       </c>
       <c r="E32" t="n">
-        <v>1.4773</v>
+        <v>1.522</v>
       </c>
       <c r="F32" t="n">
-        <v>1.4773</v>
+        <v>1.522</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>1.4773</v>
+        <v>1.522</v>
       </c>
       <c r="I32" t="n">
-        <v>1.4773</v>
+        <v>1.522</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>1.4773</v>
+        <v>1.522</v>
       </c>
       <c r="N32" t="n">
         <v>157</v>
@@ -1918,139 +1918,139 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>TaZ</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.4313</v>
+        <v>1.3406</v>
       </c>
       <c r="C33" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.8794999999999999</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0274</v>
+        <v>0.0049</v>
       </c>
       <c r="E33" t="n">
-        <v>1.4313</v>
+        <v>1.3406</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.3717</v>
+        <v>1.3406</v>
       </c>
       <c r="G33" t="n">
-        <v>1.803</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.3717</v>
+        <v>1.3406</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.2007</v>
+        <v>1.3406</v>
       </c>
       <c r="J33" t="n">
-        <v>1.803</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>139</v>
+        <v>199</v>
       </c>
       <c r="L33" t="n">
-        <v>123</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>1.6023</v>
+        <v>1.3406</v>
       </c>
       <c r="N33" t="n">
-        <v>262</v>
+        <v>199</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>TaZ</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.3451</v>
+        <v>1.3371</v>
       </c>
       <c r="C34" t="n">
-        <v>0.8825</v>
+        <v>0.8772</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.0119</v>
+        <v>0.0033</v>
       </c>
       <c r="E34" t="n">
-        <v>1.3451</v>
+        <v>1.3371</v>
       </c>
       <c r="F34" t="n">
-        <v>1.3451</v>
+        <v>1.2978</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>0.0393</v>
       </c>
       <c r="H34" t="n">
-        <v>1.3451</v>
+        <v>1.2978</v>
       </c>
       <c r="I34" t="n">
-        <v>1.3451</v>
+        <v>0.7287</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>0.0393</v>
       </c>
       <c r="K34" t="n">
-        <v>199</v>
+        <v>119</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="M34" t="n">
-        <v>1.3451</v>
+        <v>0.768</v>
       </c>
       <c r="N34" t="n">
-        <v>199</v>
+        <v>188</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>bondik</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.9288</v>
+        <v>1.0908</v>
       </c>
       <c r="C35" t="n">
-        <v>0.6094000000000001</v>
+        <v>0.7156</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.2014</v>
+        <v>-0.1089</v>
       </c>
       <c r="E35" t="n">
-        <v>0.9288</v>
+        <v>1.0908</v>
       </c>
       <c r="F35" t="n">
-        <v>0.9288</v>
+        <v>2.3692</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>-1.2784</v>
       </c>
       <c r="H35" t="n">
-        <v>0.9288</v>
+        <v>2.4525</v>
       </c>
       <c r="I35" t="n">
-        <v>0.9288</v>
+        <v>1.377</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>-1.2784</v>
       </c>
       <c r="K35" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="M35" t="n">
-        <v>0.9288</v>
+        <v>0.09860000000000002</v>
       </c>
       <c r="N35" t="n">
-        <v>95</v>
+        <v>201</v>
       </c>
     </row>
     <row r="36">
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.9241</v>
+        <v>0.9945000000000001</v>
       </c>
       <c r="C36" t="n">
-        <v>0.6063</v>
+        <v>0.6525</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.2035</v>
+        <v>-0.1527</v>
       </c>
       <c r="E36" t="n">
-        <v>0.9241</v>
+        <v>0.9945000000000001</v>
       </c>
       <c r="F36" t="n">
-        <v>0.9241</v>
+        <v>0.9945000000000001</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.9241</v>
+        <v>0.9945000000000001</v>
       </c>
       <c r="I36" t="n">
-        <v>0.9241</v>
+        <v>0.9945000000000001</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0.9241</v>
+        <v>0.9945000000000001</v>
       </c>
       <c r="N36" t="n">
         <v>94</v>
@@ -2102,93 +2102,93 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>bondik</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.9053</v>
+        <v>0.9186</v>
       </c>
       <c r="C37" t="n">
-        <v>0.5939</v>
+        <v>0.6027</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.2121</v>
+        <v>-0.1873</v>
       </c>
       <c r="E37" t="n">
-        <v>0.9053</v>
+        <v>0.9186</v>
       </c>
       <c r="F37" t="n">
-        <v>2.2627</v>
+        <v>0.9186</v>
       </c>
       <c r="G37" t="n">
-        <v>-1.3574</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>2.5713</v>
+        <v>0.9186</v>
       </c>
       <c r="I37" t="n">
-        <v>1.3885</v>
+        <v>0.9186</v>
       </c>
       <c r="J37" t="n">
-        <v>-1.3574</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L37" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.03110000000000013</v>
+        <v>0.9186</v>
       </c>
       <c r="N37" t="n">
-        <v>201</v>
+        <v>95</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Shara</t>
+          <t>wayLander</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.8428</v>
+        <v>0.8001</v>
       </c>
       <c r="C38" t="n">
-        <v>0.5528999999999999</v>
+        <v>0.5249</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.2405</v>
+        <v>-0.2413</v>
       </c>
       <c r="E38" t="n">
-        <v>0.8428</v>
+        <v>0.8001</v>
       </c>
       <c r="F38" t="n">
-        <v>0.8428</v>
+        <v>0.8001</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.8428</v>
+        <v>0.8001</v>
       </c>
       <c r="I38" t="n">
-        <v>0.8428</v>
+        <v>0.8001</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>95</v>
+        <v>137</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.8428</v>
+        <v>0.8001</v>
       </c>
       <c r="N38" t="n">
-        <v>95</v>
+        <v>137</v>
       </c>
     </row>
     <row r="39">
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.8099</v>
+        <v>0.7967</v>
       </c>
       <c r="C39" t="n">
-        <v>0.5314</v>
+        <v>0.5227000000000001</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.2555</v>
+        <v>-0.2429</v>
       </c>
       <c r="E39" t="n">
-        <v>0.8099</v>
+        <v>0.7967</v>
       </c>
       <c r="F39" t="n">
-        <v>0.8099</v>
+        <v>0.7967</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.8099</v>
+        <v>0.7967</v>
       </c>
       <c r="I39" t="n">
-        <v>0.8099</v>
+        <v>0.7967</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.8099</v>
+        <v>0.7967</v>
       </c>
       <c r="N39" t="n">
         <v>199</v>
@@ -2240,139 +2240,139 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>wayLander</t>
+          <t>Shara</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.7968</v>
+        <v>0.7261</v>
       </c>
       <c r="C40" t="n">
-        <v>0.5228</v>
+        <v>0.4764</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.2615</v>
+        <v>-0.275</v>
       </c>
       <c r="E40" t="n">
-        <v>0.7968</v>
+        <v>0.7261</v>
       </c>
       <c r="F40" t="n">
-        <v>0.7968</v>
+        <v>0.7261</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.7968</v>
+        <v>0.7261</v>
       </c>
       <c r="I40" t="n">
-        <v>0.7968</v>
+        <v>0.7261</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>137</v>
+        <v>95</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0.7968</v>
+        <v>0.7261</v>
       </c>
       <c r="N40" t="n">
-        <v>137</v>
+        <v>95</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>RpK</t>
+          <t>fox</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.7622</v>
+        <v>0.6798999999999999</v>
       </c>
       <c r="C41" t="n">
-        <v>0.5001</v>
+        <v>0.4461</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.2772</v>
+        <v>-0.2961</v>
       </c>
       <c r="E41" t="n">
-        <v>0.7622</v>
+        <v>0.6798999999999999</v>
       </c>
       <c r="F41" t="n">
-        <v>0.7622</v>
+        <v>0.6798999999999999</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.7622</v>
+        <v>0.6798999999999999</v>
       </c>
       <c r="I41" t="n">
-        <v>0.7622</v>
+        <v>0.6798999999999999</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.7622</v>
+        <v>0.6798999999999999</v>
       </c>
       <c r="N41" t="n">
-        <v>109</v>
+        <v>94</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>fox</t>
+          <t>RpK</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.68</v>
+        <v>0.6787</v>
       </c>
       <c r="C42" t="n">
-        <v>0.4461</v>
+        <v>0.4453</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.3147</v>
+        <v>-0.2966</v>
       </c>
       <c r="E42" t="n">
-        <v>0.68</v>
+        <v>0.6787</v>
       </c>
       <c r="F42" t="n">
-        <v>0.68</v>
+        <v>0.6787</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.68</v>
+        <v>0.6787</v>
       </c>
       <c r="I42" t="n">
-        <v>0.68</v>
+        <v>0.6787</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.68</v>
+        <v>0.6787</v>
       </c>
       <c r="N42" t="n">
-        <v>94</v>
+        <v>109</v>
       </c>
     </row>
     <row r="43">
@@ -2382,28 +2382,28 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.6796</v>
+        <v>0.6286</v>
       </c>
       <c r="C43" t="n">
-        <v>0.4459</v>
+        <v>0.4124</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.3148</v>
+        <v>-0.3194</v>
       </c>
       <c r="E43" t="n">
-        <v>0.6796</v>
+        <v>0.6286</v>
       </c>
       <c r="F43" t="n">
-        <v>0.6796</v>
+        <v>0.6286</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.6796</v>
+        <v>0.6286</v>
       </c>
       <c r="I43" t="n">
-        <v>0.6796</v>
+        <v>0.6286</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -2415,7 +2415,7 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.6796</v>
+        <v>0.6286</v>
       </c>
       <c r="N43" t="n">
         <v>109</v>
@@ -2428,28 +2428,28 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.5271</v>
+        <v>0.6278</v>
       </c>
       <c r="C44" t="n">
-        <v>0.3458</v>
+        <v>0.4119</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.3843</v>
+        <v>-0.3198</v>
       </c>
       <c r="E44" t="n">
-        <v>0.5271</v>
+        <v>0.6278</v>
       </c>
       <c r="F44" t="n">
-        <v>0.5271</v>
+        <v>0.6278</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.5271</v>
+        <v>0.6278</v>
       </c>
       <c r="I44" t="n">
-        <v>0.5271</v>
+        <v>0.6278</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -2461,7 +2461,7 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.5271</v>
+        <v>0.6278</v>
       </c>
       <c r="N44" t="n">
         <v>109</v>
@@ -2470,553 +2470,553 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>chrisJ</t>
+          <t>Xizt</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.4942</v>
+        <v>0.4767</v>
       </c>
       <c r="C45" t="n">
-        <v>0.3242</v>
+        <v>0.3128</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.3992</v>
+        <v>-0.3886</v>
       </c>
       <c r="E45" t="n">
-        <v>0.4942</v>
+        <v>0.4767</v>
       </c>
       <c r="F45" t="n">
-        <v>0.4942</v>
+        <v>0.4767</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.4942</v>
+        <v>0.4767</v>
       </c>
       <c r="I45" t="n">
-        <v>0.4942</v>
+        <v>0.4767</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0.4942</v>
+        <v>0.4767</v>
       </c>
       <c r="N45" t="n">
-        <v>162</v>
+        <v>182</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Xizt</t>
+          <t>markeloff</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.4886</v>
+        <v>0.4356</v>
       </c>
       <c r="C46" t="n">
-        <v>0.3206</v>
+        <v>0.2858</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.4018</v>
+        <v>-0.4074</v>
       </c>
       <c r="E46" t="n">
-        <v>0.4886</v>
+        <v>0.4356</v>
       </c>
       <c r="F46" t="n">
-        <v>0.4886</v>
+        <v>0.4356</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.4886</v>
+        <v>0.4356</v>
       </c>
       <c r="I46" t="n">
-        <v>0.4886</v>
+        <v>0.4356</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>182</v>
+        <v>95</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0.4886</v>
+        <v>0.4356</v>
       </c>
       <c r="N46" t="n">
-        <v>182</v>
+        <v>95</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>markeloff</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.4785</v>
+        <v>0.4246</v>
       </c>
       <c r="C47" t="n">
-        <v>0.3139</v>
+        <v>0.2786</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.4064</v>
+        <v>-0.4124</v>
       </c>
       <c r="E47" t="n">
-        <v>0.4785</v>
+        <v>0.4246</v>
       </c>
       <c r="F47" t="n">
-        <v>0.4785</v>
+        <v>0.4246</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.4785</v>
+        <v>0.4246</v>
       </c>
       <c r="I47" t="n">
-        <v>0.4785</v>
+        <v>0.4246</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>95</v>
+        <v>53</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0.4785</v>
+        <v>0.4246</v>
       </c>
       <c r="N47" t="n">
-        <v>95</v>
+        <v>53</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>Spiidi</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.4754</v>
+        <v>0.3946</v>
       </c>
       <c r="C48" t="n">
-        <v>0.3119</v>
+        <v>0.2589</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.4078</v>
+        <v>-0.426</v>
       </c>
       <c r="E48" t="n">
-        <v>0.4754</v>
+        <v>0.3946</v>
       </c>
       <c r="F48" t="n">
-        <v>0.4754</v>
+        <v>0.3946</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.4754</v>
+        <v>0.3946</v>
       </c>
       <c r="I48" t="n">
-        <v>0.4754</v>
+        <v>0.3946</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>53</v>
+        <v>162</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0.4754</v>
+        <v>0.3946</v>
       </c>
       <c r="N48" t="n">
-        <v>53</v>
+        <v>162</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Spiidi</t>
+          <t>SmithZz</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.4721</v>
+        <v>0.3897</v>
       </c>
       <c r="C49" t="n">
-        <v>0.3097</v>
+        <v>0.2557</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.4093</v>
+        <v>-0.4283</v>
       </c>
       <c r="E49" t="n">
-        <v>0.4721</v>
+        <v>0.3897</v>
       </c>
       <c r="F49" t="n">
-        <v>0.4721</v>
+        <v>0.3897</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.4721</v>
+        <v>0.3897</v>
       </c>
       <c r="I49" t="n">
-        <v>0.4721</v>
+        <v>0.3897</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>162</v>
+        <v>109</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0.4721</v>
+        <v>0.3897</v>
       </c>
       <c r="N49" t="n">
-        <v>162</v>
+        <v>109</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>AdreN</t>
+          <t>chrisJ</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.4598</v>
+        <v>0.3732</v>
       </c>
       <c r="C50" t="n">
-        <v>0.3017</v>
+        <v>0.2448</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.4149</v>
+        <v>-0.4358</v>
       </c>
       <c r="E50" t="n">
-        <v>0.4598</v>
+        <v>0.3732</v>
       </c>
       <c r="F50" t="n">
-        <v>0.4598</v>
+        <v>0.3732</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0.4598</v>
+        <v>0.3732</v>
       </c>
       <c r="I50" t="n">
-        <v>0.4598</v>
+        <v>0.3732</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>137</v>
+        <v>162</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>0.4598</v>
+        <v>0.3732</v>
       </c>
       <c r="N50" t="n">
-        <v>137</v>
+        <v>162</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>AdreN</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.3656</v>
+        <v>0.3664</v>
       </c>
       <c r="C51" t="n">
-        <v>0.2399</v>
+        <v>0.2404</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.4578</v>
+        <v>-0.4389</v>
       </c>
       <c r="E51" t="n">
-        <v>0.3656</v>
+        <v>0.3664</v>
       </c>
       <c r="F51" t="n">
-        <v>0.3656</v>
+        <v>0.3664</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>0.3656</v>
+        <v>0.3664</v>
       </c>
       <c r="I51" t="n">
-        <v>0.3656</v>
+        <v>0.3664</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>53</v>
+        <v>137</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>0.3656</v>
+        <v>0.3664</v>
       </c>
       <c r="N51" t="n">
-        <v>53</v>
+        <v>137</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SmithZz</t>
+          <t>Happy</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.3217</v>
+        <v>0.3184</v>
       </c>
       <c r="C52" t="n">
-        <v>0.2111</v>
+        <v>0.2089</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.4778</v>
+        <v>-0.4607</v>
       </c>
       <c r="E52" t="n">
-        <v>0.3217</v>
+        <v>0.3184</v>
       </c>
       <c r="F52" t="n">
-        <v>0.3217</v>
+        <v>0.3184</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>0.3217</v>
+        <v>0.3184</v>
       </c>
       <c r="I52" t="n">
-        <v>0.3217</v>
+        <v>0.3184</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>109</v>
+        <v>53</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>0.3217</v>
+        <v>0.3184</v>
       </c>
       <c r="N52" t="n">
-        <v>109</v>
+        <v>53</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Dosia</t>
+          <t>reltuC</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.3136</v>
+        <v>0.3144</v>
       </c>
       <c r="C53" t="n">
-        <v>0.2057</v>
+        <v>0.2063</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.4814</v>
+        <v>-0.4626</v>
       </c>
       <c r="E53" t="n">
-        <v>0.3136</v>
+        <v>0.3144</v>
       </c>
       <c r="F53" t="n">
-        <v>0.3136</v>
+        <v>0.3144</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>0.3136</v>
+        <v>0.3144</v>
       </c>
       <c r="I53" t="n">
-        <v>0.3136</v>
+        <v>0.3144</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>137</v>
+        <v>182</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>0.3136</v>
+        <v>0.3144</v>
       </c>
       <c r="N53" t="n">
-        <v>137</v>
+        <v>182</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ScreaM</t>
+          <t>DAVEY</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.3046</v>
+        <v>0.2634</v>
       </c>
       <c r="C54" t="n">
-        <v>0.1998</v>
+        <v>0.1728</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.4855</v>
+        <v>-0.4858</v>
       </c>
       <c r="E54" t="n">
-        <v>0.3046</v>
+        <v>0.2634</v>
       </c>
       <c r="F54" t="n">
-        <v>0.3046</v>
+        <v>0.2634</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>0.3046</v>
+        <v>0.2634</v>
       </c>
       <c r="I54" t="n">
-        <v>0.3046</v>
+        <v>0.2634</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>109</v>
+        <v>40</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>0.3046</v>
+        <v>0.2634</v>
       </c>
       <c r="N54" t="n">
-        <v>109</v>
+        <v>40</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>DAVEY</t>
+          <t>Dosia</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.2706</v>
+        <v>0.2591</v>
       </c>
       <c r="C55" t="n">
-        <v>0.1775</v>
+        <v>0.17</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.501</v>
+        <v>-0.4878</v>
       </c>
       <c r="E55" t="n">
-        <v>0.2706</v>
+        <v>0.2591</v>
       </c>
       <c r="F55" t="n">
-        <v>0.2706</v>
+        <v>0.2591</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>0.2706</v>
+        <v>0.2591</v>
       </c>
       <c r="I55" t="n">
-        <v>0.2706</v>
+        <v>0.2591</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>40</v>
+        <v>137</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>0.2706</v>
+        <v>0.2591</v>
       </c>
       <c r="N55" t="n">
-        <v>40</v>
+        <v>137</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>reltuC</t>
+          <t>ScreaM</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.2212</v>
+        <v>0.2205</v>
       </c>
       <c r="C56" t="n">
-        <v>0.1451</v>
+        <v>0.1447</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.5235</v>
+        <v>-0.5053</v>
       </c>
       <c r="E56" t="n">
-        <v>0.2212</v>
+        <v>0.2205</v>
       </c>
       <c r="F56" t="n">
-        <v>0.2212</v>
+        <v>0.2205</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>0.2212</v>
+        <v>0.2205</v>
       </c>
       <c r="I56" t="n">
-        <v>0.2212</v>
+        <v>0.2205</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>182</v>
+        <v>109</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>0.2212</v>
+        <v>0.2205</v>
       </c>
       <c r="N56" t="n">
-        <v>182</v>
+        <v>109</v>
       </c>
     </row>
     <row r="57">
@@ -3026,28 +3026,28 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.1571</v>
+        <v>0.1087</v>
       </c>
       <c r="C57" t="n">
-        <v>0.1031</v>
+        <v>0.0713</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.5527</v>
+        <v>-0.5563</v>
       </c>
       <c r="E57" t="n">
-        <v>0.1571</v>
+        <v>0.1087</v>
       </c>
       <c r="F57" t="n">
-        <v>0.1571</v>
+        <v>0.1087</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>0.1571</v>
+        <v>0.1087</v>
       </c>
       <c r="I57" t="n">
-        <v>0.1571</v>
+        <v>0.1087</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -3059,7 +3059,7 @@
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>0.1571</v>
+        <v>0.1087</v>
       </c>
       <c r="N57" t="n">
         <v>53</v>
@@ -3072,28 +3072,28 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.1139</v>
+        <v>0.0916</v>
       </c>
       <c r="C58" t="n">
-        <v>0.0747</v>
+        <v>0.0601</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.5724</v>
+        <v>-0.5641</v>
       </c>
       <c r="E58" t="n">
-        <v>0.1139</v>
+        <v>0.0916</v>
       </c>
       <c r="F58" t="n">
-        <v>0.1139</v>
+        <v>0.0916</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>0.1139</v>
+        <v>0.0916</v>
       </c>
       <c r="I58" t="n">
-        <v>0.1139</v>
+        <v>0.0916</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -3105,7 +3105,7 @@
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>0.1139</v>
+        <v>0.0916</v>
       </c>
       <c r="N58" t="n">
         <v>95</v>
@@ -3118,28 +3118,28 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.0162</v>
+        <v>-0.0583</v>
       </c>
       <c r="C59" t="n">
-        <v>0.0106</v>
+        <v>-0.0382</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.6168</v>
+        <v>-0.6323</v>
       </c>
       <c r="E59" t="n">
-        <v>0.0162</v>
+        <v>-0.0583</v>
       </c>
       <c r="F59" t="n">
-        <v>0.0162</v>
+        <v>-0.0583</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>0.0162</v>
+        <v>-0.0583</v>
       </c>
       <c r="I59" t="n">
-        <v>0.0162</v>
+        <v>-0.0583</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -3151,7 +3151,7 @@
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>0.0162</v>
+        <v>-0.0583</v>
       </c>
       <c r="N59" t="n">
         <v>162</v>
@@ -3164,28 +3164,28 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.1061</v>
+        <v>-0.09470000000000001</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.0696</v>
+        <v>-0.0621</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.6725</v>
+        <v>-0.6489</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.1061</v>
+        <v>-0.09470000000000001</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.1061</v>
+        <v>-0.09470000000000001</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.1061</v>
+        <v>-0.09470000000000001</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.1061</v>
+        <v>-0.09470000000000001</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -3197,7 +3197,7 @@
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>-0.1061</v>
+        <v>-0.09470000000000001</v>
       </c>
       <c r="N60" t="n">
         <v>137</v>
@@ -3210,28 +3210,28 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.202</v>
+        <v>-0.1626</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.1325</v>
+        <v>-0.1067</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.7161999999999999</v>
+        <v>-0.6798999999999999</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.202</v>
+        <v>-0.1626</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.202</v>
+        <v>-0.1626</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.202</v>
+        <v>-0.1626</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.202</v>
+        <v>-0.1626</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -3243,7 +3243,7 @@
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>-0.202</v>
+        <v>-0.1626</v>
       </c>
       <c r="N61" t="n">
         <v>44</v>
@@ -3256,28 +3256,28 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.2181</v>
+        <v>-0.1851</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.1431</v>
+        <v>-0.1214</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.7235</v>
+        <v>-0.6901</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.2181</v>
+        <v>-0.1851</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.2181</v>
+        <v>-0.1851</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.2181</v>
+        <v>-0.1851</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.2181</v>
+        <v>-0.1851</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -3289,7 +3289,7 @@
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.2181</v>
+        <v>-0.1851</v>
       </c>
       <c r="N62" t="n">
         <v>53</v>
@@ -3302,28 +3302,28 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.2304</v>
+        <v>-0.2103</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.1512</v>
+        <v>-0.138</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.7291</v>
+        <v>-0.7016</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.2304</v>
+        <v>-0.2103</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.2304</v>
+        <v>-0.2103</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.2304</v>
+        <v>-0.2103</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.2304</v>
+        <v>-0.2103</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -3335,7 +3335,7 @@
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.2304</v>
+        <v>-0.2103</v>
       </c>
       <c r="N63" t="n">
         <v>94</v>
@@ -3344,185 +3344,185 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>arya</t>
+          <t>Zeus</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.2823</v>
+        <v>-0.2152</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.1852</v>
+        <v>-0.1412</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.7527</v>
+        <v>-0.7038</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.2823</v>
+        <v>-0.2152</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.2823</v>
+        <v>-0.2176</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>0.0024</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.2823</v>
+        <v>-0.2176</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.2823</v>
+        <v>-0.1222</v>
       </c>
       <c r="J64" t="n">
-        <v>0</v>
+        <v>0.0024</v>
       </c>
       <c r="K64" t="n">
-        <v>40</v>
+        <v>96</v>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="M64" t="n">
-        <v>-0.2823</v>
+        <v>-0.1198</v>
       </c>
       <c r="N64" t="n">
-        <v>40</v>
+        <v>201</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Maikelele</t>
+          <t>B1ad3</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.2857</v>
+        <v>-0.2717</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.1874</v>
+        <v>-0.1783</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.7543</v>
+        <v>-0.7296</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.2857</v>
+        <v>-0.2717</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.2857</v>
+        <v>-0.2717</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.2857</v>
+        <v>-0.2717</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.2857</v>
+        <v>-0.2717</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.2857</v>
+        <v>-0.2717</v>
       </c>
       <c r="N65" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>B1ad3</t>
+          <t>Maikelele</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.3116</v>
+        <v>-0.2726</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.2044</v>
+        <v>-0.1788</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.766</v>
+        <v>-0.73</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.3116</v>
+        <v>-0.2726</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.3116</v>
+        <v>-0.2726</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.3116</v>
+        <v>-0.2726</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.3116</v>
+        <v>-0.2726</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>-0.3116</v>
+        <v>-0.2726</v>
       </c>
       <c r="N66" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Zeus</t>
+          <t>arya</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.3272</v>
+        <v>-0.276</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.2147</v>
+        <v>-0.1811</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.7732</v>
+        <v>-0.7315</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.3272</v>
+        <v>-0.276</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.365</v>
+        <v>-0.276</v>
       </c>
       <c r="G67" t="n">
-        <v>0.0378</v>
+        <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.365</v>
+        <v>-0.276</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.1971</v>
+        <v>-0.276</v>
       </c>
       <c r="J67" t="n">
-        <v>0.0378</v>
+        <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>96</v>
+        <v>40</v>
       </c>
       <c r="L67" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>-0.1593</v>
+        <v>-0.276</v>
       </c>
       <c r="N67" t="n">
-        <v>201</v>
+        <v>40</v>
       </c>
     </row>
     <row r="68">
@@ -3532,28 +3532,28 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.4288</v>
+        <v>-0.4016</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.2813</v>
+        <v>-0.2635</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.8194</v>
+        <v>-0.7887</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.4288</v>
+        <v>-0.4016</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.4288</v>
+        <v>-0.4016</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.4288</v>
+        <v>-0.4016</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.4288</v>
+        <v>-0.4016</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -3565,7 +3565,7 @@
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>-0.4288</v>
+        <v>-0.4016</v>
       </c>
       <c r="N68" t="n">
         <v>44</v>
@@ -3578,28 +3578,28 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-0.4709</v>
+        <v>-0.4255</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.3089</v>
+        <v>-0.2792</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.8386</v>
+        <v>-0.7996</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.4709</v>
+        <v>-0.4255</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.4709</v>
+        <v>-0.4255</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.4709</v>
+        <v>-0.4255</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.4709</v>
+        <v>-0.4255</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -3611,7 +3611,7 @@
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>-0.4709</v>
+        <v>-0.4255</v>
       </c>
       <c r="N69" t="n">
         <v>182</v>
@@ -3624,28 +3624,28 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-0.5281</v>
+        <v>-0.5575</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.3465</v>
+        <v>-0.3658</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.8646</v>
+        <v>-0.8598</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.5281</v>
+        <v>-0.5575</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.5281</v>
+        <v>-0.5575</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>-0.5281</v>
+        <v>-0.5575</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.5281</v>
+        <v>-0.5575</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -3657,7 +3657,7 @@
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>-0.5281</v>
+        <v>-0.5575</v>
       </c>
       <c r="N70" t="n">
         <v>137</v>
@@ -3670,28 +3670,28 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-0.6052</v>
+        <v>-0.5865</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.3971</v>
+        <v>-0.3848</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.8997000000000001</v>
+        <v>-0.873</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.6052</v>
+        <v>-0.5865</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.6052</v>
+        <v>-0.5865</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>-0.6052</v>
+        <v>-0.5865</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.6052</v>
+        <v>-0.5865</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -3703,7 +3703,7 @@
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>-0.6052</v>
+        <v>-0.5865</v>
       </c>
       <c r="N71" t="n">
         <v>53</v>
@@ -3716,28 +3716,28 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-0.6636</v>
+        <v>-0.6393</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.4354</v>
+        <v>-0.4194</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.9263</v>
+        <v>-0.897</v>
       </c>
       <c r="E72" t="n">
-        <v>-0.6636</v>
+        <v>-0.6393</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.6636</v>
+        <v>-0.6393</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>-0.6636</v>
+        <v>-0.6393</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.6636</v>
+        <v>-0.6393</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -3749,7 +3749,7 @@
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>-0.6636</v>
+        <v>-0.6393</v>
       </c>
       <c r="N72" t="n">
         <v>44</v>
@@ -3762,28 +3762,28 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-0.6706</v>
+        <v>-0.644</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.44</v>
+        <v>-0.4225</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.9295</v>
+        <v>-0.8992</v>
       </c>
       <c r="E73" t="n">
-        <v>-0.6706</v>
+        <v>-0.644</v>
       </c>
       <c r="F73" t="n">
-        <v>-0.6706</v>
+        <v>-0.644</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>-0.6706</v>
+        <v>-0.644</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.6706</v>
+        <v>-0.644</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -3795,7 +3795,7 @@
         <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>-0.6706</v>
+        <v>-0.644</v>
       </c>
       <c r="N73" t="n">
         <v>44</v>
@@ -3808,28 +3808,28 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-0.8199</v>
+        <v>-0.803</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.5379</v>
+        <v>-0.5268</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.9974</v>
+        <v>-0.9716</v>
       </c>
       <c r="E74" t="n">
-        <v>-0.8199</v>
+        <v>-0.803</v>
       </c>
       <c r="F74" t="n">
-        <v>-0.8199</v>
+        <v>-0.803</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>-0.8199</v>
+        <v>-0.803</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.8199</v>
+        <v>-0.803</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -3841,7 +3841,7 @@
         <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>-0.8199</v>
+        <v>-0.803</v>
       </c>
       <c r="N74" t="n">
         <v>40</v>
@@ -3854,28 +3854,28 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-0.9302</v>
+        <v>-0.9389</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.6103</v>
+        <v>-0.616</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.0476</v>
+        <v>-1.0335</v>
       </c>
       <c r="E75" t="n">
-        <v>-0.9302</v>
+        <v>-0.9389</v>
       </c>
       <c r="F75" t="n">
-        <v>-0.9302</v>
+        <v>-0.9389</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>-0.9302</v>
+        <v>-0.9389</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.9302</v>
+        <v>-0.9389</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -3887,7 +3887,7 @@
         <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>-0.9302</v>
+        <v>-0.9389</v>
       </c>
       <c r="N75" t="n">
         <v>44</v>
@@ -3900,28 +3900,28 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-1.0481</v>
+        <v>-1.0499</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.6876</v>
+        <v>-0.6888</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.1013</v>
+        <v>-1.0841</v>
       </c>
       <c r="E76" t="n">
-        <v>-1.0481</v>
+        <v>-1.0499</v>
       </c>
       <c r="F76" t="n">
-        <v>-1.0481</v>
+        <v>-1.0499</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>-1.0481</v>
+        <v>-1.0499</v>
       </c>
       <c r="I76" t="n">
-        <v>-1.0481</v>
+        <v>-1.0499</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -3933,7 +3933,7 @@
         <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>-1.0481</v>
+        <v>-1.0499</v>
       </c>
       <c r="N76" t="n">
         <v>40</v>
@@ -3946,28 +3946,28 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-1.0766</v>
+        <v>-1.0565</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.7063</v>
+        <v>-0.6931</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.1143</v>
+        <v>-1.0871</v>
       </c>
       <c r="E77" t="n">
-        <v>-1.0766</v>
+        <v>-1.0565</v>
       </c>
       <c r="F77" t="n">
-        <v>-1.0766</v>
+        <v>-1.0565</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>-1.0766</v>
+        <v>-1.0565</v>
       </c>
       <c r="I77" t="n">
-        <v>-1.0766</v>
+        <v>-1.0565</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -3979,7 +3979,7 @@
         <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>-1.0766</v>
+        <v>-1.0565</v>
       </c>
       <c r="N77" t="n">
         <v>182</v>
@@ -3992,28 +3992,28 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-1.1625</v>
+        <v>-1.1809</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.7627</v>
+        <v>-0.7748</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.1534</v>
+        <v>-1.1437</v>
       </c>
       <c r="E78" t="n">
-        <v>-1.1625</v>
+        <v>-1.1809</v>
       </c>
       <c r="F78" t="n">
-        <v>-1.1625</v>
+        <v>-1.1809</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>-1.1625</v>
+        <v>-1.1809</v>
       </c>
       <c r="I78" t="n">
-        <v>-1.1625</v>
+        <v>-1.1809</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -4025,7 +4025,7 @@
         <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>-1.1625</v>
+        <v>-1.1809</v>
       </c>
       <c r="N78" t="n">
         <v>40</v>
@@ -4038,28 +4038,28 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-1.3084</v>
+        <v>-1.3137</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.8584000000000001</v>
+        <v>-0.8619</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.2198</v>
+        <v>-1.2042</v>
       </c>
       <c r="E79" t="n">
-        <v>-1.3084</v>
+        <v>-1.3137</v>
       </c>
       <c r="F79" t="n">
-        <v>-1.3084</v>
+        <v>-1.3137</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>-1.3084</v>
+        <v>-1.3137</v>
       </c>
       <c r="I79" t="n">
-        <v>-1.3084</v>
+        <v>-1.3137</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -4071,7 +4071,7 @@
         <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>-1.3084</v>
+        <v>-1.3137</v>
       </c>
       <c r="N79" t="n">
         <v>162</v>
@@ -4084,31 +4084,31 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-2.4509</v>
+        <v>-2.214</v>
       </c>
       <c r="C80" t="n">
-        <v>-1.608</v>
+        <v>-1.4526</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.7399</v>
+        <v>-1.6144</v>
       </c>
       <c r="E80" t="n">
-        <v>-2.4509</v>
+        <v>-2.214</v>
       </c>
       <c r="F80" t="n">
-        <v>-1.9871</v>
+        <v>-1.7855</v>
       </c>
       <c r="G80" t="n">
-        <v>-0.4638</v>
+        <v>-0.4285</v>
       </c>
       <c r="H80" t="n">
-        <v>-1.9871</v>
+        <v>-1.7855</v>
       </c>
       <c r="I80" t="n">
-        <v>-1.073</v>
+        <v>-1.0025</v>
       </c>
       <c r="J80" t="n">
-        <v>-0.4638</v>
+        <v>-0.4285</v>
       </c>
       <c r="K80" t="n">
         <v>98</v>
@@ -4117,7 +4117,7 @@
         <v>51</v>
       </c>
       <c r="M80" t="n">
-        <v>-1.5368</v>
+        <v>-1.431</v>
       </c>
       <c r="N80" t="n">
         <v>149</v>
@@ -4130,28 +4130,28 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-3.2177</v>
+        <v>-3.0751</v>
       </c>
       <c r="C81" t="n">
-        <v>-2.1111</v>
+        <v>-2.0175</v>
       </c>
       <c r="D81" t="n">
-        <v>-2.089</v>
+        <v>-2.0066</v>
       </c>
       <c r="E81" t="n">
-        <v>-3.2177</v>
+        <v>-3.0751</v>
       </c>
       <c r="F81" t="n">
-        <v>-3.2177</v>
+        <v>-3.0751</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>-3.2177</v>
+        <v>-3.0751</v>
       </c>
       <c r="I81" t="n">
-        <v>-3.2177</v>
+        <v>-3.0751</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -4163,7 +4163,7 @@
         <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>-3.2177</v>
+        <v>-3.0751</v>
       </c>
       <c r="N81" t="n">
         <v>182</v>
@@ -4269,10 +4269,10 @@
         <v>1.16</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3654</v>
+        <v>0.3107</v>
       </c>
       <c r="J2" t="n">
-        <v>13.1544</v>
+        <v>11.1852</v>
       </c>
     </row>
     <row r="3">
@@ -4309,10 +4309,10 @@
         <v>1.14</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3293</v>
+        <v>0.2766</v>
       </c>
       <c r="J3" t="n">
-        <v>11.8548</v>
+        <v>9.957599999999999</v>
       </c>
     </row>
     <row r="4">
@@ -4349,10 +4349,10 @@
         <v>0.99</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0249</v>
+        <v>-0.018</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.8964</v>
+        <v>-0.648</v>
       </c>
     </row>
     <row r="5">
@@ -4389,10 +4389,10 @@
         <v>0.91</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1349</v>
+        <v>-0.1159</v>
       </c>
       <c r="J5" t="n">
-        <v>-4.8564</v>
+        <v>-4.1724</v>
       </c>
     </row>
     <row r="6">
@@ -4429,10 +4429,10 @@
         <v>0.77</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2812</v>
+        <v>-0.2624</v>
       </c>
       <c r="J6" t="n">
-        <v>-10.1232</v>
+        <v>-9.446400000000001</v>
       </c>
     </row>
     <row r="7">
@@ -4469,10 +4469,10 @@
         <v>1.4</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9503</v>
+        <v>0.9376</v>
       </c>
       <c r="J7" t="n">
-        <v>34.2108</v>
+        <v>33.7536</v>
       </c>
     </row>
     <row r="8">
@@ -4509,10 +4509,10 @@
         <v>1.36</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8725000000000001</v>
+        <v>0.8532</v>
       </c>
       <c r="J8" t="n">
-        <v>31.41</v>
+        <v>30.7152</v>
       </c>
     </row>
     <row r="9">
@@ -4549,10 +4549,10 @@
         <v>1.16</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4568</v>
+        <v>0.4221</v>
       </c>
       <c r="J9" t="n">
-        <v>16.4448</v>
+        <v>15.1956</v>
       </c>
     </row>
     <row r="10">
@@ -4589,10 +4589,10 @@
         <v>1.05</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1695</v>
+        <v>0.1433</v>
       </c>
       <c r="J10" t="n">
-        <v>6.102</v>
+        <v>5.1588</v>
       </c>
     </row>
     <row r="11">
@@ -4629,10 +4629,10 @@
         <v>1.03</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1041</v>
+        <v>0.0837</v>
       </c>
       <c r="J11" t="n">
-        <v>3.7476</v>
+        <v>3.0132</v>
       </c>
     </row>
     <row r="12">
@@ -4669,10 +4669,10 @@
         <v>0.97</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0426</v>
+        <v>0.08409999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7668</v>
+        <v>1.5138</v>
       </c>
     </row>
     <row r="13">
@@ -4709,10 +4709,10 @@
         <v>0.67</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.3287</v>
+        <v>-0.319</v>
       </c>
       <c r="J13" t="n">
-        <v>-5.9166</v>
+        <v>-5.742</v>
       </c>
     </row>
     <row r="14">
@@ -4749,10 +4749,10 @@
         <v>0.53</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.4514</v>
+        <v>-0.4461</v>
       </c>
       <c r="J14" t="n">
-        <v>-8.1252</v>
+        <v>-8.0298</v>
       </c>
     </row>
     <row r="15">
@@ -4789,10 +4789,10 @@
         <v>0.4</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.5659</v>
+        <v>-0.572</v>
       </c>
       <c r="J15" t="n">
-        <v>-10.1862</v>
+        <v>-10.296</v>
       </c>
     </row>
     <row r="16">
@@ -4829,10 +4829,10 @@
         <v>0.35</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6102</v>
+        <v>-0.623</v>
       </c>
       <c r="J16" t="n">
-        <v>-10.9836</v>
+        <v>-11.214</v>
       </c>
     </row>
     <row r="17">
@@ -4869,10 +4869,10 @@
         <v>1.89</v>
       </c>
       <c r="I17" t="n">
-        <v>1.6649</v>
+        <v>1.6956</v>
       </c>
       <c r="J17" t="n">
-        <v>29.9682</v>
+        <v>30.5208</v>
       </c>
     </row>
     <row r="18">
@@ -4909,10 +4909,10 @@
         <v>1.79</v>
       </c>
       <c r="I18" t="n">
-        <v>1.5392</v>
+        <v>1.5719</v>
       </c>
       <c r="J18" t="n">
-        <v>27.7056</v>
+        <v>28.2942</v>
       </c>
     </row>
     <row r="19">
@@ -4949,10 +4949,10 @@
         <v>1.64</v>
       </c>
       <c r="I19" t="n">
-        <v>1.3079</v>
+        <v>1.346</v>
       </c>
       <c r="J19" t="n">
-        <v>23.5422</v>
+        <v>24.228</v>
       </c>
     </row>
     <row r="20">
@@ -4989,10 +4989,10 @@
         <v>1.38</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8568</v>
+        <v>0.8517</v>
       </c>
       <c r="J20" t="n">
-        <v>15.4224</v>
+        <v>15.3306</v>
       </c>
     </row>
     <row r="21">
@@ -5029,10 +5029,10 @@
         <v>1.26</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6193</v>
+        <v>0.5963000000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>11.1474</v>
+        <v>10.7334</v>
       </c>
     </row>
     <row r="22">
@@ -5069,10 +5069,10 @@
         <v>1.2</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4643</v>
+        <v>0.4197</v>
       </c>
       <c r="J22" t="n">
-        <v>15.7862</v>
+        <v>14.2698</v>
       </c>
     </row>
     <row r="23">
@@ -5109,10 +5109,10 @@
         <v>0.97</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.047</v>
+        <v>-0.0376</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.598</v>
+        <v>-1.2784</v>
       </c>
     </row>
     <row r="24">
@@ -5149,10 +5149,10 @@
         <v>0.8</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.2397</v>
+        <v>-0.2205</v>
       </c>
       <c r="J24" t="n">
-        <v>-8.149800000000001</v>
+        <v>-7.497</v>
       </c>
     </row>
     <row r="25">
@@ -5189,10 +5189,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3439</v>
+        <v>-0.3283</v>
       </c>
       <c r="J25" t="n">
-        <v>-11.6926</v>
+        <v>-11.1622</v>
       </c>
     </row>
     <row r="26">
@@ -5229,10 +5229,10 @@
         <v>0.67</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.3622</v>
+        <v>-0.3478</v>
       </c>
       <c r="J26" t="n">
-        <v>-12.3148</v>
+        <v>-11.8252</v>
       </c>
     </row>
     <row r="27">
@@ -5269,10 +5269,10 @@
         <v>1.36</v>
       </c>
       <c r="I27" t="n">
-        <v>0.7647</v>
+        <v>0.749</v>
       </c>
       <c r="J27" t="n">
-        <v>25.9998</v>
+        <v>25.466</v>
       </c>
     </row>
     <row r="28">
@@ -5309,10 +5309,10 @@
         <v>1.26</v>
       </c>
       <c r="I28" t="n">
-        <v>0.6145</v>
+        <v>0.6029</v>
       </c>
       <c r="J28" t="n">
-        <v>20.893</v>
+        <v>20.4986</v>
       </c>
     </row>
     <row r="29">
@@ -5349,10 +5349,10 @@
         <v>1.23</v>
       </c>
       <c r="I29" t="n">
-        <v>0.5676</v>
+        <v>0.5585</v>
       </c>
       <c r="J29" t="n">
-        <v>19.2984</v>
+        <v>18.989</v>
       </c>
     </row>
     <row r="30">
@@ -5389,10 +5389,10 @@
         <v>1.17</v>
       </c>
       <c r="I30" t="n">
-        <v>0.4711</v>
+        <v>0.4465</v>
       </c>
       <c r="J30" t="n">
-        <v>16.0174</v>
+        <v>15.181</v>
       </c>
     </row>
     <row r="31">
@@ -5429,10 +5429,10 @@
         <v>0.83</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.5501</v>
+        <v>-0.5118</v>
       </c>
       <c r="J31" t="n">
-        <v>-18.7034</v>
+        <v>-17.4012</v>
       </c>
     </row>
     <row r="32">
@@ -5469,10 +5469,10 @@
         <v>1.16</v>
       </c>
       <c r="I32" t="n">
-        <v>0.3676</v>
+        <v>0.3128</v>
       </c>
       <c r="J32" t="n">
-        <v>12.866</v>
+        <v>10.948</v>
       </c>
     </row>
     <row r="33">
@@ -5509,10 +5509,10 @@
         <v>1.15</v>
       </c>
       <c r="I33" t="n">
-        <v>0.3496</v>
+        <v>0.2957</v>
       </c>
       <c r="J33" t="n">
-        <v>12.236</v>
+        <v>10.3495</v>
       </c>
     </row>
     <row r="34">
@@ -5549,10 +5549,10 @@
         <v>1.07</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1943</v>
+        <v>0.1537</v>
       </c>
       <c r="J34" t="n">
-        <v>6.8005</v>
+        <v>5.3795</v>
       </c>
     </row>
     <row r="35">
@@ -5589,10 +5589,10 @@
         <v>0.89</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1568</v>
+        <v>-0.137</v>
       </c>
       <c r="J35" t="n">
-        <v>-5.488</v>
+        <v>-4.795</v>
       </c>
     </row>
     <row r="36">
@@ -5629,10 +5629,10 @@
         <v>0.65</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.3916</v>
+        <v>-0.3804</v>
       </c>
       <c r="J36" t="n">
-        <v>-13.706</v>
+        <v>-13.314</v>
       </c>
     </row>
     <row r="37">
@@ -5669,10 +5669,10 @@
         <v>1.48</v>
       </c>
       <c r="I37" t="n">
-        <v>0.9411</v>
+        <v>0.9271</v>
       </c>
       <c r="J37" t="n">
-        <v>32.9385</v>
+        <v>32.4485</v>
       </c>
     </row>
     <row r="38">
@@ -5709,10 +5709,10 @@
         <v>1.37</v>
       </c>
       <c r="I38" t="n">
-        <v>0.7836</v>
+        <v>0.7675999999999999</v>
       </c>
       <c r="J38" t="n">
-        <v>27.426</v>
+        <v>26.866</v>
       </c>
     </row>
     <row r="39">
@@ -5749,10 +5749,10 @@
         <v>1.08</v>
       </c>
       <c r="I39" t="n">
-        <v>0.2652</v>
+        <v>0.2328</v>
       </c>
       <c r="J39" t="n">
-        <v>9.282</v>
+        <v>8.148</v>
       </c>
     </row>
     <row r="40">
@@ -5789,10 +5789,10 @@
         <v>0.97</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.1622</v>
+        <v>-0.1306</v>
       </c>
       <c r="J40" t="n">
-        <v>-5.677</v>
+        <v>-4.571</v>
       </c>
     </row>
     <row r="41">
@@ -5829,10 +5829,10 @@
         <v>0.84</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.5223</v>
+        <v>-0.4823</v>
       </c>
       <c r="J41" t="n">
-        <v>-18.2805</v>
+        <v>-16.8805</v>
       </c>
     </row>
     <row r="42">
@@ -5869,10 +5869,10 @@
         <v>1.45</v>
       </c>
       <c r="I42" t="n">
-        <v>0.9344</v>
+        <v>0.9236</v>
       </c>
       <c r="J42" t="n">
-        <v>28.032</v>
+        <v>27.708</v>
       </c>
     </row>
     <row r="43">
@@ -5909,10 +5909,10 @@
         <v>1.21</v>
       </c>
       <c r="I43" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.5494</v>
       </c>
       <c r="J43" t="n">
-        <v>16.83</v>
+        <v>16.482</v>
       </c>
     </row>
     <row r="44">
@@ -5949,10 +5949,10 @@
         <v>0.9</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.346</v>
+        <v>-0.3037</v>
       </c>
       <c r="J44" t="n">
-        <v>-10.38</v>
+        <v>-9.111000000000001</v>
       </c>
     </row>
     <row r="45">
@@ -5989,10 +5989,10 @@
         <v>0.84</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.4973</v>
+        <v>-0.4551</v>
       </c>
       <c r="J45" t="n">
-        <v>-14.919</v>
+        <v>-13.653</v>
       </c>
     </row>
     <row r="46">
@@ -6029,10 +6029,10 @@
         <v>0.7</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.8132</v>
+        <v>-0.7894</v>
       </c>
       <c r="J46" t="n">
-        <v>-24.396</v>
+        <v>-23.682</v>
       </c>
     </row>
     <row r="47">
@@ -6069,10 +6069,10 @@
         <v>1.08</v>
       </c>
       <c r="I47" t="n">
-        <v>0.2194</v>
+        <v>0.1758</v>
       </c>
       <c r="J47" t="n">
-        <v>6.582</v>
+        <v>5.274</v>
       </c>
     </row>
     <row r="48">
@@ -6109,10 +6109,10 @@
         <v>0.99</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.0232</v>
+        <v>-0.0171</v>
       </c>
       <c r="J48" t="n">
-        <v>-0.696</v>
+        <v>-0.513</v>
       </c>
     </row>
     <row r="49">
@@ -6149,10 +6149,10 @@
         <v>0.95</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.0834</v>
+        <v>-0.0687</v>
       </c>
       <c r="J49" t="n">
-        <v>-2.502</v>
+        <v>-2.061</v>
       </c>
     </row>
     <row r="50">
@@ -6189,10 +6189,10 @@
         <v>0.95</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.0834</v>
+        <v>-0.0687</v>
       </c>
       <c r="J50" t="n">
-        <v>-2.502</v>
+        <v>-2.061</v>
       </c>
     </row>
     <row r="51">
@@ -6229,10 +6229,10 @@
         <v>0.84</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.2084</v>
+        <v>-0.188</v>
       </c>
       <c r="J51" t="n">
-        <v>-6.252</v>
+        <v>-5.64</v>
       </c>
     </row>
     <row r="52">
@@ -6269,10 +6269,10 @@
         <v>1.76</v>
       </c>
       <c r="I52" t="n">
-        <v>1.2578</v>
+        <v>1.2573</v>
       </c>
       <c r="J52" t="n">
-        <v>26.4138</v>
+        <v>26.4033</v>
       </c>
     </row>
     <row r="53">
@@ -6309,10 +6309,10 @@
         <v>1.43</v>
       </c>
       <c r="I53" t="n">
-        <v>0.8336</v>
+        <v>0.8225</v>
       </c>
       <c r="J53" t="n">
-        <v>17.5056</v>
+        <v>17.2725</v>
       </c>
     </row>
     <row r="54">
@@ -6349,10 +6349,10 @@
         <v>1.39</v>
       </c>
       <c r="I54" t="n">
-        <v>0.7799</v>
+        <v>0.7698</v>
       </c>
       <c r="J54" t="n">
-        <v>16.3779</v>
+        <v>16.1658</v>
       </c>
     </row>
     <row r="55">
@@ -6389,10 +6389,10 @@
         <v>1.34</v>
       </c>
       <c r="I55" t="n">
-        <v>0.7117</v>
+        <v>0.7033</v>
       </c>
       <c r="J55" t="n">
-        <v>14.9457</v>
+        <v>14.7693</v>
       </c>
     </row>
     <row r="56">
@@ -6429,10 +6429,10 @@
         <v>0.98</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.1643</v>
+        <v>-0.1403</v>
       </c>
       <c r="J56" t="n">
-        <v>-3.4503</v>
+        <v>-2.9463</v>
       </c>
     </row>
     <row r="57">
@@ -6469,10 +6469,10 @@
         <v>0.78</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.2456</v>
+        <v>-0.2306</v>
       </c>
       <c r="J57" t="n">
-        <v>-5.1576</v>
+        <v>-4.8426</v>
       </c>
     </row>
     <row r="58">
@@ -6509,10 +6509,10 @@
         <v>0.78</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.2456</v>
+        <v>-0.2306</v>
       </c>
       <c r="J58" t="n">
-        <v>-5.1576</v>
+        <v>-4.8426</v>
       </c>
     </row>
     <row r="59">
@@ -6549,10 +6549,10 @@
         <v>0.77</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.2554</v>
+        <v>-0.2405</v>
       </c>
       <c r="J59" t="n">
-        <v>-5.3634</v>
+        <v>-5.0505</v>
       </c>
     </row>
     <row r="60">
@@ -6589,10 +6589,10 @@
         <v>0.75</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.2744</v>
+        <v>-0.2596</v>
       </c>
       <c r="J60" t="n">
-        <v>-5.7624</v>
+        <v>-5.4516</v>
       </c>
     </row>
     <row r="61">
@@ -6629,10 +6629,10 @@
         <v>0.52</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.479</v>
+        <v>-0.4749</v>
       </c>
       <c r="J61" t="n">
-        <v>-10.059</v>
+        <v>-9.972899999999999</v>
       </c>
     </row>
     <row r="62">
@@ -6669,10 +6669,10 @@
         <v>1.18</v>
       </c>
       <c r="I62" t="n">
-        <v>0.3187</v>
+        <v>0.3082</v>
       </c>
       <c r="J62" t="n">
-        <v>11.4732</v>
+        <v>11.0952</v>
       </c>
     </row>
     <row r="63">
@@ -6709,10 +6709,10 @@
         <v>0.98</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.0411</v>
+        <v>-0.0317</v>
       </c>
       <c r="J63" t="n">
-        <v>-1.4796</v>
+        <v>-1.1412</v>
       </c>
     </row>
     <row r="64">
@@ -6749,10 +6749,10 @@
         <v>0.91</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.1328</v>
+        <v>-0.1141</v>
       </c>
       <c r="J64" t="n">
-        <v>-4.7808</v>
+        <v>-4.1076</v>
       </c>
     </row>
     <row r="65">
@@ -6789,10 +6789,10 @@
         <v>0.89</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.1555</v>
+        <v>-0.1358</v>
       </c>
       <c r="J65" t="n">
-        <v>-5.598</v>
+        <v>-4.8888</v>
       </c>
     </row>
     <row r="66">
@@ -6829,10 +6829,10 @@
         <v>0.88</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.1665</v>
+        <v>-0.1465</v>
       </c>
       <c r="J66" t="n">
-        <v>-5.994</v>
+        <v>-5.274</v>
       </c>
     </row>
     <row r="67">
@@ -6869,10 +6869,10 @@
         <v>1.33</v>
       </c>
       <c r="I67" t="n">
-        <v>0.4544</v>
+        <v>0.3881</v>
       </c>
       <c r="J67" t="n">
-        <v>16.3584</v>
+        <v>13.9716</v>
       </c>
     </row>
     <row r="68">
@@ -6909,10 +6909,10 @@
         <v>1.26</v>
       </c>
       <c r="I68" t="n">
-        <v>0.375</v>
+        <v>0.3139</v>
       </c>
       <c r="J68" t="n">
-        <v>13.5</v>
+        <v>11.3004</v>
       </c>
     </row>
     <row r="69">
@@ -6949,10 +6949,10 @@
         <v>1.08</v>
       </c>
       <c r="I69" t="n">
-        <v>0.1465</v>
+        <v>0.113</v>
       </c>
       <c r="J69" t="n">
-        <v>5.274</v>
+        <v>4.068</v>
       </c>
     </row>
     <row r="70">
@@ -6989,10 +6989,10 @@
         <v>1.04</v>
       </c>
       <c r="I70" t="n">
-        <v>0.08169999999999999</v>
+        <v>0.0599</v>
       </c>
       <c r="J70" t="n">
-        <v>2.9412</v>
+        <v>2.1564</v>
       </c>
     </row>
     <row r="71">
@@ -7029,10 +7029,10 @@
         <v>0.97</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.0687</v>
+        <v>-0.0545</v>
       </c>
       <c r="J71" t="n">
-        <v>-2.4732</v>
+        <v>-1.962</v>
       </c>
     </row>
     <row r="72">
@@ -7069,10 +7069,10 @@
         <v>1.59</v>
       </c>
       <c r="I72" t="n">
-        <v>1.2031</v>
+        <v>1.2182</v>
       </c>
       <c r="J72" t="n">
-        <v>31.2806</v>
+        <v>31.6732</v>
       </c>
     </row>
     <row r="73">
@@ -7109,10 +7109,10 @@
         <v>1.4</v>
       </c>
       <c r="I73" t="n">
-        <v>0.9275</v>
+        <v>0.9171</v>
       </c>
       <c r="J73" t="n">
-        <v>24.115</v>
+        <v>23.8446</v>
       </c>
     </row>
     <row r="74">
@@ -7149,10 +7149,10 @@
         <v>1.24</v>
       </c>
       <c r="I74" t="n">
-        <v>0.6173</v>
+        <v>0.59</v>
       </c>
       <c r="J74" t="n">
-        <v>16.0498</v>
+        <v>15.34</v>
       </c>
     </row>
     <row r="75">
@@ -7189,10 +7189,10 @@
         <v>1.24</v>
       </c>
       <c r="I75" t="n">
-        <v>0.6173</v>
+        <v>0.59</v>
       </c>
       <c r="J75" t="n">
-        <v>16.0498</v>
+        <v>15.34</v>
       </c>
     </row>
     <row r="76">
@@ -7229,10 +7229,10 @@
         <v>1.07</v>
       </c>
       <c r="I76" t="n">
-        <v>0.2107</v>
+        <v>0.1815</v>
       </c>
       <c r="J76" t="n">
-        <v>5.4782</v>
+        <v>4.719</v>
       </c>
     </row>
     <row r="77">
@@ -7269,10 +7269,10 @@
         <v>1.21</v>
       </c>
       <c r="I77" t="n">
-        <v>0.5023</v>
+        <v>0.4507</v>
       </c>
       <c r="J77" t="n">
-        <v>13.0598</v>
+        <v>11.7182</v>
       </c>
     </row>
     <row r="78">
@@ -7309,10 +7309,10 @@
         <v>0.99</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.0045</v>
       </c>
       <c r="J78" t="n">
-        <v>-0.2288</v>
+        <v>-0.117</v>
       </c>
     </row>
     <row r="79">
@@ -7349,10 +7349,10 @@
         <v>0.77</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.266</v>
+        <v>-0.2476</v>
       </c>
       <c r="J79" t="n">
-        <v>-6.916</v>
+        <v>-6.4376</v>
       </c>
     </row>
     <row r="80">
@@ -7389,10 +7389,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.3409</v>
+        <v>-0.3252</v>
       </c>
       <c r="J80" t="n">
-        <v>-8.8634</v>
+        <v>-8.4552</v>
       </c>
     </row>
     <row r="81">
@@ -7429,10 +7429,10 @@
         <v>0.53</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.4835</v>
+        <v>-0.4809</v>
       </c>
       <c r="J81" t="n">
-        <v>-12.571</v>
+        <v>-12.5034</v>
       </c>
     </row>
     <row r="82">
@@ -7469,10 +7469,10 @@
         <v>1.27</v>
       </c>
       <c r="I82" t="n">
-        <v>0.7083</v>
+        <v>0.6761</v>
       </c>
       <c r="J82" t="n">
-        <v>19.1241</v>
+        <v>18.2547</v>
       </c>
     </row>
     <row r="83">
@@ -7509,10 +7509,10 @@
         <v>1.19</v>
       </c>
       <c r="I83" t="n">
-        <v>0.5345</v>
+        <v>0.4961</v>
       </c>
       <c r="J83" t="n">
-        <v>14.4315</v>
+        <v>13.3947</v>
       </c>
     </row>
     <row r="84">
@@ -7549,10 +7549,10 @@
         <v>1.11</v>
       </c>
       <c r="I84" t="n">
-        <v>0.3475</v>
+        <v>0.3106</v>
       </c>
       <c r="J84" t="n">
-        <v>9.3825</v>
+        <v>8.386200000000001</v>
       </c>
     </row>
     <row r="85">
@@ -7589,10 +7589,10 @@
         <v>1.02</v>
       </c>
       <c r="I85" t="n">
-        <v>0.08169999999999999</v>
+        <v>0.0645</v>
       </c>
       <c r="J85" t="n">
-        <v>2.2059</v>
+        <v>1.7415</v>
       </c>
     </row>
     <row r="86">
@@ -7629,10 +7629,10 @@
         <v>1.01</v>
       </c>
       <c r="I86" t="n">
-        <v>0.0404</v>
+        <v>0.0298</v>
       </c>
       <c r="J86" t="n">
-        <v>1.0908</v>
+        <v>0.8046</v>
       </c>
     </row>
     <row r="87">
@@ -7669,10 +7669,10 @@
         <v>1.25</v>
       </c>
       <c r="I87" t="n">
-        <v>0.5253</v>
+        <v>0.4667</v>
       </c>
       <c r="J87" t="n">
-        <v>14.1831</v>
+        <v>12.6009</v>
       </c>
     </row>
     <row r="88">
@@ -7709,10 +7709,10 @@
         <v>1</v>
       </c>
       <c r="I88" t="n">
-        <v>0.003</v>
+        <v>0.0015</v>
       </c>
       <c r="J88" t="n">
-        <v>0.081</v>
+        <v>0.0405</v>
       </c>
     </row>
     <row r="89">
@@ -7749,10 +7749,10 @@
         <v>0.9</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.1444</v>
+        <v>-0.1252</v>
       </c>
       <c r="J89" t="n">
-        <v>-3.8988</v>
+        <v>-3.3804</v>
       </c>
     </row>
     <row r="90">
@@ -7789,10 +7789,10 @@
         <v>0.86</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.1882</v>
+        <v>-0.1678</v>
       </c>
       <c r="J90" t="n">
-        <v>-5.0814</v>
+        <v>-4.5306</v>
       </c>
     </row>
     <row r="91">
@@ -7829,10 +7829,10 @@
         <v>0.84</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.2092</v>
+        <v>-0.1887</v>
       </c>
       <c r="J91" t="n">
-        <v>-5.6484</v>
+        <v>-5.0949</v>
       </c>
     </row>
     <row r="92">
@@ -7869,10 +7869,10 @@
         <v>1.27</v>
       </c>
       <c r="I92" t="n">
-        <v>0.7073</v>
+        <v>0.6751</v>
       </c>
       <c r="J92" t="n">
-        <v>20.5117</v>
+        <v>19.5779</v>
       </c>
     </row>
     <row r="93">
@@ -7909,10 +7909,10 @@
         <v>1.18</v>
       </c>
       <c r="I93" t="n">
-        <v>0.5112</v>
+        <v>0.4727</v>
       </c>
       <c r="J93" t="n">
-        <v>14.8248</v>
+        <v>13.7083</v>
       </c>
     </row>
     <row r="94">
@@ -7949,10 +7949,10 @@
         <v>1.16</v>
       </c>
       <c r="I94" t="n">
-        <v>0.4655</v>
+        <v>0.4268</v>
       </c>
       <c r="J94" t="n">
-        <v>13.4995</v>
+        <v>12.3772</v>
       </c>
     </row>
     <row r="95">
@@ -7989,10 +7989,10 @@
         <v>1.02</v>
       </c>
       <c r="I95" t="n">
-        <v>0.081</v>
+        <v>0.0639</v>
       </c>
       <c r="J95" t="n">
-        <v>2.349</v>
+        <v>1.8531</v>
       </c>
     </row>
     <row r="96">
@@ -8029,10 +8029,10 @@
         <v>0.99</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.0798</v>
+        <v>-0.0591</v>
       </c>
       <c r="J96" t="n">
-        <v>-2.3142</v>
+        <v>-1.7139</v>
       </c>
     </row>
     <row r="97">
@@ -8069,10 +8069,10 @@
         <v>1.66</v>
       </c>
       <c r="I97" t="n">
-        <v>1.0773</v>
+        <v>1.0617</v>
       </c>
       <c r="J97" t="n">
-        <v>31.2417</v>
+        <v>30.7893</v>
       </c>
     </row>
     <row r="98">
@@ -8109,10 +8109,10 @@
         <v>1.1</v>
       </c>
       <c r="I98" t="n">
-        <v>0.2443</v>
+        <v>0.1998</v>
       </c>
       <c r="J98" t="n">
-        <v>7.0847</v>
+        <v>5.7942</v>
       </c>
     </row>
     <row r="99">
@@ -8149,10 +8149,10 @@
         <v>0.86</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.1955</v>
+        <v>-0.1748</v>
       </c>
       <c r="J99" t="n">
-        <v>-5.6695</v>
+        <v>-5.0692</v>
       </c>
     </row>
     <row r="100">
@@ -8189,10 +8189,10 @@
         <v>0.86</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.1955</v>
+        <v>-0.1748</v>
       </c>
       <c r="J100" t="n">
-        <v>-5.6695</v>
+        <v>-5.0692</v>
       </c>
     </row>
     <row r="101">
@@ -8229,10 +8229,10 @@
         <v>0.78</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.2767</v>
+        <v>-0.2579</v>
       </c>
       <c r="J101" t="n">
-        <v>-8.0243</v>
+        <v>-7.4791</v>
       </c>
     </row>
     <row r="102">
@@ -8269,10 +8269,10 @@
         <v>1.82</v>
       </c>
       <c r="I102" t="n">
-        <v>1.4796</v>
+        <v>1.5098</v>
       </c>
       <c r="J102" t="n">
-        <v>32.5512</v>
+        <v>33.2156</v>
       </c>
     </row>
     <row r="103">
@@ -8309,10 +8309,10 @@
         <v>1.51</v>
       </c>
       <c r="I103" t="n">
-        <v>1.0875</v>
+        <v>1.1005</v>
       </c>
       <c r="J103" t="n">
-        <v>23.925</v>
+        <v>24.211</v>
       </c>
     </row>
     <row r="104">
@@ -8349,10 +8349,10 @@
         <v>1.37</v>
       </c>
       <c r="I104" t="n">
-        <v>0.8643</v>
+        <v>0.8524</v>
       </c>
       <c r="J104" t="n">
-        <v>19.0146</v>
+        <v>18.7528</v>
       </c>
     </row>
     <row r="105">
@@ -8389,10 +8389,10 @@
         <v>1.13</v>
       </c>
       <c r="I105" t="n">
-        <v>0.3581</v>
+        <v>0.3261</v>
       </c>
       <c r="J105" t="n">
-        <v>7.8782</v>
+        <v>7.1742</v>
       </c>
     </row>
     <row r="106">
@@ -8429,10 +8429,10 @@
         <v>1.05</v>
       </c>
       <c r="I106" t="n">
-        <v>0.1407</v>
+        <v>0.1136</v>
       </c>
       <c r="J106" t="n">
-        <v>3.0954</v>
+        <v>2.4992</v>
       </c>
     </row>
     <row r="107">
@@ -8469,10 +8469,10 @@
         <v>0.76</v>
       </c>
       <c r="I107" t="n">
-        <v>-0.2623</v>
+        <v>-0.248</v>
       </c>
       <c r="J107" t="n">
-        <v>-5.7706</v>
+        <v>-5.456</v>
       </c>
     </row>
     <row r="108">
@@ -8509,10 +8509,10 @@
         <v>0.74</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.2815</v>
+        <v>-0.2674</v>
       </c>
       <c r="J108" t="n">
-        <v>-6.193</v>
+        <v>-5.8828</v>
       </c>
     </row>
     <row r="109">
@@ -8549,10 +8549,10 @@
         <v>0.74</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.2815</v>
+        <v>-0.2674</v>
       </c>
       <c r="J109" t="n">
-        <v>-6.193</v>
+        <v>-5.8828</v>
       </c>
     </row>
     <row r="110">
@@ -8589,10 +8589,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.3261</v>
+        <v>-0.3125</v>
       </c>
       <c r="J110" t="n">
-        <v>-7.1742</v>
+        <v>-6.875</v>
       </c>
     </row>
     <row r="111">
@@ -8629,10 +8629,10 @@
         <v>0.57</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.4324</v>
+        <v>-0.4238</v>
       </c>
       <c r="J111" t="n">
-        <v>-9.5128</v>
+        <v>-9.323600000000001</v>
       </c>
     </row>
     <row r="112">
@@ -8669,10 +8669,10 @@
         <v>1.45</v>
       </c>
       <c r="I112" t="n">
-        <v>1.0367</v>
+        <v>1.04</v>
       </c>
       <c r="J112" t="n">
-        <v>26.9542</v>
+        <v>27.04</v>
       </c>
     </row>
     <row r="113">
@@ -8709,10 +8709,10 @@
         <v>1.37</v>
       </c>
       <c r="I113" t="n">
-        <v>0.8963</v>
+        <v>0.8784999999999999</v>
       </c>
       <c r="J113" t="n">
-        <v>23.3038</v>
+        <v>22.841</v>
       </c>
     </row>
     <row r="114">
@@ -8749,10 +8749,10 @@
         <v>1.19</v>
       </c>
       <c r="I114" t="n">
-        <v>0.5253</v>
+        <v>0.49</v>
       </c>
       <c r="J114" t="n">
-        <v>13.6578</v>
+        <v>12.74</v>
       </c>
     </row>
     <row r="115">
@@ -8789,10 +8789,10 @@
         <v>1.03</v>
       </c>
       <c r="I115" t="n">
-        <v>0.1073</v>
+        <v>0.0867</v>
       </c>
       <c r="J115" t="n">
-        <v>2.7898</v>
+        <v>2.2542</v>
       </c>
     </row>
     <row r="116">
@@ -8829,10 +8829,10 @@
         <v>0.87</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.4545</v>
+        <v>-0.4136</v>
       </c>
       <c r="J116" t="n">
-        <v>-11.817</v>
+        <v>-10.7536</v>
       </c>
     </row>
     <row r="117">
@@ -8869,10 +8869,10 @@
         <v>1.26</v>
       </c>
       <c r="I117" t="n">
-        <v>0.5323</v>
+        <v>0.473</v>
       </c>
       <c r="J117" t="n">
-        <v>13.8398</v>
+        <v>12.298</v>
       </c>
     </row>
     <row r="118">
@@ -8909,10 +8909,10 @@
         <v>1.06</v>
       </c>
       <c r="I118" t="n">
-        <v>0.1695</v>
+        <v>0.1325</v>
       </c>
       <c r="J118" t="n">
-        <v>4.407</v>
+        <v>3.445</v>
       </c>
     </row>
     <row r="119">
@@ -8949,10 +8949,10 @@
         <v>1.02</v>
       </c>
       <c r="I119" t="n">
-        <v>0.073</v>
+        <v>0.0522</v>
       </c>
       <c r="J119" t="n">
-        <v>1.898</v>
+        <v>1.3572</v>
       </c>
     </row>
     <row r="120">
@@ -8989,10 +8989,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.0993</v>
+        <v>-0.0824</v>
       </c>
       <c r="J120" t="n">
-        <v>-2.5818</v>
+        <v>-2.1424</v>
       </c>
     </row>
     <row r="121">
@@ -9029,10 +9029,10 @@
         <v>0.74</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.3108</v>
+        <v>-0.2935</v>
       </c>
       <c r="J121" t="n">
-        <v>-8.0808</v>
+        <v>-7.631</v>
       </c>
     </row>
     <row r="122">
@@ -9069,10 +9069,10 @@
         <v>1.97</v>
       </c>
       <c r="I122" t="n">
-        <v>1.6552</v>
+        <v>1.7</v>
       </c>
       <c r="J122" t="n">
-        <v>34.7592</v>
+        <v>35.7</v>
       </c>
     </row>
     <row r="123">
@@ -9109,10 +9109,10 @@
         <v>1.56</v>
       </c>
       <c r="I123" t="n">
-        <v>1.1497</v>
+        <v>1.165</v>
       </c>
       <c r="J123" t="n">
-        <v>24.1437</v>
+        <v>24.465</v>
       </c>
     </row>
     <row r="124">
@@ -9149,10 +9149,10 @@
         <v>1.35</v>
       </c>
       <c r="I124" t="n">
-        <v>0.8248</v>
+        <v>0.8115</v>
       </c>
       <c r="J124" t="n">
-        <v>17.3208</v>
+        <v>17.0415</v>
       </c>
     </row>
     <row r="125">
@@ -9189,10 +9189,10 @@
         <v>1.25</v>
       </c>
       <c r="I125" t="n">
-        <v>0.6254999999999999</v>
+        <v>0.6012999999999999</v>
       </c>
       <c r="J125" t="n">
-        <v>13.1355</v>
+        <v>12.6273</v>
       </c>
     </row>
     <row r="126">
@@ -9229,10 +9229,10 @@
         <v>0.86</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.5133</v>
+        <v>-0.48</v>
       </c>
       <c r="J126" t="n">
-        <v>-10.7793</v>
+        <v>-10.08</v>
       </c>
     </row>
     <row r="127">
@@ -9269,10 +9269,10 @@
         <v>1.06</v>
       </c>
       <c r="I127" t="n">
-        <v>0.2741</v>
+        <v>0.2471</v>
       </c>
       <c r="J127" t="n">
-        <v>5.7561</v>
+        <v>5.1891</v>
       </c>
     </row>
     <row r="128">
@@ -9309,10 +9309,10 @@
         <v>0.67</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.3421</v>
+        <v>-0.3294</v>
       </c>
       <c r="J128" t="n">
-        <v>-7.1841</v>
+        <v>-6.9174</v>
       </c>
     </row>
     <row r="129">
@@ -9349,10 +9349,10 @@
         <v>0.62</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.3861</v>
+        <v>-0.3747</v>
       </c>
       <c r="J129" t="n">
-        <v>-8.1081</v>
+        <v>-7.8687</v>
       </c>
     </row>
     <row r="130">
@@ -9389,10 +9389,10 @@
         <v>0.61</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.3949</v>
+        <v>-0.384</v>
       </c>
       <c r="J130" t="n">
-        <v>-8.292899999999999</v>
+        <v>-8.064</v>
       </c>
     </row>
     <row r="131">
@@ -9429,10 +9429,10 @@
         <v>0.46</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.527</v>
+        <v>-0.5285</v>
       </c>
       <c r="J131" t="n">
-        <v>-11.067</v>
+        <v>-11.0985</v>
       </c>
     </row>
     <row r="132">
@@ -9469,10 +9469,10 @@
         <v>1.4</v>
       </c>
       <c r="I132" t="n">
-        <v>0.9556</v>
+        <v>0.9449</v>
       </c>
       <c r="J132" t="n">
-        <v>23.89</v>
+        <v>23.6225</v>
       </c>
     </row>
     <row r="133">
@@ -9509,10 +9509,10 @@
         <v>1.26</v>
       </c>
       <c r="I133" t="n">
-        <v>0.6761</v>
+        <v>0.644</v>
       </c>
       <c r="J133" t="n">
-        <v>16.9025</v>
+        <v>16.1</v>
       </c>
     </row>
     <row r="134">
@@ -9549,10 +9549,10 @@
         <v>1.13</v>
       </c>
       <c r="I134" t="n">
-        <v>0.3899</v>
+        <v>0.3545</v>
       </c>
       <c r="J134" t="n">
-        <v>9.7475</v>
+        <v>8.862500000000001</v>
       </c>
     </row>
     <row r="135">
@@ -9589,10 +9589,10 @@
         <v>1.1</v>
       </c>
       <c r="I135" t="n">
-        <v>0.3147</v>
+        <v>0.2811</v>
       </c>
       <c r="J135" t="n">
-        <v>7.8675</v>
+        <v>7.0275</v>
       </c>
     </row>
     <row r="136">
@@ -9629,10 +9629,10 @@
         <v>0.97</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.1665</v>
+        <v>-0.135</v>
       </c>
       <c r="J136" t="n">
-        <v>-4.1625</v>
+        <v>-3.375</v>
       </c>
     </row>
     <row r="137">
@@ -9669,10 +9669,10 @@
         <v>1.05</v>
       </c>
       <c r="I137" t="n">
-        <v>0.1548</v>
+        <v>0.1191</v>
       </c>
       <c r="J137" t="n">
-        <v>3.87</v>
+        <v>2.9775</v>
       </c>
     </row>
     <row r="138">
@@ -9709,10 +9709,10 @@
         <v>1.03</v>
       </c>
       <c r="I138" t="n">
-        <v>0.1062</v>
+        <v>0.0781</v>
       </c>
       <c r="J138" t="n">
-        <v>2.655</v>
+        <v>1.9525</v>
       </c>
     </row>
     <row r="139">
@@ -9749,10 +9749,10 @@
         <v>1.02</v>
       </c>
       <c r="I139" t="n">
-        <v>0.07920000000000001</v>
+        <v>0.0563</v>
       </c>
       <c r="J139" t="n">
-        <v>1.98</v>
+        <v>1.4075</v>
       </c>
     </row>
     <row r="140">
@@ -9789,10 +9789,10 @@
         <v>0.98</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.0405</v>
+        <v>-0.0314</v>
       </c>
       <c r="J140" t="n">
-        <v>-1.0125</v>
+        <v>-0.785</v>
       </c>
     </row>
     <row r="141">
@@ -9829,10 +9829,10 @@
         <v>0.71</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.3346</v>
+        <v>-0.3186</v>
       </c>
       <c r="J141" t="n">
-        <v>-8.365</v>
+        <v>-7.965</v>
       </c>
     </row>
     <row r="142">
@@ -9869,10 +9869,10 @@
         <v>1.84</v>
       </c>
       <c r="I142" t="n">
-        <v>1.5368</v>
+        <v>1.5745</v>
       </c>
       <c r="J142" t="n">
-        <v>39.9568</v>
+        <v>40.937</v>
       </c>
     </row>
     <row r="143">
@@ -9909,10 +9909,10 @@
         <v>1.45</v>
       </c>
       <c r="I143" t="n">
-        <v>1.0232</v>
+        <v>1.025</v>
       </c>
       <c r="J143" t="n">
-        <v>26.6032</v>
+        <v>26.65</v>
       </c>
     </row>
     <row r="144">
@@ -9949,10 +9949,10 @@
         <v>1.18</v>
       </c>
       <c r="I144" t="n">
-        <v>0.4959</v>
+        <v>0.4634</v>
       </c>
       <c r="J144" t="n">
-        <v>12.8934</v>
+        <v>12.0484</v>
       </c>
     </row>
     <row r="145">
@@ -9989,10 +9989,10 @@
         <v>0.9</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.388</v>
+        <v>-0.3481</v>
       </c>
       <c r="J145" t="n">
-        <v>-10.088</v>
+        <v>-9.050599999999999</v>
       </c>
     </row>
     <row r="146">
@@ -10029,10 +10029,10 @@
         <v>0.86</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.4904</v>
+        <v>-0.4519</v>
       </c>
       <c r="J146" t="n">
-        <v>-12.7504</v>
+        <v>-11.7494</v>
       </c>
     </row>
     <row r="147">
@@ -10069,10 +10069,10 @@
         <v>1.09</v>
       </c>
       <c r="I147" t="n">
-        <v>0.281</v>
+        <v>0.2364</v>
       </c>
       <c r="J147" t="n">
-        <v>7.306</v>
+        <v>6.1464</v>
       </c>
     </row>
     <row r="148">
@@ -10109,10 +10109,10 @@
         <v>1.04</v>
       </c>
       <c r="I148" t="n">
-        <v>0.1668</v>
+        <v>0.1331</v>
       </c>
       <c r="J148" t="n">
-        <v>4.3368</v>
+        <v>3.4606</v>
       </c>
     </row>
     <row r="149">
@@ -10149,10 +10149,10 @@
         <v>0.8</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.2353</v>
+        <v>-0.2173</v>
       </c>
       <c r="J149" t="n">
-        <v>-6.1178</v>
+        <v>-5.6498</v>
       </c>
     </row>
     <row r="150">
@@ -10189,10 +10189,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.3385</v>
+        <v>-0.3228</v>
       </c>
       <c r="J150" t="n">
-        <v>-8.801</v>
+        <v>-8.392799999999999</v>
       </c>
     </row>
     <row r="151">
@@ -10229,10 +10229,10 @@
         <v>0.46</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.5416</v>
+        <v>-0.5467</v>
       </c>
       <c r="J151" t="n">
-        <v>-14.0816</v>
+        <v>-14.2142</v>
       </c>
     </row>
     <row r="152">
@@ -10269,10 +10269,10 @@
         <v>0.99</v>
       </c>
       <c r="I152" t="n">
-        <v>-0.0016</v>
+        <v>0.0052</v>
       </c>
       <c r="J152" t="n">
-        <v>-0.04</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="153">
@@ -10309,10 +10309,10 @@
         <v>0.83</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.2048</v>
+        <v>-0.188</v>
       </c>
       <c r="J153" t="n">
-        <v>-5.12</v>
+        <v>-4.7</v>
       </c>
     </row>
     <row r="154">
@@ -10349,10 +10349,10 @@
         <v>0.73</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.2994</v>
+        <v>-0.2824</v>
       </c>
       <c r="J154" t="n">
-        <v>-7.485</v>
+        <v>-7.06</v>
       </c>
     </row>
     <row r="155">
@@ -10389,10 +10389,10 @@
         <v>0.72</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.3087</v>
+        <v>-0.292</v>
       </c>
       <c r="J155" t="n">
-        <v>-7.7175</v>
+        <v>-7.3</v>
       </c>
     </row>
     <row r="156">
@@ -10429,10 +10429,10 @@
         <v>0.71</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.3179</v>
+        <v>-0.3015</v>
       </c>
       <c r="J156" t="n">
-        <v>-7.9475</v>
+        <v>-7.5375</v>
       </c>
     </row>
     <row r="157">
@@ -10469,10 +10469,10 @@
         <v>1.65</v>
       </c>
       <c r="I157" t="n">
-        <v>1.2776</v>
+        <v>1.2958</v>
       </c>
       <c r="J157" t="n">
-        <v>31.94</v>
+        <v>32.395</v>
       </c>
     </row>
     <row r="158">
@@ -10509,10 +10509,10 @@
         <v>1.63</v>
       </c>
       <c r="I158" t="n">
-        <v>1.252</v>
+        <v>1.269</v>
       </c>
       <c r="J158" t="n">
-        <v>31.3</v>
+        <v>31.725</v>
       </c>
     </row>
     <row r="159">
@@ -10549,10 +10549,10 @@
         <v>1.21</v>
       </c>
       <c r="I159" t="n">
-        <v>0.5508999999999999</v>
+        <v>0.522</v>
       </c>
       <c r="J159" t="n">
-        <v>13.7725</v>
+        <v>13.05</v>
       </c>
     </row>
     <row r="160">
@@ -10589,10 +10589,10 @@
         <v>1.11</v>
       </c>
       <c r="I160" t="n">
-        <v>0.316</v>
+        <v>0.2842</v>
       </c>
       <c r="J160" t="n">
-        <v>7.9</v>
+        <v>7.105</v>
       </c>
     </row>
     <row r="161">
@@ -10629,10 +10629,10 @@
         <v>1.02</v>
       </c>
       <c r="I161" t="n">
-        <v>0.0469</v>
+        <v>0.0297</v>
       </c>
       <c r="J161" t="n">
-        <v>1.1725</v>
+        <v>0.7425</v>
       </c>
     </row>
     <row r="162">
@@ -10669,10 +10669,10 @@
         <v>1.7</v>
       </c>
       <c r="I162" t="n">
-        <v>0.8142</v>
+        <v>0.7435</v>
       </c>
       <c r="J162" t="n">
-        <v>20.355</v>
+        <v>18.5875</v>
       </c>
     </row>
     <row r="163">
@@ -10709,10 +10709,10 @@
         <v>1.42</v>
       </c>
       <c r="I163" t="n">
-        <v>0.5364</v>
+        <v>0.4675</v>
       </c>
       <c r="J163" t="n">
-        <v>13.41</v>
+        <v>11.6875</v>
       </c>
     </row>
     <row r="164">
@@ -10749,10 +10749,10 @@
         <v>1.36</v>
       </c>
       <c r="I164" t="n">
-        <v>0.4734</v>
+        <v>0.4076</v>
       </c>
       <c r="J164" t="n">
-        <v>11.835</v>
+        <v>10.19</v>
       </c>
     </row>
     <row r="165">
@@ -10789,10 +10789,10 @@
         <v>0.92</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.1433</v>
+        <v>-0.1248</v>
       </c>
       <c r="J165" t="n">
-        <v>-3.5825</v>
+        <v>-3.12</v>
       </c>
     </row>
     <row r="166">
@@ -10829,10 +10829,10 @@
         <v>0.83</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.2419</v>
+        <v>-0.2237</v>
       </c>
       <c r="J166" t="n">
-        <v>-6.0475</v>
+        <v>-5.5925</v>
       </c>
     </row>
     <row r="167">
@@ -10869,10 +10869,10 @@
         <v>1.31</v>
       </c>
       <c r="I167" t="n">
-        <v>0.5053</v>
+        <v>0.5204</v>
       </c>
       <c r="J167" t="n">
-        <v>12.6325</v>
+        <v>13.01</v>
       </c>
     </row>
     <row r="168">
@@ -10909,10 +10909,10 @@
         <v>0.95</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.0796</v>
+        <v>-0.0665</v>
       </c>
       <c r="J168" t="n">
-        <v>-1.99</v>
+        <v>-1.6625</v>
       </c>
     </row>
     <row r="169">
@@ -10949,10 +10949,10 @@
         <v>0.82</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.2234</v>
+        <v>-0.2035</v>
       </c>
       <c r="J169" t="n">
-        <v>-5.585</v>
+        <v>-5.0875</v>
       </c>
     </row>
     <row r="170">
@@ -10989,10 +10989,10 @@
         <v>0.75</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.2918</v>
+        <v>-0.2734</v>
       </c>
       <c r="J170" t="n">
-        <v>-7.295</v>
+        <v>-6.835</v>
       </c>
     </row>
     <row r="171">
@@ -11029,10 +11029,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.3478</v>
+        <v>-0.3325</v>
       </c>
       <c r="J171" t="n">
-        <v>-8.695</v>
+        <v>-8.3125</v>
       </c>
     </row>
     <row r="172">
@@ -11069,10 +11069,10 @@
         <v>0.97</v>
       </c>
       <c r="I172" t="n">
-        <v>-0.0212</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="J172" t="n">
-        <v>-0.4876</v>
+        <v>-0.2208</v>
       </c>
     </row>
     <row r="173">
@@ -11109,10 +11109,10 @@
         <v>0.85</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.1736</v>
+        <v>-0.158</v>
       </c>
       <c r="J173" t="n">
-        <v>-3.9928</v>
+        <v>-3.634</v>
       </c>
     </row>
     <row r="174">
@@ -11149,10 +11149,10 @@
         <v>0.74</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.2841</v>
+        <v>-0.2692</v>
       </c>
       <c r="J174" t="n">
-        <v>-6.5343</v>
+        <v>-6.1916</v>
       </c>
     </row>
     <row r="175">
@@ -11189,10 +11189,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.3284</v>
+        <v>-0.3139</v>
       </c>
       <c r="J175" t="n">
-        <v>-7.5532</v>
+        <v>-7.2197</v>
       </c>
     </row>
     <row r="176">
@@ -11229,10 +11229,10 @@
         <v>0.37</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.6094000000000001</v>
+        <v>-0.6242</v>
       </c>
       <c r="J176" t="n">
-        <v>-14.0162</v>
+        <v>-14.3566</v>
       </c>
     </row>
     <row r="177">
@@ -11269,10 +11269,10 @@
         <v>1.65</v>
       </c>
       <c r="I177" t="n">
-        <v>1.2682</v>
+        <v>1.2864</v>
       </c>
       <c r="J177" t="n">
-        <v>29.1686</v>
+        <v>29.5872</v>
       </c>
     </row>
     <row r="178">
@@ -11309,10 +11309,10 @@
         <v>1.53</v>
       </c>
       <c r="I178" t="n">
-        <v>1.1138</v>
+        <v>1.1279</v>
       </c>
       <c r="J178" t="n">
-        <v>25.6174</v>
+        <v>25.9417</v>
       </c>
     </row>
     <row r="179">
@@ -11349,10 +11349,10 @@
         <v>1.44</v>
       </c>
       <c r="I179" t="n">
-        <v>0.9866</v>
+        <v>0.987</v>
       </c>
       <c r="J179" t="n">
-        <v>22.6918</v>
+        <v>22.701</v>
       </c>
     </row>
     <row r="180">
@@ -11389,10 +11389,10 @@
         <v>1.27</v>
       </c>
       <c r="I180" t="n">
-        <v>0.6701</v>
+        <v>0.6473</v>
       </c>
       <c r="J180" t="n">
-        <v>15.4123</v>
+        <v>14.8879</v>
       </c>
     </row>
     <row r="181">
@@ -11429,10 +11429,10 @@
         <v>0.99</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.1222</v>
+        <v>-0.1042</v>
       </c>
       <c r="J181" t="n">
-        <v>-2.8106</v>
+        <v>-2.3966</v>
       </c>
     </row>
     <row r="182">
@@ -11469,10 +11469,10 @@
         <v>1.37</v>
       </c>
       <c r="I182" t="n">
-        <v>0.496</v>
+        <v>0.4278</v>
       </c>
       <c r="J182" t="n">
-        <v>14.384</v>
+        <v>12.4062</v>
       </c>
     </row>
     <row r="183">
@@ -11509,10 +11509,10 @@
         <v>1.34</v>
       </c>
       <c r="I183" t="n">
-        <v>0.4632</v>
+        <v>0.3966</v>
       </c>
       <c r="J183" t="n">
-        <v>13.4328</v>
+        <v>11.5014</v>
       </c>
     </row>
     <row r="184">
@@ -11549,10 +11549,10 @@
         <v>1.32</v>
       </c>
       <c r="I184" t="n">
-        <v>0.441</v>
+        <v>0.3756</v>
       </c>
       <c r="J184" t="n">
-        <v>12.789</v>
+        <v>10.8924</v>
       </c>
     </row>
     <row r="185">
@@ -11589,10 +11589,10 @@
         <v>1.23</v>
       </c>
       <c r="I185" t="n">
-        <v>0.3381</v>
+        <v>0.2805</v>
       </c>
       <c r="J185" t="n">
-        <v>9.8049</v>
+        <v>8.134499999999999</v>
       </c>
     </row>
     <row r="186">
@@ -11629,10 +11629,10 @@
         <v>0.5</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.5326</v>
+        <v>-0.541</v>
       </c>
       <c r="J186" t="n">
-        <v>-15.4454</v>
+        <v>-15.689</v>
       </c>
     </row>
     <row r="187">
@@ -11669,10 +11669,10 @@
         <v>1.21</v>
       </c>
       <c r="I187" t="n">
-        <v>0.3683</v>
+        <v>0.3633</v>
       </c>
       <c r="J187" t="n">
-        <v>10.6807</v>
+        <v>10.5357</v>
       </c>
     </row>
     <row r="188">
@@ -11709,10 +11709,10 @@
         <v>1.2</v>
       </c>
       <c r="I188" t="n">
-        <v>0.3547</v>
+        <v>0.3483</v>
       </c>
       <c r="J188" t="n">
-        <v>10.2863</v>
+        <v>10.1007</v>
       </c>
     </row>
     <row r="189">
@@ -11749,10 +11749,10 @@
         <v>0.9</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.141</v>
+        <v>-0.1227</v>
       </c>
       <c r="J189" t="n">
-        <v>-4.089</v>
+        <v>-3.5583</v>
       </c>
     </row>
     <row r="190">
@@ -11789,10 +11789,10 @@
         <v>0.68</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.3593</v>
+        <v>-0.3449</v>
       </c>
       <c r="J190" t="n">
-        <v>-10.4197</v>
+        <v>-10.0021</v>
       </c>
     </row>
     <row r="191">
@@ -11829,10 +11829,10 @@
         <v>0.65</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.3865</v>
+        <v>-0.3744</v>
       </c>
       <c r="J191" t="n">
-        <v>-11.2085</v>
+        <v>-10.8576</v>
       </c>
     </row>
     <row r="192">
@@ -11869,10 +11869,10 @@
         <v>1.19</v>
       </c>
       <c r="I192" t="n">
-        <v>0.4325</v>
+        <v>0.3759</v>
       </c>
       <c r="J192" t="n">
-        <v>11.6775</v>
+        <v>10.1493</v>
       </c>
     </row>
     <row r="193">
@@ -11909,10 +11909,10 @@
         <v>1.09</v>
       </c>
       <c r="I193" t="n">
-        <v>0.2452</v>
+        <v>0.199</v>
       </c>
       <c r="J193" t="n">
-        <v>6.6204</v>
+        <v>5.373</v>
       </c>
     </row>
     <row r="194">
@@ -11949,10 +11949,10 @@
         <v>0.88</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.1639</v>
+        <v>-0.1444</v>
       </c>
       <c r="J194" t="n">
-        <v>-4.4253</v>
+        <v>-3.8988</v>
       </c>
     </row>
     <row r="195">
@@ -11989,10 +11989,10 @@
         <v>0.85</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.1959</v>
+        <v>-0.1757</v>
       </c>
       <c r="J195" t="n">
-        <v>-5.2893</v>
+        <v>-4.7439</v>
       </c>
     </row>
     <row r="196">
@@ -12029,10 +12029,10 @@
         <v>0.68</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.3603</v>
+        <v>-0.346</v>
       </c>
       <c r="J196" t="n">
-        <v>-9.7281</v>
+        <v>-9.342000000000001</v>
       </c>
     </row>
     <row r="197">
@@ -12069,10 +12069,10 @@
         <v>1.37</v>
       </c>
       <c r="I197" t="n">
-        <v>0.9067</v>
+        <v>0.8893</v>
       </c>
       <c r="J197" t="n">
-        <v>24.4809</v>
+        <v>24.0111</v>
       </c>
     </row>
     <row r="198">
@@ -12109,10 +12109,10 @@
         <v>1.34</v>
       </c>
       <c r="I198" t="n">
-        <v>0.8469</v>
+        <v>0.8243</v>
       </c>
       <c r="J198" t="n">
-        <v>22.8663</v>
+        <v>22.2561</v>
       </c>
     </row>
     <row r="199">
@@ -12149,10 +12149,10 @@
         <v>1.21</v>
       </c>
       <c r="I199" t="n">
-        <v>0.5748</v>
+        <v>0.5381</v>
       </c>
       <c r="J199" t="n">
-        <v>15.5196</v>
+        <v>14.5287</v>
       </c>
     </row>
     <row r="200">
@@ -12189,10 +12189,10 @@
         <v>1.08</v>
       </c>
       <c r="I200" t="n">
-        <v>0.2661</v>
+        <v>0.2335</v>
       </c>
       <c r="J200" t="n">
-        <v>7.1847</v>
+        <v>6.3045</v>
       </c>
     </row>
     <row r="201">
@@ -12229,10 +12229,10 @@
         <v>0.71</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.8143</v>
+        <v>-0.7937</v>
       </c>
       <c r="J201" t="n">
-        <v>-21.9861</v>
+        <v>-21.4299</v>
       </c>
     </row>
     <row r="202">
@@ -12269,10 +12269,10 @@
         <v>0.96</v>
       </c>
       <c r="I202" t="n">
-        <v>-0.0624</v>
+        <v>-0.0513</v>
       </c>
       <c r="J202" t="n">
-        <v>-1.6224</v>
+        <v>-1.3338</v>
       </c>
     </row>
     <row r="203">
@@ -12309,10 +12309,10 @@
         <v>0.93</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.1021</v>
+        <v>-0.0877</v>
       </c>
       <c r="J203" t="n">
-        <v>-2.6546</v>
+        <v>-2.2802</v>
       </c>
     </row>
     <row r="204">
@@ -12349,10 +12349,10 @@
         <v>0.91</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.1261</v>
+        <v>-0.1101</v>
       </c>
       <c r="J204" t="n">
-        <v>-3.2786</v>
+        <v>-2.8626</v>
       </c>
     </row>
     <row r="205">
@@ -12389,10 +12389,10 @@
         <v>0.79</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.25</v>
+        <v>-0.2308</v>
       </c>
       <c r="J205" t="n">
-        <v>-6.5</v>
+        <v>-6.0008</v>
       </c>
     </row>
     <row r="206">
@@ -12429,10 +12429,10 @@
         <v>0.77</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.2694</v>
+        <v>-0.2505</v>
       </c>
       <c r="J206" t="n">
-        <v>-7.0044</v>
+        <v>-6.513</v>
       </c>
     </row>
     <row r="207">
@@ -12469,10 +12469,10 @@
         <v>1.75</v>
       </c>
       <c r="I207" t="n">
-        <v>1.4175</v>
+        <v>1.4445</v>
       </c>
       <c r="J207" t="n">
-        <v>36.855</v>
+        <v>37.557</v>
       </c>
     </row>
     <row r="208">
@@ -12509,10 +12509,10 @@
         <v>1.72</v>
       </c>
       <c r="I208" t="n">
-        <v>1.3793</v>
+        <v>1.4036</v>
       </c>
       <c r="J208" t="n">
-        <v>35.8618</v>
+        <v>36.4936</v>
       </c>
     </row>
     <row r="209">
@@ -12549,10 +12549,10 @@
         <v>1.05</v>
       </c>
       <c r="I209" t="n">
-        <v>0.158</v>
+        <v>0.132</v>
       </c>
       <c r="J209" t="n">
-        <v>4.108</v>
+        <v>3.432</v>
       </c>
     </row>
     <row r="210">
@@ -12589,10 +12589,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.2794</v>
+        <v>-0.2425</v>
       </c>
       <c r="J210" t="n">
-        <v>-7.2644</v>
+        <v>-6.305</v>
       </c>
     </row>
     <row r="211">
@@ -12629,10 +12629,10 @@
         <v>0.88</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.4437</v>
+        <v>-0.4048</v>
       </c>
       <c r="J211" t="n">
-        <v>-11.5362</v>
+        <v>-10.5248</v>
       </c>
     </row>
     <row r="212">
@@ -12669,10 +12669,10 @@
         <v>1.37</v>
       </c>
       <c r="I212" t="n">
-        <v>0.713</v>
+        <v>0.6582</v>
       </c>
       <c r="J212" t="n">
-        <v>18.538</v>
+        <v>17.1132</v>
       </c>
     </row>
     <row r="213">
@@ -12709,10 +12709,10 @@
         <v>0.93</v>
       </c>
       <c r="I213" t="n">
-        <v>-0.1098</v>
+        <v>-0.0924</v>
       </c>
       <c r="J213" t="n">
-        <v>-2.8548</v>
+        <v>-2.4024</v>
       </c>
     </row>
     <row r="214">
@@ -12749,10 +12749,10 @@
         <v>0.88</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.1674</v>
+        <v>-0.1473</v>
       </c>
       <c r="J214" t="n">
-        <v>-4.3524</v>
+        <v>-3.8298</v>
       </c>
     </row>
     <row r="215">
@@ -12789,10 +12789,10 @@
         <v>0.86</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.1889</v>
+        <v>-0.1685</v>
       </c>
       <c r="J215" t="n">
-        <v>-4.9114</v>
+        <v>-4.381</v>
       </c>
     </row>
     <row r="216">
@@ -12829,10 +12829,10 @@
         <v>0.85</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.1995</v>
+        <v>-0.1789</v>
       </c>
       <c r="J216" t="n">
-        <v>-5.187</v>
+        <v>-4.6514</v>
       </c>
     </row>
     <row r="217">
@@ -12869,10 +12869,10 @@
         <v>1.28</v>
       </c>
       <c r="I217" t="n">
-        <v>0.7236</v>
+        <v>0.6929</v>
       </c>
       <c r="J217" t="n">
-        <v>18.8136</v>
+        <v>18.0154</v>
       </c>
     </row>
     <row r="218">
@@ -12909,10 +12909,10 @@
         <v>1.19</v>
       </c>
       <c r="I218" t="n">
-        <v>0.5303</v>
+        <v>0.493</v>
       </c>
       <c r="J218" t="n">
-        <v>13.7878</v>
+        <v>12.818</v>
       </c>
     </row>
     <row r="219">
@@ -12949,10 +12949,10 @@
         <v>1.19</v>
       </c>
       <c r="I219" t="n">
-        <v>0.5303</v>
+        <v>0.493</v>
       </c>
       <c r="J219" t="n">
-        <v>13.7878</v>
+        <v>12.818</v>
       </c>
     </row>
     <row r="220">
@@ -12989,10 +12989,10 @@
         <v>1.07</v>
       </c>
       <c r="I220" t="n">
-        <v>0.238</v>
+        <v>0.2069</v>
       </c>
       <c r="J220" t="n">
-        <v>6.188</v>
+        <v>5.3794</v>
       </c>
     </row>
     <row r="221">
@@ -13029,10 +13029,10 @@
         <v>0.99</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.0834</v>
+        <v>-0.0626</v>
       </c>
       <c r="J221" t="n">
-        <v>-2.1684</v>
+        <v>-1.6276</v>
       </c>
     </row>
     <row r="222">
@@ -13069,10 +13069,10 @@
         <v>0.89</v>
       </c>
       <c r="I222" t="n">
-        <v>-0.1138</v>
+        <v>-0.096</v>
       </c>
       <c r="J222" t="n">
-        <v>-2.5036</v>
+        <v>-2.112</v>
       </c>
     </row>
     <row r="223">
@@ -13109,10 +13109,10 @@
         <v>0.78</v>
       </c>
       <c r="I223" t="n">
-        <v>-0.236</v>
+        <v>-0.2216</v>
       </c>
       <c r="J223" t="n">
-        <v>-5.192</v>
+        <v>-4.8752</v>
       </c>
     </row>
     <row r="224">
@@ -13149,10 +13149,10 @@
         <v>0.65</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.3573</v>
+        <v>-0.3458</v>
       </c>
       <c r="J224" t="n">
-        <v>-7.8606</v>
+        <v>-7.6076</v>
       </c>
     </row>
     <row r="225">
@@ -13189,10 +13189,10 @@
         <v>0.57</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.4274</v>
+        <v>-0.4188</v>
       </c>
       <c r="J225" t="n">
-        <v>-9.402799999999999</v>
+        <v>-9.2136</v>
       </c>
     </row>
     <row r="226">
@@ -13229,10 +13229,10 @@
         <v>0.42</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.5591</v>
+        <v>-0.5649</v>
       </c>
       <c r="J226" t="n">
-        <v>-12.3002</v>
+        <v>-12.4278</v>
       </c>
     </row>
     <row r="227">
@@ -13269,10 +13269,10 @@
         <v>1.56</v>
       </c>
       <c r="I227" t="n">
-        <v>1.1435</v>
+        <v>1.16</v>
       </c>
       <c r="J227" t="n">
-        <v>25.157</v>
+        <v>25.52</v>
       </c>
     </row>
     <row r="228">
@@ -13309,10 +13309,10 @@
         <v>1.5</v>
       </c>
       <c r="I228" t="n">
-        <v>1.0662</v>
+        <v>1.0799</v>
       </c>
       <c r="J228" t="n">
-        <v>23.4564</v>
+        <v>23.7578</v>
       </c>
     </row>
     <row r="229">
@@ -13349,10 +13349,10 @@
         <v>1.5</v>
       </c>
       <c r="I229" t="n">
-        <v>1.0662</v>
+        <v>1.0799</v>
       </c>
       <c r="J229" t="n">
-        <v>23.4564</v>
+        <v>23.7578</v>
       </c>
     </row>
     <row r="230">
@@ -13389,10 +13389,10 @@
         <v>1.49</v>
       </c>
       <c r="I230" t="n">
-        <v>1.0528</v>
+        <v>1.0652</v>
       </c>
       <c r="J230" t="n">
-        <v>23.1616</v>
+        <v>23.4344</v>
       </c>
     </row>
     <row r="231">
@@ -13429,10 +13429,10 @@
         <v>1.19</v>
       </c>
       <c r="I231" t="n">
-        <v>0.4882</v>
+        <v>0.4588</v>
       </c>
       <c r="J231" t="n">
-        <v>10.7404</v>
+        <v>10.0936</v>
       </c>
     </row>
     <row r="232">
@@ -13469,10 +13469,10 @@
         <v>1.38</v>
       </c>
       <c r="I232" t="n">
-        <v>0.7734</v>
+        <v>0.7311</v>
       </c>
       <c r="J232" t="n">
-        <v>16.2414</v>
+        <v>15.3531</v>
       </c>
     </row>
     <row r="233">
@@ -13509,10 +13509,10 @@
         <v>1.06</v>
       </c>
       <c r="I233" t="n">
-        <v>0.1992</v>
+        <v>0.159</v>
       </c>
       <c r="J233" t="n">
-        <v>4.1832</v>
+        <v>3.339</v>
       </c>
     </row>
     <row r="234">
@@ -13549,10 +13549,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.3439</v>
+        <v>-0.3283</v>
       </c>
       <c r="J234" t="n">
-        <v>-7.2219</v>
+        <v>-6.8943</v>
       </c>
     </row>
     <row r="235">
@@ -13589,10 +13589,10 @@
         <v>0.63</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.3983</v>
+        <v>-0.3868</v>
       </c>
       <c r="J235" t="n">
-        <v>-8.3643</v>
+        <v>-8.1228</v>
       </c>
     </row>
     <row r="236">
@@ -13629,10 +13629,10 @@
         <v>0.57</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.4514</v>
+        <v>-0.4453</v>
       </c>
       <c r="J236" t="n">
-        <v>-9.4794</v>
+        <v>-9.3513</v>
       </c>
     </row>
     <row r="237">
@@ -13669,10 +13669,10 @@
         <v>1.68</v>
       </c>
       <c r="I237" t="n">
-        <v>1.3139</v>
+        <v>1.3339</v>
       </c>
       <c r="J237" t="n">
-        <v>27.5919</v>
+        <v>28.0119</v>
       </c>
     </row>
     <row r="238">
@@ -13709,10 +13709,10 @@
         <v>1.38</v>
       </c>
       <c r="I238" t="n">
-        <v>0.8868</v>
+        <v>0.8741</v>
       </c>
       <c r="J238" t="n">
-        <v>18.6228</v>
+        <v>18.3561</v>
       </c>
     </row>
     <row r="239">
@@ -13749,10 +13749,10 @@
         <v>1.36</v>
       </c>
       <c r="I239" t="n">
-        <v>0.8494</v>
+        <v>0.8343</v>
       </c>
       <c r="J239" t="n">
-        <v>17.8374</v>
+        <v>17.5203</v>
       </c>
     </row>
     <row r="240">
@@ -13789,10 +13789,10 @@
         <v>1.18</v>
       </c>
       <c r="I240" t="n">
-        <v>0.4827</v>
+        <v>0.4522</v>
       </c>
       <c r="J240" t="n">
-        <v>10.1367</v>
+        <v>9.4962</v>
       </c>
     </row>
     <row r="241">
@@ -13829,10 +13829,10 @@
         <v>1.07</v>
       </c>
       <c r="I241" t="n">
-        <v>0.2066</v>
+        <v>0.1771</v>
       </c>
       <c r="J241" t="n">
-        <v>4.3386</v>
+        <v>3.7191</v>
       </c>
     </row>
     <row r="242">
@@ -13869,10 +13869,10 @@
         <v>1.5</v>
       </c>
       <c r="I242" t="n">
-        <v>0.6214</v>
+        <v>0.5499000000000001</v>
       </c>
       <c r="J242" t="n">
-        <v>17.3992</v>
+        <v>15.3972</v>
       </c>
     </row>
     <row r="243">
@@ -13909,10 +13909,10 @@
         <v>1.27</v>
       </c>
       <c r="I243" t="n">
-        <v>0.3774</v>
+        <v>0.318</v>
       </c>
       <c r="J243" t="n">
-        <v>10.5672</v>
+        <v>8.904</v>
       </c>
     </row>
     <row r="244">
@@ -13949,10 +13949,10 @@
         <v>1.17</v>
       </c>
       <c r="I244" t="n">
-        <v>0.2613</v>
+        <v>0.2137</v>
       </c>
       <c r="J244" t="n">
-        <v>7.3164</v>
+        <v>5.9836</v>
       </c>
     </row>
     <row r="245">
@@ -13989,10 +13989,10 @@
         <v>1.11</v>
       </c>
       <c r="I245" t="n">
-        <v>0.1822</v>
+        <v>0.1445</v>
       </c>
       <c r="J245" t="n">
-        <v>5.1016</v>
+        <v>4.046</v>
       </c>
     </row>
     <row r="246">
@@ -14029,10 +14029,10 @@
         <v>1.07</v>
       </c>
       <c r="I246" t="n">
-        <v>0.1232</v>
+        <v>0.09420000000000001</v>
       </c>
       <c r="J246" t="n">
-        <v>3.4496</v>
+        <v>2.6376</v>
       </c>
     </row>
     <row r="247">
@@ -14069,10 +14069,10 @@
         <v>1.33</v>
       </c>
       <c r="I247" t="n">
-        <v>0.5256999999999999</v>
+        <v>0.5432</v>
       </c>
       <c r="J247" t="n">
-        <v>14.7196</v>
+        <v>15.2096</v>
       </c>
     </row>
     <row r="248">
@@ -14109,10 +14109,10 @@
         <v>1.08</v>
       </c>
       <c r="I248" t="n">
-        <v>0.1791</v>
+        <v>0.162</v>
       </c>
       <c r="J248" t="n">
-        <v>5.0148</v>
+        <v>4.536</v>
       </c>
     </row>
     <row r="249">
@@ -14149,10 +14149,10 @@
         <v>0.92</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.1179</v>
+        <v>-0.1012</v>
       </c>
       <c r="J249" t="n">
-        <v>-3.3012</v>
+        <v>-2.8336</v>
       </c>
     </row>
     <row r="250">
@@ -14189,10 +14189,10 @@
         <v>0.7</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.3402</v>
+        <v>-0.3244</v>
       </c>
       <c r="J250" t="n">
-        <v>-9.525600000000001</v>
+        <v>-9.0832</v>
       </c>
     </row>
     <row r="251">
@@ -14229,10 +14229,10 @@
         <v>0.57</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.4565</v>
+        <v>-0.4516</v>
       </c>
       <c r="J251" t="n">
-        <v>-12.782</v>
+        <v>-12.6448</v>
       </c>
     </row>
     <row r="252">
@@ -14269,10 +14269,10 @@
         <v>1.27</v>
       </c>
       <c r="I252" t="n">
-        <v>0.5754</v>
+        <v>0.5194</v>
       </c>
       <c r="J252" t="n">
-        <v>14.385</v>
+        <v>12.985</v>
       </c>
     </row>
     <row r="253">
@@ -14309,10 +14309,10 @@
         <v>1.19</v>
       </c>
       <c r="I253" t="n">
-        <v>0.439</v>
+        <v>0.383</v>
       </c>
       <c r="J253" t="n">
-        <v>10.975</v>
+        <v>9.574999999999999</v>
       </c>
     </row>
     <row r="254">
@@ -14349,10 +14349,10 @@
         <v>0.98</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.0369</v>
+        <v>-0.0288</v>
       </c>
       <c r="J254" t="n">
-        <v>-0.9225</v>
+        <v>-0.72</v>
       </c>
     </row>
     <row r="255">
@@ -14389,10 +14389,10 @@
         <v>0.68</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.3582</v>
+        <v>-0.3436</v>
       </c>
       <c r="J255" t="n">
-        <v>-8.955</v>
+        <v>-8.59</v>
       </c>
     </row>
     <row r="256">
@@ -14429,10 +14429,10 @@
         <v>0.46</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.5503</v>
+        <v>-0.5582</v>
       </c>
       <c r="J256" t="n">
-        <v>-13.7575</v>
+        <v>-13.955</v>
       </c>
     </row>
     <row r="257">
@@ -14469,10 +14469,10 @@
         <v>1.54</v>
       </c>
       <c r="I257" t="n">
-        <v>1.1631</v>
+        <v>1.1769</v>
       </c>
       <c r="J257" t="n">
-        <v>29.0775</v>
+        <v>29.4225</v>
       </c>
     </row>
     <row r="258">
@@ -14509,10 +14509,10 @@
         <v>1.33</v>
       </c>
       <c r="I258" t="n">
-        <v>0.8171</v>
+        <v>0.7932</v>
       </c>
       <c r="J258" t="n">
-        <v>20.4275</v>
+        <v>19.83</v>
       </c>
     </row>
     <row r="259">
@@ -14549,10 +14549,10 @@
         <v>1.05</v>
       </c>
       <c r="I259" t="n">
-        <v>0.1726</v>
+        <v>0.1462</v>
       </c>
       <c r="J259" t="n">
-        <v>4.315</v>
+        <v>3.655</v>
       </c>
     </row>
     <row r="260">
@@ -14589,10 +14589,10 @@
         <v>1.03</v>
       </c>
       <c r="I260" t="n">
-        <v>0.1073</v>
+        <v>0.0867</v>
       </c>
       <c r="J260" t="n">
-        <v>2.6825</v>
+        <v>2.1675</v>
       </c>
     </row>
     <row r="261">
@@ -14629,10 +14629,10 @@
         <v>0.96</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.2022</v>
+        <v>-0.1676</v>
       </c>
       <c r="J261" t="n">
-        <v>-5.055</v>
+        <v>-4.19</v>
       </c>
     </row>
     <row r="262">
@@ -14669,10 +14669,10 @@
         <v>1.7</v>
       </c>
       <c r="I262" t="n">
-        <v>1.3179</v>
+        <v>1.3392</v>
       </c>
       <c r="J262" t="n">
-        <v>26.358</v>
+        <v>26.784</v>
       </c>
     </row>
     <row r="263">
@@ -14709,10 +14709,10 @@
         <v>1.59</v>
       </c>
       <c r="I263" t="n">
-        <v>1.1806</v>
+        <v>1.1979</v>
       </c>
       <c r="J263" t="n">
-        <v>23.612</v>
+        <v>23.958</v>
       </c>
     </row>
     <row r="264">
@@ -14749,10 +14749,10 @@
         <v>1.55</v>
       </c>
       <c r="I264" t="n">
-        <v>1.1298</v>
+        <v>1.1464</v>
       </c>
       <c r="J264" t="n">
-        <v>22.596</v>
+        <v>22.928</v>
       </c>
     </row>
     <row r="265">
@@ -14789,10 +14789,10 @@
         <v>1.23</v>
       </c>
       <c r="I265" t="n">
-        <v>0.5748</v>
+        <v>0.549</v>
       </c>
       <c r="J265" t="n">
-        <v>11.496</v>
+        <v>10.98</v>
       </c>
     </row>
     <row r="266">
@@ -14829,10 +14829,10 @@
         <v>1.21</v>
       </c>
       <c r="I266" t="n">
-        <v>0.5314</v>
+        <v>0.5037</v>
       </c>
       <c r="J266" t="n">
-        <v>10.628</v>
+        <v>10.074</v>
       </c>
     </row>
     <row r="267">
@@ -14869,10 +14869,10 @@
         <v>0.79</v>
       </c>
       <c r="I267" t="n">
-        <v>-0.2209</v>
+        <v>-0.2059</v>
       </c>
       <c r="J267" t="n">
-        <v>-4.418</v>
+        <v>-4.118</v>
       </c>
     </row>
     <row r="268">
@@ -14909,10 +14909,10 @@
         <v>0.75</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.262</v>
+        <v>-0.2486</v>
       </c>
       <c r="J268" t="n">
-        <v>-5.24</v>
+        <v>-4.972</v>
       </c>
     </row>
     <row r="269">
@@ -14949,10 +14949,10 @@
         <v>0.63</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.3723</v>
+        <v>-0.362</v>
       </c>
       <c r="J269" t="n">
-        <v>-7.446</v>
+        <v>-7.24</v>
       </c>
     </row>
     <row r="270">
@@ -14989,10 +14989,10 @@
         <v>0.57</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.4244</v>
+        <v>-0.4161</v>
       </c>
       <c r="J270" t="n">
-        <v>-8.488</v>
+        <v>-8.321999999999999</v>
       </c>
     </row>
     <row r="271">
@@ -15029,10 +15029,10 @@
         <v>0.46</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.5211</v>
+        <v>-0.5217000000000001</v>
       </c>
       <c r="J271" t="n">
-        <v>-10.422</v>
+        <v>-10.434</v>
       </c>
     </row>
     <row r="272">
@@ -15069,10 +15069,10 @@
         <v>1.08</v>
       </c>
       <c r="I272" t="n">
-        <v>0.2801</v>
+        <v>0.2404</v>
       </c>
       <c r="J272" t="n">
-        <v>7.0025</v>
+        <v>6.01</v>
       </c>
     </row>
     <row r="273">
@@ -15109,10 +15109,10 @@
         <v>0.75</v>
       </c>
       <c r="I273" t="n">
-        <v>-0.2779</v>
+        <v>-0.2615</v>
       </c>
       <c r="J273" t="n">
-        <v>-6.9475</v>
+        <v>-6.5375</v>
       </c>
     </row>
     <row r="274">
@@ -15149,10 +15149,10 @@
         <v>0.72</v>
       </c>
       <c r="I274" t="n">
-        <v>-0.3053</v>
+        <v>-0.2892</v>
       </c>
       <c r="J274" t="n">
-        <v>-7.6325</v>
+        <v>-7.23</v>
       </c>
     </row>
     <row r="275">
@@ -15189,10 +15189,10 @@
         <v>0.66</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.3599</v>
+        <v>-0.3459</v>
       </c>
       <c r="J275" t="n">
-        <v>-8.9975</v>
+        <v>-8.647500000000001</v>
       </c>
     </row>
     <row r="276">
@@ -15229,10 +15229,10 @@
         <v>0.61</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.4048</v>
+        <v>-0.3937</v>
       </c>
       <c r="J276" t="n">
-        <v>-10.12</v>
+        <v>-9.842499999999999</v>
       </c>
     </row>
     <row r="277">
@@ -15269,10 +15269,10 @@
         <v>1.47</v>
       </c>
       <c r="I277" t="n">
-        <v>1.0582</v>
+        <v>1.0649</v>
       </c>
       <c r="J277" t="n">
-        <v>26.455</v>
+        <v>26.6225</v>
       </c>
     </row>
     <row r="278">
@@ -15309,10 +15309,10 @@
         <v>1.42</v>
       </c>
       <c r="I278" t="n">
-        <v>0.9797</v>
+        <v>0.9736</v>
       </c>
       <c r="J278" t="n">
-        <v>24.4925</v>
+        <v>24.34</v>
       </c>
     </row>
     <row r="279">
@@ -15349,10 +15349,10 @@
         <v>1.21</v>
       </c>
       <c r="I279" t="n">
-        <v>0.5648</v>
+        <v>0.532</v>
       </c>
       <c r="J279" t="n">
-        <v>14.12</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="280">
@@ -15389,10 +15389,10 @@
         <v>1.12</v>
       </c>
       <c r="I280" t="n">
-        <v>0.358</v>
+        <v>0.3247</v>
       </c>
       <c r="J280" t="n">
-        <v>8.949999999999999</v>
+        <v>8.1175</v>
       </c>
     </row>
     <row r="281">
@@ -15429,10 +15429,10 @@
         <v>0.88</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.4358</v>
+        <v>-0.3955</v>
       </c>
       <c r="J281" t="n">
-        <v>-10.895</v>
+        <v>-9.887499999999999</v>
       </c>
     </row>
     <row r="282">
@@ -15469,10 +15469,10 @@
         <v>1.42</v>
       </c>
       <c r="I282" t="n">
-        <v>0.9883999999999999</v>
+        <v>0.9832</v>
       </c>
       <c r="J282" t="n">
-        <v>40.5244</v>
+        <v>40.3112</v>
       </c>
     </row>
     <row r="283">
@@ -15509,10 +15509,10 @@
         <v>1.24</v>
       </c>
       <c r="I283" t="n">
-        <v>0.6323</v>
+        <v>0.5991</v>
       </c>
       <c r="J283" t="n">
-        <v>25.9243</v>
+        <v>24.5631</v>
       </c>
     </row>
     <row r="284">
@@ -15549,10 +15549,10 @@
         <v>1.24</v>
       </c>
       <c r="I284" t="n">
-        <v>0.6323</v>
+        <v>0.5991</v>
       </c>
       <c r="J284" t="n">
-        <v>25.9243</v>
+        <v>24.5631</v>
       </c>
     </row>
     <row r="285">
@@ -15589,10 +15589,10 @@
         <v>1.22</v>
       </c>
       <c r="I285" t="n">
-        <v>0.5899</v>
+        <v>0.5556</v>
       </c>
       <c r="J285" t="n">
-        <v>24.1859</v>
+        <v>22.7796</v>
       </c>
     </row>
     <row r="286">
@@ -15629,10 +15629,10 @@
         <v>0.79</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.6452</v>
+        <v>-0.6121</v>
       </c>
       <c r="J286" t="n">
-        <v>-26.4532</v>
+        <v>-25.0961</v>
       </c>
     </row>
     <row r="287">
@@ -15669,10 +15669,10 @@
         <v>1.07</v>
       </c>
       <c r="I287" t="n">
-        <v>0.2008</v>
+        <v>0.1591</v>
       </c>
       <c r="J287" t="n">
-        <v>8.232799999999999</v>
+        <v>6.5231</v>
       </c>
     </row>
     <row r="288">
@@ -15709,10 +15709,10 @@
         <v>1.02</v>
       </c>
       <c r="I288" t="n">
-        <v>0.0805</v>
+        <v>0.0572</v>
       </c>
       <c r="J288" t="n">
-        <v>3.3005</v>
+        <v>2.3452</v>
       </c>
     </row>
     <row r="289">
@@ -15749,10 +15749,10 @@
         <v>1</v>
       </c>
       <c r="I289" t="n">
-        <v>0.0058</v>
+        <v>0.0033</v>
       </c>
       <c r="J289" t="n">
-        <v>0.2378</v>
+        <v>0.1353</v>
       </c>
     </row>
     <row r="290">
@@ -15789,10 +15789,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.0955</v>
+        <v>-0.0799</v>
       </c>
       <c r="J290" t="n">
-        <v>-3.9155</v>
+        <v>-3.2759</v>
       </c>
     </row>
     <row r="291">
@@ -15829,10 +15829,10 @@
         <v>0.72</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.3246</v>
+        <v>-0.3078</v>
       </c>
       <c r="J291" t="n">
-        <v>-13.3086</v>
+        <v>-12.6198</v>
       </c>
     </row>
     <row r="292">
@@ -15869,10 +15869,10 @@
         <v>0.77</v>
       </c>
       <c r="I292" t="n">
-        <v>-0.2494</v>
+        <v>-0.2352</v>
       </c>
       <c r="J292" t="n">
-        <v>-5.2374</v>
+        <v>-4.9392</v>
       </c>
     </row>
     <row r="293">
@@ -15909,10 +15909,10 @@
         <v>0.73</v>
       </c>
       <c r="I293" t="n">
-        <v>-0.2882</v>
+        <v>-0.2749</v>
       </c>
       <c r="J293" t="n">
-        <v>-6.0522</v>
+        <v>-5.7729</v>
       </c>
     </row>
     <row r="294">
@@ -15949,10 +15949,10 @@
         <v>0.72</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.2976</v>
+        <v>-0.2844</v>
       </c>
       <c r="J294" t="n">
-        <v>-6.2496</v>
+        <v>-5.9724</v>
       </c>
     </row>
     <row r="295">
@@ -15989,10 +15989,10 @@
         <v>0.67</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.3417</v>
+        <v>-0.3292</v>
       </c>
       <c r="J295" t="n">
-        <v>-7.1757</v>
+        <v>-6.9132</v>
       </c>
     </row>
     <row r="296">
@@ -16029,10 +16029,10 @@
         <v>0.51</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.4826</v>
+        <v>-0.4789</v>
       </c>
       <c r="J296" t="n">
-        <v>-10.1346</v>
+        <v>-10.0569</v>
       </c>
     </row>
     <row r="297">
@@ -16069,10 +16069,10 @@
         <v>2.36</v>
       </c>
       <c r="I297" t="n">
-        <v>1.9372</v>
+        <v>1.9818</v>
       </c>
       <c r="J297" t="n">
-        <v>40.6812</v>
+        <v>41.6178</v>
       </c>
     </row>
     <row r="298">
@@ -16109,10 +16109,10 @@
         <v>1.68</v>
       </c>
       <c r="I298" t="n">
-        <v>1.2895</v>
+        <v>1.3103</v>
       </c>
       <c r="J298" t="n">
-        <v>27.0795</v>
+        <v>27.5163</v>
       </c>
     </row>
     <row r="299">
@@ -16149,10 +16149,10 @@
         <v>1.61</v>
       </c>
       <c r="I299" t="n">
-        <v>1.2026</v>
+        <v>1.2211</v>
       </c>
       <c r="J299" t="n">
-        <v>25.2546</v>
+        <v>25.6431</v>
       </c>
     </row>
     <row r="300">
@@ -16189,10 +16189,10 @@
         <v>0.96</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.249</v>
+        <v>-0.2215</v>
       </c>
       <c r="J300" t="n">
-        <v>-5.229</v>
+        <v>-4.6515</v>
       </c>
     </row>
     <row r="301">
@@ -16229,10 +16229,10 @@
         <v>0.8</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.6654</v>
+        <v>-0.6425</v>
       </c>
       <c r="J301" t="n">
-        <v>-13.9734</v>
+        <v>-13.4925</v>
       </c>
     </row>
     <row r="302">
@@ -16269,10 +16269,10 @@
         <v>0.93</v>
       </c>
       <c r="I302" t="n">
-        <v>-0.0465</v>
+        <v>-0.0235</v>
       </c>
       <c r="J302" t="n">
-        <v>-0.8835</v>
+        <v>-0.4465</v>
       </c>
     </row>
     <row r="303">
@@ -16309,10 +16309,10 @@
         <v>0.71</v>
       </c>
       <c r="I303" t="n">
-        <v>-0.2958</v>
+        <v>-0.2842</v>
       </c>
       <c r="J303" t="n">
-        <v>-5.6202</v>
+        <v>-5.3998</v>
       </c>
     </row>
     <row r="304">
@@ -16349,10 +16349,10 @@
         <v>0.61</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.3866</v>
+        <v>-0.3779</v>
       </c>
       <c r="J304" t="n">
-        <v>-7.3454</v>
+        <v>-7.1801</v>
       </c>
     </row>
     <row r="305">
@@ -16389,10 +16389,10 @@
         <v>0.54</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.4467</v>
+        <v>-0.4405</v>
       </c>
       <c r="J305" t="n">
-        <v>-8.487299999999999</v>
+        <v>-8.3695</v>
       </c>
     </row>
     <row r="306">
@@ -16429,10 +16429,10 @@
         <v>0.27</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.6843</v>
+        <v>-0.7114</v>
       </c>
       <c r="J306" t="n">
-        <v>-13.0017</v>
+        <v>-13.5166</v>
       </c>
     </row>
     <row r="307">
@@ -16469,10 +16469,10 @@
         <v>2.09</v>
       </c>
       <c r="I307" t="n">
-        <v>1.7581</v>
+        <v>1.8109</v>
       </c>
       <c r="J307" t="n">
-        <v>33.4039</v>
+        <v>34.4071</v>
       </c>
     </row>
     <row r="308">
@@ -16509,10 +16509,10 @@
         <v>1.96</v>
       </c>
       <c r="I308" t="n">
-        <v>1.6097</v>
+        <v>1.6497</v>
       </c>
       <c r="J308" t="n">
-        <v>30.5843</v>
+        <v>31.3443</v>
       </c>
     </row>
     <row r="309">
@@ -16549,10 +16549,10 @@
         <v>1.47</v>
       </c>
       <c r="I309" t="n">
-        <v>1.0154</v>
+        <v>1.0279</v>
       </c>
       <c r="J309" t="n">
-        <v>19.2926</v>
+        <v>19.5301</v>
       </c>
     </row>
     <row r="310">
@@ -16589,10 +16589,10 @@
         <v>1.22</v>
       </c>
       <c r="I310" t="n">
-        <v>0.5375</v>
+        <v>0.51</v>
       </c>
       <c r="J310" t="n">
-        <v>10.2125</v>
+        <v>9.69</v>
       </c>
     </row>
     <row r="311">
@@ -16629,10 +16629,10 @@
         <v>1.1</v>
       </c>
       <c r="I311" t="n">
-        <v>0.2545</v>
+        <v>0.2192</v>
       </c>
       <c r="J311" t="n">
-        <v>4.8355</v>
+        <v>4.1648</v>
       </c>
     </row>
     <row r="312">
@@ -16669,10 +16669,10 @@
         <v>1.28</v>
       </c>
       <c r="I312" t="n">
-        <v>0.5521</v>
+        <v>0.4923</v>
       </c>
       <c r="J312" t="n">
-        <v>16.0109</v>
+        <v>14.2767</v>
       </c>
     </row>
     <row r="313">
@@ -16709,10 +16709,10 @@
         <v>1.26</v>
       </c>
       <c r="I313" t="n">
-        <v>0.5203</v>
+        <v>0.4608</v>
       </c>
       <c r="J313" t="n">
-        <v>15.0887</v>
+        <v>13.3632</v>
       </c>
     </row>
     <row r="314">
@@ -16749,10 +16749,10 @@
         <v>1.22</v>
       </c>
       <c r="I314" t="n">
-        <v>0.4555</v>
+        <v>0.3974</v>
       </c>
       <c r="J314" t="n">
-        <v>13.2095</v>
+        <v>11.5246</v>
       </c>
     </row>
     <row r="315">
@@ -16789,10 +16789,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.1034</v>
+        <v>-0.0858</v>
       </c>
       <c r="J315" t="n">
-        <v>-2.9986</v>
+        <v>-2.4882</v>
       </c>
     </row>
     <row r="316">
@@ -16829,10 +16829,10 @@
         <v>0.57</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.4673</v>
+        <v>-0.4654</v>
       </c>
       <c r="J316" t="n">
-        <v>-13.5517</v>
+        <v>-13.4966</v>
       </c>
     </row>
     <row r="317">
@@ -16869,10 +16869,10 @@
         <v>1.67</v>
       </c>
       <c r="I317" t="n">
-        <v>1.3634</v>
+        <v>1.3925</v>
       </c>
       <c r="J317" t="n">
-        <v>39.5386</v>
+        <v>40.3825</v>
       </c>
     </row>
     <row r="318">
@@ -16909,10 +16909,10 @@
         <v>1.02</v>
       </c>
       <c r="I318" t="n">
-        <v>0.08550000000000001</v>
+        <v>0.0677</v>
       </c>
       <c r="J318" t="n">
-        <v>2.4795</v>
+        <v>1.9633</v>
       </c>
     </row>
     <row r="319">
@@ -16949,10 +16949,10 @@
         <v>0.99</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.075</v>
+        <v>-0.0549</v>
       </c>
       <c r="J319" t="n">
-        <v>-2.175</v>
+        <v>-1.5921</v>
       </c>
     </row>
     <row r="320">
@@ -16989,10 +16989,10 @@
         <v>0.98</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.1164</v>
+        <v>-0.0897</v>
       </c>
       <c r="J320" t="n">
-        <v>-3.3756</v>
+        <v>-2.6013</v>
       </c>
     </row>
     <row r="321">
@@ -17029,10 +17029,10 @@
         <v>0.83</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.5369</v>
+        <v>-0.4965</v>
       </c>
       <c r="J321" t="n">
-        <v>-15.5701</v>
+        <v>-14.3985</v>
       </c>
     </row>
     <row r="322">
@@ -17069,10 +17069,10 @@
         <v>1.66</v>
       </c>
       <c r="I322" t="n">
-        <v>1.2664</v>
+        <v>1.2862</v>
       </c>
       <c r="J322" t="n">
-        <v>24.0616</v>
+        <v>24.4378</v>
       </c>
     </row>
     <row r="323">
@@ -17109,10 +17109,10 @@
         <v>1.65</v>
       </c>
       <c r="I323" t="n">
-        <v>1.254</v>
+        <v>1.2734</v>
       </c>
       <c r="J323" t="n">
-        <v>23.826</v>
+        <v>24.1946</v>
       </c>
     </row>
     <row r="324">
@@ -17149,10 +17149,10 @@
         <v>1.42</v>
       </c>
       <c r="I324" t="n">
-        <v>0.9451000000000001</v>
+        <v>0.9446</v>
       </c>
       <c r="J324" t="n">
-        <v>17.9569</v>
+        <v>17.9474</v>
       </c>
     </row>
     <row r="325">
@@ -17189,10 +17189,10 @@
         <v>1.35</v>
       </c>
       <c r="I325" t="n">
-        <v>0.8157</v>
+        <v>0.8045</v>
       </c>
       <c r="J325" t="n">
-        <v>15.4983</v>
+        <v>15.2855</v>
       </c>
     </row>
     <row r="326">
@@ -17229,10 +17229,10 @@
         <v>1.27</v>
       </c>
       <c r="I326" t="n">
-        <v>0.6568000000000001</v>
+        <v>0.6354</v>
       </c>
       <c r="J326" t="n">
-        <v>12.4792</v>
+        <v>12.0726</v>
       </c>
     </row>
     <row r="327">
@@ -17269,10 +17269,10 @@
         <v>1.01</v>
       </c>
       <c r="I327" t="n">
-        <v>0.1781</v>
+        <v>0.1798</v>
       </c>
       <c r="J327" t="n">
-        <v>3.3839</v>
+        <v>3.4162</v>
       </c>
     </row>
     <row r="328">
@@ -17309,10 +17309,10 @@
         <v>0.72</v>
       </c>
       <c r="I328" t="n">
-        <v>-0.2864</v>
+        <v>-0.2743</v>
       </c>
       <c r="J328" t="n">
-        <v>-5.4416</v>
+        <v>-5.2117</v>
       </c>
     </row>
     <row r="329">
@@ -17349,10 +17349,10 @@
         <v>0.54</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.447</v>
+        <v>-0.4407</v>
       </c>
       <c r="J329" t="n">
-        <v>-8.493</v>
+        <v>-8.3733</v>
       </c>
     </row>
     <row r="330">
@@ -17429,10 +17429,10 @@
         <v>0.34</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.623</v>
+        <v>-0.6385</v>
       </c>
       <c r="J331" t="n">
-        <v>-11.837</v>
+        <v>-12.1315</v>
       </c>
     </row>
     <row r="332">
@@ -17469,10 +17469,10 @@
         <v>1.37</v>
       </c>
       <c r="I332" t="n">
-        <v>0.6792</v>
+        <v>0.6202</v>
       </c>
       <c r="J332" t="n">
-        <v>40.0728</v>
+        <v>36.5918</v>
       </c>
     </row>
     <row r="333">
@@ -17509,10 +17509,10 @@
         <v>1.22</v>
       </c>
       <c r="I333" t="n">
-        <v>0.4473</v>
+        <v>0.3901</v>
       </c>
       <c r="J333" t="n">
-        <v>26.3907</v>
+        <v>23.0159</v>
       </c>
     </row>
     <row r="334">
@@ -17549,10 +17549,10 @@
         <v>1.07</v>
       </c>
       <c r="I334" t="n">
-        <v>0.1809</v>
+        <v>0.1454</v>
       </c>
       <c r="J334" t="n">
-        <v>10.6731</v>
+        <v>8.5786</v>
       </c>
     </row>
     <row r="335">
@@ -17589,10 +17589,10 @@
         <v>0.92</v>
       </c>
       <c r="I335" t="n">
-        <v>-0.1318</v>
+        <v>-0.1126</v>
       </c>
       <c r="J335" t="n">
-        <v>-7.7762</v>
+        <v>-6.6434</v>
       </c>
     </row>
     <row r="336">
@@ -17629,10 +17629,10 @@
         <v>0.91</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.1437</v>
+        <v>-0.124</v>
       </c>
       <c r="J336" t="n">
-        <v>-8.478300000000001</v>
+        <v>-7.316</v>
       </c>
     </row>
     <row r="337">
@@ -17669,10 +17669,10 @@
         <v>1.32</v>
       </c>
       <c r="I337" t="n">
-        <v>0.8347</v>
+        <v>0.8113</v>
       </c>
       <c r="J337" t="n">
-        <v>49.2473</v>
+        <v>47.8667</v>
       </c>
     </row>
     <row r="338">
@@ -17709,10 +17709,10 @@
         <v>1.15</v>
       </c>
       <c r="I338" t="n">
-        <v>0.457</v>
+        <v>0.4151</v>
       </c>
       <c r="J338" t="n">
-        <v>26.963</v>
+        <v>24.4909</v>
       </c>
     </row>
     <row r="339">
@@ -17749,10 +17749,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I339" t="n">
-        <v>-0.2391</v>
+        <v>-0.2009</v>
       </c>
       <c r="J339" t="n">
-        <v>-14.1069</v>
+        <v>-11.8531</v>
       </c>
     </row>
     <row r="340">
@@ -17789,10 +17789,10 @@
         <v>0.91</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.3242</v>
+        <v>-0.2823</v>
       </c>
       <c r="J340" t="n">
-        <v>-19.1278</v>
+        <v>-16.6557</v>
       </c>
     </row>
     <row r="341">
@@ -17829,10 +17829,10 @@
         <v>0.91</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.3242</v>
+        <v>-0.2823</v>
       </c>
       <c r="J341" t="n">
-        <v>-19.1278</v>
+        <v>-16.6557</v>
       </c>
     </row>
     <row r="342">
@@ -17869,10 +17869,10 @@
         <v>2</v>
       </c>
       <c r="I342" t="n">
-        <v>1.6599</v>
+        <v>1.7039</v>
       </c>
       <c r="J342" t="n">
-        <v>28.2183</v>
+        <v>28.9663</v>
       </c>
     </row>
     <row r="343">
@@ -17909,10 +17909,10 @@
         <v>1.67</v>
       </c>
       <c r="I343" t="n">
-        <v>1.2697</v>
+        <v>1.2914</v>
       </c>
       <c r="J343" t="n">
-        <v>21.5849</v>
+        <v>21.9538</v>
       </c>
     </row>
     <row r="344">
@@ -17949,10 +17949,10 @@
         <v>1.53</v>
       </c>
       <c r="I344" t="n">
-        <v>1.0981</v>
+        <v>1.1171</v>
       </c>
       <c r="J344" t="n">
-        <v>18.6677</v>
+        <v>18.9907</v>
       </c>
     </row>
     <row r="345">
@@ -17989,10 +17989,10 @@
         <v>1.39</v>
       </c>
       <c r="I345" t="n">
-        <v>0.8819</v>
+        <v>0.8778</v>
       </c>
       <c r="J345" t="n">
-        <v>14.9923</v>
+        <v>14.9226</v>
       </c>
     </row>
     <row r="346">
@@ -18029,10 +18029,10 @@
         <v>1.13</v>
       </c>
       <c r="I346" t="n">
-        <v>0.3338</v>
+        <v>0.2995</v>
       </c>
       <c r="J346" t="n">
-        <v>5.6746</v>
+        <v>5.0915</v>
       </c>
     </row>
     <row r="347">
@@ -18069,10 +18069,10 @@
         <v>1.1</v>
       </c>
       <c r="I347" t="n">
-        <v>0.3976</v>
+        <v>0.3791</v>
       </c>
       <c r="J347" t="n">
-        <v>6.7592</v>
+        <v>6.4447</v>
       </c>
     </row>
     <row r="348">
@@ -18109,10 +18109,10 @@
         <v>0.75</v>
       </c>
       <c r="I348" t="n">
-        <v>-0.2612</v>
+        <v>-0.2478</v>
       </c>
       <c r="J348" t="n">
-        <v>-4.4404</v>
+        <v>-4.2126</v>
       </c>
     </row>
     <row r="349">
@@ -18149,10 +18149,10 @@
         <v>0.66</v>
       </c>
       <c r="I349" t="n">
-        <v>-0.3465</v>
+        <v>-0.3359</v>
       </c>
       <c r="J349" t="n">
-        <v>-5.8905</v>
+        <v>-5.7103</v>
       </c>
     </row>
     <row r="350">
@@ -18189,10 +18189,10 @@
         <v>0.44</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.5381</v>
+        <v>-0.5407999999999999</v>
       </c>
       <c r="J350" t="n">
-        <v>-9.1477</v>
+        <v>-9.1936</v>
       </c>
     </row>
     <row r="351">
@@ -18229,10 +18229,10 @@
         <v>0.23</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.7215</v>
+        <v>-0.7571</v>
       </c>
       <c r="J351" t="n">
-        <v>-12.2655</v>
+        <v>-12.8707</v>
       </c>
     </row>
     <row r="352">
@@ -18269,10 +18269,10 @@
         <v>1.35</v>
       </c>
       <c r="I352" t="n">
-        <v>0.8498</v>
+        <v>0.8293</v>
       </c>
       <c r="J352" t="n">
-        <v>21.245</v>
+        <v>20.7325</v>
       </c>
     </row>
     <row r="353">
@@ -18309,10 +18309,10 @@
         <v>1.35</v>
       </c>
       <c r="I353" t="n">
-        <v>0.8498</v>
+        <v>0.8293</v>
       </c>
       <c r="J353" t="n">
-        <v>21.245</v>
+        <v>20.7325</v>
       </c>
     </row>
     <row r="354">
@@ -18349,10 +18349,10 @@
         <v>1.27</v>
       </c>
       <c r="I354" t="n">
-        <v>0.6895</v>
+        <v>0.6599</v>
       </c>
       <c r="J354" t="n">
-        <v>17.2375</v>
+        <v>16.4975</v>
       </c>
     </row>
     <row r="355">
@@ -18389,10 +18389,10 @@
         <v>1.13</v>
       </c>
       <c r="I355" t="n">
-        <v>0.3836</v>
+        <v>0.3499</v>
       </c>
       <c r="J355" t="n">
-        <v>9.59</v>
+        <v>8.7475</v>
       </c>
     </row>
     <row r="356">
@@ -18429,10 +18429,10 @@
         <v>0.97</v>
       </c>
       <c r="I356" t="n">
-        <v>-0.174</v>
+        <v>-0.1428</v>
       </c>
       <c r="J356" t="n">
-        <v>-4.35</v>
+        <v>-3.57</v>
       </c>
     </row>
     <row r="357">
@@ -18469,10 +18469,10 @@
         <v>0.9</v>
       </c>
       <c r="I357" t="n">
-        <v>-0.133</v>
+        <v>-0.1174</v>
       </c>
       <c r="J357" t="n">
-        <v>-3.325</v>
+        <v>-2.935</v>
       </c>
     </row>
     <row r="358">
@@ -18509,10 +18509,10 @@
         <v>0.88</v>
       </c>
       <c r="I358" t="n">
-        <v>-0.1555</v>
+        <v>-0.1391</v>
       </c>
       <c r="J358" t="n">
-        <v>-3.8875</v>
+        <v>-3.4775</v>
       </c>
     </row>
     <row r="359">
@@ -18549,10 +18549,10 @@
         <v>0.82</v>
       </c>
       <c r="I359" t="n">
-        <v>-0.2169</v>
+        <v>-0.1988</v>
       </c>
       <c r="J359" t="n">
-        <v>-5.4225</v>
+        <v>-4.97</v>
       </c>
     </row>
     <row r="360">
@@ -18589,10 +18589,10 @@
         <v>0.79</v>
       </c>
       <c r="I360" t="n">
-        <v>-0.2459</v>
+        <v>-0.2275</v>
       </c>
       <c r="J360" t="n">
-        <v>-6.1475</v>
+        <v>-5.6875</v>
       </c>
     </row>
     <row r="361">
@@ -18629,10 +18629,10 @@
         <v>0.75</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.284</v>
+        <v>-0.2661</v>
       </c>
       <c r="J361" t="n">
-        <v>-7.1</v>
+        <v>-6.6525</v>
       </c>
     </row>
     <row r="362">
@@ -18669,10 +18669,10 @@
         <v>1.57</v>
       </c>
       <c r="I362" t="n">
-        <v>1.198</v>
+        <v>1.2129</v>
       </c>
       <c r="J362" t="n">
-        <v>31.148</v>
+        <v>31.5354</v>
       </c>
     </row>
     <row r="363">
@@ -18709,10 +18709,10 @@
         <v>1.52</v>
       </c>
       <c r="I363" t="n">
-        <v>1.1303</v>
+        <v>1.1428</v>
       </c>
       <c r="J363" t="n">
-        <v>29.3878</v>
+        <v>29.7128</v>
       </c>
     </row>
     <row r="364">
@@ -18749,10 +18749,10 @@
         <v>1.31</v>
       </c>
       <c r="I364" t="n">
-        <v>0.772</v>
+        <v>0.7461</v>
       </c>
       <c r="J364" t="n">
-        <v>20.072</v>
+        <v>19.3986</v>
       </c>
     </row>
     <row r="365">
@@ -18789,10 +18789,10 @@
         <v>0.84</v>
       </c>
       <c r="I365" t="n">
-        <v>-0.5325</v>
+        <v>-0.4943</v>
       </c>
       <c r="J365" t="n">
-        <v>-13.845</v>
+        <v>-12.8518</v>
       </c>
     </row>
     <row r="366">
@@ -18829,10 +18829,10 @@
         <v>0.79</v>
       </c>
       <c r="I366" t="n">
-        <v>-0.6492</v>
+        <v>-0.617</v>
       </c>
       <c r="J366" t="n">
-        <v>-16.8792</v>
+        <v>-16.042</v>
       </c>
     </row>
     <row r="367">
@@ -18869,10 +18869,10 @@
         <v>1.07</v>
       </c>
       <c r="I367" t="n">
-        <v>0.2003</v>
+        <v>0.1588</v>
       </c>
       <c r="J367" t="n">
-        <v>5.2078</v>
+        <v>4.1288</v>
       </c>
     </row>
     <row r="368">
@@ -18909,10 +18909,10 @@
         <v>1.05</v>
       </c>
       <c r="I368" t="n">
-        <v>0.1559</v>
+        <v>0.12</v>
       </c>
       <c r="J368" t="n">
-        <v>4.0534</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="369">
@@ -18949,10 +18949,10 @@
         <v>0.9</v>
       </c>
       <c r="I369" t="n">
-        <v>-0.1429</v>
+        <v>-0.124</v>
       </c>
       <c r="J369" t="n">
-        <v>-3.7154</v>
+        <v>-3.224</v>
       </c>
     </row>
     <row r="370">
@@ -18989,10 +18989,10 @@
         <v>0.89</v>
       </c>
       <c r="I370" t="n">
-        <v>-0.1541</v>
+        <v>-0.1347</v>
       </c>
       <c r="J370" t="n">
-        <v>-4.0066</v>
+        <v>-3.5022</v>
       </c>
     </row>
     <row r="371">
@@ -19029,10 +19029,10 @@
         <v>0.85</v>
       </c>
       <c r="I371" t="n">
-        <v>-0.1971</v>
+        <v>-0.1768</v>
       </c>
       <c r="J371" t="n">
-        <v>-5.1246</v>
+        <v>-4.5968</v>
       </c>
     </row>
     <row r="372">
@@ -19069,10 +19069,10 @@
         <v>0.95</v>
       </c>
       <c r="I372" t="n">
-        <v>-0.0767</v>
+        <v>-0.0643</v>
       </c>
       <c r="J372" t="n">
-        <v>-1.8408</v>
+        <v>-1.5432</v>
       </c>
     </row>
     <row r="373">
@@ -19109,10 +19109,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I373" t="n">
-        <v>-0.08989999999999999</v>
+        <v>-0.07630000000000001</v>
       </c>
       <c r="J373" t="n">
-        <v>-2.1576</v>
+        <v>-1.8312</v>
       </c>
     </row>
     <row r="374">
@@ -19149,10 +19149,10 @@
         <v>0.92</v>
       </c>
       <c r="I374" t="n">
-        <v>-0.1147</v>
+        <v>-0.0993</v>
       </c>
       <c r="J374" t="n">
-        <v>-2.7528</v>
+        <v>-2.3832</v>
       </c>
     </row>
     <row r="375">
@@ -19189,10 +19189,10 @@
         <v>0.9</v>
       </c>
       <c r="I375" t="n">
-        <v>-0.1379</v>
+        <v>-0.1211</v>
       </c>
       <c r="J375" t="n">
-        <v>-3.3096</v>
+        <v>-2.9064</v>
       </c>
     </row>
     <row r="376">
@@ -19229,10 +19229,10 @@
         <v>0.67</v>
       </c>
       <c r="I376" t="n">
-        <v>-0.3632</v>
+        <v>-0.3489</v>
       </c>
       <c r="J376" t="n">
-        <v>-8.716799999999999</v>
+        <v>-8.3736</v>
       </c>
     </row>
     <row r="377">
@@ -19269,10 +19269,10 @@
         <v>1.74</v>
       </c>
       <c r="I377" t="n">
-        <v>1.4033</v>
+        <v>1.4292</v>
       </c>
       <c r="J377" t="n">
-        <v>33.6792</v>
+        <v>34.3008</v>
       </c>
     </row>
     <row r="378">
@@ -19309,10 +19309,10 @@
         <v>1.36</v>
       </c>
       <c r="I378" t="n">
-        <v>0.8579</v>
+        <v>0.8403</v>
       </c>
       <c r="J378" t="n">
-        <v>20.5896</v>
+        <v>20.1672</v>
       </c>
     </row>
     <row r="379">
@@ -19349,10 +19349,10 @@
         <v>1.26</v>
       </c>
       <c r="I379" t="n">
-        <v>0.6626</v>
+        <v>0.6353</v>
       </c>
       <c r="J379" t="n">
-        <v>15.9024</v>
+        <v>15.2472</v>
       </c>
     </row>
     <row r="380">
@@ -19389,10 +19389,10 @@
         <v>1.24</v>
       </c>
       <c r="I380" t="n">
-        <v>0.6217</v>
+        <v>0.5931</v>
       </c>
       <c r="J380" t="n">
-        <v>14.9208</v>
+        <v>14.2344</v>
       </c>
     </row>
     <row r="381">
@@ -19429,10 +19429,10 @@
         <v>0.77</v>
       </c>
       <c r="I381" t="n">
-        <v>-0.7048</v>
+        <v>-0.6785</v>
       </c>
       <c r="J381" t="n">
-        <v>-16.9152</v>
+        <v>-16.284</v>
       </c>
     </row>
     <row r="382">
@@ -19469,10 +19469,10 @@
         <v>1.66</v>
       </c>
       <c r="I382" t="n">
-        <v>1.2667</v>
+        <v>1.2864</v>
       </c>
       <c r="J382" t="n">
-        <v>26.6007</v>
+        <v>27.0144</v>
       </c>
     </row>
     <row r="383">
@@ -19509,10 +19509,10 @@
         <v>1.62</v>
       </c>
       <c r="I383" t="n">
-        <v>1.2168</v>
+        <v>1.2352</v>
       </c>
       <c r="J383" t="n">
-        <v>25.5528</v>
+        <v>25.9392</v>
       </c>
     </row>
     <row r="384">
@@ -19549,10 +19549,10 @@
         <v>1.48</v>
       </c>
       <c r="I384" t="n">
-        <v>1.0375</v>
+        <v>1.049</v>
       </c>
       <c r="J384" t="n">
-        <v>21.7875</v>
+        <v>22.029</v>
       </c>
     </row>
     <row r="385">
@@ -19589,10 +19589,10 @@
         <v>1.43</v>
       </c>
       <c r="I385" t="n">
-        <v>0.9622000000000001</v>
+        <v>0.9638</v>
       </c>
       <c r="J385" t="n">
-        <v>20.2062</v>
+        <v>20.2398</v>
       </c>
     </row>
     <row r="386">
@@ -19629,10 +19629,10 @@
         <v>1.15</v>
       </c>
       <c r="I386" t="n">
-        <v>0.3928</v>
+        <v>0.3606</v>
       </c>
       <c r="J386" t="n">
-        <v>8.248799999999999</v>
+        <v>7.5726</v>
       </c>
     </row>
     <row r="387">
@@ -19669,10 +19669,10 @@
         <v>1.18</v>
       </c>
       <c r="I387" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.5414</v>
       </c>
       <c r="J387" t="n">
-        <v>11.697</v>
+        <v>11.3694</v>
       </c>
     </row>
     <row r="388">
@@ -19709,10 +19709,10 @@
         <v>0.63</v>
       </c>
       <c r="I388" t="n">
-        <v>-0.3729</v>
+        <v>-0.3623</v>
       </c>
       <c r="J388" t="n">
-        <v>-7.8309</v>
+        <v>-7.6083</v>
       </c>
     </row>
     <row r="389">
@@ -19749,10 +19749,10 @@
         <v>0.53</v>
       </c>
       <c r="I389" t="n">
-        <v>-0.4604</v>
+        <v>-0.4546</v>
       </c>
       <c r="J389" t="n">
-        <v>-9.6684</v>
+        <v>-9.5466</v>
       </c>
     </row>
     <row r="390">
@@ -19789,10 +19789,10 @@
         <v>0.45</v>
       </c>
       <c r="I390" t="n">
-        <v>-0.5306999999999999</v>
+        <v>-0.5325</v>
       </c>
       <c r="J390" t="n">
-        <v>-11.1447</v>
+        <v>-11.1825</v>
       </c>
     </row>
     <row r="391">
@@ -19829,10 +19829,10 @@
         <v>0.44</v>
       </c>
       <c r="I391" t="n">
-        <v>-0.5395</v>
+        <v>-0.5424</v>
       </c>
       <c r="J391" t="n">
-        <v>-11.3295</v>
+        <v>-11.3904</v>
       </c>
     </row>
     <row r="392">
@@ -19869,10 +19869,10 @@
         <v>1.26</v>
       </c>
       <c r="I392" t="n">
-        <v>0.5567</v>
+        <v>0.5001</v>
       </c>
       <c r="J392" t="n">
-        <v>15.0309</v>
+        <v>13.5027</v>
       </c>
     </row>
     <row r="393">
@@ -19909,10 +19909,10 @@
         <v>1.04</v>
       </c>
       <c r="I393" t="n">
-        <v>0.1383</v>
+        <v>0.1049</v>
       </c>
       <c r="J393" t="n">
-        <v>3.7341</v>
+        <v>2.8323</v>
       </c>
     </row>
     <row r="394">
@@ -19949,10 +19949,10 @@
         <v>0.93</v>
       </c>
       <c r="I394" t="n">
-        <v>-0.1063</v>
+        <v>-0.0905</v>
       </c>
       <c r="J394" t="n">
-        <v>-2.8701</v>
+        <v>-2.4435</v>
       </c>
     </row>
     <row r="395">
@@ -19989,10 +19989,10 @@
         <v>0.86</v>
       </c>
       <c r="I395" t="n">
-        <v>-0.1839</v>
+        <v>-0.1642</v>
       </c>
       <c r="J395" t="n">
-        <v>-4.9653</v>
+        <v>-4.4334</v>
       </c>
     </row>
     <row r="396">
@@ -20029,10 +20029,10 @@
         <v>0.52</v>
       </c>
       <c r="I396" t="n">
-        <v>-0.4999</v>
+        <v>-0.5004999999999999</v>
       </c>
       <c r="J396" t="n">
-        <v>-13.4973</v>
+        <v>-13.5135</v>
       </c>
     </row>
     <row r="397">
@@ -20069,10 +20069,10 @@
         <v>1.44</v>
       </c>
       <c r="I397" t="n">
-        <v>1.0235</v>
+        <v>1.0245</v>
       </c>
       <c r="J397" t="n">
-        <v>27.6345</v>
+        <v>27.6615</v>
       </c>
     </row>
     <row r="398">
@@ -20109,10 +20109,10 @@
         <v>1.38</v>
       </c>
       <c r="I398" t="n">
-        <v>0.9182</v>
+        <v>0.9024</v>
       </c>
       <c r="J398" t="n">
-        <v>24.7914</v>
+        <v>24.3648</v>
       </c>
     </row>
     <row r="399">
@@ -20149,10 +20149,10 @@
         <v>1.05</v>
       </c>
       <c r="I399" t="n">
-        <v>0.1743</v>
+        <v>0.1477</v>
       </c>
       <c r="J399" t="n">
-        <v>4.7061</v>
+        <v>3.9879</v>
       </c>
     </row>
     <row r="400">
@@ -20189,10 +20189,10 @@
         <v>1.04</v>
       </c>
       <c r="I400" t="n">
-        <v>0.1426</v>
+        <v>0.1186</v>
       </c>
       <c r="J400" t="n">
-        <v>3.8502</v>
+        <v>3.2022</v>
       </c>
     </row>
     <row r="401">
@@ -20229,10 +20229,10 @@
         <v>0.95</v>
       </c>
       <c r="I401" t="n">
-        <v>-0.2323</v>
+        <v>-0.1954</v>
       </c>
       <c r="J401" t="n">
-        <v>-6.2721</v>
+        <v>-5.2758</v>
       </c>
     </row>
     <row r="402">
@@ -20269,10 +20269,10 @@
         <v>1.25</v>
       </c>
       <c r="I402" t="n">
-        <v>0.6785</v>
+        <v>0.6437</v>
       </c>
       <c r="J402" t="n">
-        <v>19.6765</v>
+        <v>18.6673</v>
       </c>
     </row>
     <row r="403">
@@ -20309,10 +20309,10 @@
         <v>1.19</v>
       </c>
       <c r="I403" t="n">
-        <v>0.5451</v>
+        <v>0.5051</v>
       </c>
       <c r="J403" t="n">
-        <v>15.8079</v>
+        <v>14.6479</v>
       </c>
     </row>
     <row r="404">
@@ -20349,10 +20349,10 @@
         <v>1.11</v>
       </c>
       <c r="I404" t="n">
-        <v>0.3534</v>
+        <v>0.3138</v>
       </c>
       <c r="J404" t="n">
-        <v>10.2486</v>
+        <v>9.100199999999999</v>
       </c>
     </row>
     <row r="405">
@@ -20389,10 +20389,10 @@
         <v>0.98</v>
       </c>
       <c r="I405" t="n">
-        <v>-0.1113</v>
+        <v>-0.0852</v>
       </c>
       <c r="J405" t="n">
-        <v>-3.2277</v>
+        <v>-2.4708</v>
       </c>
     </row>
     <row r="406">
@@ -20429,10 +20429,10 @@
         <v>0.82</v>
       </c>
       <c r="I406" t="n">
-        <v>-0.5551</v>
+        <v>-0.5151</v>
       </c>
       <c r="J406" t="n">
-        <v>-16.0979</v>
+        <v>-14.9379</v>
       </c>
     </row>
     <row r="407">
@@ -20469,10 +20469,10 @@
         <v>1.33</v>
       </c>
       <c r="I407" t="n">
-        <v>0.637</v>
+        <v>0.5780999999999999</v>
       </c>
       <c r="J407" t="n">
-        <v>18.473</v>
+        <v>16.7649</v>
       </c>
     </row>
     <row r="408">
@@ -20509,10 +20509,10 @@
         <v>1.23</v>
       </c>
       <c r="I408" t="n">
-        <v>0.478</v>
+        <v>0.4192</v>
       </c>
       <c r="J408" t="n">
-        <v>13.862</v>
+        <v>12.1568</v>
       </c>
     </row>
     <row r="409">
@@ -20549,10 +20549,10 @@
         <v>1.05</v>
       </c>
       <c r="I409" t="n">
-        <v>0.1445</v>
+        <v>0.1117</v>
       </c>
       <c r="J409" t="n">
-        <v>4.1905</v>
+        <v>3.2393</v>
       </c>
     </row>
     <row r="410">
@@ -20589,10 +20589,10 @@
         <v>0.89</v>
       </c>
       <c r="I410" t="n">
-        <v>-0.1605</v>
+        <v>-0.1403</v>
       </c>
       <c r="J410" t="n">
-        <v>-4.6545</v>
+        <v>-4.0687</v>
       </c>
     </row>
     <row r="411">
@@ -20629,10 +20629,10 @@
         <v>0.63</v>
       </c>
       <c r="I411" t="n">
-        <v>-0.413</v>
+        <v>-0.4044</v>
       </c>
       <c r="J411" t="n">
-        <v>-11.977</v>
+        <v>-11.7276</v>
       </c>
     </row>
     <row r="412">
@@ -20669,10 +20669,10 @@
         <v>1.45</v>
       </c>
       <c r="I412" t="n">
-        <v>1.0764</v>
+        <v>1.0885</v>
       </c>
       <c r="J412" t="n">
-        <v>38.7504</v>
+        <v>39.186</v>
       </c>
     </row>
     <row r="413">
@@ -20709,10 +20709,10 @@
         <v>1.28</v>
       </c>
       <c r="I413" t="n">
-        <v>0.7534999999999999</v>
+        <v>0.7235</v>
       </c>
       <c r="J413" t="n">
-        <v>27.126</v>
+        <v>26.046</v>
       </c>
     </row>
     <row r="414">
@@ -20749,10 +20749,10 @@
         <v>0.88</v>
       </c>
       <c r="I414" t="n">
-        <v>-0.4013</v>
+        <v>-0.3582</v>
       </c>
       <c r="J414" t="n">
-        <v>-14.4468</v>
+        <v>-12.8952</v>
       </c>
     </row>
     <row r="415">
@@ -20789,10 +20789,10 @@
         <v>0.82</v>
       </c>
       <c r="I415" t="n">
-        <v>-0.5483</v>
+        <v>-0.5076000000000001</v>
       </c>
       <c r="J415" t="n">
-        <v>-19.7388</v>
+        <v>-18.2736</v>
       </c>
     </row>
     <row r="416">
@@ -20829,10 +20829,10 @@
         <v>0.75</v>
       </c>
       <c r="I416" t="n">
-        <v>-0.7078</v>
+        <v>-0.6757</v>
       </c>
       <c r="J416" t="n">
-        <v>-25.4808</v>
+        <v>-24.3252</v>
       </c>
     </row>
     <row r="417">
@@ -20869,10 +20869,10 @@
         <v>1.66</v>
       </c>
       <c r="I417" t="n">
-        <v>1.0606</v>
+        <v>1.0384</v>
       </c>
       <c r="J417" t="n">
-        <v>38.1816</v>
+        <v>37.3824</v>
       </c>
     </row>
     <row r="418">
@@ -20909,10 +20909,10 @@
         <v>1.19</v>
       </c>
       <c r="I418" t="n">
-        <v>0.3955</v>
+        <v>0.3411</v>
       </c>
       <c r="J418" t="n">
-        <v>14.238</v>
+        <v>12.2796</v>
       </c>
     </row>
     <row r="419">
@@ -20949,10 +20949,10 @@
         <v>0.97</v>
       </c>
       <c r="I419" t="n">
-        <v>-0.067</v>
+        <v>-0.0528</v>
       </c>
       <c r="J419" t="n">
-        <v>-2.412</v>
+        <v>-1.9008</v>
       </c>
     </row>
     <row r="420">
@@ -20989,10 +20989,10 @@
         <v>0.89</v>
       </c>
       <c r="I420" t="n">
-        <v>-0.1679</v>
+        <v>-0.1477</v>
       </c>
       <c r="J420" t="n">
-        <v>-6.0444</v>
+        <v>-5.3172</v>
       </c>
     </row>
     <row r="421">
@@ -21029,10 +21029,10 @@
         <v>0.86</v>
       </c>
       <c r="I421" t="n">
-        <v>-0.2007</v>
+        <v>-0.1803</v>
       </c>
       <c r="J421" t="n">
-        <v>-7.2252</v>
+        <v>-6.4908</v>
       </c>
     </row>
   </sheetData>
